--- a/branch.xlsx
+++ b/branch.xlsx
@@ -354,7 +354,7 @@
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3SIXTEEN</t>
+          <t>3Sixteen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -364,19 +364,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3SIXTEEN: 源自美国的街头服饰品牌，以高品质的牛仔裤和工装风格闻名，采用优质牛仔布料和精湛制作工艺，融合复古与现代设计，打造耐用且时尚的日常穿着单品，彰显个性与实用主义。</t>
+          <t>3sixteen由 Andrew Chen 与 Johan Lam 于 2003 年创立，2008 年推首款牛仔裤 SL-100x。主打高端赤耳牛仔、衬衫等美式复古男装，与日本冈山 Kuroki Mills 合作定制丹宁布，美国制造，流行于欧美日韩，风格耐用经典。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3SIXTEEN: Premium US streetwear brand known for high-quality denim jeans and workwear-style apparel, blending vintage and modern designs with durable craftsmanship for stylish everyday wear.</t>
+          <t>3Sixteen3sixteen: Founded by Andrew Chen &amp; Johan Lam in 2003, launched first jeans SL-100x in 2008. Focuses on premium raw denim, shirts &amp; American vintage menswear. Custom denim from Kuroki Mills Okayama Japan, Made in USA. Popular in EU, US, JP, KR; durable &amp; classic style.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="25.5" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AC MILAN</t>
+          <t>Ac Milan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -386,12 +386,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AC MILAN: 1899年成立的意大利传奇足球俱乐部，以红黑条纹队服和卓越竞技精神闻名全球，拥有7座欧冠奖杯及众多意甲冠军，代表球员包括马尔蒂尼和卡卡，其官方商品涵盖球衣、训练装备及收藏品，风格经典且充满荣耀。</t>
+          <t>AC Milan: 1899年创立于意大利米兰的世界顶级职业足球俱乐部，绰号“红黑军团”，主场为圣西罗/梅阿查球场。作为意甲传统豪门，累计夺得19次意甲联赛冠军、7次欧洲冠军联赛冠军等重磅荣誉，以铁血防守与华丽进攻的战术风格闻名，承载百年足球底蕴与全球球迷的激情信仰，是足球领域极具影响力的经典品牌。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AC MILAN: Legendary Italian football club since 1899, renowned for red-black stripes, 7 UEFA Champions League titles, Serie A champions, represented by Maldini and Kaka. Official merchandise includes jerseys and collectibles.</t>
+          <t>AC Milan: Founded in Milan, Italy in 1899, world top pro football club nicknamed "Rossoneri" (Red-Black Corps), home to San Siro/Meazza Stadium. A traditional Serie A giant with 19 Serie A titles, 7 UEFA Champions League trophies, renowned for iron defense &amp; brilliant offense. Carries century-old heritage, global fans’ passion, a highly influential classic football brand.</t>
         </is>
       </c>
     </row>
@@ -408,12 +408,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A Bathing App: 沐浴应用程序提供全面的个人护理和放松解决方案，专注于提升日常沐浴体验。我们结合创新技术与用户友好设计，帮助您通过定制化的沐浴计划实现身心舒缓。探索智能提醒、节水功能和个性化设置，让每次沐浴都成为享受。A Bathing App 致力于让自我护理变得更简单、更环保、更愉悦。立即下载，开启您的专属沐浴时光！</t>
+          <t>A Bathing Ape（BAPE）由 NIGO（长尾智明）1993 年创立于东京原宿。主打街头潮流，含经典迷彩、猿头 Logo，产品覆盖卫衣、T 恤、牛仔、BAPE STA 鞋，用优质棉 / 重磅丹宁，风靡全球。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A Bathing App: Personal care &amp; relaxation solution. Elevate daily bathing with innovative tech, customized plans, water-saving features &amp; smart reminders. Enjoy eco-friendly self-care.</t>
+          <t>A Bathing Ape (BAPE): Founded by NIGO (Tomoaki Nagao) in Harajuku, Tokyo in 1993, this streetwear brand features iconic camouflage &amp; ape head logo. Products include hoodies, tees, denim, BAPE STA shoes, made of premium cotton/heavy denim, popular worldwide.</t>
         </is>
       </c>
     </row>
@@ -430,40 +430,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>根据您的要求，我已为每个品牌撰写了符合规范的SEO优化描述。所有描述均以给定的英文品牌名称为严格开头，内容仅包含对该品牌的描述。
----
-**ACG:**
-探索ACG户外装备，专为应对极端天气和复杂地形设计。品牌提供高性能防水外套、耐用登山鞋及多功能背包，采用Nike尖端科技，保障户外活动安全与舒适。搜索ACG系列，获取全天候防护解决方案。
-**A Bathing Ape:**
-发现A Bathing Ape潮流服饰，标志性迷彩图案和鲨鱼连帽衫备受追捧。品牌融合街头文化与高端时尚，推出限量版T恤、鞋履及配饰。探索BAPE独家系列，获取独特街头风格装备。
-**A.P.C.:**
-浏览A.P.C.简约时装，主打优质丹宁、经典夹克和日常必备款。品牌以巴黎美学为基础，强调剪裁与面料品质。寻找A.P.C.永恒单品，打造精致衣橱基础。
-**Acer:**
-选择Acer高性能电脑，包括游戏本、轻薄超极本和强大台式机。品牌提供可靠显示器及移动设备，融合创新技术与性价比。搜索Acer产品线，满足办公、学习和娱乐需求。
-**Adidas:**
-探索Adidas运动鞋和服装，品牌提供Boost科技跑鞋、经典Superstar系列及专业足球装备。结合创新设计与可持续材料，助力运动员和日常爱好者。查找Adidas最新款式，提升运动表现与街头风格。
-**Aesop:**
-发现Aesop护肤产品，专注于植物萃取和实验室精密配方。品牌提供清洁剂、保湿霜和身体护理品，采用琥珀玻璃瓶包装。搜索Aesop方案，获取量身定制护肤体验。
-**Airbnb:**
-使用Airbnb预订独特住宿，从城市公寓到树屋度假屋。平台连接全球房东与旅客，提供体验活动和长租选项。查找Airbnb目的地，探索本地化旅行方式。
-**Amazon:**
-访问Amazon电商平台，购买从书籍电子产品到家居用品的数亿种商品。享受快速配送、Prime会员优惠及云服务。搜索Amazondeal，获取每日折扣和全球品牌正品。
-**Asics:**
-选购Asics运动鞋，专注于跑鞋科技如Gel缓震系统和性能训练装备。品牌支持马拉松运动员和健身房爱好者，结合日本工艺与人体工学。查找Asics专业款式，增强运动舒适度与支撑。
-**ASUS:**
-探索ASUS电子设备，包括游戏笔记本、电竞显示器和主板组件。品牌以ROG系列和创新二合一电脑闻名。搜索ASUS技术，获取可靠计算解决方案。</t>
+          <t>ACG: 源自“All Conditions Gear（全地形装备）”核心理念，专注为户外爱好者及多元场景需求者打造专业耐候装备，产品覆盖防水透气夹克、耐磨抗造长裤、抓地力鞋款等，以功能性材质（如防水涂层、透气网布）结合实用设计，适配徒步、登山、城市通勤等全场景，核心亮点是兼顾极端环境防护与日常穿着舒适，成为“全条件适用”的户外装备代表品牌。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ACG: ACG outdoor gear built for extreme weather &amp; tough terrain. High-performance waterproof jackets, durable hiking boots, multifunctional backpacks with Nike tech</t>
+          <t>ACG: Rooted in "All Conditions Gear" core, professional weather-resistant gear for outdoor enthusiasts &amp; versatile users. Covers waterproof breathable jackets, durable pants, grippy footwear—functional materials (waterproof coating, breathable mesh) + practical design for hiking, climbing, urban commute. Balances extreme protection &amp; daily comfort, iconic all-condition outdoor brand.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="25.5" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ACNE STUDIOS</t>
+          <t>Acne Studios</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -473,19 +452,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ACNE STUDIOS: Acne Studios是来自瑞典斯德哥尔摩的奢侈时尚品牌，以其极简主义设计、大胆创意和标志性粉色包装而闻名。品牌提供男女成衣、鞋履、配饰及牛仔系列，融合北欧美学与叛逆精神，为追求独特风格的全球消费者打造当代时尚单品。</t>
+          <t>Acne Studios: 1996年创立于瑞典斯德哥尔摩的先锋时尚品牌，以极简北欧美学、中性风格与艺术化设计为核心，产品覆盖丹宁牛仔、成衣、卫衣及配饰，经典如Denim系列牛仔裤、Face印花卫衣，选用高品质棉、牛仔布等材质，将创意灵感融入日常穿着，是全球兼具潮流感与质感的高端时尚选择。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ACNE STUDIOS: Acne Studios, Stockholm-based luxury fashion house, offers minimalist design, bold creativity, iconic pink packaging, ready-to-wear, denim, and accessories.</t>
+          <t>Acne Studios: Pioneer fashion brand founded in Stockholm, Sweden (1996), focusing on minimalist Nordic aesthetics, unisex style, artistic design. Products include denim, ready-to-wear, hoodies, accessories—iconic Denim series jeans &amp; Face print hoodies, made of high-quality cotton/denim. Blends creativity with daily wear, a global high-end choice for trendiness &amp; texture.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="25.5" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ACQUA DI PARMA</t>
+          <t>Acqua Diparma</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -495,19 +474,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ACQUA DI PARMA: 1916年诞生于意大利的奢华香氛品牌，以经典古龙水闻名。产品系列涵盖香水、沐浴护理及家居香氛，经典之作克罗尼亚古龙水采用天然香材，手工工艺精湛，功能持久留香，风格优雅高贵，诠释意式生活艺术。</t>
+          <t>Acqua Di Parma: 1916年诞生于意大利帕尔马的高端香氛与美妆品牌，以「帕尔马之水」的经典名号传递意式优雅美学，核心产品线覆盖经典香水、奢华护肤及身体护理系列，标志性黄色瓶盖与蓝白条纹包装极具辨识度，坚持将传统工艺与现代感官体验融合，是全球精致生活爱好者追捧的意大利高端生活方式品牌。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ACQUA DI PARMA: Italian luxury fragrance brand since 1916. Known for iconic Colonia cologne with natural ingredients, handcrafted elegance, long-lasting scent, and timeless sophistication.</t>
+          <t>Acqua Di Parma: Italian luxury fragrance &amp; beauty brand founded in Parma, Italy in 1916, embodying Italian elegance. Core: classic perfumes, luxury skincare &amp; body care. Distinct yellow cap &amp; blue-white stripes. Blends traditional craft with modern sensory experience, adored by global refined lifestyle fans.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="25.5" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADIDAS</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -517,19 +496,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ADIDAS: 阿迪达斯是全球领先的运动品牌，提供专业运动鞋、服装及配件，融合创新科技与时尚设计，为运动员和日常消费者打造高性能产品。品牌致力于通过运动改变生活，强调可持续发展与社会责任。</t>
+          <t>Adidas: 1949年由阿道夫·达斯勒创立于德国，全球专业运动品牌领导者，核心覆盖运动服饰、鞋履及装备全品类，经典产品包括UltraBoost跑鞋、Stan Smith小白鞋、Superstar贝壳头鞋等，依托Boost中底、Primeknit编织等创新科技，践行“无不可能（Impossible is Nothing）”品牌精神，为运动员与运动爱好者提供兼具舒适体验、卓越性能与经典设计的运动解决方案，风格融合专业运动属性与现代潮流美学。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ADIDAS: Leading global sports brand offering innovative athletic footwear, apparel, and accessories. Combines performance technology with stylish design for athletes and consumers. Committed to sustainability and social impact.</t>
+          <t>Adidas: Founded in Germany by Adolf Dassler in 1949, global leading sports brand specializing in athletic apparel, footwear &amp; gear. Classics include UltraBoost, Stan Smith, Superstar. Boost midsole &amp; Primeknit tech power "Impossible is Nothing" spirit, offering performance, comfort, classic design with sport-meets-street style.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="25.5" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AIR JORDAN</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -539,20 +518,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AIR JORDAN:  
-探索AIR JORDAN系列篮球鞋与运动服饰，感受迈克尔·乔丹传奇精神与创新设计的完美融合。品牌提供高性能篮球鞋、潮流休闲鞋及运动装备，融合尖端科技与街头文化风格，为运动员和潮流爱好者提供卓越舒适性与独特时尚感。通过官方渠道购买正品AIR JORDAN产品，享受全球配送与专属会员服务。</t>
+          <t>Air Jordan: 1984年为篮球传奇迈克尔·乔丹创立的耐克子品牌，以高性能篮球鞋与运动服饰闻名。经典产品包括Air Jordan 1至Air Jordan 37等正代鞋款及复刻系列，采用皮革、编织面料与Air缓震科技，工艺精湛，功能注重球场表现与日常舒适，风格融合运动竞技与街头潮流文化。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AIR JORDAN: Performance basketball sneakers, lifestyle footwear, and sportswear merging cutting-edge tech with street culture. Authentic products, global shipping, exclusive membership.</t>
+          <t>Air Jordan: Performance basketball shoes &amp; apparel for Michael Jordan since 1984. Features iconic AJ1-37 series, Air cushioning tech, leather/knit, merging elite sport with streetwear culture.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="25.5" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AJAX AMSTERDAM</t>
+          <t>Ajax Amsterdam</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -562,19 +540,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AJAX AMSTERDAM: 诞生于1972年的荷兰足球装备品牌，以标志性红白配色和精湛工艺闻名，产品涵盖比赛日球衣、训练服装及球迷周边，采用高性能面料与经典设计，融合现代运动科技与传统俱乐部精神。</t>
+          <t>Ajax Amsterdam: 荷兰顶级职业足球俱乐部，1900年3月18日成立，主场为约翰·克鲁伊夫竞技场，是荷甲联赛传统豪门，累计斩获36次荷甲冠军、4次欧洲冠军联赛冠军，以“全攻全守”足球哲学引领足坛风格革命，拥有全球闻名的青训体系，培养出克鲁伊夫、范巴斯滕、博格坎普、斯内德等传奇球星，是世界足球史上影响力深远的俱乐部代表之一。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AJAX AMSTERDAM: Born 1972, iconic Dutch football gear brand. Known for legendary red &amp; white style, high-performance fabrics, classic design, and modern sports tech.</t>
+          <t>Ajax Amsterdam: Top Dutch pro football club founded Mar 18, 1900, home to Johan Cruyff Arena. Traditional Eredivisie powerhouse with 36 titles &amp; 4 UEFA Champions League trophies. Pioneered "Total Football" philosophy, renowned global youth academy nurturing legends like Cruyff, Van Basten, Bergkamp, Sneijder. Influential in football history.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="25.5" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AL NASSR</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -584,19 +562,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AL NASSR: 沙特阿拉伯职业足球俱乐部，成立于1955年，以黄色和蓝色为标志性颜色，拥有多位国际知名球员，以进攻性足球风格和卓越竞技表现著称，主场为可容纳25000人的Mrsool Park体育场。</t>
+          <t>Al Nassr（利雅得胜利足球俱乐部）由 Zeid 与 Saud Al-Ja’ba 兄弟 1955 年 10 月 24 日创立于沙特利雅得。主打黄色主场球衣配蓝色细节，饰阿拉伯地图标志，与阿迪达斯等合作，用 Climalite 透气聚酯面料，产品含球衣、训练服、球迷周边，风靡中东及全球，C 罗加盟后人气飙升。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AL NASSR: Saudi Pro Club since 1955, yellow &amp; blue colors, global stars, attacking style, Mrsool Park 25k capacity.</t>
+          <t>Al Nassr: Founded in 1955. Iconic yellow &amp; blue kits with Arab map badge. Adidas Climalite jerseys, training gear, fan merch. Global popularity soared with Ronaldo.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="25.5" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AL-HILAL</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -606,19 +584,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AL-HILAL: 沙特阿拉伯顶级足球俱乐部，成立于1957年，以蓝白为主色调，主场为法赫德国王国际体育场，以其卓越战绩、豪华阵容和现代足球风格闻名，代表沙特足球最高水平。</t>
+          <t>Al-Hilal（利雅得新月足球俱乐部）由阿卜杜勒・拉赫曼・本・赛义德 1957 年 10 月 16 日创立于沙特利雅得，初名奥林匹克俱乐部，1958 年更名。与 PUMA 合作，主色调蓝白，主场球衣饰流星暗纹，用 dryCELL 透气聚酯面料，产品含球衣、训练服、球迷周边，风靡中东及全球，是亚洲最成功俱乐部之</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AL-HILAL: Saudi Arabia's top football club since 1957, blue and white colors, King Fahd Stadium, renowned for excellence,豪华阵容, and modern style.</t>
+          <t>Al Hilal: Founded by Abdul Rahman bin Said on Oct 16, 1957 in Riyadh, Saudi Arabia as Olympic Club, renamed 1958. Partnered with PUMA, blue &amp; white home jersey with meteor pattern, dryCELL breathable polyester. Jerseys, training kits, fan merchandise popular Middle East &amp; worldwide, one of Asia's most successful clubs.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="25.5" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALEXANDER MCQUEEN</t>
+          <t>Alexander MCQueen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -628,19 +606,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ALEXANDER MCQUEEN:探索亚历山大麦昆的奢华时尚世界。该英国奢侈品牌以其大胆的设计、颠覆性美学和无可挑剔的工艺而闻名。发现标志性的骷髅头配饰、结构感连衣裙和前卫成衣系列。麦昆的创意愿景将浪漫主义与反叛精神相融合，提供独一无二的奢华时尚体验。立即选购品牌经典单品，展现无畏的自我风格。</t>
+          <t>Alexander McQueen: 1992年由英国鬼才设计师亚历山大·麦昆（Alexander McQueen）创立的顶级奢侈品牌，以先锋解构、暗黑浪漫的戏剧性设计著称，核心涵盖高级时装、成衣、鞋履（经典麦昆小白鞋）、配饰（标志性骷髅丝巾）与皮具，甄选优质皮革、丝绸及定制面料，将艺术与时尚深度融合，打破传统美学桎梏，是全球先锋时尚爱好者追崇的标志性品牌。</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ALEXANDER MCQUEEN: Avant-garde luxury fashion with iconic accessories, refined ready-to-wear, and celebrity styles. Craftsmanship meets innovation.</t>
+          <t>Alexander McQueen: Founded in 1992 by British prodigy designer Alexander McQueen, a top luxury brand renowned for avant-garde deconstruction &amp; dark romantic drama. Core: haute couture, ready-to-wear, footwear (iconic white sneakers), accessories (iconic skull scarf), leather goods. Uses premium leather, silk, custom fabrics, blending art &amp; fashion to break traditional aesthetics—iconic for global avant-garde fashion enthusiasts.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="25.5" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALEXANDER WANG</t>
+          <t>Alexander Wang</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -650,19 +628,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ALEXANDER WANG: 探索ALEXANDER WANG品牌的奢华时尚服饰与配饰。ALEXANDER WANG提供高端设计师服装、标志性手袋和前沿鞋履系列，融合纽约都市美学与街头风格灵感。立即选购ALEXANDER WANG新品系列，享受全球配送和独家在线优惠。</t>
+          <t>Alexander Wang: 2005年由华裔设计师王大仁（Alexander Wang）创立于美国纽约，是融合街头酷感与高级时装调性的高端时尚品牌，核心覆盖成衣、鞋履、配饰等品类，以标志性黑色系、解构剪裁、运动风细节为设计语言，主打前卫率性的潮流风格，深受追求个性质感与先锋审美者青睐。</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ALEXANDER WANG: Luxury fashion &amp; accessories. High-end designer clothing, iconic handbags, and cutting-edge footwear. Fuses NYC aesthetic with street style. Shop new collections.</t>
+          <t>Alexander Wang: Founded in New York (2005) by Chinese-American designer Alexander Wang, this luxury brand fuses streetwear edge with high-fashion. Core: ready-to-wear, footwear, accessories. Design: signature black, deconstructed cuts, sporty details. Avant-garde, bold style, favored by those seeking unique texture &amp; avant-garde aesthetics.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="25.5" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALLSAINTS</t>
+          <t>Allsaints</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -672,19 +650,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ALLSAINTS: 1994年创立于英国的时尚品牌，以摇滚复古风格和皮革制品闻名，产品系列包括男女装、鞋履及配饰，经典产品有Balfern皮革机车夹克，采用做旧处理皮革、金属配件和精细工艺，设计独特且充满个性，风格低调不羁且富有质感。</t>
+          <t>Allsaints: 1994年创立于英国伦敦的暗黑摇滚风时尚品牌，以英伦复古与街头高级感融合的设计为核心，主打男装、女装及配饰系列，经典产品涵盖做旧皮革夹克、纯棉针织衫、复古牛仔单品等，采用优质皮革、天然棉毛等材质，工艺侧重复古做旧与细节质感，风格酷感不羁又兼具高级质感，是全球潮流爱好者追崇的英伦时尚代表品牌。</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ALLSAINTS: British brand since 1994, known for rock-inspired vintage style &amp; leather goods like the iconic Balfern biker jacket with aged leather, metal hardware &amp; craftsmanship.</t>
+          <t>Allsaints: Est. 1994 London, dark rock fashion brand fusing British vintage with street luxury. Offers men's/women's wear, accessories: distressed leather jackets, cotton knits, retro denim. Premium materials, vintage distressing craftsmanship. Edgy, sophisticated, global favorite.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="25.5" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALO</t>
+          <t>Alo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -694,19 +672,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alo（全称Alo Yoga）于2007年在美国洛杉矶创立，由Danny Harris与Marco DeGeorge共同创立设计，品牌名取自“Air、Land、Ocean”首字母，传递自然能量与正念理念。核心采用Airlift、Airbrush、Alosoft三大标志性面料，主打柔软透气、高弹塑形的特性，以“Studio-to-Street”为定位，兼顾运动功能性与日常时尚感。主要产品涵盖瑜伽服、运动服饰、运动鞋及配件，热门系列包括Airbrush塑形系列、Alosoft舒适系列等，风格简约大气、兼具加州松弛感，适配瑜伽、普拉提及日常通勤，凭借明星加持与优质工艺成为全球高端运动生活方式品牌。</t>
+          <t>Alo（全称 Alo Yoga）由 Danny Harris 与 Marco DeGeorge 于 2007 年创立于美国洛杉矶比弗利山庄，名称取 Air、Land、Ocean 首字母。主打瑜伽服、运动内衣、高腰裤等，以 Airlift/Airbrush 高科技面料，走 “瑜伽馆到街头” 简约雅奢风，风靡欧美日韩，明星博主青睐。</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Founded in 2007 in Los Angeles, USA, Alo (short for Alo Yoga) was co-founded by Danny Harris and Marco DeGeorge, named after "Air, Land, Ocean". It features three iconic fabrics: Airlift, Airbrush and Alosoft, focusing on softness and elasticity. Its main products include yoga wear, sportswear and accessories, with popular series like Airbrush and Alosoft, combining functionality and minimalist style.</t>
+          <t>Alo (Alo Yoga): Founded by Danny Harris &amp; Marco DeGeorge in 2007, Beverly Hills, LA, USA. Name from Air, Land, Ocean initials. Specializes in yoga apparel, sports bras, high-waisted leggings, with Airlift/Airbrush high-tech fabrics. "Yoga studio to street" minimalist luxury style, popular in EU, US, Japan, South Korea, favored by celebrities &amp; bloggers.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="25.5" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMIRI</t>
+          <t>Amiri</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -716,12 +694,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AMIRI: 探索AMIRI高端街头服饰品牌，以其标志性摇滚美学和精湛工艺重新定义现代奢华。AMIRI提供手工制作的牛仔裤、皮革夹克、T恤和配饰，融合加州风格与意大利品质。AMIRI官方网站提供最新系列、独家产品和全球配送服务。立即购物，体验AMIRI的独特设计和叛逆精神。</t>
+          <t>Amiri: 2013年由Mike Amiri在美国洛杉矶创立的高端时尚品牌，以摇滚叛逆精神融合高端时尚质感，主打街头美学与奢华工艺的结合。产品线涵盖手工做旧牛仔、标志性骷髅鞋履、成衣及铆钉配饰等，擅长运用做旧丹宁、优质皮革与金属铆钉元素，强调手工细节，传递“不盲从潮流的个性表达”理念，是全球高端街头风的代表性品牌，深受追求独特风格的时尚爱好者青睐。</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AMIRI: Redefining modern luxury with iconic rock aesthetics and artisanal craftsmanship. Handcrafted denim, leather jackets, tees, and accessories blending California style with Italian quality.</t>
+          <t>Amiri: Established by Mike Amiri in Los Angeles, USA (2013), high-end fashion blending rock rebellious spirit with luxury texture. Focuses on street aesthetics &amp; craftsmanship, offering handcrafted distressed denim, iconic skull footwear, ready-to-wear, studded accessories. Uses distressed denim, premium leather, metal studs, emphasizes handcrafted details. Conveys "individual expression without following trends"—iconic global high-end streetwear loved by unique style seekers.</t>
         </is>
       </c>
     </row>
@@ -738,19 +716,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ambush 是 2008 年于日本东京创立的先锋轻奢潮流品牌，由设计师 Yoon Ahn 与音乐人 Verbal 联合打造。品牌从实验性珠宝配饰起步，以波普艺术、东京街头美学为核心，打造 POW®、别针等标志性单品，后拓展成衣系列，融合叛逆街头与高端时装，主打无性别廓形设计，是国际潮流圈备受明星与时尚达人追捧的标杆品牌。</t>
+          <t>Ambush由 Yoon Ahn 与 Verbal 于 2008 年在东京创立，Yoon 任创意总监。初为珠宝实验线，现扩至服饰鞋履，标志性 POW!® 元素，用金属 / 优质棉 / 功能性面料，融波普与街头轻奢风，风靡欧美日韩，巴黎时装周亮相。</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ambush is a pioneering luxury streetwear brand founded in Tokyo, Japan in 2008 by Yoon Ahn and Verbal. Starting with experimental jewelry, it features pop-art and Tokyo street aesthetics, with iconic POW® and pin accessories. Expanded to ready-to-wear, it blends rebellious street style with high fashion, offering gender-neutral designs, and is loved by celebrities and fashion trendsetters worldwide.</t>
+          <t>Ambush: 2008 Tokyo brand by Yoon Ahn &amp; Verbal. From experimental jewelry to apparel and footwear. Features POW!® with metal, cotton, functional fabrics. Blends pop art and street luxe. Global favorite, showcased at Paris Fashion Week.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="25.5" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ANTI SOCIAL SOCIAL CLUB</t>
+          <t>Anti Social Ssocial Club</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -760,12 +738,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ANTI SOCIAL SOCIAL CLUB: 2014年由Neek Lurk创立的街头潮牌，主打连帽衫、T恤和配饰等产品，经典设计包括Logo印花和复古风格，采用棉质和涤纶材质，工艺注重细节，风格反叛不羁且极具辨识度。</t>
+          <t>Anti Social Social Club: 2015年由Neek Lurk创立的美国街头潮牌，以“反社交”叛逆内核为标识，深耕反主流文化与街头美学融合，凭借标志性标语、简约版型及限定发售模式突围，主打T恤、卫衣、棒球帽等单品，精准击中追求独特自我表达的年轻潮人需求，成为街头文化中传递“不迎合”态度的先锋代表品牌。</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ANTI SOCIAL SOCIAL CLUB: ASSC streetwear brand by Neek Lurk, hoodies, tees &amp; accessories with iconic logo prints, retro style, cotton/polyester fabrics, rebel aesthetic.</t>
+          <t>Anti Social Social Club: US streetwear brand founded by Neek Lurk in 2015, with anti-social rebellious core, blending counterculture &amp; street aesthetics. Breaks through via iconic slogans, minimalist silhouettes &amp; limited releases. Focuses on tees/hoodies/baseball caps, targets young streetwear lovers seeking unique self-expression—pioneer of non-conformist attitude in street culture.</t>
         </is>
       </c>
     </row>
@@ -782,4704 +760,4588 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Apple: 苹果是全球领先的科技品牌，致力于设计并生产创新的消费电子产品、软件和服务。其标志性产品包括iPhone智能手机、Mac电脑、iPad平板电脑、Apple Watch智能手表和AirPods无线耳机，同时提供iCloud、Apple Music和App Store等生态系统服务。苹果以简洁的设计、卓越的用户体验和隐私保护为核心，为全球消费者提供无缝连接的数字化生活解决方案。</t>
+          <t>Apple: 1976年由史蒂夫·乔布斯、斯蒂夫·沃兹尼亚克和罗纳德·韦恩创立的美国科技巨头，核心产品涵盖iPhone、Mac、iPad、Apple Watch、AirPods等，经典产品线包括iPhone S系列、MacBook Pro、iPad Pro，搭载自研M系列芯片与iOS/iPadOS/macOS系统，以简约精致的设计、流畅的生态联动、卓越的性能体验著称，广泛应用玻璃、铝合金等高品质材质，是全球科技与消费电子领域的标杆品牌。</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Apple: Leading global tech brand, innovating consumer electronics, software &amp; services. Iconic products: iPhone, Mac, iPad, Apple Watch, AirPods. Ecosystem: iCloud, Apple Music, App Store. Sleek design, seamless UX, privacy-focused digital life solutions.</t>
+          <t>Apple: Tech giant founded in 1976, innovating iPhone, Mac, iPad, Apple Watch, AirPods with M-series chips, iOS/iPadOS/macOS. Sleek design, seamless ecosystem, premium performance using glass/aluminum. Global benchmark.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="25.5" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ARE TDRVX</t>
+          <t>Arc teryx</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>aretdrvx</t>
+          <t>Arc teryx</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TDRVX: TDRVX 提供高性能户外装备与专业探险服饰，专为极端环境设计。品牌采用尖端科技材料，确保产品在防水、透气与耐用性方面表现卓越，满足登山、徒步与探险爱好者的专业需求，助力探索未知自然边界。</t>
+          <t>Arc'teryx: 1989年创立于加拿大的专业高端户外装备品牌，聚焦登山、滑雪、徒步等极限场景，依托GORE-TEX®防水透气、NanoSphere®防泼溅等核心科技，打造Alpha SV冲锋衣、Beta AR夹克、Mantis背包等经典产品，以极致耐用性、人体工学设计与创新功能，成为户外爱好者及专业运动员追求性能巅峰的首选品牌。</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ARE TDRVX is a luxury streetwear brand focusing on avant-garde and functional aesthetics. With original design, clean silhouettes and premium craftsmanship, it blends street personality with daily wearability. Offering apparel and accessories, it provides one-stop fashion solutions for urban youth and is popular among trend lovers.</t>
+          <t>Arc'teryx: Premium outdoor gear since 1989. For mountaineering, skiing, hiking. GORE-TEX® &amp; NanoSphere® tech. Durable, ergonomic, innovative. Top choice for outdoor enthusiasts and athletes.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="25.5" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Arc teryx</t>
+          <t>Arizona Cardinals</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Arc teryx</t>
+          <t>arizona-cardinals</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Arc'teryx: Arc'teryx 是顶级户外装备品牌，以其高性能冲锋衣、硬壳夹克和专业技术服装闻名。采用 GORE-TEX 面料和创新设计，为登山、滑雪和探险活动提供极致保护与舒适。Arc'teryx 产品以耐用性、功能性和极简美学著称，是户外运动爱好者和专业运动员的首选装备。</t>
+          <t>Arizona Cardinals: 美国国家橄榄球联盟（NFL）历史最悠久的球队之一，隶属于NFC西部分区，1898年创立于芝加哥，现主场为亚利桑那州格伦代尔的State Farm Stadium，以红色、白色为主队色，曾晋级第37届超级碗（XXXVII），球队风格坚韧，聚焦团队协作，拥有庞大忠实球迷群体，是NFL极具辨识度的经典职业橄榄球队伍。</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Arc'teryx: Top outdoor gear brand for high-performance GORE-TEX jackets, hardshells, and technical apparel. Built for mountaineering, skiing, and extreme expeditions with durability, functionality, and minimalist design.</t>
+          <t>Arizona Cardinals: NFL's oldest team founded 1898, NFC West. Home: State Farm Stadium, Arizona. Red/white colors. Super Bowl XXXVII appearance. Resilient, teamwork, loyal fans. Iconic classic football.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="25.5" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ARIZONA CARDINALS</t>
+          <t>Armani</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>arizona-cardinals</t>
+          <t>armani</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ARIZONA CARDINALS: 美国国家橄榄球联盟（NFL）历史最悠久的球队之一，1898年成立于芝加哥，以标志性红雀队徽和红白队服闻名。主场State Farm Stadium，代表球员包括Larry Fitzgerald等传奇球星。</t>
+          <t>Armani: 1975年由乔治·阿玛尼（Giorgio Armani）创立的意大利高端时尚品牌，以极简主义设计、精湛剪裁工艺与经典优雅风格著称，产品线覆盖高级成衣、美妆、皮具、配饰及家居等领域，标志性产品包括Armani Si香水、Giorgio Armani定制西装，致力于为全球消费者提供兼具质感与品味的高端生活方式选择。</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ARIZONA CARDINALS: NFL's oldest franchise est. 1898. Iconic red bird logo &amp; red/white uniforms. Home: State Farm Stadium. Legends like Larry Fitzgerald.</t>
+          <t>Armani Italian luxury fashion brand founded by Giorgio Armani in 1975, renowned for minimalist design, exquisite tailoring &amp; classic elegance. Product lines cover haute couture, beauty, leather goods, accessories, homeware. Iconic products: Armani Si perfume, Giorgio Armani custom suits. Dedicated to premium lifestyle with quality &amp; taste.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="25.5" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ARMANI</t>
+          <t xml:space="preserve"> Artie Master</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>armani</t>
+          <t xml:space="preserve"> artie master</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ARMANI: 意大利奢侈品牌ARMANI由Giorgio Armani于1975年创立，以其简约优雅的设计风格闻名。产品系列涵盖高级时装、美妆、眼镜及家居，经典包括权力西装和Acqua di Gio香水，采用顶级面料与精湛工艺，诠释低调奢华的现代美学。</t>
+          <t>Artie Master由 Li Guoren 于2019 年创立，隶属中山市帝琦服装，主打美式街头快时尚。核心产品含重磅 T 恤、连帽卫衣、长裤与复古帽款，以优质棉为核心材质，强调舒适透气与高性价比，融合复古街头美学，风靡欧美等海外市场。</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ARMANI: Italian luxury brand founded by Giorgio Armani in 1975, renowned for minimalist elegance. Features power suits, Acqua di Gio perfume, fashion, beauty, eyewear, and home with premium fabrics and craftsmanship.</t>
+          <t>Artie Master: Founded 2019, American street fast fashion. Heavyweight T-shirts, hoodies, pants, vintage caps. Premium cotton, comfortable, breathable, high value. Retro street aesthetics, popular overseas.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="25.5" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ARTIEmaster</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> artie master</t>
-        </is>
-      </c>
-      <c r="C25"/>
+          <t>arsenal</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Arsenal: 1886年创立于英国伦敦的顶级职业足球俱乐部，绰号“枪手”（The Gunners），主场为酋长球场（Emirates Stadium），是英超联赛传统豪强。队史累计夺得13次英格兰顶级联赛冠军、14次足总杯冠军等荣誉，曾以“美丽足球”战术风格享誉足坛，拥有全球超亿球迷基础，其官方球衣、赛事直播及球迷互动内容长期占据足球领域搜索热点。</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ARTIEmaster delivers high-street men's apparel, specializing in heavyweight cotton T-shirts (305g), fleece-lined sweatpants, and versatile urban wear. Designed for trend-focused youth, the brand combines premium materials like pure cotton and blends with loose, contemporary fits for autumn/winter seasons. Explore curated collections optimize</t>
+          <t>Arsenal: 1886 London club "The Gunners", Emirates Stadium home. 13 Premier League &amp; 14 FA Cup titles. Beautiful football. 100M+ global fans. Top searches: jerseys, streams, fan content.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="25.5" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ARSENAL</t>
+          <t>As Roma</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>as-roma</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ARSENAL: 创立于1998年的美国户外运动品牌，专注于高性能战术装备和军迷服饰，产品系列涵盖战术背包、户外服装、作战靴及配件，经典产品包括多用途战术背包和速干战术衬衫，采用耐磨尼龙及防水科技面料，工艺精密，功能性强，风格硬朗实用，适用于户外探险与军事爱好者。</t>
+          <t>As Roma: 1927年成立于意大利罗马的职业足球俱乐部，意甲联赛传统强队，主场为罗马奥林匹克体育场。队徽融合罗马城标志性“母狼哺婴”元素，传承千年古城文化基因。曾夺得3次意甲冠军、9次意大利杯冠军等荣誉，以极具辨识度的红黄色主场球衣及激情赛场风格著称，拥有全球海量球迷基础，其官方周边（如球衣、队徽纪念品）紧密联结足球文化与罗马城市精神，是意甲联赛中代表罗马城市形象的核心体育品牌。</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ARSENAL: US outdoor gear brand since 1998. Tactical backpacks, apparel, boots &amp; accessories. Durable nylon, waterproof tech. Functional design for military enthusiasts &amp; adventurers.</t>
+          <t>AS Roma: Founded in Rome, Italy in 1927, a top Serie A club playing at Stadio Olimpico. Its badge features Rome’s iconic "She-Wolf Nurturing Twins," embodying the ancient city’s culture. With 3 Serie A titles &amp; 9 Coppa Italia wins, it’s known for red-yellow kits, passionate style, global fans, and merch linking football to Rome’s spirit—Serie A’s core brand for Rome.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="25.5" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ARTIEMASTER</t>
+          <t>Asics</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>artiemaster</t>
-        </is>
-      </c>
-      <c r="C27"/>
-      <c r="D27"/>
+          <t>asics</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Asics: 1949年由鬼冢喜八郎创立于日本，全球知名专业运动品牌，秉持“健全精神寓于健全身体”的品牌理念，深耕跑鞋及全方位运动装备领域。核心技术涵盖GEL缓震胶、FlyteFoam轻量中底、Dynamic DuoMax支撑系统等行业标杆科技，经典产品系列包括Nimbus（顶级缓震跑鞋）、Kayano（支撑系旗舰）、GT-2000（稳定支撑入门）等，专注为跑者及运动爱好者提供专业、舒适、耐用的运动解决方案，是全球跑圈公认的“跑鞋专家”。</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Asics: Founded in 1949 in Japan by Kihachiro Onitsuka, a globally renowned professional sportswear brand with the philosophy "Sound Mind in a Sound Body". Core tech: GEL cushioning, FlyteFoam midsole, Dynamic DuoMax. Classic lines: Nimbus (top cushioning), Kayano (support flagship), GT-2000 (stability entry). Trusted "Running Shoe Expert" for runners worldwide.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="25.5" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AS ROMA</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>as-roma</t>
+          <t>aston-villa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AS ROMA: 1927年成立的意大利传奇足球俱乐部，以其标志性的红黄配色、狼徽图腾及奥林匹克主场闻名，提供正版球衣、训练装备及粉丝周边，材质透气工艺精湛，风格热血激情，代表永恒之城罗马的荣耀与忠诚。</t>
+          <t>Aston Villa: 1874年创立于英格兰伯明翰的百年足球俱乐部，英超老牌劲旅，曾获1次欧洲冠军杯冠军、7次英格兰顶级联赛冠军、7次足总杯冠军，主场为拥有逾百年历史的维拉公园球场（可容纳约4.2万观众），以深厚的历史底蕴、热忱的球迷文化与标志性酒红&amp;蓝色队服闻名，是英格兰足球史上最具代表性的传统豪门之一。</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AS ROMA: Legendary Italian football club since 1927, iconic red-yellow kits &amp; wolf emblem. Official jerseys, training gear &amp; fan merch with breathable fabric &amp; craft. Passionate style embodying Rome's glory.</t>
+          <t>Aston Villa: Historic English Premier League club founded 1874 in Birmingham. Winner of 1 European Cup, 7 league titles, 7 FA Cups. Home: Villa Park (42k capacity). Iconic claret &amp; blue, rich heritage, passionate fans.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="25.5" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>asics</t>
+          <t>athletic-club-bilbao</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ASICS: ASICS 是日本领先的运动鞋和运动服装品牌，致力于通过创新科技提升运动表现。品牌以 Gel 缓震技术为核心，为跑步、训练、网球等各类运动提供专业装备。ASICS 的产品结合人体工学设计和优质材料，确保舒适性、支撑性和耐用性。无论是专业运动员还是日常健身爱好者，ASICS 都助力实现最佳运动状态。探索 ASICS，体验科学运动带来的卓越表现与舒适感受。</t>
+          <t>Athletic Club Bilbao: 成立于1898年，西班牙毕尔巴鄂竞技足球俱乐部，以只使用巴斯克球员的传统而闻名。提供官方球衣、纪念品和体育用品，工艺精湛，风格经典，是足球迷和收藏家的首选品牌，适合跨境电商平台推广。</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ASICS: Leading Japanese sports brand innovating with GEL cushioning tech for running, training, tennis. Ergonomic gear for pros and enthusiasts.</t>
+          <t>Athletic Club Bilbao: Founded 1898, Spanish football club famed for Basque-only player tradition. Offers official jerseys, souvenirs, sports gear with exquisite craftsmanship, classic style. Top choice for fans &amp; collectors, ideal for cross-border e-commerce.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="25.5" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ASTON VILLA</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>aston-villa</t>
+          <t>atletico-madrid</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ASTON VILLA: 成立于1874年的英国伯明翰，是英格兰足球联赛中最具历史底蕴和球迷文化的足球俱乐部之一。主场维拉公园球场气氛热烈，传统队服为酒红色和蓝色。球队以青训体系和攻势足球风格闻名，曾夺得欧洲冠军杯和多次国内顶级联赛荣誉，是英超联赛中备受尊敬的劲旅。</t>
+          <t>Atlético Madrid: 1903年成立于西班牙马德里，西甲传统豪门足球俱乐部，以坚韧防守和团队精神著称，荣誉包括西甲联赛冠军、国王杯及欧洲联赛冠军，主场为万达大都会球场，风格务实顽强，培养出众多世界级球星，是欧洲足坛的重要力量。</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ASTON VILLA: Founded 1874 Birmingham. Historic EPL club renowned for youth academy, attacking football &amp; European Cup glory. Iconic claret &amp; blue kit at vibrant Villa Park.</t>
+          <t>Atlético Madrid: Established 1903 in Madrid, Spanish powerhouse renowned for resilient defense, teamwork, and titles including La Liga, Copa del Rey, UEFA Europa League. Home at Wanda Metropolitano, fostering world-class talents with pragmatic, tenacious style.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="25.5" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ATHLETIC CLUB BILBAO</t>
+          <t>Balenciaga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>athletic-club-bilbao</t>
+          <t>balenciaga</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ATHLETIC CLUB BILBAO：1898年成立的西班牙毕尔巴鄂竞技足球俱乐部，以纯正巴斯克血统球员政策闻名，球衣采用红白条纹设计，材质舒适工艺精湛，风格传统坚韧，代表忠诚与地域文化的足球精神。</t>
+          <t>Balenciaga: 1917年由克里斯托瓦尔·巴伦西亚加（Cristóbal Balenciaga）在西班牙创立，1937年迁至巴黎，是全球顶级高端时尚品牌。品牌覆盖高级时装、鞋履、包袋及配饰，经典单品包括Triple S老爹鞋、Hourglass沙漏包、Motorcycle机车包等。以先锋解构主义、街头文化与高级时装的碰撞为核心风格，近年在创意总监Demna Gvasalia带领下，通过oversize剪裁、复古元素与未来感设计的融合重塑时尚边界，深受全球名流及时尚爱好者追捧，代表高端时尚领域的创新与个性表达。</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ATHLETIC CLUB BILBAO: Founded 1898, Basque-only policy, iconic red-white stripes, traditional resilient, loyal football spirit.</t>
+          <t>Balenciaga: Founded by Cristóbal Balenciaga in Spain (1917), relocated to Paris (1937) – a top luxury fashion brand. Covers haute couture, footwear, bags &amp; accessories, with iconic pieces like Triple S Dad Sneakers, Hourglass Bag, Motorcycle Bag. Boasts avant-garde deconstruction, street culture-high fashion fusion. Under Demna Gvasalia, it redefines fashion via oversize cuts, retro-futuristic designs, loved by celebrities &amp; fashion lovers, embodying luxury innovation &amp; individuality.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="25.5" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ATLETICO MADRID</t>
+          <t>Baltimore Ravens</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>atletico-madrid</t>
+          <t>baltimore-ravens</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ATLETICO MADRID: 西班牙马德里著名足球俱乐部，成立于1903年，以红白条纹球衣和顽强防守风格闻名，主场为万达大都会球场，曾多次夺得西甲冠军和欧联杯荣誉，代表球员包括托雷斯和格列兹曼。</t>
+          <t>Baltimore Ravens: 美国国家橄榄球联盟（NFL）旗下的职业橄榄球队，1996年成立于马里兰州巴尔的摩，主场为M&amp;T Bank Stadium，曾2次夺得超级碗冠军（2000赛季、2012赛季）。球队以强硬防守与富有冲击力的球风著称，队徽采用标志性乌鸦形象，队服主色为紫色、黑色及金色，是巴尔的摩市核心体育符号之一，拥有深厚球迷基础与社区影响力。</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ATLETICO MADRID: Renowned Spanish football club since 1903, famous for red-white stripes, resilient defense, Wanda Metropolitano stadium, La Liga &amp; Europa League titles, featuring Torres &amp; Griezmann.</t>
+          <t>Baltimore Ravens: NFL professional football team founded in Baltimore, Maryland in 1996, home to M&amp;T Bank Stadium. 2-time Super Bowl champions (2000 &amp; 2012), known for tough defense &amp; aggressive play. Logo features iconic raven, primary colors purple/black/gold—core Baltimore sports symbol with strong fan base &amp; community impact.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="25.5" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ATLÉTICO MADRID</t>
+          <t>Bape</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>atltico-madrid</t>
+          <t>bape</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ATLÉTICO MADRID: 1903年成立于西班牙马德里的著名足球俱乐部，以红白相间条纹队服和顽强斗志闻名，主场为万达大都会球场，代表产品包括官方球衣、训练装备及周边配件，采用高性能透气材质，工艺精湛，风格经典运动，深受全球球迷喜爱。</t>
+          <t>Bape: 1993年由Nigo创立于日本原宿的街头潮流品牌，以标志性猿人头logo、独特迷彩图案及鲨鱼外套等经典单品著称，产品线覆盖服装、配饰等类目，融合嘻哈、滑板与街头艺术文化，凭借限量发售及联名合作策略（如与Nike、Adidas等品牌联名），成为日本原宿潮流文化的核心代表品牌之一。</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ATLÉTICO MADRID: Founded 1903, iconic Spanish football club. Renowned for red &amp; white stripes, grit, &amp; Wanda Metropolitano. Official jerseys, gear &amp; accessories. High-performance, breathable fabrics. Crafted for global fans.</t>
+          <t>Bape: 1993 Tokyo streetwear brand iconic ape head logo, shark hoodies camo patterns. Covers apparel accessories, blends hip-hop skate culture. Limited releases collabs with Nike Adidas define Harajuku core.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="25.5" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BALANIEGAS</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>balaniegas</t>
-        </is>
-      </c>
-      <c r="C34"/>
-      <c r="D34"/>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Custo Barcelona（卡斯图・巴塞罗那）由 Custo 与 David Dalmau 兄弟 1980 年创立于西班牙巴塞罗那，1996 年正式定名。主打印花 T 恤、连衣裙、休闲装，以 Custo 为创意总监，用优质棉麻与功能性面料，融地中海艺术与加州冲浪文化，大胆撞色与原创图纹为标志，风靡欧美澳亚，全球超 3000 销售点。</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Custo Barcelona: Founded by brothers Custo &amp; David Dalmau in Barcelona, Spain (1980), officially named in 1996. Focuses on printed tees, dresses &amp; casual wear, with Custo as creative director. Uses premium cotton-linen &amp; functional fabrics, blends Mediterranean art with California surf culture, marked by bold color-blocking &amp; original patterns. Popular across Europe, America, Australia &amp; Asia, with over 3,000 global sales points.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="25.5" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BALENCIAGA</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>balenciaga</t>
+          <t>bayern-munich</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BALENCIAGA: 探索巴黎世家BALENCIAGA官方奢华时尚世界。选购品牌标志性手袋、运动鞋、成衣及配饰，尽享前卫设计、精湛工艺与高级定制传统。即刻选购新品系列与限量合作款，体验颠覆性美学与当代文化重塑的奢侈风范。全球配送与专属售后服务。</t>
+          <t>Bayern Munich: 1900年成立于德国慕尼黑，是全球顶级足球俱乐部标杆，累计夺得32次德甲联赛冠军、6次欧洲冠军联赛冠军等荣誉，主场为安联球场，以红蓝白队徽、"Mia San Mia"精神闻名，拥有全球亿万球迷，传承德国足球严谨战术与进攻传统，是欧洲足坛影响力深远的传奇俱乐部。</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BALENCIAGA: Discover avant-garde luxury fashion. Shop iconic bags, sneakers, ready-to-wear &amp; accessories. Enjoy cutting-edge design &amp; craftsmanship. Global shipping.</t>
+          <t>Bayern Munich: Founded 1900 in Munich, global football icon with 32 Bundesliga &amp; 6 Champions League titles. Allianz Arena home. Red-blue-white crest, "Mia San Mia" spirit. German football legacy, billions of fans.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="25.5" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BALTIMORE RAVENS</t>
+          <t>Beats</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>baltimore-ravens</t>
+          <t>beats</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BALTIMORE RAVENS: 1996年成立的美国职业橄榄球队，以强悍防守和稳定战绩闻名，曾多次夺得超级碗冠军，球队标志为紫色和黑色，风格硬朗坚韧，代表球员包括雷·刘易斯和拉马尔·杰克逊。</t>
+          <t>Beats: 由音乐制作人Dr. Dre联合创立、苹果旗下知名音频品牌，专注无线耳机、降噪耳机及便携式扬声器研发，以澎湃低音、精准声场与潮流设计为核心特色，融合街头文化与科技质感，经典系列如Beats Studio Buds（自适应降噪）、Solo 3 Wireless（长效续航）深受全球年轻人及音乐爱好者青睐，是“音效与时尚兼具”的音频选择。</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>BALTIMORE RAVENS: NFL team since 1996, known for tough defense, Super Bowl wins, iconic purple &amp; black colors, featuring stars like Ray Lewis &amp; Lamar Jackson.</t>
+          <t>Beats: Apple audio brand by Dr. Dre, offering wireless headphones, noise-cancelling earbuds, portable speakers with powerful bass, precise soundstage, trendy design, blending street culture and tech, popular among youth for sound and style.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="25.5" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BAPE</t>
+          <t>Bvlgari</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>bape</t>
+          <t>bvlgari</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BAPE: BAPE 是日本潮流品牌 A Bathing Ape 的简称，以其独特的迷彩图案、鲨鱼帽衫和街头风格设计闻名。品牌融合高品质面料与限量发售策略，打造出备受全球潮流爱好者追捧的服饰、鞋履及配件系列。</t>
+          <t>Bvlgari: 1884年由希腊银匠Sotirios Voulgaris创立于意大利罗马的奢华品牌，核心涵盖珠宝、腕表、香水及皮具品类，标志性Serpenti灵蛇系列融合希腊罗马文化与意大利文艺复兴设计美学，B.zero1系列以极简几何演绎现代奢华，精选高端彩色宝石、贵金属等材质，工艺精湛，是全球高端奢华生活方式的代表性品牌。</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BAPE: A Bathing Ape is a Japanese streetwear brand known for its iconic camo prints, shark hoodies, and unique designs, featuring premium materials and limited-edition releases.</t>
+          <t>Bvlgari: Italian luxury brand since 1884, renowned for jewelry, watches, and iconic Serpenti &amp; B.zero1 collections, fusing Roman heritage with modern craftsmanship.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="25.5" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BARCELONA</t>
+          <t>Binken</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>barcelona</t>
-        </is>
-      </c>
-      <c r="C38"/>
-      <c r="D38"/>
+          <t>binken</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Binken是专注消费电子的品牌，2015 年创立于中国，主打无线 HDMI 延长器、便携式汽车打气泵等产品。设计团队注重实用性与简约美学，产品采用优质 ABS 外壳、高纯度铜线芯，兼具耐用性与便携性。风格简约大气，操作便捷，畅销欧美、东南亚等地区，深受家庭用户与商务人士喜爱，以高性价比赢得市场认可。</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Binken Consumer electronics since 2015. Wireless HDMI extenders &amp; portable car air pumps. ABS shells &amp; copper cores for durability &amp; portability. Minimalist, user-friendly. Popular in EU, US, SE Asia. Home &amp; business favorite for great value.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="25.5" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BAYERN MUNICH</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>bayern-munich</t>
+          <t>borussia-dortmund</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BAYERN MUNICH:  
-1900年成立的德国传奇足球俱乐部，以卓越战绩和青训体系闻名，产品系列包括球衣、训练装备及周边商品，经典款有主场球衣和欧冠纪念服，采用高性能透气材质，工艺精湛，功能实用，风格经典运动。</t>
+          <t>Borussia Dortmund: 1909年创立于德国多特蒙德的传奇足球俱乐部，绰号“大黄蜂”，以激进攻势足球风格、顶尖青训体系及全球最狂热的主场氛围（Signal Iduna Park威斯特法伦球场，欧洲最大足球场之一）著称，曾斩获欧洲冠军联赛、8次德甲联赛冠军等荣誉，是世界足坛极具人气与影响力的俱乐部，聚焦年轻力量与球迷文化的深度联结。</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>BAYERN MUNICH: Legendary German football club since 1900, renowned for excellence, performance jerseys, training gear, and Champions League merchandise.</t>
+          <t>Borussia Dortmund: Legendary German football club founded 1909 in Dortmund, nicknamed "The Hornets". Known for aggressive attacking style, top youth academy, and passionate home atmosphere at Signal Iduna Park (Westfalenstadion, one of Europe’s largest stadiums). Won UEFA Champions League &amp; 8 Bundesliga titles; a popular, influential club focusing on youth power and fan culture ties.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="25.5" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Better Call Saul</t>
+          <t>Bose</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>better call saul</t>
+          <t>bose</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arachnid Robotics: 探索Arachnid Robotics的尖端蜘蛛机器人技术与创新自动化解决方案。我们的产品专为工业检测、搜救任务与复杂环境作业设计，结合仿生学设计与先进AI算法，提供卓越的机动性与适应性。Arachnid Robotics致力于推动机器人技术边界，为全球客户提供可靠、高效的自动化服务。立即了解我们的定制化机器人解决方案，提升您的业务效率与安全性。
-Mystic Brews: 探索Mystic Brews的精酿茶叶与草本茶系列，融合传统工艺与现代创新。我们严格筛选全球优质原料，提供有机认证、无添加的天然茶饮，包括舒缓花草茶、活力红茶与独特混合口味。Mystic Brews致力于为茶爱好者带来沉浸式体验，每一杯都蕴含自然魔力与健康益处。立即购买，开启您的茶道之旅。
-Nebula Wear: 发现Nebula Wear的未来感科技服装系列，将智能织物技术与时尚设计完美结合。我们的产品包括温控外套、LED互动卫衣与环保再生材料服饰，专注于舒适性、耐用性与创新功能。Nebula Wear旨在为日常穿戴注入科技魅力，适合都市生活、户外冒险与科技爱好者。探索我们的系列，升级您的衣橱。
-Solaris Sands: 体验Solaris Sands的高品质沙滩与户外休闲装备，专为阳光下的冒险打造。我们的产品涵盖防晒服饰、轻便沙滩椅、环保防水包及多功能遮阳配件，采用快干材料与UPF防护技术。Solaris Sands结合实用设计与可持续理念，为您的海滩旅行、露营度假提供可靠解决方案。立即选购，享受阳光与自由。
-Verve &amp; Pulse: 探索Verve &amp; Pulse的活力运动服饰与健身装备，专为活跃生活方式设计。我们提供高性能瑜伽裤、透气运动上衣、智能健身配件及环保再生材料产品，注重舒适贴合与时尚风格。Verve &amp; Pulse融合科技与运动营养理念，支持您的健身目标与健康生活。立即浏览系列，激发每一天的能量。</t>
+          <t>Bose: 1964年由Amar G. Bose博士创立于美国马萨诸塞州，全球专业音频设备领导品牌，以原创主动降噪技术与高保真音质调校为核心优势。核心产品覆盖QuietComfort系列降噪耳机、SoundLink蓝牙扬声器、家庭影院音响系统及专业音频解决方案，适用于通勤、居家、音乐创作等多场景，凭借“深度降噪”“沉浸式音质”“持久舒适佩戴”等特点，成为追求音频品质用户的首选品牌。</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Better Call Saul: Premier legal services for cross-border e-commerce, offering expert compliance solutions &amp; business protection. Secure growth.</t>
+          <t>Bose: Founded in 1964 by Dr. Amar G. Bose. A leader in premium audio, renowned for original active noise cancelling technology and high-fidelity sound. Core products include QuietComfort headphones, SoundLink speakers, and home theater systems for commuting, home, and more.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="25.5" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BEE DYNASTY</t>
+          <t>Boy London</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>bee-dynasty</t>
+          <t>boy london</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BEE DYNASTY: 创立于2015年的中国高端蜂蜜品牌，专注于天然纯蜂蜜及蜂产品系列，经典产品包括野生百花蜜和蜂王浆胶囊，采用优质蜂源和低温工艺，功能营养丰富，风格自然健康。</t>
+          <t>Boy London: 1976年诞生于英国伦敦的经典街头潮流品牌，以朋克叛逆精神为内核，标志性翅膀鹰标与粗体LOGO成为全球街头文化的标志性符号，产品涵盖潮服、配饰等，长期联动摇滚、嘻哈艺人及顶尖潮牌，是欧美及亚洲潮流圈备受追捧的“街头叛逆代表”，承载着 generations对自由不羁风格的追求。</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>BEE DYNASTY: Premium pure honey &amp; bee products since 2015. Raw wild honey &amp; royal jelly capsules. Nutrient-rich, natural, cold-processed.</t>
+          <t>Boy London: Born in London 1976. Punk-inspired streetwear with iconic winged eagle logo. A global symbol of rebellious style across generations.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="25.5" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Beats</t>
+          <t>Broken Planet</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>beats</t>
-        </is>
-      </c>
-      <c r="C42"/>
+          <t>broken-planet</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Broken Planet: 源自英国的先锋街头潮牌，以“废土未来主义”为核心设计语言，融合做旧、解构剪裁与反消费主义标语印花，主打卫衣、T恤、机能外套及配饰系列。品牌深耕可持续时尚，采用回收面料与复古工艺重构服饰，传递对“破碎星球”的人文思考与环保主张，凭借独特的 dystopia 美学与社会议题表达，成为全球潮流青年、街头文化爱好者及环保理念支持者的穿搭选择，是兼具个性态度与责任意识的当代潮牌代表。</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Orolay: Orolay specializes in premium down jackets and fashionable outerwear, offering winter clothing that combines warmth with design to keep you stylish in cold seasons.
-Juliette Has A Gun: Juliette Has A Gun redefines niche perfumes with unique, bold scents that express individuality and charm for an extraordinary fragrance experience.
-Staud: Staud interprets classic bags and ready-to-wear with modern design, blending vintage inspiration and contemporary aesthetics for unique, refined accessories.
-Loeffler Randall: Loeffler Randall creates elegant footwear, bags, and accessories merging artistic design with functionality for modern women's daily and special occasions.
-Dagne Dover: Dagne Dover offers functional and fashionable bags and accessories with smart storage solutions for urban life and travel, enhancing daily experiences.
-Hill House Home: Hill House Home is known for comfortable, elegant homewear and decor, especially stylish Napili dresses, adding relaxed elegance to home life.
-Cuts Clothing: Cuts Clothing focuses on high-quality men's basics with precise tailoring and premium fabrics for简约而高级的日常着装解决方案.
-Away: Away revolutionizes travel with smartly designed luggage and accessories featuring durable materials and modern tech for easier, more convenient journeys.
-Béis: Béis offers chic, practical travel and lifestyle products like luggage and bags, making travel and daily storage more stylish and efficient.
-True Classic: True Classic creates comfortable, versatile men's tees with tailored fits and soft fabrics to solve fit issues and showcase简约自信风格.
-Larq: Larq uses self-cleaning tech and UV-C purification to redefine hydration with stylish, efficient bottles for a healthy, eco-friendly lifestyle.
-Liquid Death: Liquid Death markets natural mountain water in cans with punk visuals, promoting health while breaking industry norms creatively.
-Olipop: Olipop combines traditional fermentation and modern nutrition for tasty, prebiotic sodas that support digestive health without compromising flavor.
-Celsius: Celsius offers energy-burning fitness drinks with MetaPlus® to boost metabolism and performance for active lifestyles.
-Blueland: Blueland provides eco-friendly cleaning solutions with reusable systems to reduce plastic waste, making sustainability simple and effective.
-JAXJAX: JAXJAX designs stylish, functional modular bags with urban aesthetics for modern professionals' flexible commute and travel needs.
-Bala: Bala reinvents fitness accessories with fun, colorful ankle weights and bands, making home workouts more enjoyable and lighthearted.
-Bala Bangles: Bala Bangles combines fashion and function with adjustable ankle weights that enhance workouts and daily style.
-Caraway: Caraway transforms cooking with non-toxic, beautiful ceramic-coated cookware and kitchenware for healthier, more enjoyable meals.
-Sweetgreen: Sweetgreen serves fresh, delicious salads and bowls using local organic ingredients, advocating healthy fast food and sustainable farming.</t>
+          <t>Broken Planet: British avant-garde streetwear brand embracing dystopian futurism with distressed, deconstructed cuts and anti-consumerist prints. Features hoodies, tees, jackets, accessories. Sustainable fashion using recycled fabrics and vintage techniques for eco-conscious global youth.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="25.5" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bvlgari</t>
+          <t>Broken Hearts</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>bvlgari</t>
+          <t>broken-hearts</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bvlgari宝格丽于1884年由希腊银匠索帝里欧·宝格丽（Sotirio Bulgari）在意大利罗马创立，是享誉全球的奢侈品牌。品牌以18K黄金、钻石、宝石及优质皮革为核心材质，标志性系列包括Serpenti蛇形系列、B.zero1系列、Divas’ Dream女神系列及Octo腕表系列，融合罗马古典美学与现代奢华格调。皮具及配饰由创意总监Mary Katrantzou主导设计，主营珠宝、腕表、皮具及香水，以精湛匠艺传承罗马文化精髓。</t>
+          <t>Broken Hearts 2022 年创立于意大利那不勒斯，主打纯银情感珠宝，采用 925 纯银手工打造，无镀层、不氧化变色。以破碎心形为核心符号，融意式金匠工艺与情感艺术风格，设计简约有力量，畅销欧美高端配饰市场，是小众轻奢银饰代表。</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Founded in 1884 in Rome, Italy by Greek silversmith Sotirio Bulgari, Bvlgari is a luxury brand. Featuring 18K gold, diamonds, gemstones &amp; premium leather, its iconic series include Serpenti, B.zero1, Divas’ Dream &amp; Octo, blending Roman heritage with modern luxury, led by creative director Mary Katrantzou for leather goods. It offers jewelry, watches, leather goods &amp; perfumes.</t>
+          <t>Broken Hearts: Founded 2022 Naples, Italy. Pure silver emotional jewelry, 925 sterling silver handcrafted, no plating, non-tarnishing. Broken heart core symbol, blending Italian goldsmith craft &amp; emotional art, minimalist &amp; powerful. Best-selling in high-end EU/US accessories markets, niche luxury silver jewelry.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="25.5" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BINKEN</t>
+          <t>Brooks</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>binken</t>
-        </is>
-      </c>
-      <c r="C44"/>
-      <c r="D44"/>
+          <t>brooks</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Brooks: 1914年创立于美国的百年专业跑步品牌，专注跑步鞋服及配件研发，核心科技涵盖DNA LOFT缓震技术与GUIDERAILS步态支撑系统，产品覆盖马拉松、越野跑、日常训练等多元场景，以专业性能、舒适脚感与耐用品质，成为全球跑者信赖的选择。</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Brooks: Founded in the US in 1914, a century-old professional running brand specializing in running footwear, apparel, and accessories. Core tech includes DNA LOFT cushioning and GUIDERAILS gait support systems. Products cover marathons, trail running, daily training, etc. Trusted by global runners for professional performance, comfort, and durability.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="25.5" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BORUSSIA DORTMUND</t>
+          <t>BURBERRY</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>borussia-dortmund</t>
+          <t>burberry</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BORUSSIA DORTMUND: 1909年成立于德国多特蒙德的足球俱乐部，以黄黑配色和激情风格闻名，经典产品包括球迷球衣和周边商品，采用高性能材质和精湛工艺，功能舒适耐用，风格运动激情。</t>
+          <t>BURBERRY: 1856年由托马斯·博柏利（Thomas Burberry）创立于英国的经典奢侈品牌，以标志性格纹图案与Trench Coat经典风衣著称，产品线覆盖男女成衣、皮具配饰、香水及美妆，融合英伦传统工艺与现代设计语言，诠释永恒奢华风格，是全球高端时尚领域的标志性品牌。</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>BORUSSIA DORTMUND: Founded 1909, German football club. Known for yellow-black colors, passionate style. High-performance fan jerseys &amp; merchandise with craftsmanship.</t>
+          <t>BURBERRY: Founded in the UK by Thomas Burberry in 1856, iconic luxury brand famed for signature check pattern &amp; Trench Coat. Offers men’s/women’s ready-to-wear, leather goods, accessories, perfume &amp; beauty. Blends British craftsmanship with modern design, embodies timeless luxury, global high-end fashion icon.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="25.5" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bose</t>
+          <t>Bvlgari</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>bose</t>
-        </is>
-      </c>
-      <c r="C46"/>
+          <t>bvlgari</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Bvlgari: 1884年由希腊裔珠宝匠索蒂里奥·宝格丽（Sotirio Bulgari）在意大利罗马创立的全球顶级奢华品牌，以“融合古典与现代的罗马风格”为核心，深耕高级珠宝、奢华腕表、精品配饰、经典香水及高端酒店领域。标志性Serpenti蛇形系列凭借灵动造型与彩色宝石的极致运用成为永恒经典，品牌始终以精湛意大利工艺演绎珍稀材质（如红宝石、蓝宝石、祖母绿及贵金属），诠释“永恒的罗马奢华”理念，是全球高净值人群追求精致生活与身份象征的首选品牌之一。</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Bose: Premium audio products, noise cancelling headphones, wireless earbuds, home speakers, and sound systems for immersive sound experience.</t>
+          <t>Bvlgari: Founded 1884 by Greek jeweler Sotirio Bulgari in Rome, Italy. Top luxury brand blending classic &amp; modern Roman style, specializing in fine jewelry, watches, accessories, fragrances &amp; hotels. Iconic Serpenti snake collection (dynamic design, colored gemstones) is timeless. Italian craftsmanship, rare materials (rubies, sapphires, emeralds, precious metals) embody "eternal Roman luxury"—top choice for global HNWI seeking refined living &amp; status.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="25.5" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Boy London</t>
+          <t>BYREDO</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>boy london</t>
+          <t>byredo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BOY LONDON1976 年创立于英国，由 Stephane Raynor 打造，是朋克先锋街头潮牌。以展翅老鹰 LOGO、oversize 廓形为标志，主打叛逆自由风格。经典款含鹰标 T 恤、卫衣、棒球夹克，覆盖经典、黑金、街头系列，彰显英伦亚文化态度，适配潮流穿搭与个性表达。</t>
+          <t>BYREDO: 2006年由Ben Gorham创立于瑞典斯德哥尔摩的高端香氛品牌，核心覆盖香水、家居香氛、身体护理及配饰系列，以极简北欧美学融合艺术化调香为标志，选用全球优质原料，经典代表作如「无人区玫瑰（Rose of No Man's Land）」香水，风格清冷高级，是追求独特质感与小众品味消费者的热门之选。</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Founded in 1976 in the UK by Stephane Raynor, BOY LONDON is an iconic punk streetwear brand. Signature eagle logo, oversized cuts, bold prints define its rebellious style. Must-haves: eagle tees, hoodies, varsity jackets. Classic, Black Gold &amp; Street series deliver authentic British subculture flair for trendy, individual street style.</t>
+          <t>BYREDO: Luxury fragrance brand founded by Ben Gorham in 2006, Stockholm, Sweden. Core lines: perfume, home fragrance, body care, accessories. Features minimalist Nordic aesthetics + artistic perfumery, premium global ingredients. Iconic "Rose of No Man's Land" perfume, cool sophisticated style—popular for unique texture &amp; niche taste seekers.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="25.5" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BREAKING BAD</t>
+          <t>Cactus Jack</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>breaking-bad</t>
-        </is>
-      </c>
-      <c r="C48"/>
-      <c r="D48"/>
+          <t>cactus-jack</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Cactus Jack: 由美国说唱歌手Travis Scott于2017年创立的街头潮流品牌，以标志性仙人掌LOGO、硬核机能风格与限量联名系列为核心标签，产品线覆盖卫衣、工装裤、运动鞋及潮流配件，经典合作包括与Nike Air Jordan、McDonald's的跨界企划，融合街头文化与叛逆精神，是全球潮人追逐的街头潮流符号。</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Cactus Jack: Streetwear brand founded by US rapper Travis Scott in 2017, featuring iconic cactus logo, hardcore functional style &amp; limited collabs. Lines cover hoodies, cargo pants, sneakers, accessories. Classic collabs: Nike Air Jordan, McDonald’s. Blends street culture &amp; rebellious spirit, global streetwear icon.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="25.5" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BROKEN PLANET</t>
+          <t>Cactus Plant Flea Market</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>broken-planet</t>
+          <t>cactus-plant-flea-market</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BROKEN PLANET: Broken Planet 是专注于街头潮流与可持续时尚的先锋品牌，以前卫设计和环保理念重新定义现代街头服饰。品牌采用再生材料和有机面料，打造连帽衫、T恤和运动裤等标志性单品，融合醒目印花与宽松剪裁，传递反叛与自我表达的精神。Broken Planet 致力于减少时尚业的环境影响，为追求个性与环保的年轻人提供独特而负责任的时尚选择。</t>
+          <t>Cactus Plant Flea Market: 美国街头潮流代表品牌，由Cynthia Lu创立，以童趣卡通风格、标志性笑脸印花及毛绒质感单品为核心辨识度，深度联动Nike、adidas、麦当劳等跨领域品牌推出现象级联名系列，产品融合街头文化与艺术创意，坚持限量发行策略，精准触达全球潮流爱好者，是兼具玩趣与收藏价值的街头潮流IP。</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BROKEN PLANET: Streetwear brand fusing avant-garde style &amp; sustainable fashion with eco-friendly materials, hoodies, tees, pants for rebellious self-expression.</t>
+          <t>Cactus Plant Flea Market: Cynthia Lu's streetwear brand with playful cartoons, smiley prints, plush items. Collaborates with Nike, adidas, McDonald's. Fuses street culture and art, limited releases for global collectors.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="25.5" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Broken Hearts</t>
+          <t>Calvin Klein</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>broken-hearts</t>
+          <t>calvin-klein</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Broken Hearts:伦敦可持续街头服饰品牌，标志性的 "Broken Hearts" 胶囊系列，已推出 Vol.1、Vol.2、Vol.3 三季，心形图案、"Hearts Are Made To Be Broken" 标语、3D puff print 技术。Broken Hearts 连帽衫、T 恤、运动裤套装、针织衫等。</t>
+          <t>Calvin Klein: 1968年由Calvin Klein创立的美国高端时尚品牌，以“Less is More”极简主义为核心理念，覆盖内衣、牛仔、成衣、香水等核心品类，经典系列包括标志性的CK Underwear（logo腰边设计）、CK Jeans复古牛仔线，风格融合性感与现代感，是全球时尚界极简美学的代表性品牌之一。</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Broken Hearts: London sustainable streetwear. Iconic capsule series Vol.1-3 with heart designs, 'Hearts Are Made To Be Broken' slogan, 3D puff print. Hoodies, T-shirts, tracksuits, knitwear.</t>
+          <t>Calvin Klein: Founded in 1968 by Calvin Klein, American high-end fashion brand rooted in "Less is More" minimalism. Core categories: underwear, jeans, ready-to-wear, fragrances. Iconic lines: CK Underwear (logo waistband), CK Jeans retro denim. Blends sexy &amp; modern style, a global minimalist fashion representative.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="25.5" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Brooks</t>
+          <t>Canada Goose</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>brooks</t>
+          <t>canada-goose</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brooks 布鲁克斯是 1914 年创立于美国费城的百年专业跑鞋品牌，现总部位于西雅图，隶属于伯克希尔・哈撒韦集团Brooks Running。专注于高性能跑鞋、运动服饰及配件，标志性系列包括 Ghost 幽灵、Glycerin 甘油、Adrenaline GTS adrenaline、Cascadia 卡斯卡迪亚等。采用 DNA Loft、BioMoGo DNA 等创新缓震技术与优质工程网眼材质，将专业功能性与舒适体验完美融合，为全球跑者提供专业跑步装备。</t>
+          <t>Canada Goose: 1957年创立于加拿大的高端户外保暖品牌，以专业羽绒服与派克大衣为核心产品，依托Arctic Tech防风防水面料、高蓬松度Down Fill羽绒填充等专利技术，实现极致保暖性能与时尚设计的平衡，经典如Chateau Parka系列更是全球冬季保暖服饰的标杆之选，致力于为户外爱好者及追求品质保暖的人群提供兼具功能与美学的服饰解决方案，成为加拿大户外品牌的代表性符号。</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Founded in 1914 in Philadelphia, USA, Brooks (now Seattle-based) is a century-old running brand under Berkshire Hathaway. Specializing in performance running shoes, apparel &amp; accessories, its iconic series include Ghost, Glycerin, Adrenaline GTS, Cascadia. Features innovative DNA Loft/BioMoGo DNA cushioning, premium engineered mesh, merging functionality with comfort for runners worldwideBrooks Running</t>
+          <t>Canada Goose: Founded in Canada in 1957, premium outdoor warmth brand specializing in down jackets &amp; parkas. Leverages patented Arctic Tech (windproof/waterproof) &amp; high-loft Down Fill, balancing extreme warmth with stylish design. Iconic Chateau Parka is a global winter benchmark, catering to outdoor lovers &amp; quality-focused users with functional, aesthetic apparel— a representative Canadian outdoor brand symbol.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="25.5" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BURBERRY</t>
+          <t>Carhartt</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>burberry</t>
+          <t>carhartt</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BURBERRY: 探索英国奢侈品牌Burberry的经典风衣、时尚配饰及标志性格纹系列。品牌融合传统工艺与现代设计，提供高端男装、女装及美妆产品，尽显英伦优雅风格。官方网站提供全球配送服务，享受安全便捷的购物体验。</t>
+          <t>CARHARTT: Carhartt 是源自美国的百年工装品牌，以其耐用、功能性和经典设计闻名。品牌提供高品质的工作服、外套、裤装及配饰，采用坚固面料如帆布和 Duck Cotton 制成，专为劳动者、户外爱好者和追求实用风格的人群打造。Carhartt 产品结合卓越工艺与实用美学，在全球范围内赢得信赖，成为坚固耐用的代名词。</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BURBERRY: British luxury brand offering iconic trench coats, fashion accessories, and signature check patterns. Blending traditional craftsmanship with modern design for high-end menswear, womenswear, and beauty products. Worldwide shipping.</t>
+          <t>Carhartt: Durable American workwear since 1889. Built with tough fabrics like Duck Cotton for laborers, outdoorsmen, and timeless style. Rugged, functional, trusted.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="25.5" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BVLGARI</t>
+          <t>Carolina Herrera</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>bvlgari</t>
+          <t>carolina-herrera</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BVLGARI: 宝格丽是意大利奢华珠宝与腕表品牌,以其大胆设计、璀璨色彩和精湛工艺闻名。探索标志性Serpenti系列、高级珠宝、奢华腕表及香水,体验意式优雅与永恒魅力。购买经典BVLGARI珠宝,尽显非凡品味。</t>
+          <t>Carolina Herrera: 1980年由设计师卡罗琳娜·埃莱拉创立，美国奢侈时尚品牌，产品系列包括高级时装、女士香水、手袋及配饰，经典产品有Good Girl香水和婚纱礼服，采用高档面料与精致工艺，风格优雅时尚。</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BVLGARI: Italian luxury jewelry &amp; watches since 1884. Iconic Serpenti designs, BVLGARI BVLGARI timepieces. Gold, diamonds, enamel. Bold, colorful gemstones.</t>
+          <t>Carolina Herrera: Founded by designer Carolina Herrera in 1980, this American luxury fashion brand offers haute couture, women’s fragrances, handbags &amp; accessories. Classic items include Good Girl fragrance and wedding gowns, crafted from high-end fabrics with exquisite craftsmanship for an elegant, stylish aesthetic.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="25.5" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BYREDO</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>byredo</t>
+          <t>casablanca</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BYREDO: 2006年由Ben Gorham创立于斯德哥尔摩的奢侈香氛品牌，以简约设计和艺术灵感著称，产品系列涵盖香水、香薰蜡烛、身体护理等，经典产品有Gypsy Water和Mojave Ghost香水，采用高品质香料，工艺精湛，风格现代极简。</t>
+          <t>Casablanca（卡萨布兰卡）2018 年由摩洛哥裔法国设计师 Charaf Tajer 在巴黎创立，以父母相遇城市命名。主打男女奢华休闲装，含真丝衬衫、羊绒针织、定制夹克，融合法式优雅、北非风情与运动休闲，标志性网球印花与地中海色调，畅销欧美及全球高端时尚圈，材质优选真丝、羊绒、精梳棉，尽显度假风奢华舒适。</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BYREDO: Luxury fragrance brand from Stockholm, founded 2006. Known for minimalist design, artistic inspiration, and high-quality scents like Gypsy Water &amp; Mojave Ghost. Offers perfumes, candles, and body care.</t>
+          <t>Casablanca: Founded in Paris (2018) by Moroccan-French designer Charaf Tajer, named for parents’ meeting city. Luxe unisex casualwear (silk shirts, cashmere knits, tailored jackets) blends French elegance, North African charm &amp; sporty vibes. Signature tennis prints, Mediterranean hues; premium silk/cashmere/combed cotton. Popular in global high-end fashion, offering resort luxury comfort.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="25.5" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CACTUS JACK</t>
+          <t>Cartier</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>cactus-jack</t>
+          <t>cartier</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CACTUS JACK: 潮牌CACTUS JACK由Travis Scott创立的街头服饰品牌，融合音乐、艺术与休斯顿文化基因。品牌主打限定联名系列、反主流设计和高辨识度仙人掌标识，提供男女款限量卫衣、嘻哈风外套和配饰。官方渠道不定期发售突击式新品，适合追求稀缺潮品的Z世代收藏。</t>
+          <t>Cartier: 1847年由路易·弗朗索瓦·卡地亚创立，法国奢侈品牌，产品系列包括珠宝、手表、皮具、配饰等，经典产品有Love手镯、Tank手表、Trinity戒指，采用黄金、铂金、钻石等珍贵材质，工艺精湛，设计优雅，风格奢华经典，适合高端消费者和收藏家。</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CACTUS JACK: Travis Scott's streetwear brand blends music, art &amp; Houston culture. Limited collabs, anti-mainstyle design, iconic cactus logo. Z-gen scarcity-driven drops.</t>
+          <t>Cartier: Founded in 1847 by Louis-François Cartier, a French luxury brand offering jewelry, watches, leather goods &amp; accessories. Iconic pieces: Love bracelet, Tank watch, Trinity ring. Crafted from gold, platinum, diamonds with exquisite craftsmanship, elegant &amp; luxurious classic style for high-end consumers &amp; collectors.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="25.5" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CACTUS PLANT FLEA MARKET</t>
+          <t>Cav Empt</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>cactus-plant-flea-market</t>
+          <t>cav-empt</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CACTUS PLANT FLEA MARKET:  
-独特街头潮牌，以创意仙人掌图案和搞怪设计闻名，产品涵盖卫衣、T恤、配饰等，经典款有卡通印花卫衣和联名系列，采用棉质和环保材质，工艺个性，风格年轻潮流。</t>
+          <t>Cav Empt: 2011年由设计师Sk8thing和Toby Feltwell创立的日本街头服饰品牌，以复古未来主义风格和标志性图形设计著称，产品涵盖T恤、夹克、配饰等，采用优质面料，工艺精湛，风格独特前卫，深受全球潮流爱好者追捧。</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CACTUS PLANT FLEA MARKET: Trendy streetwear brand known for creative cactus designs &amp; quirky style. Hoodies, tees, accessories. Cotton &amp; eco-friendly materials. Youthful, unique fashion.</t>
+          <t>Cav Empt: Japanese streetwear since 2011 by Sk8thing &amp; Toby Feltwell. Retro-futuristic graphics, premium fabrics, crafted for global trendsetters.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="25.5" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CALVIN KLEIN</t>
+          <t>CDG  Play</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>calvin-klein</t>
+          <t>cdg</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CALVIN KLEIN: 探索 Calvin Klein 的时尚世界，享受高端内衣、香水、牛仔和配饰系列。购买经典 Calvin Klein 内衣和现代服装，体验奢华品质与简约设计。立即选购 Calvin Klein 产品，享受全球配送和专属优惠。</t>
+          <t>CDG Play: 日本时尚品牌Comme des Garçons（川久保玲）旗下经典潮流副线，1999年推出，以标志性“爱心眼睛”logo为核心识别，融合简约街头与高端设计风格，产品涵盖T恤、卫衣、包包、鞋履等潮流单品，是全球追求潮流辨识度与品牌文化的年轻人喜爱的热门潮流品牌。</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CALVIN KLEIN: Discover luxury essentials - premium underwear, fragrance, denim &amp; accessories. Experience minimalist design &amp; quality. Shop now with global shipping.</t>
+          <t>CDG Play: Iconic "heart eyes" logo streetwear line by Comme des Garçons, launched 1999. Blends minimalist street with high-end design in T-shirts, hoodies, bags, shoes. Global youth favorite.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="25.5" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CANADA GOOSE</t>
+          <t>Celine</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>canada-goose</t>
+          <t>celine</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CANADA GOOSE: 加拿大高端户外服饰品牌，专为极地探险设计。自1957年创立以来，Canada Goose以其卓越的保暖技术、精湛工艺与严苛材质标准闻名，产品涵盖派克大衣、羽绒夹克及配饰，融合功能性与都市风格，为全球探险家及都市精英提供抵御严寒的终极装备。</t>
+          <t>Celine: 1945年由Céline Vipiana创立于法国巴黎的高端奢侈品牌，以简约优雅的法式风格为核心，主打高级时装、手袋、皮具、鞋履及配饰，标志性元素包括凯旋门扣（Triomphe Hardware）、经典Box Bag手袋与Triomphe帆布系列，融合实用主义与精湛工艺，长期为追求经典质感与永恒时尚的全球高端消费者提供兼具设计感与耐用性的奢侈品，是法式高级时尚的代表品牌之一。</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CANADA GOOSE: Luxury outerwear since 1957, designed for extreme cold. Expertly crafted parkas, jackets &amp; accessories fusing Arctic exploration technology with metropolitan style.</t>
+          <t>Celine: Founded in Paris, France in 1945 by Céline Vipiana, a high-end luxury brand with minimalist elegant French style, specializing in haute couture, handbags, leather goods, footwear &amp; accessories. Signature elements: Triomphe Hardware, classic Box Bag, Triomphe Canvas series. Blending utilitarianism &amp; exquisite craftsmanship, it caters to global high-end consumers pursuing classic texture &amp; timeless fashion, offering durable, design-driven luxury— a French high fashion representative.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="25.5" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CARHARTT</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>carhartt</t>
+          <t>celtic</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CARHARTT: Carhartt 是源自美国的百年工装品牌，以其耐用、功能性和经典设计闻名。品牌提供高品质的工作服、外套、裤装及配饰，采用坚固面料如帆布和 Duck Cotton 制成，专为劳动者、户外爱好者和追求实用风格的人群打造。Carhartt 产品结合卓越工艺与实用美学，在全球范围内赢得信赖，成为坚固耐用的代名词。</t>
+          <t>Celtic（凯尔特人足球俱乐部）1887 年由 Brother Walfrid 创立于苏格兰格拉斯哥。主营球衣、训练服及球迷周边，与阿迪达斯合作，主色调绿白，采用透气速干聚酯面料，融入凯尔特十字经典元素，风格经典复古，风靡英国及全球，是苏超顶级传统豪门。</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Carhartt: Durable workwear brand since 1889. Known for functional jackets, pants &amp; accessories made with rugged Duck Cotton canvas. Built for workers &amp; outdoor enthusiasts.</t>
+          <t>Celtic FC: Founded 1887 in Glasgow by Brother Walfrid. Adidas jerseys, training gear, fan merch in green/white. Breathable quick-dry polyester with Celtic cross. Classic retro style, UK &amp; global favorite, top SPL traditional.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="25.5" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CAROLINA HERRERA</t>
+          <t>Chanel</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>carolina-herrera</t>
+          <t>chanel</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CAROLINA HERRERA:  
-由Carolina Herrera于1981年创立，纽约奢华时尚品牌，以优雅礼服、高级成衣及标志性香水闻名。经典产品包括Good Girl高跟鞋和CH Carolina Herrera系列，选用精致面料与创新工艺，融合现代摩登与经典风格，展现永恒魅力与奢华气质。</t>
+          <t>Chanel: 1910年由可可·香奈儿（Coco Chanel）创立于法国巴黎，全球顶级奢侈品牌，以“简约优雅”的设计哲学重塑女性时尚边界。核心品类覆盖高级定制时装、经典皮具（如Classic Flap菱格纹手袋）、传奇香水（No.5香氛）、美妆及腕表珠宝，标志性元素包括双C logo、粗花呢面料、小黑裙与山茶花。品牌坚持精湛手工工艺，融合经典与现代美学，传递独立自信的女性精神，是跨越百年的时尚传奇象征。</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CAROLINA HERRERA: NYC luxury fashion house since 1981. Elegant gowns, ready-to-wear &amp; iconic fragrances. Good Girl heels &amp; CH Carolina Herrera line. Modern luxury with timeless appeal.</t>
+          <t>Chanel: Founded in 1910 Paris by Coco Chanel, a timeless luxury brand synonymous with simple elegance. Iconic for tweed, little black dress, camellia, and legendary No.5 perfume. Embodies confident femininity.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="25.5" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CASABLANCA</t>
+          <t>Cheng KeLun</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>casablanca</t>
+          <t>chengKeLun</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Casablanca: 探索Casablanca品牌的精致家居与时尚配饰。品牌以摩洛哥风情为灵感，融合现代设计，为您带来独特的装饰与生活方式产品。从优雅的家居摆件到时尚的日常用品，Casablanca致力于提升生活品质，展现异域文化与现代美学的完美结合。选购Casablanca，开启您的灵感之旅，打造充满艺术气息的个性空间。品牌注重细节与工艺，每一件产品都讲述着Casablanca的传奇故事。</t>
+          <t>Cheng KeLun（程可伦）专注男士抗菌内裤，采用 3A 级抗菌纯棉面料，透气亲肤。设计简约舒适，主打银罐装平角裤，贴合人体工学，无束缚感。风格简约百搭，适合日常穿着，畅销中国及东南亚地区，深受注重品质生活男士喜爱</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CASABLANCA: Moroccan-inspired modern home decor &amp; fashion accessories. Elevate lifestyle with unique, artful products blending exotic culture and contemporary aesthetics.</t>
+          <t>Cheng KeLun: Men's antibacterial underwear with 3A antibacterial cotton, breathable &amp; skin-friendly. Sleek, comfortable, ergonomic silver can-packaged boxer briefs, unrestrictive. Minimalist, versatile for daily wear, popular in China &amp; Southeast Asia, loved by quality-focused men.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="25.5" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cartier</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>cartier</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cartier卡地亚于1847年由路易·弗朗索瓦·卡地亚（Louis-François Cartier）在法国巴黎创立，是全球顶级奢侈品牌。品牌以18K黄金、铂金、钻石、宝石及优质皮革为核心材质，标志性系列包括Santos山度士系列、Tank坦克系列、Ballon Bleu蓝气球系列及Panthère猎豹系列，融合法式优雅与精湛匠艺。由路易·卡地亚、贞·杜桑（Jeanne Toussaint，“猎豹女士”）等设计师主导，主营珠宝、腕表、皮具及香水，传承百年法式奢华底蕴。</t>
+          <t>Chelsea 1905 年由 Gus Mears 创立于伦敦，主营球衣、训练服及球迷周边，与耐克合作，主色调蓝白。采用透气速干聚酯纤维，融入狮子队徽元素，风格经典时尚，风靡全球，是英超豪门，以华丽打法与冠军底蕴闻名。</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Founded in 1847 in Paris, France by Louis-François Cartier, Cartier is a top luxury brand. Using 18K gold, platinum, diamonds &amp; premium leather, its iconic series include Santos, Tank, Ballon Bleu &amp; Panthère, blending French elegance with exquisite craftsmanship, led by designers like Louis Cartier and Jeanne Toussaint. It offers jewelry, watches, leather goods &amp; perfumes.</t>
+          <t>Chelsea 1905: Founded by Gus Mears in London, specializes in jerseys, training kits &amp; fan merchandise. Nike partner, blue-white, breathable quick dry polyester, lion crest, classic-stylish. Premier League giant with glam play &amp; championship heritage, global hit.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="25.5" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CAV EMPT</t>
+          <t>Chicago Bears</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>cav-empt</t>
+          <t>chicago-bears</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CAV EMPT: 2012年由Sk8thing和Toby Feltwell创立的日本街头服饰品牌，融合未来主义与复古美学，产品系列包括印花夹克、图形T恤和功能性裤装，经典设计采用高科技面料和数字印花工艺，风格前卫解构，代表单品为反光镶条夹克和不对称剪裁卫衣。</t>
+          <t>Chicago Bears: 美国国家橄榄球联盟（NFL）历史最悠久的球队之一，1919年以“Decatur Staleys”为名创立，1922年更名为Chicago Bears（芝加哥熊队），主场为芝加哥 Soldier Field。队史收获多次分区冠军及1985年超级碗冠军，以标志性熊头LOGO、坚韧铁血的球风与深厚的美式橄榄球传统著称，拥有全球海量忠实球迷，是NFL文化与经典球队的代表符号。</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CAV EMPT: Japanese streetwear brand by Sk8thing &amp; Toby Feltwell. Fusion futurism &amp; retro aesthetics with tech fabrics, digital prints, deconstructed styles.</t>
+          <t>Chicago Bears: One of NFL’s oldest teams, founded 1919 as Decatur Staleys, renamed 1922. Home at Chicago’s Soldier Field, multiple division titles, 1985 Super Bowl champion. Iconic bear head logo, tough gritty style, rich football tradition, loyal global fans—NFL culture classic symbol.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="25.5" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CDG  Play</t>
+          <t>Chiclara</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>cdg</t>
+          <t>chiclara</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CDG: 探索CDG品牌的创新设计与前卫时尚，CDG提供独特服饰与配饰，融合日本街头文化与高端时装元素。品牌以标志性红心图案和不对称剪裁闻名，为追求个性表达的全球消费者打造颠覆传统的潮流单品。</t>
+          <t>Chiclara（奇克拉拉）2023 年创立于香港，专注亚洲时尚美学，与亚洲新兴设计师合作，主营男女成衣与配饰，融合东方传统与现代设计，采用棉麻、环保聚酯纤维等材质，风格简约大气又不失文化韵味，畅销欧美及亚太地区，是亚洲时尚全球化的代表性品牌。</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CDG Play: CDG offers innovative avant-garde fashion, merging Japanese street culture with high-end elements. Known for iconic red heart and asymmetric cuts.</t>
+          <t>Chiclara: Founded in Hong Kong in 2023, focuses on Asian fashion aesthetics, collaborates with emerging Asian designers, specializes in men’s &amp; women’s ready-to-wear &amp; accessories. Blends Eastern traditions with modern design, uses cotton, linen &amp; eco-friendly polyester. Minimalist yet culturally rich, popular in Europe, America &amp; Asia-Pacific—representative of Asian fashion globalization.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="25.5" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CELINE</t>
+          <t>Chrome Hearts</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>celine</t>
+          <t>chrome-hearts</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CELINE: 探索法国奢侈品牌CELINE的精致手袋、皮具、成衣及配饰系列。CELINE专注于极简主义设计与现代奢华风格，提供永恒经典的时尚单品。品牌融合巴黎美学与精湛工艺，为追求高端生活方式的消费者打造优雅而实用的产品。通过官方渠道购买正品，享受全球配送服务。</t>
+          <t>Chrome Hearts: 1988年由Richard Stark创立于美国的高端奢侈品牌，以哥特摇滚风格的手工银饰、皮革制品及服饰为核心，标志性元素包括十字架、骷髅与铆钉，坚持全手工制作打造独特质感，深受全球明星与潮流爱好者追捧，亦推出与Bape、Supreme等品牌的联名系列，诠释叛逆奢华与工艺美学的融合。</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CELINE: French luxury brand offering minimalist handbags, leather goods, ready-to-wear &amp; accessories. Timeless elegance, Parisian aesthetic &amp; craftsmanship. Official global shipping.</t>
+          <t>Chrome Hearts: Luxury brand since 1988 USA. Gothic rock handcrafted silver, leather, apparel. Iconic crosses, skulls, studs. Handmade, celeb loved. Bape, Supreme collabs. Rebellious luxury craft.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="25.5" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CELTIC</t>
+          <t>Cincinnati Bengals</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>celtic</t>
+          <t>cincinnati-bengals</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CELTIC: 凯尔特品牌专注于高品质跨境商品，结合传统工艺与现代设计，为全球消费者提供独特而可靠的产品体验。品牌严格把控生产与供应链，确保每件商品均符合国际标准，致力于通过电商平台将优质产品高效送达用户手中，满足多样化的生活需求。</t>
+          <t>Cincinnati Bengals: 美国国家橄榄球联盟（NFL）美联北区职业橄榄球队，1968年成立，主场为俄亥俄州辛辛那提的Paycor Stadium。队服以标志性橙色与黑色为主， mascot是"Who Dey" Bengal tiger形象。队史曾多次闯入季后赛，2022、2024年两度晋级超级碗；阵中拥有乔·伯罗（Joe Burrow）、贾马尔·蔡斯（Ja'Marr Chase）等明星球员，以进攻端的强劲火力著称，是NFL中极具关注度与球迷基础的球队之一。</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CELTICCELTIC: Premium cross-border goods, blending traditional craftsmanship with modern design for unique, reliable products. Rigorous quality control ensures international standards, delivering diverse lifestyle needs via e-commerce.</t>
+          <t>Cincinnati Bengals: NFL AFC North team since 1968 at Paycor Stadium. Iconic orange &amp; black, "Who Dey" tiger mascot. Super Bowl appearances 2022 &amp; 2024. Featuring Joe Burrow, Ja'Marr Chase. Known for offensive firepower and loyal fans.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="25.5" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CHANEL</t>
+          <t>Clinique</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>chanel</t>
+          <t>clinique</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CHANEL: 香奈儿是法国奢侈品牌, 以其经典优雅的时装、高级定制服、香水、化妆品和配饰而闻名。 品牌由可可·香奈儿于1910年创立, 以其永恒的设计、精湛的工艺和标志性产品（如香奈儿5号香水和经典绗缝手袋）而备受推崇。 香奈儿代表着奢华、精致和经久不衰的风格。</t>
+          <t>Clinique: 1968年由美国皮肤科医生创立的专业护肤彩妆品牌，以“无香料、无酒精、敏感肌友好”为核心研发理念，经典“倩碧三步曲”（温和洁面皂+明肌净透水+特效润肤露“黄油”）成为全球基础护肤标杆，更有匀净粉底液、小方唇釉等养肤彩妆产品，专注通过dermatologist-tested（皮肤科医生测试）的安全配方，解决不同肤质的基础护理与妆容需求，是全球敏感肌及护肤新手的信任之选。</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CHANEL: French luxury brand renowned for timeless elegance, haute couture, iconic perfumes like Chanel No. 5, and exquisite quilting handbags.</t>
+          <t>Clinique: 1968 dermatologist-founded skincare/makeup brand. Fragrance-free, alcohol-free, sensitive-skin friendly. Classic 3-Step System &amp; dermatologist-tested formulas for all skin types and beginners.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="25.5" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ChengKeLun</t>
+          <t>Cole Buxton</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>chengKeLun</t>
+          <t>cole-buxton</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>好的，遵照您的严格要求，我将为每个品牌生成符合规则的SEO友好描述。
-**ChengKeLun:** 成克伦品牌专注高品质家居用品与生活配件，致力于为全球消费者提供设计精良、耐用且实用的日常产品，提升您的居家生活体验。</t>
+          <t>Cole Buxton: 源自英国的街头服饰品牌，以极简美学融合复古运动功能性与街头文化内核著称，主打高品质纯棉、抓绒等面料打造的连帽衫、运动裤、基础T恤等经典单品，兼顾舒适穿着与潮流表达，是追求质感与个性的年轻群体首选的街头运动风品牌。</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ChengKeLun: Innovative cross-border e-commerce brand offering trendy, high-quality products with global shipping and secure payment options.</t>
+          <t>Cole Buxton: UK-based streetwear brand blending minimalist aesthetics with retro sport functionality &amp; street culture core. Offers high-quality cotton/fleece hoodies, sweatpants, basic tees—balances comfort &amp; trendy expression. Top pick for youths seeking quality, individuality in street sports style.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="25.5" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CHELSEA</t>
+          <t>Comme Des Garcons</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>chelsea</t>
-        </is>
-      </c>
-      <c r="C69"/>
-      <c r="D69"/>
+          <t>comme-des-garcons</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Comme Des Garcons: 1969年由川久保玲（Rei Kawakubo）在东京创立的日本先锋时装品牌，以“反时尚”（Anti-Fashion）核心理念打破传统边界，擅长解构主义设计，标志性元素包括不对称剪裁、不规则轮廓、黑白灰主色调及拼接工艺，产品覆盖男女装、配饰、香水（如经典Comme Des Garcons Parfums系列）及跨界联名（与Nike、Converse等品牌合作），将艺术与服饰深度融合，是全球潮流文化中极具辨识度的个性时尚符号。</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Comme Des Garcons: Avant-garde Japanese fashion by Rei Kawakubo, since 1969. Anti-Fashion, deconstruction, asymmetric cuts, patchwork, monochrome, apparel, accessories, perfumes, collaborations.</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="25.5" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CHICAGO BEARS</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>chicago-bears</t>
+          <t>converse</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CHICAGO BEARS: 成立于1920年的美国职业橄榄球队，由A.E. Staley创立，代表经典橙色和深蓝色队服，以坚韧防守和传奇球员闻名，风格硬朗传统，是NFL历史最悠久的球队之一。</t>
+          <t>Converse（匡威）1908 年由 Marquis Mills Converse 创立于美国，百年经典鞋服品牌。主打 Chuck Taylor All Star 帆布鞋，采用帆布鞋面与橡胶鞋底，兼顾复古休闲与街头风格，覆盖鞋款、服饰等。设计简约百搭，风靡全球，是潮流与日常穿搭的标志性品牌。</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CHICAGO BEARS: NFL team est. 1920, iconic orange &amp; navy uniforms, renowned for tough defense, legendary players, and hard-nosed traditional style.</t>
+          <t>Converse: Founded in the US by Marquis Mills Converse in 1908, a century-old iconic footwear &amp; apparel brand. Core product: Chuck Taylor All Star canvas shoes with canvas uppers &amp; rubber soles, blending retro casualness with street style, covering shoes &amp; apparel. Minimalist &amp; versatile design, popular worldwide, a signature brand for trendy daily outfits.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="25.5" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CHICLARA</t>
+          <t>Corteiz</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>chiclara</t>
-        </is>
-      </c>
-      <c r="C71"/>
-      <c r="D71"/>
+          <t>corteiz</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Corteiz: 英国街头潮流先锋品牌，由Clint419创立，聚焦青年文化与街头精神，以标志性“COR”标识、Bold标语及工业风设计为核心辨识度，产品覆盖卫衣、T恤、帽饰等街头单品，常与Nike、Polaroid等品牌推出联名系列，传递“社群共鸣”的品牌理念，是全球街头潮流爱好者的热门选择。</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Corteiz: UK streetwear pioneer by Clint419, focuses on youth culture &amp; street spirit with iconic COR logo, bold slogans, industrial design. Offers hoodies, tees, caps. Collaborates with Nike, Polaroid. Promotes 'community resonance', top global choice.</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="25.5" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CHROME HEARTS</t>
+          <t>Cp Company</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>chrome-hearts</t>
+          <t>cp-company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CHROME HEARTS: 探索 Chrome Hearts 的奢华银饰与手工皮具，感受哥特风格与摇滚精神的完美融合。品牌提供高端时尚配饰，包括戒指、项链和手镯，每一件作品均以精湛工艺和独特设计展现叛逆奢华。购买 Chrome Hearts 的限量版商品，体验美国奢侈品牌的永恒魅力。</t>
+          <t>Cp Company: 1971年由Massimo Osti创立的意大利高端机能服饰品牌，以先锋功能性面料、军事风格元素与实用设计著称，经典Goggle Jacket护目镜夹克为标志性单品，融合都市美学与户外性能，注重细节工艺，是机能时尚领域的代表性品牌。</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CHROME HEARTS: Luxury silver jewelry &amp; handcrafted leather goods. Gothic rock style with rebellious elegance. Rings, necklaces, bracelets &amp; limited editions.</t>
+          <t>Cp Company: Italian high-end techwear brand since 1971 by Massimo Osti. Known for functional fabrics, military style, iconic Goggle Jacket. Blends urban aesthetics with outdoor performance, craftsmanship-focused.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="25.5" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CINCINNATI BENGALS</t>
+          <t>Creed</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>cincinnati-bengals</t>
+          <t>creed</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CINCINNATI BENGALS: 美国职业橄榄球队，成立于1968年，以独特的橙黑条纹配色和猛虎形象闻名，代表产品包括球衣、帽子和周边商品，采用高性能透气材质，工艺精湛，风格运动激情。</t>
+          <t>Creed（恺芮得）1760 年由 James Henry Creed 创立于伦敦，家族 7 代传承的皇室御用奢华香氛品牌。主营高端香水，如 Aventus、Silver Mountain Water 等，由 Olivier Creed 等家族制香大师调配。采用保加利亚玫瑰、佛罗伦萨茉莉等天然原料，坚持手工制香工艺，风格典雅奢华，风靡全球，以皇室底蕴与卓越品质著称。</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CINCINNATI BENGALS: NFL team since 1968, known for iconic orange and black stripes, high-performance breathable jerseys, hats, and sportswear.</t>
+          <t>Creed: Since 1760 London, royal luxury perfumes by Creed family. Aventus, Silver Mountain Water with natural ingredients, handcrafted, elegant, globally renowned.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="25.5" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CLINIQUE</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>clinique</t>
+          <t>crocs</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CLINIQUE: 1968年由Carol Phillips创立的美国高端护肤品牌，以皮肤学专家配方和过敏测试闻名。产品系列涵盖护肤、彩妆及男士护理，经典产品包括倩碧黄油和匀净卓研修护精华。采用高效活性成分，工艺科学严谨，功能针对性修护，风格简约专业。</t>
+          <t>Crocs: 1999年诞生于美国科罗拉多州的全球休闲鞋领导品牌，以标志性洞洞鞋（Clog）和专利Croslite™轻质缓冲材质为核心，产品兼具透气、防滑、易清洁等特性，覆盖全年龄段日常出行、户外休闲等多元场景，主打“舒适无束缚”的生活理念，成为全球消费者心中“自在休闲”的鞋履代表。</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CLINIQUE: Dermatologist-developed, allergy-tested since 1968. Features Clinique Moisturizer &amp; Even Better Clinical Serum. Targeted repair with high-efficacy actives. Minimalist, professional skincare &amp; makeup.</t>
+          <t>Crocs: 1999-born Colorado global casual footwear leader. Iconic clogs with Croslite™ cushioning. Breathable, slip-resistant, easy-to-clean. For all ages, daily &amp; outdoor. Comfortable, unrestrictive lifestyle.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="25.5" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>COLE BUXTON</t>
+          <t>Cactus Jack</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>cole-buxton</t>
+          <t>mastermind-japan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>COLE BUXTON:  
-探索COLE BUXTON的前卫都市时尚系列，融合极简设计与高性能面料。品牌以中性色调和功能性剪裁重新定义现代街头服饰，为追求质感与低调风格的消费者提供日常奢华体验。精选卫衣、运动裤和外衣单品，兼顾舒适性与精致细节，展现超越季节的永恒美学。</t>
+          <t>Cactus Jack: 由美国说唱歌手Travis Scott创立的街头潮流品牌，以沙漠野性与工业街头风为核心设计语言，主打潮流服饰、联名鞋款及配件，因与Nike、Jordan Brand合作推出Air Jordan 1 Travis Scott等爆款鞋品走红，是全球潮流爱好者追捧的街头文化标杆品牌。</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>COLE BUXTON: Redefines modern streetwear with minimalist designs, high-performance fabrics, and functional cuts in neutral tones for understated luxury.</t>
+          <t>Cactus Jack: Streetwear brand founded by US rapper Travis Scott, blending desert wildness &amp; industrial street style. Specializes in apparel, collab sneakers &amp; accessories. Gained fame via Nike/Jordan Brand’s Air Jordan 1 Travis Scott, a global street culture icon for enthusiasts.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="25.5" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>COMME DES GARCONS PLAY</t>
+          <t>Dallas Cowboys</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>comme-des-garcons-play</t>
+          <t>dallas-cowboys</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>COMME DES GARCONS PLAY: 川久保玲于1973年创立的日本时尚品牌，以其标志性的爱心眼睛图案闻名，产品涵盖T恤、针织衫和配饰，采用棉质和针织材质，工艺精致，风格 playful 且 avant-garde。</t>
+          <t>Dallas Cowboys: 1960年成立的美国NFL职业橄榄球队，隶属国家橄榄球联合会（NFC）东部分区，曾5次夺得超级碗冠军，获称“美国之队”（America's Team）。球队以标志性牛仔星队徽、经典蓝银配色队服为识别，主场为达拉斯AT&amp;T体育场（AT&amp;T Stadium），是NFL历史上最具影响力、商业价值及全球球迷基础的球队之一，传承美式橄榄球的热血与文化符号。</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>COMME DES GARCONS PLAY: Rei Kawakubo's iconic Japanese fashion label since 1973, famous for playful heart-eye designs in tees, knits &amp; accessories. Avant-garde cotton &amp; knitwear.</t>
+          <t>Dallas Cowboys: NFL team est. 1960, NFC East. 5x Super Bowl champs, America's Team. Iconic star logo, blue-silver uniforms, AT&amp;T Stadium home. Influential, valuable, global football icon.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="25.5" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Denver Broncos</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>converse</t>
+          <t>denver-broncos</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Converse 匡威 1908 年诞生于美国马萨诸塞州莫尔登，由 Marquis Mills Converse 创立。核心主线为 Chuck Taylor All Star、Jack Purcell，主打帆布 + 橡胶材质，经典美式复古街头风格，面向全球年轻潮流群体，由品牌经典设计团队打造，是百年休闲鞋履标杆。</t>
+          <t>Denver Broncos: 美国国家橄榄球联盟（NFL）经典球队，1960年作为AFL创始成员成立，1970年加入NFL，主场位于丹佛的Empower Field at Mile High。队史3次夺得超级碗冠军（1997、1998、2015年），以标志性橙蓝配色队服、野性野马队标闻名，拥有庞大忠实球迷群体“Broncos Country”。球队延续坚韧拼搏的橄榄球精神，是NFL历史上极具影响力的老牌劲旅。</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Founded in 1908 in Malden, Massachusetts, USA by Marquis Mills Converse, Converse is a century-old footwear icon. Core lines: Chuck Taylor All Star &amp; Jack Purcell. Crafted with canvas &amp; rubber, it features retro street style, popular worldwide among young trendsetters, designed by its classic in-house team.</t>
+          <t>Denver Broncos: Legendary NFL team, 3x Super Bowl champions (1997, 1998, 2015). Iconic orange &amp; blue colors, wild horse logo. Heart of loyal "Broncos Country" fans. Founded 1960.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="25.5" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CORTEIZ</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>corteiz</t>
+          <t>deportivo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CORTEIZ: Corteiz 是源自英国的街头服饰品牌，以其标志性的阿尔卡特拉斯岛标志和叛逆精神闻名。品牌主打高品质的连帽衫、T恤和配饰，融合了都市文化与地下美学，深受全球年轻潮流爱好者追捧。CORTEIZ 通过限量发售和独特的营销策略，成功塑造了稀缺性和社群归属感，成为现代街头时尚的代表性力量之一。</t>
+          <t>Deportivo（拉科鲁尼亚体育俱乐部）1906 年 3 月 2 日由西班牙体育爱好者创立于拉科鲁尼亚，主营球衣、训练服及球迷周边，与 Macron 等品牌合作设计，主色调蓝白条纹。采用透气速干聚酯纤维材质，风格经典运动，融入球队 "蓝白军团" 元素，风靡西班牙及全球球迷圈，以西甲冠军底蕴与忠诚球迷文化著称。</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CORTEIZ: UK streetwear brand known for Alcatraz logo &amp; rebellious style. Premium hoodies, tees &amp; accessories blending urban culture &amp; underground aesthetics. Limited drops &amp; exclusive hype.</t>
+          <t>Deportivo(Deportivo de La Coruña): Founded by Spanish sports enthusiasts in La Coruña on Mar 2, 1906, offering jerseys, training kits &amp; fan merch. Collaborates with Macron, blue-white stripes, breathable quick-dry polyester, classic sporty style with "Blue and White Army" elements. Popular globally, known for La Liga champion heritage &amp; loyal fan culture.</t>
         </is>
       </c>
     </row>
     <row r="79" ht="25.5" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CP COMPANY</t>
+          <t>Destroy Lonely</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>cp-company</t>
+          <t>destroy-lonely</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CP COMPANY: CP Company是意大利高端机能服饰品牌，以创新面料技术和实用主义设计闻名。品牌标志性的玻璃棉材质、多功能口袋系统和可转换细节设计，彰显其工业美学与功能性融合的核心哲学。CP Company的夹克、外套和配饰系列深受潮流先锋和户外爱好者推崇，其标志性染色工艺和复古未来主义风格持续引领当代男装潮流。探索CP Company官方系列，体验融合意大利精工与军事美学的颠覆性设计。</t>
+          <t>Destroy Lonely: 美国新生代说唱歌手，以melodic trap风格见长，代表作《NOSTYLIST》《VETERAN》凭借独特flow、氛围感编曲及孤独主题歌词出圈，流媒体播放量破千万，是当下嘻哈场景中极具辨识度的艺人，其音乐融合 trap 节奏与旋律性，传递年轻一代的自我表达与情绪共鸣。</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CP COMPANY: Italian high-end functional apparel brand, innovating fabric tech with utilitarian design. Iconic glass cotton, multi-pocket systems, and convertible details fuse industrial aesthetics with functionality.</t>
+          <t>Destroy Lonely: U.S. rising rapper specializing in melodic trap, with hits "NOSTYLIST" &amp; "VETERAN". Known for unique flow, atmospheric production, lonely-themed lyrics, millions of streams. Distinctive in hip-hop, blending trap rhythm &amp; melody to convey Gen Z's self-expression &amp; emotional resonance.</t>
         </is>
       </c>
     </row>
     <row r="80" ht="25.5" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CREED</t>
+          <t>Descente</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>creed</t>
-        </is>
-      </c>
-      <c r="C80"/>
-      <c r="D80"/>
+          <t>descente</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Descente（迪桑特）1935 年由石本他家男创立于日本大阪，1961 年注册商标，名称源自法语 "滑降"。主打专业滑雪服与高端运动服饰，由滑雪名将西村一良担任顾问，采用 GORE‑TEX、COOLMAX 等科技面料，融合专业功能性与简约美学，风靡全球，是瑞士、加拿大等多国滑雪队官方赞助商。</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Descente: French for descent, founded 1935 Osaka, trademarked 1961. Expert pro ski wear &amp; sportswear with GORE-TEX, COOLMAX. Advised by ski champ Nishimura. Blends function &amp; minimalist aesthetics. Global sponsor for Swiss, Canadian ski teams.</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="25.5" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Diadora</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>crocs</t>
+          <t>diadora</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Crocs: 探索Crocs洞洞鞋的舒适与时尚，全球热销的休闲鞋履品牌。Crocs以轻便、防滑、透气著称，提供多种款式包括经典克骆格、凉鞋及工作鞋，适合日常穿着、户外活动及专业场合。购买正品Crocs，享受独特缓震科技与个性化鞋饰搭配，打造轻松活力的生活方式。</t>
+          <t>Diadora: 1948年创立于意大利的专业运动品牌，由Marcello Danieli创办，以意式精湛工艺与运动基因著称，核心产品涵盖经典运动鞋（如Mirage、N9000系列）、专业运动服饰及配件，深耕足球领域（曾赞助尤文图斯、AC米兰等顶级球队），融合复古设计与现代科技，采用优质皮革、透气网布等功能性材质，满足运动爱好者专业性能需求与潮流人士复古审美，是意大利运动文化与时尚风格结合的代表品牌。</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Crocs: Globally loved for comfort &amp; style. Lightweight, slip-resistant, breathable clog, sandals &amp; work shoes. Perfect for daily wear, outdoors &amp; work. Authentic Crocs with cushion tech &amp; Jibbitz™ charms for a轻松active lifestyle.</t>
+          <t>Diadora: Founded in 1948 Italy by Marcello Danieli, Italian craftsmanship &amp; sport heritage brand. Core products: classic sneakers (Mirage, N9000), sportswear/accessories. Deep in football (sponsored Juventus, AC Milan). Merges retro design + modern tech, premium leather/breathable mesh for pro performance &amp; retro style. Italian sport-culture fashion icon.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="25.5" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cactus Jack</t>
+          <t>Dior</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>mastermind-japan</t>
-        </is>
-      </c>
-      <c r="C82"/>
-      <c r="D82"/>
+          <t>dior</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Dior: 1946年由克里斯汀·迪奥（Christian Dior）在巴黎创立，全球法式奢华与优雅的标志性品牌，业务涵盖高级定制时装、成衣、手袋、鞋履、美妆及香水。1947年以“New Look”廓形（沙漏腰线+大裙摆）重塑时尚审美，经典产品包括藤格纹设计的Lady Dior手袋、传奇999红唇口红（哑光/滋润双质地）、J'adore真我花香调香水，凭借精湛工艺、艺术灵感与永恒风格，成为高级时尚与美妆领域的标杆，诠释着法式生活艺术的精髓。</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Dior: Founded by Christian Dior in Paris in 1946, iconic global French luxury brand covering haute couture, ready-to-wear, handbags, footwear, beauty &amp; perfume. 1947 “New Look” (hourglass waist + full skirt) redefined fashion. Classics: Cannage-patterned Lady Dior, Rouge Dior 999 (matte/satin), J’adore perfume. Exquisite craftsmanship &amp; timeless style make it a luxury fashion/beauty benchmark, embodying French art de vivre.</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="25.5" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DALLAS COWBOYS</t>
+          <t>Divide The YouthI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>dallas-cowboys</t>
+          <t>divide-the -youthI</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>DALLAS COWBOYS: 美国职业橄榄球队达拉斯牛仔成立于1960年，以蓝色和银色为主色调，经典产品包括队服、球帽和周边商品，采用高性能面料和精湛工艺，风格经典运动，代表美国橄榄球文化与精神。</t>
+          <t>Divide The Youth（青年分界）2021 年由 Tuinenburg 创立于美国加州，是网红街头服饰品牌。主营连帽衫、T 恤、外套及配饰，采用纯棉、棉混纺与抓绒材质，设计师团队打造标志性文字图案与刺绣细节，风格叛逆前卫、中性百搭，融合 Y2K 与日系原宿风，风靡全球 TikTok/Instagram 时尚圈，受 Z 世代追捧。</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Dallas Cowboys: NFL team est. 1960, blue &amp; silver, official jerseys, hats &amp; merchandise with high-performance fabrics &amp; classic sport style.</t>
+          <t>Divide The Youth: Founded by Tuinenburg in California, USA (2021), popular streetwear brand specializing in hoodies, tees, jackets &amp; accessories (cotton, blends, fleece). Signature text graphics/embroidery, rebellious avant-garde unisex style blending Y2K &amp; Japanese Harajuku, viral on global TikTok/Instagram, favored by Gen Z.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="25.5" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DENVER BRONCOS</t>
+          <t>Dolce</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>denver-broncos</t>
+          <t>dolce</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DENVER BRONCOS: 成立于1960年的美国职业橄榄球队，以橙色和深蓝色为标志色，经典队服采用高性能面料，工艺精湛，功能透气耐用，风格运动竞技，代表商品为Elite系列球衣和球迷帽。</t>
+          <t>Dolce: 
+（注：因未获取到Dolce品牌对应的中文描述内容，无法按要求生成符合SEO优化的品牌描述。）</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>DENVER BRONCOS: NFL team since 1960, iconic orange &amp; navy blue Elite jerseys and caps with high-performance, breathable, durable athletic design.</t>
+          <t>Dolce: Note: Failed to obtain the Chinese description corresponding to the Dolce brand, unable to generate a SEO-optimized brand description as required.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="25.5" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DEPORTIVO</t>
+          <t>Dyson</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>deportivo</t>
+          <t>dyson</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DEPORTIVO: 1980年创立的西班牙运动时尚品牌，以足球文化为灵感，产品涵盖运动服饰、休闲鞋履及配件，经典设计融合舒适面料与复古运动美学，主打高性价比团队装备与日常休闲系列，展现地中海热情活力风格。</t>
+          <t>Dyson: 1991年由詹姆斯·戴森（James Dyson）创立的英国创新科技品牌，以原创气旋技术（Cyclone Technology）颠覆传统清洁逻辑，核心产品线涵盖无绳吸尘器（如V15 Detect）、Supersonic吹风机、Airwrap美发造型器、Pure Hot+Cool空气净化器及Air Multiplier无叶风扇等。产品采用高强度ABS工程塑料与金属质感组件，融合简约现代设计与高效能科技，主打“无袋吸尘更洁净”“快速干发不伤发”“智能控温美发”“全域空气净化”等优势，是全球家电与个人护理领域以技术创新为标签的领先品牌。</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>DEPORTIVO DEPORTIVO: Founded 1980, Spanish sportswear brand inspired by football culture. Offers athletic apparel, casual footwear &amp; accessories. Blends comfort, retro aesthetics &amp; Mediterranean vibes for team gear &amp; leisure.</t>
+          <t>Dyson: British tech innovator since 1991. Cyclone Technology for bagless cleaning. Products: cordless vacuums, Supersonic dryers, Airwrap stylers, air purifiers. High-strength ABS &amp; metal. Leading in appliances &amp; personal care.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="25.5" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DESTROY LONELY</t>
+          <t>Dusk</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>destroy-lonely</t>
+          <t>dusk</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DESTROY LONELY: 新兴音乐艺术家，以独特风格和前卫设计著称，融合街头文化与高端时尚元素，创作出引人注目的音乐作品和视觉形象，吸引全球年轻受众关注。</t>
+          <t>Dusk 2000 年创立于澳大利亚，主营香薰蜡烛、家居香氛及简约服饰，采用天然大豆蜡、有机棉等环保材质，主打自然治愈简约风格，畅销澳洲、欧美及亚太地区，是全球热门轻奢生活方式品牌。</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>DESTROY LONELY: Emerging music artist fusing street culture with high fashion, known for avant-garde style and innovative music captivating global youth.</t>
+          <t>Dusk: Founded in Australia in 2000, specializes in scented candles, home fragrances &amp; minimalist apparel. Uses eco-friendly materials like natural soy wax &amp; organic cotton, with natural healing minimalist style. Sold in Australia, Europe, Americas &amp; Asia-Pacific, a globally popular luxury lifestyle brand.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="25.5" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Descente</t>
+          <t>Emporio Armani</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>descente</t>
+          <t>emporio-armani</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Descente（迪桑特）是 1935 年创立于日本大阪的高端专业运动品牌，品牌名源自法语 “滑降”，三箭头 LOGO 象征滑雪核心技术。品牌以滑雪为基因，覆盖滑雪、铁人三项、综训、高尔夫等领域，凭借专业运动科技与精准功能性剪裁，兼顾专业竞技性能与都市穿搭，打造高品质高端运动服饰装备。</t>
+          <t>Emporio Armani: 1981年由Giorgio Armani创立，意大利奢侈时尚品牌副线，专注于年轻潮流服装与配饰，产品系列包括男女装、眼镜、手表及香水，经典设计含标志性Logo和简约剪裁，采用高级面料与精湛工艺，风格现代优雅、时尚动感，适合日常穿着与特殊场合。</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Descente is a premium professional sportswear brand founded in Osaka, Japan in 1935. Derived from French “descent” with a three-arrow logo representing skiing techniques, it roots in skiing and covers skiing, triathlon, training and golf. With professional sports tech and functional tailoring, it balances performance and urban wear for high-quality sportswear.</t>
+          <t>Emporio Armani: Luxury fashion brand founded in 1981, offering modern, elegant apparel and accessories for youthful, dynamic styles. Features iconic logo and tailored designs.</t>
         </is>
       </c>
     </row>
     <row r="88" ht="25.5" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DIADORA</t>
+          <t>Enfants Riches Deprimes</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>diadora</t>
+          <t>enfants-riches-deprimes</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>DIADORA: 1948年创立于意大利的运动品牌，以专业足球鞋和复古运动鞋闻名，经典产品有Baggio Icon和S8000，采用优质皮革和环保材质，工艺精湛，功能舒适耐用，风格兼具运动性能与意式复古时尚。</t>
+          <t>Enfants Riches Deprimes: 源自法国的高端街头时尚品牌，以“颓废奢华”风格著称，融合街头叛逆精神与高级时装工艺，选用羊绒、丝绸等珍稀面料结合做旧、破洞、标语刺绣等标志性设计，主打卫衣、外套、针织品等系列，精准定位追求独特个性与暗黑高级感的潮流精英，是全球先锋时尚圈推崇的“反主流奢华”代表品牌。</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>DIADORA: Italian sportswear brand since 1948, renowned for professional football boots &amp; retro sneakers like Baggio Icon &amp; S8000. Crafted with premium leather, eco-friendly materials,精湛工艺 for comfort, durability,运动性能 &amp; Italian retro style.</t>
+          <t>Enfants Riches Déprimés: French luxury streetwear brand with depressed luxury style, merging street rebellion and high-fashion using cashmere, silk, distressed designs on hoodies, jackets for elite trendsetters, an anti-mainstream luxury icon.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="25.5" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DIOR</t>
+          <t>Essentials</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>dior</t>
+          <t>essentials</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>DIOR: 探索DIOR迪奥品牌的奢华时尚世界。DIOR迪奥提供高级时装、美妆产品及配饰，以其经典设计和法式优雅闻名。从标志性手袋到迷人香水，DIOR迪奥为全球消费者带来精致生活方式体验。立即选购DIOR迪奥正品，尽享品牌专属优惠与全球配送服务。</t>
+          <t>Essentials（Fear of God Essentials）2018 年由 Jerry Lorenzo 创立于美国洛杉矶，是 Fear of God 副线。主营卫衣、T 恤、卫裤等基础款，Jerry Lorenzo 主导设计，采用重磅纯棉、抓绒等优质面料，主打 oversized 剪裁、中性色调与极简徽标，风格高级休闲，风靡全球 Z 世代，是高街潮流代表品牌。</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>DIOR: Luxury fashion, beauty &amp; accessories. French elegance, iconic bags &amp; fragrances. Shop authentic DIOR online for exclusive offers &amp; global delivery.</t>
+          <t>ESSENTIALS: Launched in 2018 by Jerry Lorenzo in LA, this Fear of God line offers core styles like hoodies and sweatpants in heavyweight cotton and fleece, featuring oversized fits, neutral tones, and minimalist branding for elevated, global streetwear.</t>
         </is>
       </c>
     </row>
     <row r="90" ht="25.5" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DIVIDE THE YOUTH</t>
+          <t>Fear Of God</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>divide-the -youthI</t>
+          <t>fear-of-god</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DIVIDE THE YOUTH: Divide The Youth 是一家专注于年轻世代个性化表达与可持续时尚的先锋服饰品牌。我们以独特的设计语言、高品质的环保面料和前卫的剪裁，为不甘被定义的年轻人提供打破常规的日常穿着选择。品牌致力于通过服装鼓励自我探索与社群连接，重塑Z世代的潮流身份认同。</t>
+          <t>Fear-Of-God: 2013年由Jerry Lorenzo创立的美国高端街头服饰品牌，以“街头文化与高级时尚融合”为核心调性，主打oversize宽松剪裁、中性化设计语言，采用重磅棉、优质皮革等质感面料，经典单品涵盖Essentials基础系列、水洗牛仔夹克、高街连帽衫，曾与Nike等头部品牌推出联名系列，专注为追求潮流质感与独特风格的青年群体，打造兼具实用性与设计辨识度的高端街头服饰。</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>DIVIDE THE YOUTH: Pioneering sustainable fashion for Gen Z. Unconventional designs, eco fabrics, and avant-garde cuts for self-expression and community.</t>
+          <t>Fear Of God: Founded 2013 by Jerry Lorenzo, US high-end streetwear blending street culture &amp; luxury fashion. Oversize, gender-neutral designs (heavy cotton/premium leather). Classics: Essentials line, washed denim jackets, high-street hoodies. Nike collaborations. For youth seeking trendy texture &amp; unique style, practical recognizable streetwear.</t>
         </is>
       </c>
     </row>
     <row r="91" ht="25.5" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DOLCE</t>
+          <t>Fendi</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>dolce</t>
-        </is>
-      </c>
-      <c r="C91"/>
-      <c r="D91"/>
+          <t>fendi</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Fendi: 1925年由Adele Casagrande与Edoardo Fendi创立于意大利罗马，全球顶级奢侈品牌，以高级时装、皮具、配饰及香水等品类著称。品牌核心识别为标志性双F logo（FF图案）与传承近百年的精湛皮草工艺，经典产品涵盖Baguette法棍手袋、Peekaboo手袋及Fendi Roma Amor系列。作为“罗马奢华美学”的代表，Fendi融合意大利传统手工技艺与现代先锋设计，风格兼具奢华优雅与创意张力，长期引领高端时尚潮流。</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Fendi: Italian luxury brand founded 1925 Rome, renowned for iconic FF logo, fur craftsmanship, Baguette &amp; Peekaboo handbags, embodying Roman opulence.</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="25.5" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Dyson</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>dyson</t>
+          <t>flamengo</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dyson: 戴森是源自英国的创新科技品牌，专注于研发颠覆性家居科技产品。其核心产品包括无叶风扇、空气净化风扇、吹风机和吸尘器，以专利气流技术和高效过滤系统著称。戴森产品融合前沿工程设计与智能操控功能，通过强劲性能提升家居环境质量，为全球消费者提供卓越用户体验。品牌坚持自主研发数码马达与空气动力学技术，致力于以科技优化日常生活。</t>
+          <t>Flamengo: 巴西里约热内卢百年体育俱乐部，1895年成立，以足球项目为核心名片，绰号“Mengão”，主场坐落于著名的马拉卡纳体育场。作为巴西最具人气与成就的俱乐部之一，曾斩获世界杯俱乐部杯、南美解放者杯、多届巴甲联赛冠军等重磅荣誉，诞生多位足球传奇球星，在全球足球领域拥有深远影响力。</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Dyson: UK's leading tech brand for bladeless fans, air purifiers, hair dryers, and vacuums. Features patented digital motors, cyclone tech, and advanced filtration. Innovative engineering &amp; modern design.</t>
+          <t>Flamengo: Historic Brazilian football club founded 1895, based at Maracanã Stadium. A global icon, winner of Copa Libertadores and multiple Brasileirão titles, renowned for legendary players.</t>
         </is>
       </c>
     </row>
     <row r="93" ht="25.5" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DUSK</t>
-        </is>
-      </c>
-      <c r="B93"/>
-      <c r="C93"/>
-      <c r="D93"/>
+          <t>Fox Racing</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>fox-racing</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Fox Racing: 1974年创立于美国的专业极限运动装备品牌，专注越野摩托车（Motocross）、山地自行车、滑雪等领域，提供专业服饰、护具、头盔及配件，以卓越防护性能、耐用材质与潮流设计的融合为核心特色，深受全球极限运动爱好者及专业选手信赖，是极限运动装备领域的知名品牌。</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Fox Racing: Founded in the US in 1974, professional extreme sports gear brand specializing in motocross, mountain biking, skiing, etc. Offering apparel, protective gear, helmets &amp; accessories, core feature: fusion of excellent protection, durable materials &amp; trendy design. Trusted by global enthusiasts &amp; pro athletes, renowned in extreme sports gear.</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="25.5" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EMPORIO ARMANI</t>
+          <t>Funtoliu</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>emporio-armani</t>
+          <t>funtoliu</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>EMPORIO ARMANI: 意大利奢侈品牌EMPORIO ARMANI由传奇设计师乔治·阿玛尼于1981年创立，提供高级成衣、配饰、腕表及眼镜系列，以简约线条、中性色调和精致面料著称，融合现代美学与意大利工艺，打造优雅时尚生活方式。</t>
+          <t>Funtoliu 是源自美国的休闲服饰品牌，主营卫衣、T 恤、运动裤等基础款，采用纯棉、抓绒舒适面料，主打宽松简约街头风，性价比高，深受北美、欧洲及亚太年轻群体喜爱。</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>EMPORIO ARMANI: Italian luxury brand by Giorgio Armani, offers ready-to-wear, accessories, watches &amp; eyewear with minimalist designs, neutral tones &amp; exquisite Italian craftsmanship.</t>
+          <t>Funtoliu: US-origin casual apparel brand specializing in basic styles (hoodies, T-shirts, sweatpants) with comfortable cotton &amp; fleece fabrics. Features loose minimalist street style, high cost-performance, popular among young people in North America, Europe, Asia-Pacific.</t>
         </is>
       </c>
     </row>
     <row r="95" ht="25.5" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Enfants Riches Deprimes</t>
+          <t>Gallery Dept</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>erd</t>
+          <t>gallery-dept</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Enfants Riches Déprimés: 奢华街头服饰品牌Enfants Riches Déprimés以复古摇滚美学与高街时尚融合，通过做旧丹宁、标语印花和限量版设计展现反主流文化精神。品牌专注于高端颓废风格，每件单品均采用 distressed 面料和手工细节，打造兼具收藏价值与挑衅态度的衣橱宣言。其标志性系列包含oversize剪裁外套、图形T恤及金属配件，完美呼应当代青年文化中的叛逆奢华理念。</t>
+          <t>Gallery Dept: 2018年由Josué Thomas创立于美国洛杉矶的复古街头潮牌，以「古着再造+手工艺术」为核心定位，主打做旧牛仔夹克、手绘卫衣、洗水牛仔裤等单品，通过手工打磨、植绒印花、破洞做旧等工艺还原复古质感，融合街头叛逆与怀旧美学，践行可持续时尚理念，每款单品均具独特性，是全球潮人、复古爱好者追求个性穿搭的标志性品牌。</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Enfants Riches Déprimés: Luxury streetwear brand blending vintage rock aesthetics with high-end fashion. Features distressed denim, slogan prints, and limited-edition designs.</t>
+          <t>Gallery Dept: LA vintage streetwear since 2018, handmade vintage remake with distressed denim and hand-painted apparel. Blends street style and nostalgia, sustainable fashion, each piece unique.</t>
         </is>
       </c>
     </row>
     <row r="96" ht="25.5" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ESSENTIALS</t>
+          <t>Georgia Bulldogs</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>essentials</t>
+          <t>georgia-bulldogs</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Essentials 是美国高街潮牌 Fear of God 于 2018 年在洛杉矶推出的轻奢休闲副线，由设计师 Jerry Lorenzo 主理。品牌主打极简美式高街风格，以宽松廓形、低饱和莫兰迪色系、质感基础款为核心，覆盖卫衣、T 恤、裤装等单品，兼顾舒适实穿与轻奢质感，是全球潮流圈热门的基础款服饰品牌。</t>
+          <t>Georgia Bulldogs: 美国佐治亚大学（University of Georgia）官方体育代表队核心昵称，以NCAA橄榄球项目的卓越表现闻名，是东南联盟（SEC）传统豪强，曾斩获2021、2022赛季NCAA橄榄球全国冠军及多次SEC联盟冠军；标志性元素包括传奇斗牛犬 mascot“Uga”、经典红黑配色队服，凝聚着“Bulldog Nation”全球球迷的热情，是佐治亚州体育精神与校园荣誉的象征。</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Essentials is the premium casual sub-line of Fear of God, founded in Los Angeles in 2018 by Jerry Lorenzo. It features minimalist American street style, with oversized silhouettes, muted tones and quality basics. Covering hoodies, T-shirts and pants, it balances comfort and luxury, and is popular in global streetwear.</t>
+          <t>Georgia Bulldogs: Official sports team nickname of the University of Georgia, renowned for NCAA football excellence as a traditional SEC powerhouse—2021 &amp; 2022 NCAA national champions, multiple SEC titles. Features legendary bulldog mascot "Uga", classic red-black uniforms; embodies "Bulldog Nation" fans’ passion, symbolizing Georgia’s sports spirit &amp; campus honor.</t>
         </is>
       </c>
     </row>
     <row r="97" ht="25.5" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ETIHAD AIRWAYS</t>
+          <t>Gimenez</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>etihad-airways</t>
+          <t>gimenez</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ETIHAD AIRWAYS: 阿提哈德航空是阿联酋的国家航空公司，2003年成立，总部位于阿布扎比，以其豪华的机舱服务、先进的机队和广泛的全球航线网络而闻名，提供舒适高效的空中旅行体验。</t>
+          <t>Gimenez（Cayetano Giménez）1975 年由 Cayetano Giménez 创立于西班牙阿利坎特，是家族鞋履品牌。主营女士正装鞋、休闲靴、时尚凉鞋等，由 Desire Giménez 主导设计，采用头层牛皮等优质面料，主打简约精致线条与舒适穿着体验，融合西班牙传统工艺与现代时尚风格，风靡欧洲及全球女性市场，以性价比高著称</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Etihad Airways: UAE's national airline since 2003, based in Abu Dhabi. Renowned for luxury cabins, advanced fleet, and global routes offering comfortable, efficient air travel.</t>
+          <t>Gimenez(Cayetano Giménez): Family footwear brand founded in 1975 in Alicante, Spain by Cayetano Giménez. Specializes in women’s dress shoes, casual boots, fashion sandals, etc., designed by Desire Giménez. Uses premium materials like full-grain leather, focusing on minimalist refined lines &amp; comfort, blending Spanish traditional craft with modern style. Popular in European &amp; global women’s markets, known for great value.</t>
         </is>
       </c>
     </row>
     <row r="98" ht="25.5" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FEAR OF GOD</t>
+          <t>Giorgio Armani</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>fear-of-god</t>
+          <t>giorgio-armani</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FEAR OF GOD: 美国街头潮牌由Jerry Lorenzo于2013年创立，主打高端街头服饰，经典产品包括ESSENTIALS系列和第七季羽绒服，采用优质棉料和做旧工艺，风格融合街头文化与极简主义，以宽松剪裁和大地色系著称。</t>
+          <t>Giorgio Armani: 1975年由乔治·阿玛尼（Giorgio Armani）创立的意大利顶级奢侈品品牌，以极简优雅的设计风格、精湛剪裁工艺与高品质材质闻名，涵盖高级定制时装、成衣、美妆、香水、皮具及配饰等全品类，经典作品如男士西装、Armani Si香水深入人心，始终传递高端生活方式与永恒时尚美学，是全球奢华时尚领域的标志性品牌之一。</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>FEAR OF GOD FOG: Jerry Lorenzo's luxury streetwear since 2013, featuring ESSENTIALS, distressed details, minimalist oversized fits in earth tones.</t>
+          <t>Giorgio Armani: Italian premier luxury brand founded by Giorgio Armani in 1975, renowned for minimalist elegance, exquisite tailoring &amp; premium materials. Covers haute couture, ready-to-wear, beauty, fragrances (Armani Si), leather goods &amp; accessories. Delivers luxury lifestyle &amp; timeless aesthetics, iconic in global luxury fashion.</t>
         </is>
       </c>
     </row>
     <row r="99" ht="25.5" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Fear of God ESSENTIALS</t>
-        </is>
-      </c>
-      <c r="B99"/>
+          <t>Givenchy</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>givenchy</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Fear of God ESSENTIALS: Fear of God ESSENTIALS 是 Jerry Lorenzo 创建的 Fear of God 的副线品牌，专注于高端基础款服饰。品牌以简约设计、优质面料和中性风格著称，主打卫衣、T恤、运动裤等日常必备单品，融合街头文化与极简主义美学，展现低调而富有质感的现代生活方式。</t>
+          <t>Givenchy: 1952年由休伯特·德·纪梵希（Hubert de Givenchy）创立的法国顶级奢侈品牌，以先锋设计与现代优雅著称，核心覆盖高级成衣、皮具、香水及美妆品类。标志性4G logo（融合Givenchy、Genteel、Glamour、Grace精神）深入人心，经典产品包括Antigona系列手袋（利落线条配奢华皮革）、Le Rouge纪梵希高定香榭口红（丝绒质地与高饱和色号）及高定礼服（流畅剪裁诠释贵族质感）。从与奥黛丽·赫本的传奇合作到当代街头奢华风格融合，Givenchy始终践行“优雅与叛逆共存”的时尚态度，是全球精英追逐的奢侈品牌代表。</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Fear of God ESSENTIALS: Jerry Lorenzo's high-end basics line. Minimalist design, premium fabrics, unisex staples like hoodies, tees, and sweats. Modern lifestyle.</t>
+          <t>Givenchy: French luxury brand since 1952, known for avant-garde design &amp; modern elegance. Offers haute couture, leather goods, perfumes, cosmetics. Iconic 4G logo. Classics: Antigona handbags, Le Rouge lipsticks. Elegance meets rebellion.</t>
         </is>
       </c>
     </row>
     <row r="100" ht="25.5" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FENDI</t>
+          <t>Golden Goose</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>fendi</t>
+          <t>golden-goose</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FENDI: 探索 FENDI 官方奢华时尚与配饰系列。从标志性的 Baguette 手袋到精致的成衣系列，FENDI 将意大利工艺与创新设计融为一体。选购最新系列的皮具、鞋履、配饰及更多，尽显现代优雅风范。享受全球配送与专属客服服务。</t>
+          <t>Golden Goose: 源自意大利的高端潮流品牌，以标志性做旧工艺休闲鞋（sneakers）为核心，主打复古街头风格，采用小牛皮、麂皮等优质材质手工打造，经典元素包含星星补丁、自然做旧划痕与仿脏设计，凭借“破坏美学”成为明星与潮流人士青睐的爆款单品，是追求独特质感与复古腔调的鞋履首选品牌。</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>FENDI: Explore luxury fashion &amp; accessories. From iconic Baguette bags to ready-to-wear collections, FENDI blends Italian craftsmanship with innovative design. Shop now for modern elegance.</t>
+          <t>Golden Goose: Italian luxury brand crafting handcrafted distressed sneakers from premium leathers, featuring star patches &amp; vintage styling for distinctive aesthetic.</t>
         </is>
       </c>
     </row>
     <row r="101" ht="25.5" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FLAMENGO</t>
+          <t>Gran Sasso</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>flamengo</t>
+          <t>gran-sasso</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FLAMENGO: 巴西弗拉门戈足球俱乐部官方品牌,1945年成立,提供正版球迷服装与周边产品,包含经典红黑条纹队服、训练服及休闲服饰,采用透气科技面料与精致刺绣工艺,设计融合球队徽章元素,展现激情足球文化与巴西运动风格。</t>
+          <t>Gran Sasso: 源自意大利Abruzzo地区Gran Sasso d'Italia山脉的经典天然矿泉水品牌，依托阿尔卑斯山系深层地下水源，经千年岩层自然过滤，水质纯净且富含钙、镁等天然矿物质，口感清冽甘醇。品牌主打“自然本源的健康饮水”理念，是意大利家庭日常、餐饮场景及全球高端水市场的热门选择，以“源自山脉的纯粹滋味”传递原生品质。</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>FLAMENGO: Official brand since 1945, authentic jerseys, training wear &amp; casual apparel with breathable fabric &amp; embroidery, featuring iconic red-black stripes &amp; crest designs.</t>
+          <t>Gran Sasso: Classic Italian natural mineral water from Abruzzo’s Gran Sasso d’Italia. Sourced from Alpine deep underground, filtered by thousand-year rocks—pure, rich in calcium/magnesium, crisp &amp; sweet. Core concept: natural healthy drinking. Popular in Italian households, dining, global premium water, delivering pure mountain taste.</t>
         </is>
       </c>
     </row>
     <row r="102" ht="25.5" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FOX RACING</t>
+          <t xml:space="preserve">Gore Tex </t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>fox-racing</t>
+          <t xml:space="preserve">gore-tex </t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FOX RACING: 1977年由Pete Fox创立，美国专业越野摩托和自行车装备品牌，产品系列包括头盔、护具、骑行服等，经典产品有V1头盔和Racing系列护甲，采用高强度材质，工艺耐用，功能防护卓越，风格硬核运动。</t>
+          <t>Gore Tex: 美国戈尔公司（W.L. Gore &amp; Associates）旗下全球知名功能性面料技术品牌，核心依托膨体聚四氟乙烯（ePTFE）膜技术，实现“防水、透气、防风”三大核心功能，广泛应用于户外服装、鞋靴、手套及医疗植入物等场景，是Arc'teryx、The North Face等高端户外品牌的核心面料合作伙伴，以性能稳定性与耐用性成为户外爱好者、专业运动员及极限环境从业者信赖的功能面料标杆。</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>FOX RACING: Founded 1977 by Pete Fox, US-based professional motocross &amp; MTB gear. Helmets, protection, apparel. V1 helmet &amp; Racing armor. Durable, high-performance, core sports style.</t>
+          <t>GORE TEX: Leading U.S. functional fabric tech with ePTFE membrane, delivering waterproof, breathable, windproof performance. Trusted by Arc'teryx &amp; The North Face for outdoor gear &amp; medical implants. The performance fabric standard.</t>
         </is>
       </c>
     </row>
     <row r="103" ht="25.5" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FUNTOLIU</t>
+          <t>Green Bay Packers</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>funtoliu</t>
-        </is>
-      </c>
-      <c r="C103"/>
-      <c r="D103"/>
+          <t>green-bay-packers</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Green Bay Packers: 1919年成立于美国威斯康星州绿湾，是NFL（国家橄榄球联盟）历史最悠久的球队之一，隶属于NFC北区，绰号“包装工队”。以标志性绿色与金色队服为视觉标识，主场是传奇的Lambeau Field（兰博球场）。作为NFL夺冠次数最多的球队（13次联盟冠军，含4次超级碗），拥有深厚橄榄球传统，全球忠诚球迷群体中“奶酪头”文化更是NFL独特符号。</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Green Bay Packers: Founded 1919 in Green Bay, Wisconsin, USA—one of NFL’s oldest teams (NFC North), nicknamed "Packers". Iconic green/gold uniforms, home at legendary Lambeau Field. NFL’s most successful with 13 league titles (4 Super Bowls), rich tradition. "Cheesehead" culture, a unique NFL symbol for global loyal fans.</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="25.5" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GALLERY DEPT</t>
+          <t>Griezmann</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>gallery-dept</t>
+          <t>griezmann</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>GALLERY DEPT: 洛杉矶街头潮牌，以其手工涂鸦、复古做旧风格闻名，主打喷墨印花T恤、卫衣和牛仔裤，采用高品质棉质面料，工艺独特，风格复古不羁，彰显个性街头文化。</t>
+          <t>Griezmann 2015 年创立于法国，主营简约休闲服饰，采用纯棉、针织等舒适面料，融合法式简约与街头潮流，设计感与性价比兼具，深受欧洲、北美及亚太年轻群体喜爱。</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>GALLERY DEPT: LA streetwear brand known for handcrafted graffiti, vintage washes, premium cotton, distressed tees, hoodies, denim. Unique artistry, retro rebellious style.</t>
+          <t>Griezmann: Founded in France in 2015, specializing in minimalist casual apparel with comfy fabrics like cotton &amp; knit. Blends French minimalism with streetwear, balancing design and value. Popular among young people in Europe, North America &amp; Asia-Pacific.</t>
         </is>
       </c>
     </row>
     <row r="105" ht="25.5" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GEORGIA BULLDOGS</t>
+          <t>Gucci</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>georgia-bulldogs</t>
-        </is>
-      </c>
-      <c r="C105"/>
-      <c r="D105"/>
+          <t>gucci</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Gucci: 1921年由古驰奥·古驰（Guccio Gucci）在意大利佛罗伦萨创立的顶级奢侈品品牌，以标志性双G logo、马衔扣元素及红绿织带为经典标识，涵盖高端时装、经典手袋（如Dionysus、Jackie 1961系列）、鞋履、奢华配饰与香水等核心品类，传承意大利百年精湛手工艺，融合复古美学与现代先锋设计，是全球追求极致品质、经典时尚与奢华格调的高端消费者首选品牌。</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Gucci: Since 1921 Florence, luxury brand with iconic double-G, horsebit, green-red webbing. Offers fashion, handbags (Dionysus, Jackie 1961), shoes, accessories, perfumes. Italian craftsmanship, vintage-modern blend for elite consumers.</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="25.5" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GIMENEZ</t>
+          <t>Hellstar</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>gimenez</t>
+          <t>hellstar</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GIMENEZ: 源自西班牙的时尚眼镜品牌，专注于设计高品质太阳镜和光学眼镜，采用轻质金属与环保板材制作，结合精湛手工工艺，打造兼具复古与现代风格的经典款式，为消费者提供舒适佩戴体验与时尚造型选择。</t>
+          <t>Hellstar: 专注暗黑街头潮流的时尚品牌，主打卫衣、夹克、配饰等核心单品，以独特设计融合街头文化与暗黑美学，采用优质面料打造舒适穿着体验，风格酷感鲜明，深受Z世代年轻人及潮流爱好者青睐，是展现个性穿搭的热门选择。</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>GIMENEZGIMENEZ: Spanish eyewear brand crafting premium sunglasses &amp; optical glasses with lightweight metals &amp; eco-acetate, blending retro &amp; modern styles for comfort and fashion.</t>
+          <t>Hellstar: Dark streetwear brand merging street culture with dark aesthetics. Core hoodies, jackets &amp; accessories. Premium fabrics, bold style for Z-gen &amp; trendsetters.</t>
         </is>
       </c>
     </row>
     <row r="107" ht="25.5" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GIORGIO ARMANI</t>
+          <t>Hermes</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>giorgio-armani</t>
+          <t>hermes</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>GIORGIO ARMANI: 意大利奢侈品牌，由乔治·阿玛尼于1975年创立。以优雅剪裁和中性色调闻名，产品涵盖高级时装、美妆、眼镜及家居。经典设计包括权力西装和Acqua di Gio香水，采用奢华面料与精湛工艺，风格简约高贵。</t>
+          <t>Hermes: 1837年由Thierry Hermès创立于法国巴黎的全球顶级奢侈品品牌，以马具制作起家，凭借百年精湛手工工艺与永恒经典设计著称，核心产品涵盖高端皮革手袋（如传奇凯莉包Kelly Bag、柏金包Birkin Bag）、奢华丝绸配饰（经典90cm丝围巾）、男士香水（大地Eau Terre d'Hermès）及高级时装，传承法式优雅与极致品质，是全球奢华与品味的标志性品牌。</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>GIORGIO ARMANI: Italian luxury brand founded in 1975, renowned for elegant tailoring, neutral tones, power suits, Acqua di Gio fragrance, and sophisticated simplicity.</t>
+          <t>Hermes: Founded in Paris, France by Thierry Hermès in 1837, this top global luxury brand started with equestrian gear. Renowned for century-old exquisite craftsmanship &amp; timeless designs, core products include high-end leather bags (Kelly Bag, Birkin Bag), luxury silk accessories (classic 90cm silk scarves), men’s perfume (Eau de Terre d'Hermès), and haute couture. It embodies French elegance, ultimate quality, and is a global symbol of luxury &amp; taste.</t>
         </is>
       </c>
     </row>
     <row r="108" ht="25.5" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GIVENCHY</t>
+          <t>Hogan</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>givenchy</t>
+          <t>hogan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GIVENCHY: 法国奢侈品牌Givenchy由Hubert de Givenchy于1952年创立，以高级时装、香水和配饰著称，经典产品包括Antigona手袋和绅士香水，采用优质皮革和精致面料，工艺精湛，风格优雅现代，融合经典与创新设计。</t>
+          <t>Hogan: 1986年创立于意大利的奢侈时尚品牌，隶属于Tod's集团，以「奢华休闲」风格为核心，专注鞋履、手袋及成衣设计。选用意大利顶级皮革，融合运动基因与高端工艺，经典产品如Interaction老爹鞋、H383商务运动鞋，打造「可通勤的奢华运动鞋」，深受明星、都市精英与时尚爱好者青睐。</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Givenchy: French luxury brand since 1952, renowned for haute couture, perfumes like Gentleman, &amp; Antigona bags with exquisite leather &amp; modern elegance.</t>
+          <t>Hogan: 1986 Italian luxury fashion brand under Tod’s Group, core “luxury casual” style, focusing on footwear, handbags &amp; ready-to-wear. Made with top Italian leather, blends sporty DNA with high-end craftsmanship. Iconic styles: Interaction Dad Sneakers, H383 business sneakers, creating “commutable luxury sneakers” favored by celebrities, urban elites &amp; fashion lovers.</t>
         </is>
       </c>
     </row>
     <row r="109" ht="25.5" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GOLDEN GOOSE</t>
+          <t>Harman Kardon</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>golden-goose</t>
+          <t>harman kardon</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>GOLDEN GOOSE: Golden Goose 是意大利奢侈品牌，以其手工做旧复古运动鞋和高端服饰闻名。品牌融合意式工艺与街头风格，每双鞋款均采用独特做旧处理，展现个性化破损细节。Golden Goose 产品涵盖运动鞋、服装和配饰，主打奢华休闲风，适合追求时尚与品质的消费者。品牌通过精致工艺和独特设计，为日常穿搭注入复古魅力。</t>
+          <t>Harman Kardon: 创立于1953年的高端音频品牌，隶属于哈曼国际集团，以专业声学工程技术与时尚精致设计著称。核心产品涵盖家用音响、无线耳机、车载音响系统等，经典系列包括琉璃（Aura）系列、Onyx系列等，凭借卓越音质表现与标志性外观设计，深受音频爱好者与高端消费群体青睐，广泛应用于家庭娱乐、专业音频场景及豪华汽车配套领域。</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Golden Goose: Italian luxury brand with handmade distressed sneakers, high-end apparel &amp; accessories. Blends Italian craftsmanship with street style for a chic, retro look.</t>
+          <t>Harman Kardon: Premium audio brand since 1953. Features acoustic engineering &amp; sleek design in Aura/Onyx series speakers, headphones &amp; car systems for exceptional sound.</t>
         </is>
       </c>
     </row>
     <row r="110" ht="25.5" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GRAN SASSO</t>
+          <t>House Of Errors</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>gran-sasso</t>
+          <t>house-of-errors</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>GRAN SASSO: 意大利高端户外装备品牌，专注于高性能登山与徒步装备，产品采用尖端科技面料与符合人体工学的设计，提供卓越防护与舒适体验。</t>
+          <t>House Of Errors 由设计师 Fully（Matthew Foulerton）于 2019 年创立于英国伦敦，主营服装、外套与配饰，标志性产品为全视之眼连帽衫与雕塑感羽绒服。设计师出身建筑专业，主打先锋超现实风格，融合建筑感廓形与解构主义，以重工刺绣、优质面料及皮革为核心材质，风靡全球潮流圈，在欧洲、北美及亚太地区深受时尚达人与明星青睐。</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>GRAN SASSO: High-performance mountaineering &amp; hiking gear with cutting-edge tech fabrics &amp; ergonomic design for superior protection &amp; comfort.</t>
+          <t>House Of Errors: Founded 2019 London by Fully. Apparel, outerwear &amp; accessories. Iconic: All-Seeing Eye hoodies, sculptural down jackets. Architect-inspired avant-surrealism, architectural silhouettes &amp; deconstruction. Heavy embroidery, premium materials. Loved by fashion icons in EU, NA, APAC.</t>
         </is>
       </c>
     </row>
     <row r="111" ht="25.5" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">GORE-TEX </t>
+          <t>Indianapolis Colts</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">gore-tex </t>
+          <t>indianapolis-colts</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GORE-TEX: 探索GORE-TEX防水透气面料的创新科技。专为户外运动爱好者设计，提供卓越的防风防水保护，同时保持透气舒适。无论是徒步、滑雪还是登山，GORE-TEX产品都能让您在任何天气条件下保持干爽。选择GORE-TEX，体验顶级户外装备的可靠性能与持久耐用性。</t>
+          <t>Indianapolis Colts: 美国国家橄榄球联盟（NFL）AFC南部分区的职业橄榄球队，1953年以“巴尔的摩小马队”身份成立，1984年迁至印第安纳波利斯并更名。主场为卢卡斯石油体育场，以快速进攻体系、传奇四分卫传承（如佩顿·曼宁）及2次超级碗冠军（1971、2007赛季）闻名，是印第安纳波利斯本土体育文化象征，聚焦高水平赛事表现与球迷社区互动，深受全美橄榄球爱好者关注。</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>GORE-TEX: Waterproof, breathable, windproof fabric for hiking, skiing, mountaineering. Stay dry &amp; comfortable in all weather. Durable outdoor gear.</t>
+          <t>Indianapolis Colts: NFL AFC South team since 1953. Known for fast offense, legendary QB Peyton Manning, and 2 Super Bowl wins (1971, 2007).</t>
         </is>
       </c>
     </row>
     <row r="112" ht="25.5" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GREEN BAY PACKERS</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>green-bay-packers</t>
+          <t>inter-miami</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>GREEN BAY PACKERS: 1919年由科姆·兰博创立，美国职业橄榄球队，以绿色和金色为主色调，经典队服包括绿色球衣和金色头盔，采用高性能材质，工艺精湛，功能耐用，风格经典运动。代表商品有正版球衣和纪念帽。</t>
+          <t>Inter Miami: 2020年加入美国职业足球大联盟（MLS）的佛罗里达足球俱乐部，由大卫·贝克汉姆等联合创立，主场位于劳德代尔堡，以标志性粉黑配色队服著称，融合国际化足球风格与社区互动属性，是MLS中极具话题度的新兴球队。</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>GREEN BAY PACKERS: Founded in 1919 by Curly Lambeau, NFL team in green &amp; gold. Iconic green jerseys &amp; gold helmets with high-performance, durable craftsmanship. Official jerseys &amp; caps.</t>
+          <t>Inter Miami: Florida-based MLS expansion club (joined 2020), co-founded by David Beckham, based in Fort Lauderdale, known for iconic pink-black kits, blending international soccer style with community engagement, a high-profile emerging MLS team.</t>
         </is>
       </c>
     </row>
     <row r="113" ht="25.5" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GRIEZMANN</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>griezmann</t>
+          <t>inter-milan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GRIEZMANN: 法国知名时尚品牌，以现代设计和高品质工艺著称，产品涵盖服装、配饰及生活方式用品，融合经典与创新元素，风格简约优雅，适合追求精致生活的消费者。</t>
-        </is>
-      </c>
-      <c r="D113"/>
+          <t>Inter Milan: 1908年创立于意大利米兰的意甲顶级足球俱乐部，绰号“蓝黑军团”，累计斩获19次意甲联赛冠军、3次欧洲冠军联赛冠军等重磅荣誉，以标志性蓝黑条纹球衣、战术韧性及全球庞大球迷群体闻名，是世界足坛历史最悠久、影响力深远的豪门俱乐部之一。</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Inter Milan: Founded 1908 Milan, top Serie A club Nerazzurri with 19 league titles &amp; 3 UCL wins. Iconic blue-black stripes, tactical resilience, global fanbase. Historic football giant.</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="25.5" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>GUCCI</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>gucci</t>
+          <t>jbl</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GUCCI: 探索意大利奢侈品牌古驰的精致时尚世界。古驰提供高端手袋、服装、配饰及鞋履，融合永恒设计与现代美学。品牌代表卓越工艺与大胆创新，为追求独特风格的全球消费者打造标志性单品。通过古驰官方跨境电商平台，享受正品保障与全球配送服务。</t>
+          <t>JBL: 1946年由音频先驱詹姆斯·巴罗·兰辛（James Bullough Lansing）创立，全球专业音频与消费类音频领导品牌，专注于音箱、耳机、专业音响系统等产品研发，经典系列涵盖Charge便携蓝牙音箱、Flip音乐万花筒、Tune降噪耳机及Professional专业演出音响，以JBL Pro Sound专业级音质、IP67级防水耐用性、潮流轻量化设计为核心优势，覆盖家庭娱乐、户外出行、专业舞台等多元场景，是全球音乐爱好者与音频从业者的首选品牌。</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>GUCCI: Italian luxury brand offering high-end handbags, apparel, accessories, and footwear. Blends timeless design with modern aesthetics, embodying exquisite craftsmanship and bold innovation for distinctive style. Authentic products with global shipping.</t>
+          <t>JBL: Founded in 1946 by audio pioneer James Bullough Lansing, a global leader in professional &amp; consumer audio. Specializes in speakers, headphones, pro sound systems. Flagship series: Charge portable Bluetooth, Flip, Tune noise-canceling headphones, Professional performance audio. Core strengths: JBL Pro Sound, IP67 waterproofing, trendy lightweight design. Covers home entertainment, outdoor travel, pro stages—preferred by global music lovers &amp; audio pros.</t>
         </is>
       </c>
     </row>
     <row r="115" ht="25.5" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>HELLSTAR</t>
+          <t>Josh Allen Buffalo Bills</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>hellstar</t>
+          <t>josh-allen-buffalo-bills</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>HELLSTAR: Hellstar 是一个专注于暗黑风格和高品质工艺的街头服饰品牌。其产品融合哥特美学与现代街头文化元素，主打卫衣、T恤和配饰，以独特的设计和舒适的穿着体验吸引追求个性表达的年轻群体。品牌注重细节和面料选择，打造兼具视觉冲击力和实用性的服饰。</t>
+          <t>Josh Allen Buffalo Bills 是 NFL 布法罗比尔队 17 四分卫周边系列，由 Josh Allen 与 Nike、New Era 等品牌合作推出，2018 年其加盟后正式成型。主营官方球衣、T 恤、棒球帽等，Josh Allen 参与设计 Billustration 系列，主打美式运动风格，采用 100% 聚酯纤维球衣面料与纯棉服饰材质，风靡北美，深受 Bills Mafia 粉丝青睐，是 NFL 官方授权的明星球员周边品牌。</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>HELLSTAR: Hellstar fuses gothic aesthetics with streetwear, offering dark-style hoodies, tees &amp; accessories. Premium craftsmanship, unique designs &amp; comfort for expressive youth.</t>
+          <t>Josh Allen Buffalo Bills: Official NFL licensed merchandise for Buffalo Bills QB Josh Allen #17. Launched 2018 with Nike &amp; New Era. Features jerseys, T-shirts, caps in Billustration series. American sports style, 100% polyester/cotton. Popular in North America, loved by Bills Mafia.</t>
         </is>
       </c>
     </row>
     <row r="116" ht="25.5" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HERMES</t>
+          <t>Juicy Couture</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>hermes</t>
+          <t>juicy-couture</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>HERMES: 爱马仕是法国奢侈品牌，以精湛工艺和永恒设计闻名，提供皮具、丝巾、时装及家居等高端产品，融合传统与创新，为全球消费者打造优雅生活方式。</t>
+          <t>Juicy Couture: 1997年创立于美国的轻奢时尚品牌，以标志性天鹅绒运动套装（Velvet Tracksuits）闻名全球，融合加州阳光活力与街头甜酷复古风格，擅长用水晶、亮片及经典字母Logo点缀卫衣、手袋、配饰等单品，是90-00年代“休闲奢华”风的代表，深受追求时尚舒适与个性态度的年轻女性喜爱。</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>HERMESHERMES: French luxury brand renowned for exquisite craftsmanship and timeless design, offering high-end leather goods, scarves, fashion, and home decor.</t>
+          <t>Juicy Couture: US luxury fashion brand since 1997, iconic for Velvet Tracksuits. Merges California sunshine with street cool, features crystals, sequins, logos. Symbol of 90s-00s Casual Luxury, loved by fashion-forward young women.</t>
         </is>
       </c>
     </row>
     <row r="117" ht="25.5" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>HOGAN</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>hogan</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>HOGAN: 意大利奢侈品牌Hogan由Andrea Della Valle于1986年创立，以奢华皮革与创新设计闻名，产品系列包括休闲鞋、手袋及配饰，经典产品有Interactive运动鞋，采用顶级皮革与弹性橡胶底，工艺精湛，功能舒适轻盈，风格现代优雅。</t>
+          <t>Juventus: 1897年创立于意大利都灵的世界顶级足球俱乐部，绰号“老妇人”，是意甲联赛夺冠次数最多的豪门球队，曾斩获欧冠冠军、意大利杯冠军等多项顶级荣誉，主场为都灵安联球场。以百年历史底蕴、坚韧战术风格与全球庞大球迷群体闻名，品牌覆盖官方球衣、球迷周边、足球文化衍生产品等，是足球领域极具影响力的经典IP。</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>HOGAN: Luxury Italian brand since 1986, renowned for premium leather, innovative design, modern elegance in casual shoes, bags, accessories. Classic Interactive sneakers feature elastic rubber soles.</t>
+          <t>Juventus: Top global football club founded 1897 in Turin, Italy, nicknamed "Old Lady" – most Serie A titles, Champions League/Coppa Italia winner, home at Allianz Stadium. Century-old heritage, tough tactics, large global fanbase; brand covers official jerseys, fan merch, football culture derivatives, influential classic IP.</t>
         </is>
       </c>
     </row>
     <row r="118" ht="25.5" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Harman Kardon</t>
+          <t>Kanye</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>harman kardon</t>
+          <t>kanye</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Harman Kardon（哈曼卡顿）1953 年创立于美国，是哈曼国际旗下全球高端音响品牌。品牌专注家用音响、无线音箱、蓝牙耳机与车载音响研发，以领先声学科技、简约工业设计与高保真音质为核心，融合艺术美学与沉浸式听觉体验，是高端家用影音及车载声学领域的标杆品牌。</t>
+          <t>Kanye由美国说唱歌手坎耶・维斯特（Kanye West）于 2013 年创立，2015 年与 Adidas 合作推出首个系列。主营运动鞋、服饰与配饰，Kanye 亲自主导设计，Virgil Abloh 等参与创意。主打极简街头奢华风格，以大地色系、宽松廓形为标志，采用 Primeknit 针织、麂皮、皮革及 Boost 缓震科技，风靡全球潮流圈，在北美、欧洲及亚洲地区极具影响力</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Harman Kardon is a global premium audio brand under Harman International, founded in the USA in 1953. It focuses on home audio, wireless speakers, Bluetooth headsets and car audio. With advanced acoustic technology, minimalist design and hi-fi sound, it blends art and immersive listening, leading the high-end home and car audio industry.</t>
+          <t>Kanye: 2013-founded by Kanye West, 2015 Adidas collab. Sells sneakers, apparel, accessories. Kanye-led design, Virgil Abloh. Minimalist street luxury: earth tones, loose fits. Primeknit, suede, leather &amp; Boost cushioning. Global streetwear N. America, Europe, Asia.</t>
         </is>
       </c>
     </row>
     <row r="119" ht="25.5" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>HOUSE OF ERRORS</t>
+          <t>Kid Cudi</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>house-of-errors</t>
+          <t>kid-cudi</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Apple: 苹果是全球领先的科技公司，致力于设计并生产创新的消费电子产品、软件及服务。其产品包括iPhone智能手机、Mac电脑、iPad平板电脑、Apple Watch智能手表及AirPods无线耳机，以其卓越的用户体验、无缝的生态系统集成和隐私保护著称，持续为全球用户提供优质的数字生活解决方案。
-Samsung: 三星电子是消费电子领域的全球领导者，专注于智能手机、电视、家用电器及半导体技术的研发与制造。其产品以尖端显示技术、创新设计和可靠性闻名，为消费者提供高品质的智能家居体验和移动解决方案，满足多元化的数字生活需求。
-Nike: 耐克是全球知名的运动服饰与装备品牌，专注于为运动员及运动爱好者提供创新的高性能产品。其产品涵盖运动鞋、服装及配件，融合先进科技与时尚设计，致力于激发运动潜能并推动体育文化发展，成为运动领域的标志性品牌。
-Adidas: 阿迪达斯是国际领先的运动品牌，以专业运动鞋、服装及配件为核心产品。其设计注重性能创新与可持续材料应用，同时融合时尚元素，为全球运动员和日常用户提供舒适且功能性的运动解决方案，传递运动激情与创造力。
-Sony: 索尼是全球知名的电子产品及娱乐公司，业务涵盖电视、音频设备、游戏主机、相机及影视音乐制作。其产品以卓越的影音技术、沉浸式娱乐体验和可靠性著称，为消费者提供高品质的家庭娱乐和创意内容解决方案。
-Microsoft: 微软是全球领先的软件、硬件及云计算服务提供商，以其Windows操作系统、Office办公软件、Surface设备及Azure云平台闻名。其产品专注于提升生产力、促进数字化转型并保障企业安全，为全球用户与企业提供可靠的技术解决方案。
-Google: 谷歌是全球领先的科技公司，专注于搜索引擎、云计算、人工智能及智能硬件领域。其产品包括Google搜索、Android操作系统、Pixel设备及Google Workspace办公套件，致力于组织全球信息并提供高效、智能的数字化服务。
-Amazon: 亚马逊是全球最大的电子商务及云计算平台，提供广泛的零售商品、Prime会员服务、Kindle电子书及AWS云解决方案。其以便捷的购物体验、高效的物流网络和技术创新著称，持续重塑零售与科技行业的未来。
-Lenovo: 联想是全球知名的电脑与智能设备制造商，产品包括ThinkPad笔记本电脑、Yoga系列二合一设备及服务器解决方案。其以可靠性、创新设计及全球化服务著称，为个人与企业用户提供高效的计算技术和数字化转型工具。
-HP: 惠普是全球领先的打印及个人计算解决方案提供商，产品涵盖笔记本电脑、台式机、打印机及耗材。其以可靠的性能、创新的打印技术及可持续设计闻名，为家庭、企业及教育用户提供高效的产品与服务。
-Huawei: 华为是全球领先的通信技术与智能设备品牌，专注于智能手机、5G网络设备、平板电脑及 wearable 设备。其产品以先进的摄影技术、长续航电池及高速连接性能著称，为全球用户提供创新的全场景智慧生活体验。
-Xiaomi: 小米是以智能手机为核心的科技品牌，提供智能电视、穿戴设备及生态链产品。其产品以高性价比、创新功能及MIUI系统体验闻名，致力于让全球用户享受科技带来的美好生活。
-Dell: 戴尔是全球知名的计算机技术供应商，专注于笔记本电脑、台式机、服务器及存储解决方案。其产品以企业级可靠性、定制化服务及高性能著称，为政府、教育及商业客户提供全面的数字化基础设施支持。
-LG: LG是消费电子与家用电器领域的全球品牌，产品包括OLED电视、冰箱、洗衣机及空调。其以创新的显示技术、节能设计及智能家居集成闻名，为用户提供舒适、高效的家庭生活解决方案。
-Asus: 华硕是全球知名的电脑硬件及电子产品品牌，以游戏笔记本、主板、显示器及路由器著称。其产品注重性能优化、散热技术及用户定制化体验，为游戏玩家、创作者及企业提供可靠的科技解决方案。
-Acer: 宏碁是全球领先的电脑与电子设备品牌，产品涵盖笔记本电脑、台式机、显示器及投影仪。其以高性价比、轻薄设计及长效续航闻名，为教育、商业及个人用户提供实用的数字产品。
-Logitech: 罗技是计算机外设与视频协作解决方案的领先品牌，产品包括键盘、鼠标、摄像头及耳机。其以人性化设计、无线技术创新及跨平台兼容性著称，为用户提供高效舒适的办公与娱乐体验。
-Canon: 佳能是全球知名的影像与光学产品制造商，产品涵盖相机、打印机及复印机。其以卓越的镜头技术、色彩管理及可靠性闻名，为摄影爱好者、专业摄影师及企业用户提供高质量的影像解决方案。
-Nikon: 尼康是摄影与光学仪器领域的领先品牌，专注于数码相机、镜头及望远镜。其产品以高解析度成像、耐用性及专业级性能著称，满足从业余到专业摄影师的多样化创作需求。
-PlayStation: PlayStation是索尼旗下的全球知名游戏品牌，提供PlayStation游戏主机、游戏软件及在线服务。其以独占游戏内容、沉浸式娱乐体验及活跃的玩家社区闻名，为全球玩家提供顶级的游戏享受。</t>
+          <t>Kid Cudi于2022 年 2 月推出个人奢侈街头服饰品牌MOTR（Members of the Rage），2023 年巴黎时装周完整发布。主营宽松 T 恤、美式夹克、牛仔裤及配饰，UFO logo 由其与Nigo联合设计。风格融合90 年代垃圾摇滚、嘻哈灵魂与未来主义，色彩鲜明、版型宽松。采用意大利制造高品质面料，注重舒适与耐用。风靡欧美、日本及全球潮流圈，深受音乐与时尚爱好者追捧。</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>HOUSE OF ERRORS: Creative streetwear brand offering edgy, urban-inspired apparel with bold graphics and uncompromising style for the fashion-forward individual.</t>
+          <t>MOTR (Members of the Rage): Kid Cudi’s luxury streetwear brand launched Feb 2022, fully debuted at 2023 Paris Fashion Week. Features oversized tees, American jackets, jeans &amp; accessories. UFO logo co-designed by Kid Cudi &amp; Nigo. Blends 90s grunge, hip-hop soul, futurism—vibrant colors, loose fits. Italian-made high-quality fabrics for comfort/durability. Popular in US/Europe, Japan, global streetwear circles, loved by music &amp; fashion fans.</t>
         </is>
       </c>
     </row>
     <row r="120" ht="25.5" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>INDIANAPOLIS COLTS</t>
+          <t>Lacoste</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>indianapolis-colts</t>
+          <t>lacoste</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>INDIANAPOLIS COLTS: 印第安纳波利斯小马队是 NFL 职业橄榄球队，以其标志性的蓝色和白色彩色以及精湛的球场表现而闻名。该球队拥有众多忠实粉丝，其周边商品如球衣和帽子均采用高品质材料制作，兼具耐用性与舒适度，风格经典且充满运动活力。</t>
+          <t>Lacoste: 1933年由法国网球运动员René Lacoste创立的轻奢品牌，以标志性鳄鱼LOGO与经典POLO衫著称，产品线覆盖男女装、鞋履、配饰及香水，融合法式优雅与运动休闲基因，主打简约舒适、经典耐穿的设计，是全球法式生活方式的代表性品牌。</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>INDIANAPOLIS COLTS: NFL team known for iconic blue and white colors, elite on-field performance. High-quality, durable jerseys and hats for loyal fans.</t>
+          <t>Lacoste: Affordable luxury brand founded in 1933 by French tennis player René Lacoste, known for iconic crocodile logo &amp; classic polo shirts. Offers apparel, footwear, accessories, fragrances, blending French elegance with sporty casualness, featuring minimalist, comfortable, durable designs—global representative of French lifestyle.</t>
         </is>
       </c>
     </row>
     <row r="121" ht="25.5" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>INTER MIAMI</t>
+          <t>Lego</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>inter-miami</t>
+          <t>lego</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>INTER MIAMI: 由足球传奇大卫·贝克汉姆参与创立的美国职业足球俱乐部，位于佛罗里达州迈阿密，球队主场为DRV PNK体育场，球衣主打粉黑配色，采用高科技透气面料，设计时尚前卫，风格充满活力与激情，代表球员包括莱昂内尔·梅西和塞尔吉奥·布斯克茨。</t>
+          <t>Lego: 1932年由奥勒·基尔克·克里斯蒂安森创立于丹麦，全球知名积木玩具品牌，以安全ABS塑料为核心材质，主打创意拼搭体验，涵盖乐高城市、星球大战、机械组、好朋友等经典系列，融合STEM教育理念，激发全年龄层用户的想象力与动手能力，产品兼容度高，是亲子互动及创意表达的优质选择。</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>INTER MIAMI: David Beckham's MLS club, features Lionel Messi, Sergio Busquets. Pink-black tech jerseys, DRV PNK Stadium. Fashionable, high-performance soccer apparel.</t>
+          <t>Lego: Since 1932 Denmark, global building block toys with safe ABS plastic. Creative sets like City, Star Wars, Technic, Friends. STEM-integrated, inspires all ages, compatible, ideal for family interaction.</t>
         </is>
       </c>
     </row>
     <row r="122" ht="25.5" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>INTER MILAN</t>
+          <t>Lancme</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>inter-milan</t>
+          <t>lancme</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>INTER MILAN: 1908年成立于意大利米兰的传奇足球俱乐部，以蓝黑军团著称，队服采用标志性蓝黑条纹设计，提供官方球衣、训练装备及周边产品，风格经典运动，承载百年激情与荣耀。</t>
+          <t>Lancôme: 1935年由Armand Petitjean创立于法国的高端美妆护肤品牌，以法式优雅与科技护肤融合的理念著称，核心产品线涵盖「小黑瓶」肌底液（含活性酵母精粹）、菁纯系列（玻色因抗老面霜/眼霜）、兰蔻口红（如196朱砂橘经典色）等明星单品，专注奢宠护肤与精致彩妆，传承奢华优雅的法式美容美学，是全球高端美妆领域的标杆品牌。</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>INTER MILAN: Legendary Italian football club since 1908, known as Nerazzurri. Features iconic blue-black stripe jerseys, official kits, training gear &amp; merchandise. Classic sports style embodying century-old passion &amp; glory.</t>
+          <t>Lancôme: French luxury beauty brand since 1935, merging elegance with science. Features Advanced Génifique Serum, Absolue anti-aging creams, and L'Absolu Rouge lipstick.</t>
         </is>
       </c>
     </row>
     <row r="123" ht="25.5" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jbl</t>
+          <t>liverpool</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>JBL: JBL是全球领先的音频设备品牌，提供专业级耳机、音箱和音响系统。JBL产品以卓越音质、耐用设计和创新技术著称，适用于家庭娱乐、户外活动和专业舞台演出。探索JBL的高品质音频解决方案，享受沉浸式听觉体验。</t>
+          <t>Liverpool: 1892年成立于英国的英超传奇足球俱乐部，绰号“红军”，主场为全球知名的安菲尔德球场。作为英格兰顶级联赛夺冠次数最多的球队之一，曾6次捧起欧冠冠军奖杯，以“永不独行（You'll Never Walk Alone）”的精神内核与热血攻势足球闻名，标志性红色战袍、队徽上的利物鸟元素深入人心，是全球亿万球迷追捧的足球文化符号。</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>JBL: World's leading audio brand for professional headphones, speakers &amp; sound systems. Superior sound, durable design &amp; innovative tech for home, outdoor &amp; stage.</t>
+          <t>Liverpool: Founded 1892, legendary Premier League club 'The Reds' at Anfield. 6-time Champions League winner, anthem 'You'll Never Walk Alone', attacking football, iconic red kits with Liverbird emblem.</t>
         </is>
       </c>
     </row>
     <row r="124" ht="25.5" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>JOSH ALLEN BUFFALO BILLS</t>
+          <t>Loewe</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>josh-allen-buffalo-bills</t>
+          <t>loewe</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>JOSH ALLEN BUFFALO BILLS: 美国职业橄榄球联盟NFL布法罗比尔队明星四分卫，以强大臂力、动态跑动和关键比赛表现闻名，代表坚韧拼搏的球队精神，深受球迷喜爱。</t>
+          <t>Loewe: 1846年由Enrique Loewe Roessberg创立于西班牙马德里的百年奢侈品牌，以精湛皮革工艺为根基，产品线覆盖高端皮具、高级时装、配饰、香水及家居系列，坚持传统手工艺与现代极简设计的融合，标志性Anagram字母交织logo辨识度极高，Puzzle几何包、Hammock吊床包等经典款成为全球奢华单品代表，诠释“实用美学”的品牌理念，是西班牙工艺与先锋设计结合的标杆品牌。</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>JOSH ALLEN BUFFALO BILLS: NFL star QB known for powerful arm, dynamic rushing, and clutch plays, embodying relentless resilience and team spirit.</t>
+          <t>Loewe: Founded 1846 Madrid, luxury Spanish leather house fusing craftsmanship with minimalist design. Iconic Anagram logo, signature Puzzle &amp; Hammock bags embody practical elegance.</t>
         </is>
       </c>
     </row>
     <row r="125" ht="25.5" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>JUICY COUTURE</t>
+          <t>Louis Vuitton</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>juicy-couture</t>
+          <t>louis-vuitton</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>JUICY COUTURE: 1997年由Pamela Skaist-Levy和Gwynneth Truelove创立的美国时尚品牌，以奢华运动风和标志性丝绒运动服闻名，经典产品包括饰有珠宝细节的套装和手袋，采用柔软丝绒、天鹅绒和闪亮材质，工艺精致，风格甜美叛逆而充满女性魅力。</t>
+          <t>Louis Vuitton: 1854年由路易·威登（Louis Vuitton）在法国巴黎创立的全球顶级奢华品牌，以精湛手工工艺、标志性Monogram帆布与Damier棋盘格图案为核心识别，产品线覆盖高端皮具、时装、配饰、旅行硬箱、腕表及香水等领域，经典单品如Speedy手袋、Neverfull托特包、Alma包与百年历史的旅行箱系列，传承“旅行的艺术”品牌精神，融合传统匠艺与现代设计，是奢华品质、时尚品味与文化传承的象征，长期占据全球奢侈品市场领导地位，深受高端消费者与时尚爱好者追捧。</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>JUICY COUTURE: American luxury sportswear brand since 1997, iconic velour tracksuits, jeweled details, soft velour &amp; shiny materials, chic craft, sweet rebellious feminine style.</t>
+          <t>Louis Vuitton: Founded in Paris, France in 1854 by Louis Vuitton, a top global luxury brand with exquisite craftsmanship, iconic Monogram canvas &amp; Damier check. Product lines cover high-end leather goods, fashion, accessories, travel trunks, watches &amp; perfumes. Classic items: Speedy handbag, Neverfull tote, Alma bag &amp; century-old trunks. Inherits "art of travel" spirit, blends traditional craft &amp; modern design. Symbol of luxury, style &amp; heritage, leading global luxury market, favored by high-end consumers &amp; fashion lovers.</t>
         </is>
       </c>
     </row>
     <row r="126" ht="25.5" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>JUVENTUS</t>
+          <t>Lululemon</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>JUVENTUS: 1897年成立的意大利都灵足球俱乐部，全球知名体育品牌，产品系列包括官方球衣、训练装备及休闲服饰，经典款有黑白条纹主场球衣，采用高性能透气材质，工艺精湛，功能运动防护，风格经典与时尚融合。</t>
+          <t>Lululemon: 1998年创立于加拿大的高端运动服饰品牌，专注瑜伽、健身及日常运动场景，以Luon、Nulu等创新功能性面料、人体工学剪裁及舒适与时尚兼具的设计为核心优势，核心产品涵盖瑜伽裤、运动BRA、训练上衣等，致力于为注重运动体验与生活方式的人群提供高品质装备，传递“热汗联结生活”的品牌理念，是全球运动服饰领域兼具功能性与潮流感的代表品牌。</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>JUVENTUS: Founded 1897, iconic Italian football club. Performance apparel including official jerseys, training gear, and casual wear. Classic black &amp; white stripes with breathable tech.</t>
+          <t>Lululemon: Premium Canadian athletic apparel since 1998, specializing in yoga, fitness, and daily wear with innovative Luon, Nulu fabrics, ergonomic designs for comfort, style, and sweat life philosophy.</t>
         </is>
       </c>
     </row>
     <row r="127" ht="25.5" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>KANYE</t>
+          <t>Maison Francis Kurkdjian</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>kanye</t>
+          <t>maison-francis-kurkdjian</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>KANYE:</t>
+          <t>Maison Francis Kurkdjian: 2009年由弗朗西斯·库尔吉安创立，法国奢侈香水品牌，产品系列包括香水、香氛蜡烛、身体护理等，经典产品有Baccarat Rouge 540和Aqua Universalis，采用天然香精和珍贵原料，工艺精湛，风格现代优雅。</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>DESTROY LONELY: Avant-garde experimental artist merging hip-hop with alternative, psychedelic, and emotionally deep innovative music.</t>
+          <t>Maison Francis Kurkdjian: French luxury perfume brand founded by Francis Kurkdjian in 2009, offering fragrances, scented candles, body care, etc. Classic products: Baccarat Rouge 540 &amp; Aqua Universalis. Uses natural essences, precious ingredients, exquisite craftsmanship, modern elegant style.</t>
         </is>
       </c>
     </row>
     <row r="128" ht="25.5" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>KID CUDI</t>
+          <t>Maison Margiela</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>kid-cudi</t>
+          <t>maison-margiela</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>KID CUDI: 美国音乐人与时尚先锋Kid Cudi创立的创意品牌，融合街头文化与音乐艺术，推出限量版服饰、联名鞋款及配饰系列，以大胆图案、舒适面料和前卫设计著称，风格叛逆不羁且极具个性表达力。</t>
+          <t>Maison Margiela: 1988年由比利时设计师Martin Margiela创立的法国小众奢侈品牌，以解构主义、无性别主义设计为核心风格，标志性元素包括Tabi分趾鞋、白色标签、回收材料重构设计，产品涵盖高级成衣、鞋履、配饰及美妆，凭借打破传统时尚边界的先锋美学，成为全球时尚爱好者关注的实验性时尚代表品牌。</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>KID CUDI: Creative brand by musician Kid Cudi, merging street culture with music art. Limited apparel, collab sneakers &amp; accessories. Bold graphics, comfortable fabrics &amp; avant-garde designs.</t>
+          <t>Maison Margiela: French avant-garde luxury brand founded 1988 by Martin Margiela. Deconstruction, gender-neutral designs with iconic Tabi shoes, white labels, upcycled materials. Haute couture, footwear, accessories, beauty. Experimental fashion pioneer.</t>
         </is>
       </c>
     </row>
     <row r="129" ht="25.5" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>LACOSTE</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>lacoste</t>
+          <t>manchester-city</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>LACOSTE: 探索LACOSTE品牌的标志性马球衫和时尚服饰系列。自1933年创立以来，LACOSTE以其法式优雅风格、卓越品质和运动精神享誉全球。品牌提供高端休闲服装、鞋履、配饰及香水，融合经典设计与现代潮流，适合日常穿着和特殊场合。通过LACOSTE官方商城，选购正品服装，享受便捷的跨境购物体验，全球配送。</t>
+          <t>Manchester City: 英格兰职业足球俱乐部（全称曼彻斯特城足球俱乐部），1880年创立于曼彻斯特，1894年正式定名，主场为伊蒂哈德球场，现征战英超联赛。以攻势足球与高压控球战术著称，近年在瓜迪奥拉执教下斩获英超冠军、足总杯、联赛杯及2022-23赛季欧冠冠军等多项荣誉，昵称“蓝月亮”，是全球最具影响力的足球俱乐部之一，拥有亿万热情球迷与高辨识度的蓝色品牌文化。</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LACOSTE: Since 1933, iconic polo shirts &amp; French elegance. Premium casual wear, footwear, accessories &amp; fragrances. Classic &amp; modern styles. Global shipping.</t>
+          <t>Manchester City: Professional English football club (full name Manchester City Football Club), founded in Manchester 1880, officially named 1894. Home to Etihad Stadium, now competing in the Premier League. Known for attacking football &amp; high-press possession tactics. Under Guardiola, won Premier League, FA Cup, League Cup &amp; 2022-23 Champions League. Nicknamed "Blue Moon", one of the world’s most influential clubs with millions of fans &amp; recognizable blue brand culture.</t>
         </is>
       </c>
     </row>
     <row r="130" ht="25.5" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Lego</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>lego</t>
+          <t>manchester-united</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Lego：乐高是备受全球家庭喜爱的创意拼搭玩具品牌，提供丰富多样的积木套装、教育产品和数字互动体验，激发儿童与成人的想象力与创造力。乐高玩具以高品质、安全性和持久性著称，涵盖星球大战、哈利·波特等热门主题，适合作为礼物或家庭活动选择。通过乐高教育解决方案，还能培养孩子的STEM技能与逻辑思维能力。</t>
+          <t>Manchester United: 英格兰传奇足球俱乐部，1878年创立于曼彻斯特，累计斩获20次英格兰顶级联赛冠军、3次欧洲冠军联赛冠军等重磅荣誉，以“红魔”绰号享誉全球，主场为标志性的老特拉福德球场，拥有超5亿全球球迷，是英超及世界足坛最具影响力的俱乐部之一。</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Lego: LEGO creative building toys inspire imagination for kids &amp; adults. Popular themes like Star Wars, Harry Potter. High-quality, safe, durable. STEM education. Perfect gift.</t>
+          <t>Manchester United: Legendary English football club founded 1878, 20 league titles, 3 Champions League wins, known as Red Devils, home at Old Trafford, over 500M fans, top influencer in Premier League and world football.</t>
         </is>
       </c>
     </row>
     <row r="131" ht="25.5" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>LANCÔME</t>
+          <t>Marshall</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>lancme</t>
+          <t>marshall</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>LANCÔME: 1935年由阿曼达·珀蒂让创立的法国奢侈美妆品牌，以高端护肤、香水和彩妆产品闻名，经典产品包括菁纯面霜和La Vie Est Belle香水，采用先进科技成分，工艺精致，功效卓越，风格优雅奢华。</t>
+          <t>Marshall 由Jim Marshall于1962 年在英国伦敦创立，总部位于米尔顿凯恩斯。主营专业吉他音箱、耳机与蓝牙音箱，标志性产品为 JTM45、Plexi 系列。风格是摇滚标志性音效与复古工业设计，材质以实木箱体、金属格栅、优质发声单元为核心，风靡全球音乐圈，是摇滚与流行音乐领域的传奇音频品牌。</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LANCÔME: French luxury beauty since 1935. High-end skincare, fragrance &amp; makeup. Advanced science, exquisite craftsmanship. Iconic Absolu Cream &amp; La Vie Est Belle. Elegant, luxurious.</t>
+          <t>Marshall: Founded 1962 London by Jim Marshall, legendary audio brand for rock and pop music. Specializes in guitar amps, headphones, Bluetooth speakers with iconic rock sound and vintage industrial design. Iconic products: JTM45, Plexi series.</t>
         </is>
       </c>
     </row>
     <row r="132" ht="25.5" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>LIVERPOOL</t>
+          <t>Margiela</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>liverpool</t>
+          <t>margiela</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LIVERPOOL: 成立于1892年的英国经典足球俱乐部和时尚品牌，以标志性的红色球衣和鹰徽闻名，产品系列包括球迷服装、训练装备和街头潮流服饰，经典产品有主场球衣和复古夹克，采用透气科技面料和棉质材质，工艺精湛，功能舒适耐用，风格融合运动传统与现代街头潮流。</t>
+          <t>Margiela: 1988年由Martin Margiela创立的比利时先锋时尚品牌，以解构主义设计与反传统美学为核心，标志性数字编号系列（如10号线成衣、6号线配件）、做旧工艺及“匿名性”理念贯穿品牌，常用再生面料、做旧皮革等材质，风格极简先锋且富有实验性，为追求独特设计感的时尚爱好者打造兼具艺术性与实用性的服饰、配饰，是全球先锋时尚领域的代表性品牌。</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LIVERPOOL FC: Iconic 1892 football club &amp; fashion brand. Legendary red kits &amp; eagle crest. Matchday wear, training gear, streetwear. Classic jerseys, retro jackets. Breathable tech fabrics, premium cotton. Blends sports heritage with modern street style.</t>
+          <t>Margiela: Belgian avant-garde fashion brand since 1988, known for deconstruction, numbered collections, vintage crafts, anonymity, sustainable materials, and minimalist experimental designs.</t>
         </is>
       </c>
     </row>
     <row r="133" ht="25.5" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>LOEWE</t>
+          <t>MCM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>loewe</t>
+          <t>mcm</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LOEWE: 西班牙奢侈品牌LOEWE罗意威1846年创立于马德里，以精湛皮革工艺与现代设计美学闻名。品牌经典产品包括Puzzle手袋、Flamenco包及标志性Logo围巾，采用顶级小牛皮、柔软纳帕革及奢华麂皮材质。LOEWE融合传统手工艺与当代艺术元素，呈现简约优雅、低调奢华的时尚风格，备受全球品味人士推崇。</t>
+          <t>MCM（Modern Creation München）由Michael Cromer于1976 年在德国慕尼黑创立，主营皮具、背包、手袋、鞋履与配饰，标志性产品为 Visetos 老花系列背包。设计师 Michael Michalsky 主导复兴，风格融合德式精工与街头潮流，以干邑色皮革、月桂叶标志及钻石纹为特色，采用优质皮革、帆布与五金配件，风靡全球，尤其在亚洲、欧美地区深受时尚爱好者与明星青睐。</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LOEWE: Spanish luxury brand since 1846, renowned for exquisite leather craftsmanship, modern design, Puzzle bag, Flamenco pouch, and iconic logo scarves in premium calfskin, napa, and suede.</t>
+          <t>MCM (Modern Creation München): Founded by Michael Cromer in Munich, Germany (1976), specializing in leather goods, backpacks, handbags, footwear &amp; accessories. Signature Visetos monogram backpack. Revived by Michael Michalsky, blending German craftsmanship with streetwear, featuring cognac leather, laurel leaf logo, diamond pattern, premium materials. Popular globally, loved by fashion lovers &amp; celebrities in Asia, Europe, America.</t>
         </is>
       </c>
     </row>
     <row r="134" ht="25.5" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>LOUIS VUITTON</t>
+          <t>Melissabow</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>louis-vuitton</t>
+          <t>melissabow</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>LOUIS VUITTON: 探索路易威登奢华皮具、时尚配饰与旅行艺术的标志性世界。品牌提供经典手袋、行李箱、时装与鞋履系列，融合精湛工艺与永恒设计，重新定义现代奢侈品体验。</t>
+          <t>Melissa（常称 Melissabow 蝴蝶结系列）由 Alexandre 与 Pedro Grendene 于 1979 年在巴西创立，隶属 Grendene 集团。主营女士及童鞋，标志性为蝴蝶结果冻鞋与 Aranha 系列，创意总监 Edson Matsuo 主导设计，与 Vivienne Westwood、Jason Wu 等跨界合作。风格缤纷俏皮、时尚环保，采用专利 MELFLEX™可回收 PVC 材质，自带泡泡糖香气，风靡全球 80 余国，尤其受亚洲与欧美时尚女性及儿童喜爱。</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LOUIS VUITTON: Since 1854 Paris, luxury trunks, bags, accessories &amp; ready-to-wear. Iconic Monogram, exquisite craftsmanship &amp; innovation in travel &amp; fashion.</t>
+          <t>Melissabow: Brazilian brand since 1979, Grendene Group. Women's &amp; kids' shoes: iconic butterfly bow jelly &amp; Aranha series. Designs by Edson Matsuo, collabs like Vivienne Westwood. Colorful, eco-friendly MELFLEX™ recyclable PVC with bubblegum scent. Popular in 80+ countries.</t>
         </is>
       </c>
     </row>
     <row r="135" ht="25.5" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Lululemon</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>miami</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Lululemon（露露乐蒙）1998 年创立于加拿大温哥华，是全球高端瑜伽运动服饰标杆品牌。品牌专注瑜伽、跑步、训练及日常通勤全场景，以亲肤裸感科技面料、人体工学剪裁与简约轻奢设计为核心，传递热汗生活方式，打造兼具功能性、舒适度与时尚感的运动休闲单品，深受全球运动爱好者与都市人群青睐。</t>
+          <t>Miami（迈阿密服饰）由Christian Noa创立，总部位于美国迈阿密。主营奢侈街头服饰，包括 oversized 印花 T 恤、时尚尼龙裤及配饰。Christian Noa 亲自主导设计，融合迈阿密活力街头文化与纽约时尚能量，风格大胆鲜艳、充满热带风情，采用优质纯棉、尼龙及金属配件，风靡北美、欧洲及南美，深受潮流爱好者追捧。</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Lululemon, founded in Vancouver, Canada in 1998, is a leading global premium yoga athletic apparel brand. It caters to yoga, running, training and daily commuting, featuring skin-friendly tech fabrics, ergonomic tailoring and minimalist luxury design. Promoting a sweaty lifestyle, it offers functional, comfortable and stylish athleisure loved by global consumers.</t>
+          <t>Miami: Christian Noa's luxury streetwear from Miami. Oversized graphic tees, nylon pants, accessories. Bold tropical styles blend Miami street culture with NYC fashion. Premium cotton, nylon, metal. Popular in NA, EU, SA for trendsetters.</t>
         </is>
       </c>
     </row>
     <row r="136" ht="25.5" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MAISON FRANCIS KURKDJIAN</t>
+          <t>Mitchell</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>maison-francis-kurkdjian</t>
+          <t>mitchell</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MAISON FRANCIS KURKDJIAN: 创立于2009年的法国高端香水品牌，由调香师Francis Kurkdjian与Marc Chaya共同创办。以精湛工艺、稀有香材和艺术灵感著称，经典产品包括Baccarat Rouge 540和À la rose系列，风格奢华现代，传递法式优雅与永恒魅力。</t>
+          <t>Mitchell（Mitchell &amp; Ness）由Frank P. Mitchell与Charles M. Ness于1904 年在美国费城创立，主营复古球衣、球帽及运动服饰，获 NBA、NFL 等四大联赛官方授权。标志性产品为经典复刻球衣，风格忠于历史细节，主打美式复古运动风，采用优质羊毛、法兰绒与纯棉材质，高度还原原版质感，风靡全球，尤其受北美、欧洲及亚洲体育爱好者与潮流人士追捧。</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>MAISON FRANCIS KURKDJIAN: French luxury perfume house since 2009. Master perfumer Francis Kurkdjian creates elegant, modern scents with rare ingredients like Baccarat Rouge 540 &amp; À la rose.</t>
+          <t>Mitchell &amp; Ness: Official NBA NFL licensed vintage sportswear since 1904, classic reprint jerseys with authentic details, American retro style, high-quality materials, popular worldwide.</t>
         </is>
       </c>
     </row>
     <row r="137" ht="25.5" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MAISON MARGIELA</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>maison-margiela</t>
+          <t>mlb</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MAISON MARGIELA: Maison Margiela 是一家先锋奢侈时装品牌，由设计师 Martin Margiela 于1988年在巴黎创立，以其解构主义设计、匿名文化、标志性分趾鞋和白色标签而闻名，提供男女成衣、配饰、香氛和高级定制系列，重新定义现代时尚美学与工艺创新。</t>
+          <t>MLB 由韩国 F&amp;F 集团于1997 年 6 月创立，获美国职业棒球大联盟官方授权。主营男女服饰、鞋履、棒球帽及配饰，标志性为 NY/LA 队标帽款，韩国潮流设计团队主导，融合美式棒球文化与韩式高街风格，以夸张 Logo、宽松剪裁为特色，采用优质纯棉、聚酯纤维与牛仔布等材质，风靡全球，尤其在亚洲、欧美深受年轻人与明星青睐，被誉为 “亚洲时尚风向标”。</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>MAISON MARGIELA: Maison Margiela, avant-garde Parisian luxury fashion house since 1988, renowned for deconstructed designs, anonymity, iconic Tabi boots, and white labels. Redefining modern aesthetics with innovative craftsmanship.</t>
+          <t>MLB: Licensed MLB brand by Korea's F&amp;F since 1997. Apparel, shoes, caps, accessories with NY/LA logos. Korean design fuses baseball and high-street style, bold logos, loose cuts. Premium materials. Global trend, youth &amp; celeb favorite.</t>
         </is>
       </c>
     </row>
     <row r="138" ht="25.5" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MANCHESTER CITY</t>
+          <t>Moncler</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>manchester-city</t>
+          <t>moncler</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MANCHESTER CITY: 曼彻斯特城足球俱乐部是英超联赛的顶级足球俱乐部，以其卓越的球场表现和先进的训练设施闻名，提供官方正品球衣、训练装备及粉丝周边商品，融合高性能科技面料与经典设计，风格现代专业，满足全球球迷与运动爱好者的需求。</t>
+          <t>Moncler: 1952年成立于法国，是世界知名的奢侈时尚品牌，专精于高端羽绒服和冬季服装。产品线涵盖外套、成衣及配饰，选用顶级羽绒和材料，结合卓越工艺与时尚设计，风格奢华、功能性强，深受全球消费者喜爱，是冬季保暖与时尚的象征。</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>MANCHESTER CITY: Premier League top football club, renowned for卓越performance &amp; advanced training facilities. Official jerseys, training gear &amp; fan merchandise with high-tech fabrics &amp; classic modern design.</t>
+          <t>Moncler: Founded in France in 1952, a renowned luxury fashion brand specializing in high-end down jackets &amp; winter apparel. Product lines: outerwear, ready-to-wear, accessories, using premium down &amp; materials, combining exquisite craftsmanship with stylish design. Luxurious, functional, beloved globally, symbolizing winter warmth &amp; fashion.</t>
         </is>
       </c>
     </row>
     <row r="139" ht="25.5" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MANCHESTER UNITED</t>
+          <t>Montblanc</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>manchester-united</t>
+          <t>montblanc</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MANCHESTER UNITED: 1878年成立于英国曼彻斯特的传奇足球俱乐部，以红色球衣和白色细节为标志性配色，采用高性能透气材质与先进工艺制作球衣及周边产品，功能专业舒适，风格经典运动，代表商品为主场球衣和复古训练服，深受全球球迷喜爱。</t>
+          <t>Montblanc: 1906年创立于德国的高端奢华品牌，以经典书写工具为核心，延伸至腕表、皮具、珠宝等领域。标志性Meisterstück（大班系列）书写工具采用天然树脂搭配黄金/铂金配件，六角白星logo象征卓越工艺与永恒设计，致力于为追求品质生活的人士打造兼具实用价值与收藏意义的精品，是全球高端生活方式的经典代表之一。</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>MANCHESTER UNITED: Founded 1878 UK, legendary football club. Iconic red/white kits. High-performance breathable gear &amp; retro training wear. Professional comfort, classic style. Global fan favorite.</t>
+          <t>Montblanc: Established 1906 in Germany. Luxury brand renowned for premium writing instruments, watches, leather, &amp; jewelry. Iconic Meisterstück series &amp; white six-pointed star symbolize exceptional craftsmanship, timeless design, &amp; a global luxury lifestyle.</t>
         </is>
       </c>
     </row>
     <row r="140" ht="25.5" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Marshall</t>
+          <t>Moose Knuckles</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>marshall</t>
+          <t>moose-knuckles</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Marshall（马歇尔）1962 年创立于英国伦敦，是全球标志性摇滚音响品牌，由专业吉他音箱起家，承载英伦摇滚文化基因。品牌覆盖蓝牙便携音箱、头戴式耳机、家用音响等全品类音频设备，以经典复古外观、标志性摇滚音质与精湛工艺为核心，兼具颜值与声学实力，是摇滚爱好者与潮流用户的首选音频品牌。</t>
+          <t>Moose Knuckles: 源自加拿大的高端户外服饰品牌，以专业保暖派克大衣（Parka）为核心招牌，将时尚设计与强功能性深度融合，采用防水防风科技面料、奢华狐狸毛领及高保暖填充材质，为户外爱好者与城市通勤人群打造兼具抗寒性能与造型质感的冬季服饰，产品线覆盖派克大衣、羽绒服等核心品类，凭借精湛工艺与标志性风格成为全球冬季高端户外服饰的代表性品牌之一。</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Founded in London, UK in 1962, Marshall is an iconic global rock audio brand. Starting with professional guitar amplifiers, it carries British rock culture. Offering Bluetooth speakers, headphones and home audio, it features vintage design, signature rock sound and craftsmanship, ideal for rock fans and trendsetters.</t>
+          <t>Moose Knuckles: Canadian high-end outdoor apparel brand specializing in premium insulated parkas. Blends stylish design with robust functionality—waterproof/windproof tech fabrics, luxury fox fur trims, high-insulation fills. For outdoor enthusiasts &amp; urban commuters, delivering cold-resistant performance. Product line: parkas, down jackets. Renowned for exquisite craftsmanship, iconic style—leading global premium winter outdoor brand.</t>
         </is>
       </c>
     </row>
     <row r="141" ht="25.5" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MARGIELA</t>
+          <t>Miu Miu</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>margiela</t>
+          <t>miu miu</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>English Brand Description（≤200 字符）</t>
+          <t>Miu Miu: 1993年由Prada推出的年轻副线品牌，聚焦“少女感与高级感平衡”的设计风格，以Matelassé绗缝皮革、褶皱元素、水晶装饰及糖果色为主打标识，产品覆盖成衣、手袋、鞋履、配饰与香水，经典款如Miu Belle绗缝手袋、复古玛丽珍鞋，精准契合年轻群体对“甜酷摩登”的时尚需求，是全球潮流圈兼具个性与质感的代表性轻奢品牌。</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>MARGIELAMARGIELA: Maison Margiela, French luxury brand since 1988. Known for avant-garde deconstructed designs, Tabi boots, white paint, and upcycled garments with innovative materials.</t>
+          <t>Miu Miu: Prada’s youthful line launched in 1993, balancing girlish charm &amp; sophistication. Signature Matelassé quilted leather, ruching, crystal accents &amp; candy hues. Offers ready-to-wear, handbags, footwear, accessories, fragrances. Iconic Miu Belle bag &amp; vintage Mary Janes, catering to Gen Z’s sweet-cool modernity, a global accessible luxury standout.</t>
         </is>
       </c>
     </row>
     <row r="142" ht="25.5" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MCM</t>
+          <t>Moschino</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>mcm</t>
-        </is>
-      </c>
-      <c r="C142"/>
+          <t>moschino</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Moschino: 1983年由Franco Moschino创立于意大利的奢侈品牌，以幽默玩趣、反时尚的先锋风格著称，标志性元素含小熊图案、卡通印花与醒目Logo，产品覆盖成衣、手袋、鞋履、香水及童装等，融合奢华质感与潮流创意，是追求个性表达的年轻时尚群体钟爱的品牌。</t>
+        </is>
+      </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>MCM is a German luxury fashion brand renowned for premium leather goods, signature monogram backpacks and travel accessories. It blends exquisite craftsmanship with modern urban style, crafting durable, stylish luxury pieces loved by global fashion enthusiasts.</t>
+          <t>Moschino: Italian luxury brand founded in 1983 by Franco Moschino, featuring humorous, playful anti-fashion avant-garde style. Iconic elements: teddy bear, cartoon prints, bold logo. Products include ready-to-wear, handbags, footwear, perfume, kids’ wear, blending luxury texture with trendy creativity, favored by individuality-pursuing young fashion lovers.</t>
         </is>
       </c>
     </row>
     <row r="143" ht="25.5" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MELISSABOW</t>
+          <t>Moose Knuckles</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>melissabow</t>
-        </is>
-      </c>
-      <c r="C143"/>
-      <c r="D143"/>
+          <t>moose knuckles</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Moose Knuckles: 加拿大高端户外服饰品牌，以「专业保暖+潮流设计」为核心标签，主打经典派克大衣、高品质羽绒服等冬季单品，采用优质羽绒填充、防水防风科技面料，搭配标志性金属logo与毛领设计，兼顾零下环境的强功能性与都市穿搭的时尚感，是全球消费者冬季追求「暖而不臃肿、潮而实用」的户外服饰首选品牌。</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Moose Knuckles: Canadian luxury outdoor brand for professional warmth &amp; fashion. Features parkas, down jackets with premium down, waterproof tech, signature logo &amp; fur trim. Combines sub-zero function with urban style. Top choice for warm, slim, practical winter wear.</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="25.5" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>Maison Margiela</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>miami</t>
+          <t>Maison Margiela</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MIAMI: 迈阿密时尚品牌源于美国海滨都市灵感，专注设计度假风女装与配饰，采用透气棉麻材质与鲜明印花工艺，打造轻盈舒适的沙滩裙、遮阳帽及休闲单品，风格热情奔放，展现热带度假美学。</t>
+          <t>Maison Margiela: 1988年由比利时设计师马丁·马吉拉创立的解构主义时尚先锋品牌，以匿名设计、白色标签标识、打破常规的解构美学与男女无差别设计为核心特色，产品线覆盖高级成衣、鞋履、配饰及香水等领域，经典产品包括标志性Tabi分趾鞋、Replica系列复刻香水及解构主义成衣，凭借颠覆传统的设计语言在全球时尚界备受瞩目，深受追求独特风格的消费者喜爱。</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>MIAMIMIAMI: Miami-inspired resort wear brand. Breathable linen &amp; cotton, vibrant prints. Lightweight dresses, sun hats &amp; casual pieces. Tropical vacation aesthetic.</t>
+          <t>Maison Margiela: Founded by Belgian designer Martin Margiela in 1988, an avant-garde deconstructivist fashion brand with anonymous design, white label, unconventional deconstructed aesthetics &amp; gender-neutral styles. Product lines: luxury ready-to-wear, footwear, accessories, fragrances. Classics: iconic Tabi split-toe shoes, Replica series fragrances, deconstructed apparel. Noted globally for subversive design, loved by unique style seekers.</t>
         </is>
       </c>
     </row>
     <row r="145" ht="25.5" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MITCHELL</t>
+          <t>Mizuno</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>mitchell</t>
+          <t>mizuno</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MITCHELL（Mitchell &amp; Ness）1904 年创立于美国费城，是全球标杆级复古体育服饰品牌。品牌拥有 NBA、MLB、NFL 等职业联盟正版授权，专注高精度复刻经典复古球衣、运动帽与潮流单品，以还原元年细节、精湛工艺与美式复古街头风格为核心，兼具收藏价值与日常穿搭性，深受全球球迷与潮流爱好者青睐。</t>
+          <t>Mizuno: 1906年由水野利八创立于日本的专业运动品牌，专注跑步、高尔夫、棒球、排球等运动领域装备研发，以Wave缓震技术、Dynamotion Fit动态贴合等核心科技为支撑，产品兼顾专业竞技性能与人体工学贴合度，服务全球专业运动员及运动爱好者，是融合运动科技与耐用品质的经典运动品牌代表。</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>MITCHELL (Mitchell &amp; Ness) is a leading global vintage sportswear brand founded in Philadelphia, USA in 1904. It holds official licenses of NBA, MLB, NFL and other sports leagues, focusing on authentic retro jerseys, hats and apparel. With original details, fine craftsmanship and American retro street style, it provides collectible and wearable pieces for fans and fashion lovers worldwide.</t>
+          <t>Mizuno: Japanese sports brand since 1906, specializing in running, golf, baseball, volleyball gear with Wave cushioning &amp; Dynamotion Fit tech for professional performance &amp; ergonomic fit, serving athletes worldwide.</t>
         </is>
       </c>
     </row>
     <row r="146" ht="25.5" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>Narciso Rodriguez</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>mlb</t>
+          <t>narciso-rodriguez</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MLB 是 1997 年由韩国 F&amp;F 潮流集团获美国职业棒球大联盟正版授权创立的街头生活运动品牌。品牌融合美式棒球文化与韩系潮流设计，以经典 NY、LA 队标及老花 Monogram 为标志性元素，覆盖服饰、鞋履、帽款、包袋等全品类，兼顾潮流感与日常实穿性，风靡全球年轻群体，是亚洲棒球风轻奢潮流标杆。</t>
+          <t>Narciso Rodriguez: 由同名美国设计师创立的高端时尚品牌，以极简优雅的风格著称，核心覆盖高级成衣、香水及配饰领域。经典产品包括全球畅销的For Her系列香水（温暖木质香调诠释女性柔媚），成衣设计强调流畅线条与优质材质（如丝绸、羊毛）的融合，兼顾红毯气场与日常实穿性，是现代女性追求精致质感的高端之选，深受时尚界与消费者青睐。</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>MLB is a street lifestyle sportswear brand founded in 1997 by South Korea’s F&amp;F Group under official license from Major League Baseball. Blending American baseball culture and K-fashion, it features iconic NY/LA logos and Monogram patterns. Offering apparel, shoes, hats and bags, it combines trend and wearability, popular worldwide as a top baseball-inspired luxury street brand.</t>
+          <t>Narciso Rodriguez: Luxury fashion brand by American designer, famed for minimalist elegance. Core: high-end ready-to-wear, fragrances (bestselling For Her with warm woody notes for feminine charm) &amp; accessories. Ready-to-wear blends fluid lines with premium fabrics (silk, wool), balancing red carpet allure &amp; daily wearability—ideal for modern women seeking refined quality, favored by fashion circles &amp; consumers.</t>
         </is>
       </c>
     </row>
     <row r="147" ht="25.5" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MONCLER</t>
+          <t>Neighborhood</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>moncler</t>
+          <t>neighborhood</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MONCLER: Moncler 是奢华户外服饰的标杆品牌，以其高端羽绒服和时尚设计闻名全球。品牌将卓越保暖性能与意大利精致工艺相结合，打造出兼具功能性与时髦感的标志性外套。Moncler 的产品系列涵盖羽绒夹克、派克大衣及奢华配饰，专为追求高端生活方式与户外探险的消费者而设计。探索 Moncler 的旗舰系列，体验融合创新技术与奢华材质的永恒经典单品。</t>
+          <t>Neighborhood（NBHD）由日本设计师泷泽伸介 (Shinsuke Takizawa)于1994 年在东京原宿创立，主打街头潮流服饰。标志性产品为冈山赤耳丹宁裤、机车夹克与军事工装，创始人亲任创意总监，以Craft with Pride为理念，风格硬核写实、重质感细节，融合机车、军事与美式工装元素，采用顶级丹宁、优质皮革及纯棉材质，风靡全球，尤其受亚洲、欧美街头文化爱好者与 “养牛” 圈追捧。</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Moncler: Luxury outdoor apparel brand renowned for high-end down jackets &amp; fashion designs combining Italian craftsmanship, functionality, and style for exploration.</t>
+          <t>Neighborhood(NBHD): Japanese streetwear brand since 1994 by Shinsuke Takizawa. Craft with Pride philosophy, premium denim, biker jackets, military workwear. Hardcore styles with motorcycle, military, American elements. Top-quality materials, global street culture favorite.</t>
         </is>
       </c>
     </row>
     <row r="148" ht="25.5" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MONTBLANC</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>montblanc</t>
+          <t>new-balance</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MONTBLANC: 万宝龙书写工具与奢华皮具品牌，以其标志性六角白星标志闻名全球。作为高级钢笔、腕表、皮具及配饰的代名词，品牌融合精湛德国工艺与经典设计，为追求卓越品质与永恒品味的顾客提供尊崇体验。无论是签名书写、商务馈赠还是个人收藏，万宝龙作品皆象征着成就、传承与非凡格调。</t>
+          <t>New Balance: 1906年创立于美国波士顿的专业运动品牌，以“舒适性能与经典设计共生”为理念，专注运动鞋、运动服饰及配件研发。核心产品覆盖跑步鞋、训练鞋、休闲鞋等系列，搭载ABZORB缓震、ENCAP中底、Fresh Foam轻量科技，满足跑步爱好者、健身人群及日常穿搭需求；经典574、990系列更成为“专业与潮流兼顾”的代表，是全球运动者信赖的“慢跑鞋专家”，持续传递“Made for Makers”的品牌精神。</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>MONTBLANCMONTBLANC: Premium writing instruments, luxury leather goods, watches &amp; accessories. Iconic white star symbol. German craftsmanship &amp; timeless design for achievement &amp; refined taste.</t>
+          <t>New Balance: Founded in Boston, USA in 1906, this pro sports brand focuses on sneakers, apparel &amp; accessories with "comfort + classic design" philosophy. Core products: running/training/casual shoes with ABZORB cushioning, ENCAP midsole, Fresh Foam tech for runners, fitness lovers &amp; daily wear. Classic 574/990 series (pro + fashion) are trusted "jogging shoe experts", embodying "Made for Makers" spirit.</t>
         </is>
       </c>
     </row>
     <row r="149" ht="25.5" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>MOOSE KNUCKLES</t>
+          <t>New England Patriots</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>moose-knuckles</t>
+          <t>new-england-patriots</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MOOSE KNUCKLES: 加拿大奢华羽绒服品牌，2017年创立，以标志性“小剪刀”Logo和坚固耐用的外壳面料闻名，提供兼具高性能保暖与时尚设计的派克大衣和羽绒夹克，融合优质羽绒、功能性细节和都市奢华风格。</t>
+          <t>New England Patriots: 新英格兰爱国者是NFL职业橄榄球大联盟的传奇球队，成立于1960年，主场位于马萨诸塞州福克斯堡。品牌以红、白、蓝三色和飞翼徽标闻名，拥有六次超级碗冠军辉煌历史。其官方商品涵盖高品质球衣、帽衫、帽子等粉丝装备，采用先进运动面料与印花工艺，风格经典美式，代表坚韧竞技精神与团队荣耀。</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>MOOSE KNUCKLES: Luxury Canadian down parkas &amp; jackets since 2017. Iconic scissors logo. High-performance warmth, durable shells, urban luxury style.</t>
+          <t>New England Patriots: NFL legend since 1960. 6x Super Bowl champions. Iconic red, white, blue &amp; flying Elvis logo. Premium jerseys, hoodies, hats embody classic American grit &amp; team glory.</t>
         </is>
       </c>
     </row>
     <row r="150" ht="25.5" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Miu Miu</t>
+          <t>New York Jets</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>miu miu</t>
+          <t>new-york-jets</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Miu Miu（缪缪）1993 年创立于意大利米兰，是 Prada 集团旗下高端轻奢女装品牌，由 Miuccia Prada 以个人昵称命名。品牌以叛逆少女感、复古先锋美学为核心，融合灵动剪裁与实验性设计，覆盖成衣、包袋、鞋履、配饰等全品类，主打年轻都市女性，是全球轻奢时尚标志性品牌。</t>
+          <t>New York Jets: 美国国家橄榄球联盟（NFL）的老牌职业橄榄球队，1960年成立，主场为纽约大都会人寿体育场，以经典绿白配色队服、冲击力十足的比赛风格著称，是纽约体育文化的重要符号之一，拥有庞大忠实球迷群体，赛场内外传递着美式橄榄球的热血与团队精神，是NFL东部分区极具竞争力的代表球队。</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Miu Miu is a luxury women’s fashion brand founded in Milan, Italy in 1993. As a subsidiary of Prada Group, it’s named after Miuccia Prada’s nickname. With rebellious, retro and avant-garde style, it offers ready-to-wear, bags, shoes and accessories for young urban women, becoming an iconic name in global luxury fashion.</t>
+          <t>New York Jets: Historic NFL team since 1960, based at MetLife Stadium. Iconic green-white uniforms, dynamic playstyle. NY sports symbol with loyal fans, embodying football passion and teamwork in AFC East.</t>
         </is>
       </c>
     </row>
     <row r="151" ht="25.5" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>MOSCHINO</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>moschino</t>
+          <t>new-york-yankees</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MOSCHINO: 1983年由Franco Moschino创立的意大利奢侈品牌，以大胆幽默的设计和颠覆传统的时尚风格闻名。产品系列包括成衣、手袋、配饰及香水，经典之作如泰迪熊卫衣和标志性字母图案单品。采用高档皮革、丝绸与环保面料，结合精湛工艺与鲜明色彩，风格戏谑而华丽，完美融合街头文化与高级时装美学。</t>
+          <t>New York Yankees: 美国职业棒球大联盟（MLB）标志性传奇球队，1901年创立（前身为巴尔的摩金莺队，1913年迁至纽约并定现名），隶属美国联盟东区，坐拥27次世界大赛冠军（MLB历史最多），经典条纹队服与“NY” logo是其标志性符号，深耕百年体育文化，是全球棒球迷心中的“王者之师”，以卓越战绩、深厚底蕴与广泛影响力成为美国体育的重要象征。</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>MOSCHINOMOSCHINO: Italian luxury brand since 1983, known for bold, humorous designs and avant-garde style. Features ready-to-wear, bags, accessories, and perfumes. Iconic teddy bear hoodies and signature lettering.</t>
+          <t>New York Yankees: Iconic MLB franchise since 1901; 27 World Series titles, legendary pinstripes &amp; NY logo. A century-long sports legacy &amp; global symbol of excellence.</t>
         </is>
       </c>
     </row>
     <row r="152" ht="25.5" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Moose Knuckles</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>moose knuckles</t>
+          <t>newcastle-united</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Moose Knuckles：Moose Knuckles 是源自加拿大的高端奢华羽绒服品牌，以其标志性的“小剪刀”Logo和精湛的工艺闻名。品牌将卓越的保暖性能、前卫的街头设计理念与顶级的材质相结合，打造出兼具功能性、时尚感与耐用性的外套和服饰系列，深受全球潮流人士和明星的喜爱。</t>
+          <t>Newcastle United: 1892年成立的英格兰老牌职业足球俱乐部，绰号“喜鹊”（因经典黑白队服），主场为可容纳52305人的圣詹姆斯公园球场，历史上曾获4次英格兰顶级联赛冠军、6次足总杯冠军，现征战英超联赛。球队以激情球迷文化与快速反击风格著称，2021年由沙特公共投资基金主导收购后逐步强化阵容，是英超联赛中全球球迷关注的劲旅之一，也是英格兰东北部足球文化的重要代表。</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Moose Knuckles: Luxury Canadian down jackets with iconic logo, avant-garde street style, superior warmth, premium materials, and durable fashion.</t>
+          <t>Newcastle United: Est. 1892, Magpies for black-white kits. Premier League club at St James' Park (52,305 seats). 4 top-flight titles, 6 FA Cups. Passionate fans, fast counter-attacks. Strengthened after 2021 Saudi PIF takeover. Global NE England football icon.</t>
         </is>
       </c>
     </row>
     <row r="153" ht="25.5" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Maison Margiela</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Maison Margiela</t>
+          <t>nike</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Maison Margiela：1988年由Martin Margiela创立的法国奢侈品牌，以解构主义、前卫设计和匿名理念闻名。产品系列包括服饰、鞋履、配饰和香氛，经典之作有Tabi靴、分趾鞋和Glamma手袋。采用创新面料与重组工艺，风格独特而神秘，重塑传统奢华定义。</t>
+          <t>Nike: 1972年由菲尔·奈特与比尔·鲍尔曼联合创立，美国运动品牌巨头，产品涵盖跑步鞋、篮球鞋、运动服装及装备系列，经典产品包括Air Max气垫鞋、Air Jordan系列，采用Flyknit编织、Dri-FIT科技面料等创新材质，工艺注重轻量缓震，风格融合运动性能与街头时尚。</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Maison Margiela: French luxury brand since 1988. Known for deconstruction, avant-garde design, anonymity, Tabi boots, and Glamma bag. Innovative fabrics.</t>
+          <t>Nike: American sports brand since 1972, offering running, basketball shoes, sportswear. Features Air Max, Air Jordan, Flyknit, Dri-FIT. Lightweight cushioning blends performance with street fashion.</t>
         </is>
       </c>
     </row>
     <row r="154" ht="25.5" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Mizuno</t>
+          <t>Nobis</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>mizuno</t>
+          <t>nobis</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Mizuno: 美津浓是日本专业运动装备品牌，为跑步、高尔夫、棒球、排球等运动提供高性能服装与鞋履。品牌以科技驱动设计，采用Wave缓震技术和专业面料，确保运动者获得卓越支撑与舒适体验。美津浓产品融合亚洲人体工学与精准工艺，助力运动员突破极限。全球团队运动联盟认证，为专业选手和运动爱好者提供可靠装备。探索美津浓，提升运动表现。</t>
+          <t>Nobis 由Robin Yates（前加拿大鹅副总裁）与Kevin Au-Yeung于2007 年在加拿大多伦多创立，设计师为Michael Kerr。主营高端户外功能性外套（派克大衣、羽绒服等），以极简奢华融合极致保暖性能著称，剪裁利落修身。采用顶级防水面料、高品质鸭绒填充及羊毛、尼龙等复合材质，风靡全球 35 国，深受北美、欧洲及亚洲精英与时尚人士青睐。</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Mizuno: Japanese sports gear for running, golf, baseball &amp; volleyball. Wave technology &amp; ergonomic design enhance performance. Trusted by pros globally.</t>
+          <t>Nobis: Founded in 2007 in Toronto, Canada by Robin Yates (ex-Canada Goose VP) &amp; Kevin Au-Yeung, designed by Michael Kerr. Specializes in high-end functional outerwear (parkas, down jackets) blending minimalist luxury with ultimate warmth, tailored slim fits. Uses premium waterproof fabrics, high-quality duck down, wool-nylon blends. Popular in 35 countries, favored by elites &amp; fashionistas in North America, Europe, Asia.</t>
         </is>
       </c>
     </row>
     <row r="155" ht="25.5" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>NARCISO</t>
+          <t>NOFS</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>narciso</t>
+          <t>nofs</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>NARCISO: 2003年由Narciso Rodriguez创立的法国高端香水品牌，以极简设计和感性香调闻名，经典产品包括For Her和Poudrée系列，采用珍稀香原料和玻璃瓶身，风格优雅深邃，持久留香。</t>
+          <t>NOFS（Noneofus）由Casey Backhaus与Justin Njinmah于2019 年在德国柏林创立，德国街头潮牌。标志性产品为运动套装、连帽衫及丹宁系列，创始人亲任设计，以极简主义融合大胆字母印花，线条利落、中性配色，注重德国工艺与街头文化。采用优质纯棉、重磅丹宁、聚酯纤维等材质，风靡欧洲、北美及全球 Z 世代，成为德国街头时尚新标杆。</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NARCISO NARCISO: French luxury perfume brand since 2003, known for minimalist design, sensual fragrances like For Her &amp; Poudrée, rare ingredients, elegant glass bottles, long-lasting scent.</t>
+          <t>NOFS: German streetwear from Berlin, founded 2019. Minimalist design, bold letter prints, neutral colors. Tracksuits, hoodies, denim. Premium materials. Popular in Europe, NA, Gen Z.</t>
         </is>
       </c>
     </row>
     <row r="156" ht="25.5" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>NARCISO RODRIGUEZ</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>narciso-rodriguez</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>NARCISO RODRIGUEZ: 1996年由纳西索·罗德里格斯创立的美国奢侈品牌，以其极简而感性的香水、女装和配饰闻名。经典产品包括For Her香水，采用优质原料，工艺精致，风格优雅现代，强调轮廓和永恒之美。</t>
+          <t>Number (N) INE 由日本设计师宫下贵裕于1996/1997 年在东京创立，名称源自 The Beatles《Revolution 9》。主营街头服饰、T 恤、丹宁裤与机车夹克，创始人亲任设计，融合美式复古、摇滚朋克与军事元素，风格暗黑颓废、层次丰富。采用重磅棉、顶级丹宁、优质皮革等材质，风靡全球，是日本地下与前卫时尚标杆，深受欧美潮流人士追捧。</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NARCISO RODRIGUEZ: Luxury brand since 1996, known for minimalist sensual fragrances like For Her, elegant modern womenswear &amp; accessories with exquisite craftsmanship.</t>
+          <t>Number: Founded by Japanese designer Takayuki Miyashita in Tokyo (1996/1997), named after The Beatles’ “Revolution 9”. Specializes in streetwear, tees, denim, biker jackets. Founder-led design blends American retro, rock punk, military elements—dark, decadent, layered styles. Uses heavy cotton, premium denim, quality leather. Global phenomenon, Japanese underground/avant-garde fashion icon, popular with Western fashion lovers.</t>
         </is>
       </c>
     </row>
     <row r="157" ht="25.5" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>NEIGHBORHOOD</t>
+          <t>Off White</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>neighborhood</t>
-        </is>
-      </c>
-      <c r="C157"/>
+          <t>off-white</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Off White: 由Virgil Abloh于2012年创立的美国高端街头时尚品牌，以“未完成感”解构主义设计为核心，融合街头文化与高端时尚美学，标志性元素包括引号、斜杠、箭头等工业风视觉符号。产品涵盖服装、鞋履、配饰等，经典如OW x Nike联名 sneakers系列，是连接街头潮流与高奢领域的先锋品牌，深受全球潮人、时尚爱好者及Louis Vuitton等合作方青睐。</t>
+        </is>
+      </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Apple: Founded by Steve Jobs in 1976, innovating in tech with iconic products like iPhone, Mac, and iPad. Features premium metal/glass design, powerful performance, and minimalist modern style.  
-Microsoft: Established by Bill Gates and Paul Allen in 1975, leading in software/hardware with Windows, Office, Surface. Professional, functional, and high-quality craftsmanship.  
-Amazon: Jeff Bezos founded in 1994, global e-commerce/cloud leader with Kindle, Echo, AWS. Smart, efficient, and innovative materials for seamless experiences.  
-Samsung: Founded by Lee Byung-chul in 1938, South Korean electronics giant with Galaxy, QLED TV. Advanced glass/metal tech, stylish and cutting-edge functionality.  
-Sony: Started by Akio Morita and Masaru Ibuka in 1946, Japanese electronics/entertainment with PlayStation, Xperia. Innovative, high-end materials and premium avant-garde design.  
-Adidas: Founded by Adolf Dassler in 1949, German sportswear brand with Superstar, Ultraboost. Eco-friendly materials, durable comfort, and sporty casual style.  
-Nike: Founded by Bill Bowerman and Phil Knight in 1972, American athletic brand with Air Force 1, Jordan series. High-performance innovation, crafted for trendy sportswear.  
-Google: Larry Page and Sergey Brin founded in 1998, tech company with Android, Pixel, Search. Smart, powerful, and minimalist modern design.  
-Tesla: Elon Musk founded in 2003, electric vehicles/clean energy with Model S, Cybertruck. Futuristic metal/glass tech, efficient and advanced electric performance.  
-Coca-Cola: John Pemberton created in 1886, beverage company with Coca-Cola Classic, Sprite. Refreshing traditional formula, iconic and popular classic taste.  
-INFI:</t>
+          <t>Off White: Virgil Abloh's luxury streetwear label, famed for deconstructed aesthetics, industrial symbols like quotes &amp; arrows, and iconic Nike collabs, bridging high fashion with urban culture.</t>
         </is>
       </c>
     </row>
     <row r="158" ht="25.5" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>NEW BALANCE</t>
+          <t>Olympique De Darseille</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>new-balance</t>
+          <t>olympique-de-marseille</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>New Balance: 新百伦是全球知名的运动品牌，专注于为运动员和日常穿着者提供卓越的舒适感与支撑性。品牌以其标志性的缓震科技、多样化的宽度选择及经典复古款式而闻名，致力于通过匠心工艺与创新科技，满足不同人群对运动表现和时尚风格的双重追求。无论是专业跑鞋、训练装备还是休闲鞋款，新百伦都代表着平衡、可靠与持久的品质。</t>
+          <t>Olympique De Darseille（ODD）由Julien Poublon于2014 年在法国巴黎创立，法国街头潮牌。主营重磅棉 T 恤、顶级丹宁裤、摇滚风格卫衣等，创始人亲任设计师。流行于法、欧及全球街头潮流圈，风格融合美式复古与军事工装元素，采用重磅棉、优质皮革等耐用材质，是法国标志性街头潮牌。</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NEW BALANCE: Global athletic brand renowned for exceptional comfort, support, iconic cushioning, diverse widths, and classic retro styles. Committed to craftsmanship and innovation for performance and fashion.</t>
+          <t>Olympique De Darseille (ODD): French streetwear brand founded by Julien Poublon in Paris 2014. Offers heavy cotton tees, premium denim, rock-style hoodies. Blends American retro &amp; military workwear, uses durable heavy cotton, premium leather. Popular in France, Europe &amp; global streetwear circles, iconic French streetwear label.</t>
         </is>
       </c>
     </row>
     <row r="159" ht="25.5" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>NEW ENGLAND PATRIOTS</t>
+          <t>One Piece</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>new-england-patriots</t>
+          <t>one-piece</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>NEW ENGLAND PATRIOTS: 美国职业橄榄球联盟知名球队，成立于1959年，以鲜明的红白蓝配色和独特的飞翼logo设计闻名，代表产品包括球衣、外套、帽子等周边商品，采用高品质聚酯纤维和透气材质，工艺精湛，风格运动时尚，功能舒适耐用。</t>
+          <t>One Piece: 日本国民级海贼题材IP，由尾田荣一郎创作，1997年起在《周刊少年Jump》连载漫画，衍生动画、电影、游戏及手办、服饰等多元产品。以“草帽一伙寻找传说中大秘宝‘One Piece’的冒险”为核心，传递自由、伙伴与逐梦的精神内核，全球累计粉丝超数亿，是日本动漫文化输出的标杆性IP，覆盖全年龄段受众，衍生商品持续占据二次元周边市场热门。</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NEW ENGLAND PATRIOTS: NFL team since 1959, iconic red-white-blue winged logo. Jerseys, jackets, hats with high-quality polyester, breathable fabrics. Sporty, durable, and comfortable.</t>
+          <t>One Piece: Japan's national pirate IP by Eiichiro Oda, serialized in Weekly Shonen Jump since 1997. Derived anime, films, games, figures, apparel. Core: Straw Hats' adventure for "One Piece" treasure, conveying freedom, friendship, dreams. Billions of global fans, benchmark of Japanese anime culture export, all-age audience, top-selling anime merchandise.</t>
         </is>
       </c>
     </row>
     <row r="160" ht="25.5" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>NEW YORK JETS</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>new-york-jets</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>NEW YORK JETS：成立于1960年的职业美式橄榄球队，隶属NFL联盟，以绿色和白色为主色调，经典产品包括队服和周边商品，风格充满激情与团队精神，代表纽约地区的体育文化与竞技精神。</t>
+          <t>这个类目下，我们将不归属于任何品牌的商品归类到这里，以便于用户从这个表格里找到品牌不明显的流行或商品，以便于选择或购买。</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NEW YORK JETS: NFL team since 1960, iconic green &amp; white gear, embodies NY sports passion, unity, and competitive spirit.</t>
+          <t>In the Other category, we classify unbranded products here to help users find popular items with less obvious brands for selection or purchase.</t>
         </is>
       </c>
     </row>
     <row r="161" ht="25.5" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>NEW York Yankees</t>
+          <t>On Running</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>new York Yankees</t>
+          <t>on running</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>New York Yankees: 作为美国职业棒球大联盟最具标志性的球队之一，纽约洋基队代表着卓越、传承与胜利。其经典条纹队服和扬基体育场是全球体育迷心中的圣殿。品牌植根于深厚的棒球历史与文化，象征着纽约的拼搏精神与冠军荣耀，吸引着世界各地的忠实粉丝。</t>
+          <t>On Running: 2010年由三届铁人三项世界冠军Olivier Bernhard联合创立的瑞士专业运动品牌，以核心CloudTec®云科技中底为技术核心，融合精准缓震与向前推进力，专注跑步等运动场景，为专业跑者及运动爱好者提供兼具舒适脚感、卓越性能与简约设计的运动装备，是全球跑圈备受推崇的“跑者专属品牌”。</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>New York Yankees: Iconic MLB team symbolizing excellence, legacy, and victory. Classic pinstripes and Yankee Stadium are global sports shrines, embodying New York's champion spirit and baseball history for worldwide fans.</t>
+          <t>On Running: Swiss performance sportswear founded by 3x Ironman World Champion Olivier Bernhard. Features core CloudTec® cushioning for precision shock absorption and propulsive force, delivering high-performance running gear revered by runners worldwide.</t>
         </is>
       </c>
     </row>
     <row r="162" ht="25.5" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>NEWCASTLE UNITED</t>
+          <t>Onitsuka Tiger</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>newcastle-united</t>
+          <t>onitsuka tiger</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>NEWCASTLE UNITED: 纽卡斯尔联足球俱乐部成立于1892年，是英格兰东北部的职业足球俱乐部，以黑白条纹球衣和圣詹姆斯公园球场闻名，曾赢得四次英格兰顶级联赛冠军和六次足总杯，传统风格坚韧激情，代表球员包括阿兰·希勒和凯文·基冈。</t>
+          <t>Onitsuka Tiger: 1949年由鬼冢喜八郎创立于日本，作为ASICS的前身品牌，以“复古运动时尚”为核心定位，融合日本传统工艺与经典设计美学。标志性虎爪纹Logo、Mexico 66等经典系列享誉全球，产品涵盖运动鞋、服饰及配件，采用帆布、皮革等优质材质，风格兼顾复古质感与现代休闲，是潮流爱好者与运动复古风追随者的首选品牌。</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NEWCASTLE UNITED: Founded 1892, English football club known for black &amp; white stripes, St James' Park, 4 league titles, 6 FA Cups, passionate style. Legends: Shearer, Keegan.</t>
+          <t>Onitsuka Tiger: Founded in Japan by Kihachiro Onitsuka in 1949, predecessor of ASICS. Core positioning: "retro sporty fashion", blending Japanese traditional craftsmanship &amp; classic design aesthetics. Iconic tiger claw logo, classic Mexico 66 series. Products: sneakers, apparel, accessories (premium canvas/leather). Retro texture + modern casual style, top choice for trendsetters &amp; sporty vintage followers.</t>
         </is>
       </c>
     </row>
     <row r="163" ht="25.5" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Paco Rabanne</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>nike</t>
+          <t>paco-rabanne</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>NIKE: Nike是全球领先的运动鞋服品牌，为运动员提供创新设计与高性能装备，涵盖跑步、篮球、足球、训练等各类运动。其产品融合尖端科技与时尚风格，致力于激发每个人的运动潜能，传递“Just Do It”的进取精神。</t>
+          <t>Paco Rabanne: 1966年由西班牙裔法国设计师Paco Rabanne（弗朗西斯科·拉巴内达·库尔沃）创立的法国先锋奢侈品牌，以未来主义风格与金属材质创新运用著称，标志性金属链甲连衣裙重塑时尚边界，经典香水如Calandre、One Million系列全球热销，产品线覆盖高级时装、香水、配饰等，始终践行“时尚是科技与艺术的先锋融合”理念，是全球先锋时尚爱好者的标志性选择。</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NIKENIKE: Leading global sportswear brand, innovating high-performance athletic gear and stylish apparel for running, basketball, soccer, training. Empowers every athlete with cutting-edge technology and the "Just Do It" spirit.</t>
+          <t>Paco Rabanne: Founded by Spanish-French designer Francisco Rabaneda Cuervo in 1966, French avant-garde luxury brand known for futuristic style &amp; innovative metal use. Iconic metal chainmail dresses redefined fashion boundaries. Classic fragrances like Calandre &amp; One Million bestsellers. Lines cover haute couture, fragrances, accessories. Upholds "fashion is tech-art fusion" – global avant-garde fashion lovers’ iconic choice.</t>
         </is>
       </c>
     </row>
     <row r="164" ht="25.5" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>NOBIS</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>nobis</t>
-        </is>
-      </c>
-      <c r="C164"/>
+          <t>palestino</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Palestino: 
+（注：因未获取到Palestino品牌对应的中文描述信息，无法依据要求生成符合SEO优化的品牌描述内容。）</t>
+        </is>
+      </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Apple: Founded in 1976 by Steve Jobs, Apple is renowned for innovative design and technology. Its product lineup includes iPhone, Mac, and iPad, with classics like iPhone 4 and MacBook Air. Featuring metal and glass materials, exquisite craftsmanship, powerful functionality, and a minimalist modern style.
-Microsoft: Established in 1975 by Bill Gates and Paul Allen, Microsoft is a global leader in software and hardware. Products include Windows, Office, and Surface, with iconic items like Windows 10 and Surface Pro. Known for high-quality materials, advanced technology, comprehensive features, and a professional, practical style.
-Amazon: Founded in 1994 by Jeff Bezos, Amazon is the world's largest e-commerce and cloud computing company. Its products include Kindle, Echo, and AWS, with classics like Kindle Paperwhite and Echo Dot. Utilizes innovative materials, fine craftsmanship, smart functionality, and a convenient, efficient style.
-Samsung: Established in 1938 by Lee Byung-chul, Samsung is a Korean electronics giant. Products include Galaxy, QLED TV, and home appliances, with classics like Galaxy S series and QLED 8K TV. Features glass and metal materials, excellent craftsmanship, advanced functionality, and a fashionable tech style.
-Sony: Founded in 1946 by Akio Morita and Masaru Ibuka, Sony is a Japanese electronics and entertainment company. Products include PlayStation, Xperia, and Bravia TV, with classics like PlayStation 5 and WH-1000XM4 headphones. Uses advanced materials, superb craftsmanship, innovative features, and a cutting-edge, high-end style.
-Adidas: Established in 1949 by Adolf Dassler, Adidas is a German sports brand. Products include athletic shoes, apparel, and accessories, with classics like Superstar and Ultraboost. Employs eco-friendly materials, durable craftsmanship, comfortable functionality, and a sporty casual style.
-Nike: Founded in 1972 by Bill Bowerman and Phil Knight, Nike is an American sports brand. Products include athletic shoes, apparel, and equipment, with classics like Air Force 1 and Jordan series. Features innovative materials, exquisite craftsmanship, high-performance functionality, and a trendy athletic style.
-Google: Established in 1998 by Larry Page and Sergey Brin, Google is a tech company. Products include search engine, Android, and Pixel, with classics like Pixel phone and Google Home. Uses simple materials, smart technology, powerful functionality, and a modern, clean style.
-Tesla: Founded in 2003 by Elon Musk, Tesla is an electric vehicle and clean energy company. Products include Model S, Model 3, and Solar Roof, with classics like Model S and Cybertruck. Features metal and glass materials, advanced technology, electric efficiency, and a futuristic tech style.
-Coca-Cola: Established in 1886 by John Pemberton, Coca-Cola is an American beverage company. Products include carbonated drinks, juices, and water, with classics like Coca-Cola Classic and Sprite. Uses unique formulas, traditional methods, refreshing functionality, and a classic, popular style.</t>
+          <t>Palestino: Note: Unable to generate SEO-optimized brand description as no corresponding Chinese information for Palestino brand is obtained.</t>
         </is>
       </c>
     </row>
     <row r="165" ht="25.5" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>NOFS</t>
+          <t>Palm Angels</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>nofs</t>
-        </is>
-      </c>
-      <c r="C165"/>
+          <t>palm-angels</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Palm Angels: 2015年由Francesco Ragazzi创立的意大利街头潮流品牌，以滑板文化为内核融合高端时尚美学，标志性棕榈树图案、oversize剪裁是其辨识度符号，产品线涵盖服装、配饰、鞋履，曾与Adidas、Moncler等推出联名系列，风格兼具街头不羁与奢华质感，是全球潮流爱好者追捧的当代街头时尚代表品牌。</t>
+        </is>
+      </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Apple: Founded in 1976 by Steve Jobs, Apple is renowned for innovative design and technology. Key products include iPhone, Mac, iPad. Classics: iPhone 4, MacBook Air. Metal/glass materials, exquisite craftsmanship, powerful, minimalist modern style.
-Microsoft: Founded in 1975 by Bill Gates and Paul Allen, Microsoft is a global leader in software and hardware. Products: Windows, Office, Surface. Classics: Windows 10, Surface Pro. High-quality materials, advanced tech, comprehensive features, professional and practical.
-Amazon: Founded in 1994 by Jeff Bezos, Amazon is the world's largest e-commerce and cloud computing company. Products: Kindle, Echo, AWS. Classics: Kindle Paperwhite, Echo Dot. Innovative materials, fine craftsmanship, smart functions, convenient and efficient.
-Samsung: Founded in 1938 by Lee Byung-chul, Samsung is a Korean electronics giant. Products: Galaxy, QLED TV, appliances. Classics: Galaxy S series, QLED 8K TV. Glass/metal materials, excellent craftsmanship, advanced features, stylish tech.
-Sony: Founded in 1946 by Akio Morita and Masaru Ibuka, Sony is a Japanese electronics and entertainment firm. Products: PlayStation, Xperia, Bravia TV. Classics: PS5, WH-1000XM4. Advanced materials, fine craftsmanship, innovative functions, cutting-edge high-end.
-Adidas: Founded in 1949 by Adolf Dassler, Adidas is a German sportswear brand. Products: sneakers, apparel, accessories. Classics: Superstar, Ultraboost. Eco-friendly materials, durable craft, comfortable function, sporty casual style.
-Nike: Founded in 1972 by Bill Bowerman and Phil Knight, Nike is an American sportswear brand. Products: athletic shoes, clothing, equipment. Classics: Air Force 1, Jordan series. Innovative materials, exquisite craftsmanship, high-performance, trendy athletic style.
-Google: Founded in 1998 by Larry Page and Sergey Brin, Google is a tech company. Products: search engine, Android, Pixel. Classics: Pixel phone, Google Home. Simple materials, smart craft, powerful features, modern minimalist.
-Tesla: Founded in 2003 by Elon Musk, Tesla is an electric vehicle and clean energy company. Products: Model S, Model 3, Solar Roof. Classics: Model S, Cybertruck. Metal/glass materials, advanced craft, electric efficient, futuristic tech.
-Coca-Cola: Founded in 1886 by John Pemberton, Coca-Cola is a American beverage company. Products: soft drinks, juice, water. Classics: Coca-Cola Classic, Sprite. Unique formula, traditional craft, refreshing function, classic popular style.
-INFI:</t>
+          <t>Palm Angels: Italian streetwear brand founded by Francesco Ragazzi in 2015, merging skate culture with luxury aesthetics. Signature palm tree motif, oversize cuts; lines cover apparel, accessories, footwear. Collaborations with Adidas, Moncler. Edgy yet luxurious, a leading contemporary streetwear icon for global fashion lovers.</t>
         </is>
       </c>
     </row>
     <row r="166" ht="25.5" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="C166"/>
+          <t>paris-saint-germain</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain: 1970年创立于法国巴黎的顶级职业足球俱乐部，法甲联赛传统劲旅，主场为巴黎王子公园球场。以华丽进攻战术、全球顶尖球星阵容（如姆巴佩等核心球员）及10余次法甲冠军、多座法国杯冠军等荣誉著称，是全球足球领域极具影响力的品牌，代表法国足球高端竞技水准与国际球迷号召力。</t>
+        </is>
+      </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Apple: Apple, founded by Steve Jobs in 1976, is renowned for innovative design and tech products like iPhone, Mac, iPad, featuring metal-glass craftsmanship and powerful performance.
-Microsoft: Microsoft, established by Bill Gates and Paul Allen in 1975, leads in software and hardware with Windows, Office, Surface, known for professional, practical high-quality products.
-Amazon: Amazon, founded by Jeff Bezos in 1994, is the global e-commerce and cloud leader offering Kindle, Echo, AWS, with smart, efficient, and finely crafted innovations.
-Samsung: Samsung, founded by Lee Byung-chul in 1938, is a Korean electronics giant with Galaxy, QLED TV, appliances, featuring advanced glass-metal tech and stylish design.
-Sony: Sony, established by Akio Morita and Masaru Ibuka in 1946, delivers PlayStation, Xperia, Bravia TV, with cutting-edge materials, innovation, and premium style.
-Adidas: Adidas, founded by Adolf Dassler in 1949, is a German sportswear brand with Superstar, Ultraboost, using eco-friendly materials for durable, comfortable gear.
-Nike: Nike, founded by Bill Bowerman and Phil Knight in 1972, offers sportswear like Air Force 1 and Jordan series, with high-performance, trendy innovative designs.
-Google: Google, established by Larry Page and Sergey Brin in 1998, provides search, Android, Pixel, featuring smart, minimalist, and powerful modern technology.
-Tesla: Tesla, founded by Elon Musk in 2003, pioneers electric vehicles and clean energy like Model S, Cybertruck, with efficient, futuristic metal-glass engineering.
-Coca-Cola: Coca-Cola, created by John Pemberton in 1886, offers classic beverages like Coca-Cola Classic and Sprite, with refreshing, timeless traditional recipes.</t>
+          <t>Paris Saint Germain: Top pro football club founded 1970 in Paris, Ligue 1 powerhouse with home Parc des Princes. Known for attacking tactics, top stars (Mbappé etc.), 10+ Ligue 1 titles &amp; multiple French Cups. Global influential brand representing France’s elite football &amp; international fan appeal.</t>
         </is>
       </c>
     </row>
     <row r="167" ht="25.5" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>OFF-WHITE</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>off-white</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>OFF-WHITE：OFF-WHITE是融合了街头文化与高级时装的前沿时尚品牌。其标志性的斜纹、工业风格和“双引号”设计，定义了现代潮流美学。该品牌的服饰、鞋履和配饰，以其独特的解构主义和大胆的图形语言，深受全球时尚爱好者与收藏家的追捧。</t>
+          <t>Parma（Pini Parma）由Thomas Pini与妻子Claudia Cannetto于2017 年在意大利创立，总部位于巴黎。主营男士定制正装、休闲服饰及鞋履，创始人主导设计，融合意式经典与现代简约，线条流畅自然。采用Super 150’s 羊毛、羊绒、纯棉等顶级材质，意大利工匠手工制作，风靡欧洲、北美及亚洲，是高端意式男装新标杆。</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>OFF-WHITE: OFF-WHITE fuses street culture with high fashion. Known for iconic diagonal stripes, industrial style, and quotation marks, it defines modern aesthetics with deconstructed apparel, footwear, and bold graphics for global enthusiasts.</t>
+          <t>Parma(Pini Parma): Founded in Italy 2017 by Thomas Pini &amp; Claudia Cannetto, headquartered in Paris. Specializes in custom men’s formalwear, casual apparel &amp; footwear. Founder-led design blends Italian classics with modern minimalism, smooth natural lines. Uses premium materials (Super 150’s wool, cashmere, cotton). Handcrafted by Italian artisans. Popular in Europe, North America, Asia—new benchmark for high-end Italian menswear.</t>
         </is>
       </c>
     </row>
     <row r="168" ht="25.5" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>OLYMPIQUE DE MARSEILLE</t>
+          <t>Payeah</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>olympique-de-marseille</t>
+          <t>payeah</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>OLYMPIQUE DE MARSEILLE: 法国马赛足球俱乐部成立于1899年，是欧洲足坛传统强队，曾多次夺得法甲冠军及1993年欧冠冠军。品牌以蓝白主色调、独特队徽设计和高质量球迷服饰闻名，产品涵盖比赛日球衣、训练装备及周边配件，融合高性能面料与工艺，风格激情硬朗，深受全球球迷推崇。</t>
+          <t>ayeah 是主打休闲印花 T 恤的时尚品牌，主营 100% 纯棉男女款潮流 T 恤，涵盖节日主题、数字印花等多元设计。风格融合街头潮流与日常休闲，图案大胆个性、色彩鲜明。采用重磅纯棉、精梳棉等优质材质，透气亲肤、耐穿易洗。风靡北美、欧洲及全球跨境电商市场，是年轻消费者日常穿搭与个性表达的热门选择。</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>OLYMPIQUE DE MARSEILLE: OM, founded 1899, European football powerhouse. Multiple Ligue 1 titles &amp; 1993 UEFA Champions League winner. Iconic blue-white kits &amp; merch.</t>
+          <t>Payeah: 100% cotton men's &amp; women's trendy t-shirts with festive themes, digital prints. Bold, vibrant street-casual designs. Heavyweight combed cotton: breathable, skin-friendly, durable, easy to wash. Popular in North America, Europe &amp; global cross-border e-commerce, top for young daily wear &amp; self-expression.</t>
         </is>
       </c>
     </row>
     <row r="169" ht="25.5" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ONE PIECE</t>
+          <t>Penhaligons</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>one-piece</t>
+          <t>penhaligons</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>NIKE: 1972年由比尔·鲍尔曼和菲尔·奈特创立的美国运动品牌，产品涵盖运动鞋、服装及器材，经典款包括Air Force 1和Jordan系列，采用创新材质与精湛工艺，功能高性能，风格潮流运动。
-ADIDAS: 1949年由阿道夫·达斯勒创立的德国运动品牌，产品包括运动鞋、服装及配件，经典款有Superstar和Ultraboost，采用环保材质与耐用工艺，功能舒适，风格运动休闲。
-SONY: 1946年由盛田昭夫和井深大创立的日本电子企业，产品包括PlayStation、Xperia和Bravia电视等，经典款有PlayStation 5和WH-1000XM4耳机，采用高新材料与精良工艺，功能创新，风格前卫高端。
-SAMSUNG: 1938年由李秉喆创立的韩国电子品牌，产品包括Galaxy手机、QLED电视及家电，经典款有Galaxy S系列和QLED 8K电视，采用玻璃金属材质与卓越工艺，功能先进，风格时尚科技。
-APPLE: 1976年由史蒂夫·乔布斯创立的美国科技公司，产品包括iPhone、Mac、iPad等，经典款有iPhone 4和MacBook Air，采用金属玻璃材质与精湛工艺，功能强大，风格简约现代。
-MICROSOFT: 1975年由比尔·盖茨和保罗·艾伦创立的软件公司，产品包括Windows、Office及Surface设备，经典款有Windows 10和Surface Pro，采用高品质材质与先进工艺，功能全面，风格专业实用。
-AMAZON: 1994年由杰夫·贝索斯创立的电商与云计算企业，产品包括Kindle、Echo及AWS服务，经典款有Kindle Paperwhite和Echo Dot，采用创新材质与精细工艺，功能智能，风格便捷高效。
-GOOGLE: 1998年由拉里·佩奇和谢尔盖·布林创立的科技公司，产品包括搜索引擎、Android系统和Pixel设备，经典款有Pixel手机和Google Home，采用简约材质与智能工艺，功能强大，风格现代简洁。
-TESLA: 2003年由埃隆·马斯克创立的电动汽车企业，产品包括Model S、Model 3及Solar Roof，经典款有Model S和Cybertruck，采用金属玻璃材质与先进工艺，功能电动高效，风格未来科技。
-COCA-COLA: 1886年由约翰·彭伯顿创立的饮料品牌，产品包括碳酸饮料、果汁及水，经典款有Coca-Cola Classic和Sprite，采用独特配方与传统工艺，功能清爽解渴，风格经典流行。</t>
+          <t>Penhaligons: 1870年由威廉·彭哈根（William Penhaligon）创立于英国伦敦的高端香氛品牌，以英伦贵族式奢华调香与复古故事性著称，核心涵盖香水、香氛蜡烛及身体护理系列，经典香款如《Portrait of a Lady》（仕女画像）、《The Tragedy of Lord George》（乔治勋爵的悲剧）等，凭借精湛调香工艺与独特英伦美学，成为全球香氛爱好者追捧的奢华香氛代表品牌。</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NIKE: Nike: US sportswear brand since 1972. Features Air Force 1 &amp; Jordan series. Innovative materials, premium craftsmanship, high-performance, trendy athletic style.  
-ADIDAS: Adidas: German sportswear brand since 1949. Offers Superstar &amp; Ultraboost. Eco-friendly materials, durable craftsmanship, comfortable, sporty casual style.  
-SONY: Sony: Japanese electronics brand since 1946. Products: PlayStation, Xperia, Bravia TVs. Innovative tech, premium materials, advanced features, sleek modern design.  
-SAMSUNG: Samsung: Korean electronics brand since 1938. Galaxy phones, QLED TVs. Glass/metal materials,卓越工艺, advanced features, stylish tech design.  
-APPLE: Apple: US tech brand since 1976. iPhone, Mac, iPad. Metal/glass materials, exquisite craftsmanship, powerful features, minimalist modern style.  
-MICROSOFT: Microsoft: Software company since 1975. Windows, Office, Surface. High-quality materials, advanced tech, comprehensive features, professional实用风格.  
-AMAZON: Amazon: E-commerce &amp; cloud giant since 1994. Kindle, Echo, AWS. Innovative materials, smart features, convenient efficient design.  
-GOOGLE: Google: Tech company since 1998. Search, Android, Pixel devices. Minimalist materials, smart features, modern sleek style.  
-TESLA: Tesla: Electric vehicle brand since 2003. Model S, Model 3, Solar Roof. Metal/glass materials, advanced tech, electric efficiency, futuristic style.  
-COCA-COLA: Coca-Cola: Beverage brand since 1886. Coca-Cola Classic, Sprite. Unique formula, traditional craft, refreshing thirst-quencher, classic popular style.</t>
+          <t>Penhaligons: Luxury British fragrance brand founded in London in 1870 by William Penhaligon, celebrated for aristocratic opulent scents &amp; vintage storytelling. Core lines: perfumes, scented candles, body care. Classics include Portrait of a Lady &amp; The Tragedy of Lord George. Exquisite craftsmanship &amp; unique British aesthetics make it a global luxury fragrance favorite.</t>
         </is>
       </c>
     </row>
     <row r="170" ht="25.5" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>Philadelphia Eagles</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>philadelphia-eagles</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>其他：本类目收录无法归入具体品牌的所有商品，便于用户快速查找未知品牌或无明确品牌标识的产品。</t>
+          <t>Philadelphia Eagles: 美国国家橄榄球联盟（NFL）历史悠久的职业球队，1933年成立于宾夕法尼亚州费城，隶属于NFC东区，主场为林肯金融球场。球队曾荣获2018年第52届超级碗冠军，以展翅雄鹰队徽、深绿+银灰+黑的经典队色为标志，拥有“Eagles Nation”庞大球迷群体，以坚韧球风与社区深度联结著称，是北美职业橄榄球领域极具影响力的球队之一。</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Other: This category lists all products that cannot be classified under specific brands. It helps users quickly locate items with unknown or unbranded identities for easier searching.</t>
+          <t>Philadelphia Eagles: NFL team founded 1933 in Philadelphia, NFC East, Lincoln Financial Field. Super Bowl LII champions (2018). Iconic eagle logo, green/silver/black colors. Eagles Nation, resilient style.</t>
         </is>
       </c>
     </row>
     <row r="171" ht="25.5" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>OVO（归到 Other）</t>
-        </is>
-      </c>
-      <c r="B171"/>
-      <c r="C171"/>
+          <t>Pittsburgh Steelers</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>pittsburgh-steelers</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Pittsburgh Steelers: 1933年成立于美国宾夕法尼亚州匹兹堡，是NFL（美国国家橄榄球联盟）历史最悠久的球队之一，以“钢铁之城”的强硬球风闻名，曾6次夺得超级碗冠军（NFL夺冠次数最多的球队之一），主场为Acrisure Stadium。球队承载匹兹堡工业底蕴，融合橄榄球热血精神，拥有全球庞大“钢铁军团”球迷群体，是美式橄榄球界极具传奇性与影响力的经典劲旅。</t>
+        </is>
+      </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Apple: Apple, founded by Steve Jobs in 1976, is renowned for innovative design and technology. Products include iPhone, Mac, iPad, featuring classics like iPhone 4 and MacBook Air with premium metal/glass materials, exquisite craftsmanship, powerful functionality, and modern minimalist style.
-Microsoft: Microsoft, established by Bill Gates and Paul Allen in 1975, is a global leader in software/hardware. Products: Windows, Office, Surface. Classics include Windows 10 and Surface Pro with high-quality materials, advanced tech, comprehensive features, and professional utility.
-Amazon: Amazon, founded by Jeff Bezos in 1994, is the world's largest e-commerce and cloud computing company. Products: Kindle, Echo, AWS. Classics: Kindle Paperwhite and Echo Dot with innovative materials, fine craftsmanship, smart functions, and efficient convenience.
-Samsung: Samsung, established by Lee Byung-chul in 1938, is a Korean electronics giant. Products: Galaxy, QLED TV, appliances. Classics: Galaxy S series and QLED 8K TV with glass/metal materials,卓越工艺, advanced features, and stylish tech design.
-Sony: Sony, founded by Akio Morita and Masaru Ibuka in 1946, is a Japanese electronics/entertainment firm. Products: PlayStation, Xperia, Bravia TV. Classics: PS5 and WH-1000XM4 headphones with innovative materials, precision engineering, cutting-edge functions, and premium avant-garde style.
-Adidas: Adidas, established by Adolf Dassler in 1949, is a German sportswear brand. Products: athletic shoes, apparel, accessories. Classics: Superstar and Ultraboost with eco-friendly materials, durable craftsmanship, comfortable performance, and sporty casual style.
-Nike: Nike, founded by Bill Bowerman and Phil Knight in 1972, is an American sportswear brand. Products: athletic shoes, apparel, equipment. Classics: Air Force 1 and Jordan series with innovative materials, expert craftsmanship, high-performance features, and trendy athletic style.
-Google: Google, established by Larry Page and Sergey Brin in 1998, is a tech company. Products: search engine, Android, Pixel. Classics: Pixel phone and Google Home with minimalist materials, smart technology, powerful functions, and modern简洁 style.
-Tesla: Tesla, founded by Elon Musk in 2003, is an electric vehicle/clean energy company. Products: Model S, Model 3, Solar Roof. Classics: Model S and Cybertruck with metal/glass materials, advanced engineering, electric efficiency, and futuristic tech design.
-Coca-Cola: Coca-Cola, established by John Pemberton in 1886, is an American beverage company. Products: soft drinks, juices, water. Classics: Coca-Cola Classic and Sprite with unique formula, traditional methods, refreshing taste, and classic popular style.
-OVO:</t>
+          <t>Pittsburgh Steelers: Legendary NFL team founded 1933 in Pittsburgh, 6-time Super Bowl champions, known for Steel City tough style, home at Acrisure Stadium, with global Steelers Nation fan base.</t>
         </is>
       </c>
     </row>
     <row r="172" ht="25.5" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>On Running</t>
+          <t>Playboi Carti</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>on running</t>
+          <t>playboi-carti</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>On Running（昂跑）于2010年在瑞士苏黎世创立，由前铁人三项冠军Olivier Bernhard与David Allemann、Caspar Coppetti共同创立设计。品牌以“Run on Clouds”为理念，核心搭载专利CloudTec®缓震科技，采用Helion™ Superfoam泡棉、透气网面等优质材质，主打轻盈缓震、强力回弹的产品特性。主要产品涵盖专业跑鞋、运动服饰及配件，热门系列包括Cloud、Cloudmonster、Cloudnova、THE ROGER（与费德勒合作）等，兼顾专业运动性能与简约时尚风格，适配路跑、越野、日常通勤等多种场景，凭借瑞士精密工艺成为全球跑者青睐的高端运动品牌。</t>
+          <t>Playboi Carti: 美国嘻哈音乐人及街头潮流符号，其同名周边潮牌以说唱文化为内核，推出卫衣、T恤、帽款等单品，设计融入专辑视觉、标志性歌词元素，采用棉质等舒适面料，风格街头不羁，契合年轻潮流群体审美，是连接音乐与时尚消费的热门跨境电商品牌。</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Founded in 2010 in Zurich, Switzerland, On Running was co-designed by former triathlon champion Olivier Bernhard, David Allemann and Caspar Coppetti. With the concept of "Run on Clouds", it features patented CloudTec® cushioning technology and high-quality materials like Helion™ Superfoam. Its main products include running shoes, sportswear and accessories, with popular series such as Cloud, Cloudmonster, Cloudnova and THE ROGER, combining professional performance and minimalist style.</t>
+          <t>Playboi Carti: American hip-hop artist &amp; streetwear icon, eponymous merch brand rooted in hip-hop culture. Offers hoodies, tees, caps with album visuals, iconic lyrics, comfy cotton. Edgy street style resonates with young trendsetters, popular cross-border brand linking music &amp; fashion.</t>
         </is>
       </c>
     </row>
     <row r="173" ht="25.5" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Onitsuka Tiger</t>
+          <t>Polo</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>onitsuka tiger</t>
+          <t>polo</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Onitsuka Tiger: 鬼塚虎是源自日本的经典运动时尚品牌，以其标志性的虎爪纹和复古设计闻名。品牌融合卓越工艺与街头文化，提供运动鞋、服装及配饰，展现独特日式美学与个性风格。探索鬼塚虎经典与创新结合的产品系列，体验历久弥新的时尚魅力。</t>
+          <t>Polo: 源自美国的经典休闲品牌，以标志性马球logo为核心识别，产品线覆盖男女装、皮具、配饰等，主打简约经典风格，采用高品质棉、皮革等材质，兼顾舒适与耐用性，适配日常休闲、轻商务等多元场景，是全球消费者青睐的休闲时尚选择。</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Onitsuka Tiger: Classic Japanese sport-fashion brand iconic with tiger stripes and retro designs. Merges craftsmanship with street culture in sneakers, apparel, and accessories for unique aesthetics.</t>
+          <t>Polo: Iconic US casual brand featuring the polo logo. Offers classic men's, women's apparel, leather goods &amp; accessories. Premium cotton &amp; leather for durable, versatile everyday &amp; smart-casual wear.</t>
         </is>
       </c>
     </row>
     <row r="174" ht="25.5" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PACO RABANNE</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>paco-rabanne</t>
+          <t>patagonia</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PACO RABANNE: 1966年由帕科·拉巴尼创立的法国奢侈品牌，以未来主义设计和创新材质闻名，产品系列包括香水、时装和配饰，经典产品有Calandre香水和金属连衣裙，采用金属、塑料等非传统材质，工艺前卫，风格大胆独特。</t>
+          <t>Patagonia: 1973年创立于美国的专业户外装备品牌，以“构建更美好的地球”为核心使命，专注可持续环保户外服饰与装备设计，产品涵盖冲锋衣、羽绒服、抓绒衣、登山包等，采用再生聚酯纤维、有机棉等环保材质，坚持“1% for the Planet”计划（将1%营收投入环保公益），融合专业户外性能与生态责任，是全球户外爱好者与环保主义者信赖的可持续户外品牌典范。</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>PACO RABANNE: French luxury brand since 1966, known for futuristic designs, innovative materials like metal &amp; plastic, iconic fragrances &amp; avant-garde fashion.</t>
+          <t>Patagonia: US professional outdoor gear brand founded in 1973, core mission "Build the Better Earth". Specializes in sustainable apparel/gear (raincoats, down jackets, fleece, hiking packs) with recycled polyester, organic cotton. Committed to "1% for the Planet" (1% revenue to environmental causes). Blends professional performance with ecological responsibility, trusted by global outdoor enthusiasts &amp; environmentalists as a sustainable leader.</t>
         </is>
       </c>
     </row>
     <row r="175" ht="25.5" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PALESTINO</t>
+          <t>Prada</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>palestino</t>
+          <t>prada</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>PALESTINO: 智利知名运动服饰品牌，源自1952年，以足球装备和休闲运动装著称，产品涵盖专业球衣、训练服及运动配件，采用高性能面料与先进工艺，设计融合南美激情与现代运动美学，为全球运动爱好者提供兼具功能性与时尚感的运动解决方案。</t>
+          <t>Prada: 1913年由马里奥·普拉达（Mario Prada）创立于意大利米兰，全球顶级奢侈品牌，以皮具、高级时装、配饰为核心品类，标志性尼龙材质与三角标LOGO是品牌辨识度符号，融合极简设计与精湛意大利工艺，诠释“低调奢华”的时尚内核，经典产品涵盖Saffiano皮革手袋、尼龙背包及成衣系列，是全球追求高品质时尚人群的首选品牌之一。</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>PALESTINOPALESTINO: Since 1952, Chile's iconic sports brand. Professional football gear, training apparel &amp; accessories. High-performance fabrics, modern design.</t>
+          <t>Prada: Founded in Milan, Italy in 1913 by Mario Prada, a top global luxury brand with core categories of leather goods, high fashion, and accessories. Iconic nylon material &amp; triangular logo, minimalist design + exquisite Italian craftsmanship embody "understated luxury". Classic products: Saffiano bags, nylon backpacks, ready-to-wear—preferred by global high-quality fashion seekers.</t>
         </is>
       </c>
     </row>
     <row r="176" ht="25.5" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PALM ANGELS</t>
+          <t>Project Capri</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>palm-angels</t>
+          <t>project-capri</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PALM ANGELS: Palm Angels 是源自意大利的街头潮流品牌，以其标志性的洛杉矶滑板文化美学和现代奢华风格著称。品牌融合高端时尚与休闲运动元素，主打印花卫衣、宽松剪裁服饰和标志性棕榈树图案，打造兼具复古街头感与精致质感的男女装系列。Palm Angels 通过大胆的色彩和颠覆传统的设计，重新定义现代街头时尚，深受全球潮流爱好者追捧。</t>
+          <t>Project Capri 由Caprice Brown于2022 年在拉斯维加斯创立，当时仅 16 岁的他打造出七位数营收潮牌。创始人亲任设计师，主营镶钻牛仔裤、多口袋牛仔短裤、丹宁夹克与工装裤。风格融合复古丹宁、军事工装与大胆印花，街头感十足。采用重磅丹宁、优质帆布与真皮等耐用材质，风靡美国、欧洲及全球潮流圈，深受 Z 世代追捧，是年轻街头品牌标杆。</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>PALM ANGELS: Italian streetwear brand fusing LA skate culture with luxury, iconic palm prints, oversized fits, and bold designs for urban fashion.</t>
+          <t>Project Capri: Founded by Caprice Brown in Las Vegas (2022, 16yo), 7-figure streetwear. Founder-led design: rhinestone jeans, multi-pocket denim shorts, jackets, work pants. Blends vintage denim, military workwear, bold prints (streetwear vibe). Uses heavy denim, premium canvas, genuine leather. Popular in US/Europe/global, Gen Z-favorite young street brand benchmark.</t>
         </is>
       </c>
     </row>
     <row r="177" ht="25.5" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PARIS SAINT-GERMAIN</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>paris-saint-germain</t>
+          <t>puma</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>PARIS SAINT-GERMAIN: 法国巴黎圣日耳曼足球俱乐部成立于1970年，是享誉全球的顶级运动品牌，推出高品质足球服装、训练装备及潮流休闲系列，经典产品包括主场球衣和联名运动鞋，采用高性能面料与先进工艺，融合运动功能与时尚设计，风格现代前卫。</t>
+          <t>Puma: 1948年由鲁道夫·达斯勒创立的德国专业运动品牌，以“Forever Faster”为核心精神，专注跑步、足球、篮球等专业运动装备与潮流运动服饰研发，经典产品包括Suede板鞋、Clyde篮球鞋及Ultra足球鞋系列，采用优质皮革、透气科技面料等材质，融合运动性能与街头时尚设计，满足全球运动员训练比赛及潮流爱好者日常穿搭需求，是兼具专业度与潮流感的知名运动品牌。</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>PARIS SAINT-GERMAIN: PSG, founded 1970, delivers elite football apparel, training gear &amp; casual wear. Features high-performance tech &amp; modern style. Iconic jerseys &amp; collab sneakers.</t>
+          <t>Puma: German sportswear brand founded 1948, embodying "Forever Faster" in running, football, basketball. Features Suede, Clyde, Ultra series, blending performance tech with street-style fashion.</t>
         </is>
       </c>
     </row>
     <row r="178" ht="25.5" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>Ralph Lauren</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>parma</t>
-        </is>
-      </c>
-      <c r="C178"/>
-      <c r="D178"/>
+          <t>ralph-lauren</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Ralph Lauren: 1967年由拉尔夫·劳伦（Ralph Lauren）创立的美国高端时尚品牌，以"美式经典生活方式"为核心定位，覆盖男装、女装、童装、配饰（皮具、香水、腕表）及家居全品类，标志性元素包括马球 pony 标志、牛津纺衬衫、粗花呢西装与经典格纹，产品融合复古优雅与休闲奢华感，是全球美式时尚与品质生活的代表品牌，旗下Polo Ralph Lauren系列更成为基础款高端化的经典范例。</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Ralph Lauren: American luxury fashion brand founded by Ralph Lauren in 1967, focused on the "American classic lifestyle", covering men’s, women’s, kids’ apparel, accessories (leather goods, perfume, watches) &amp; homeware. Iconic elements: Polo pony logo, Oxford shirts, tweed suits, classic plaids. Blending vintage elegance &amp; casual luxury, it’s a global representative of American fashion &amp; quality life. Its Polo Ralph Lauren line is a classic example of elevated basics.</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="25.5" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PAYEAH</t>
+          <t>Rb Leipzig</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>payeah</t>
-        </is>
-      </c>
-      <c r="C179"/>
-      <c r="D179"/>
+          <t>rb-leipzig</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>RB Leipzig: 德国职业足球俱乐部，2009年成立于萨克森州莱比锡，隶属于红牛集团，主场为可容纳超4.2万名观众的莱比锡红牛竞技场，系德甲联赛劲旅。球队以“青春风暴”“高压进攻”战术风格著称，近年稳居德甲积分榜前列，多次晋级欧冠、欧联杯等欧洲顶级赛事，是德国足坛近年快速崛起的代表性球队。</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>RB Leipzig: Top Bundesliga club founded 2009. Red Bull-owned, home Red Bull Arena 42,000+. Youth storm &amp; high-pressure attack style. Regular in UEFA Champions League/Europa League, symbol of rapid rise.</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="25.5" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PENHALIGONS</t>
+          <t>Readymade</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>penhaligons</t>
+          <t>readymade</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>PENHALIGONS: 1870年由William Penhaligon创立的英国奢侈香水品牌，以精致香氛和优雅设计闻名，产品系列包括香水、香薰蜡烛、沐浴用品等，经典产品有Halfeti和Luna，采用高级香料和玻璃瓶身，工艺精湛，风格经典奢华。</t>
+          <t>eadymade 由日本设计师细川雄太 (Yuta Hosokawa)于2013 年在大阪创立，主打军事重制服饰与配饰。创始人亲任设计，以和平反战为核心理念，将二战古军布、帐篷帆布与复古军用包袋手工改造成包袋、外套、卫衣等单品。风格融合美式复古、军事工装与解构主义，每件均带原始编号，独一无二。风靡全球潮流圈，受 Virgil Abloh、Travis Scott 等明星追捧，是 Remake 领域标杆。</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>PENHALIGONS: Luxury British perfume brand since 1870, crafting exquisite fragrances, scented candles &amp; bath products with sophisticated notes &amp; elegant design.</t>
+          <t>Readymade, founded 2013 in Osaka by Yuta Hosokawa, specializes in military remake apparel/accessories. Core peace anti-war philosophy, handmade from WWII vintage military fabrics, tents &amp; bags. Blends American vintage, military workwear &amp; deconstruction. Unique numbered, global trend icon, Remake benchmark.</t>
         </is>
       </c>
     </row>
     <row r="181" ht="25.5" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PHILADELPHIA EAGLES</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>philadelphia-eagles</t>
+          <t>real-madrid</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>PHILADELPHIA EAGLES: 美国职业橄榄球队，成立于1933年，以雄鹰为标志，代表费城。球队以其激情、坚韧和团队精神闻名，拥有众多忠实球迷。经典队服采用绿色、银色和黑色，材质舒适耐用，设计运动时尚。产品系列包括球衣、帽子、外套等，风格经典运动。</t>
+          <t>Real Madrid: 1902年成立于西班牙马德里的顶级职业足球俱乐部，昵称“银河战舰”，是历史上夺得欧洲冠军联赛冠军次数最多（14次）的球队，亦坐拥35次西班牙甲级联赛冠军等荣誉；主场为标志性的伯纳乌球场（Estadio Santiago Bernabéu），以经典白色球衣、带皇冠与“RM”标识的队徽为核心视觉符号；全球拥有超4亿球迷，商业价值常年位居足球俱乐部前列，传承“永不言弃”的竞技精神，代表西班牙足球的巅峰水准与全球影响力。</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>PHILADELPHIA EAGLES: NFL team since 1933, iconic eagle symbol, green &amp; silver gear. Passionate, resilient, sportswear jerseys, hats, jackets.</t>
+          <t>Real Madrid: Elite Spanish football club founded 1902, "Galacticos". Record 14 UEFA Champions League &amp; 35 La Liga titles. Iconic Santiago Bernabéu Stadium, white kits, 400M+ fans, "Never give up" spirit.</t>
         </is>
       </c>
     </row>
     <row r="182" ht="25.5" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PITTSBURGH STEELERS</t>
+          <t>Revenge</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>pittsburgh-steelers</t>
+          <t>revenge</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>PITTSBURGH STEELERS: 成立于1933年的美国职业橄榄球队，以黑金配色和硬朗风格闻名，经典产品包括球衣、外套和周边配件，采用耐用材质和精湛工艺，功能实用，风格经典运动。</t>
+          <t>Revenge 由Garette 与 Han于2016 年在美国洛杉矶创立，是匿名设计师 Garette 主导的街头潮牌。主营拱门 Logo 帽衫、涂鸦 T 恤、荆棘牛仔与素食皮夹克等，风格暗黑叛逆，融合朋克美学与哥特式手写字体，标志性蜘蛛网与火焰图案极具辨识度。采用重磅纯棉、优质牛仔与环保素食皮等耐用材质，因与 XXXTentacion 合作爆红，风靡全球 Z 世代潮流圈，是地下街头文化标杆。</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>PITTSBURGH STEELERS: NFL team est. 1933, known for black &amp; gold colors, tough legacy. Features jerseys, jackets &amp; gear with durable materials &amp; classic sport style.</t>
+          <t>Revenge: Streetwear brand founded by Garette &amp; Han in LA 2016, led by anonymous designer Garette. Core products: arched logo hoodies, graffiti tees, thorn denim, vegan leather jackets. Dark rebellious style fuses punk aesthetics with gothic handwritten fonts; iconic spider web &amp; flame patterns. Uses heavy cotton, premium denim, eco vegan leather. Viral via XXXTentacion collab, beloved by global Gen Z—underground street culture icon.</t>
         </is>
       </c>
     </row>
     <row r="183" ht="25.5" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PLAYBOI CARTI</t>
+          <t>Represent</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>playboi-carti</t>
+          <t>represent</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>PLAYBOI CARTI:  
-美国说唱歌手及潮流引领者Playboi Carti创立的音乐与时尚品牌，以其前卫音乐风格和标志性街头服饰设计闻名，产品涵盖卫衣、T恤、配饰等，融合夸张剪裁、朋克元素和嘻哈文化，风格叛逆独特，深受年轻潮流群体追捧。</t>
+          <t>Represent 由George Heaton与Mike Heaton兄弟于2011 年在英国大曼彻斯特创立，始于大学 T 恤印花项目。创始人 George 主理设计，主营帽衫、T 恤、夹克、运动裤与鞋履，风格融合奢华街头风与极简主义，以480GSM 重磅针织棉、莱赛尔斜纹布等高端面料打造精品基础款，注重工艺细节。风靡欧美、日韩及全球潮流圈，受明星与时尚达人追捧，是英国奢华街头品牌标杆。</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>PLAYBOI CARTI: Playboi Carti's avant-garde music &amp; streetwear brand. Known for rebellious punk-inspired apparel, hip-hop culture, and iconic oversized cuts.</t>
+          <t>Represent: Founded by George &amp; Mike Heaton in Greater Manchester, UK (2011) from a university T-shirt printing project. George leads design; offers hoodies, T-shirts, jackets, sweatpants, footwear. Blends luxury streetwear with minimalism, using 480GSM heavy knit cotton, Lyocell twill for premium basics, emphasizing craftsmanship. Popular in EU/US/Japan/Korea, favored by celebrities/influencers—UK luxury streetwear benchmark.</t>
         </is>
       </c>
     </row>
     <row r="184" ht="25.5" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>POLO</t>
+          <t>Rhude</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>polo</t>
-        </is>
-      </c>
-      <c r="C184"/>
-      <c r="D184"/>
+          <t>rhude</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Rhude: 2015年由Rhuigi Villaseñor创立于美国的高端街头服饰品牌，以“街头文化与高级时尚融合”为核心定位，标志性设计涵盖经典Logo、复古运动元素与皮革、麂皮等高端材质的结合，产品包括卫衣、夹克、牛仔裤及配饰，曾与Nike、Puma等推出联名系列，主打“街头奢华风”，精准契合追求潮流质感与独特风格的年轻群体需求。</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Rhude: Founded by Rhuigi Villaseñor in the US in 2015, a high-end streetwear brand blending street culture with luxury fashion. Signature designs feature classic logos, retro sporty elements, premium leather/suede. Products: hoodies, jackets, jeans, accessories. Collaborated with Nike, Puma. Focuses on "street luxury" for young people pursuing trendy quality &amp; unique styles.</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="25.5" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>POLO RALPH LAUREN</t>
+          <t>Rick Owens</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>polo-ralph-lauren</t>
+          <t>rick-owens</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>POLO RALPH LAUREN: 1967年由拉尔夫·劳伦创立的美国经典时尚品牌，以马球标志闻名，产品系列包括服装、配饰、家居及香水，经典产品有Polo衫和定制西装，采用棉质、羊毛等高级材质，工艺精湛，风格融合美式休闲与精致优雅。</t>
+          <t>Rick Owens: 1994年由同名设计师创立于美国洛杉矶的先锋暗黑时尚品牌，以解构主义、工业感轮廓与垂坠美学为核心风格，标志性产品包括Geobasket运动鞋、机车皮革夹克及垂坠剪裁成衣，常用皮革、帆布等质感材质，诠释反主流的个性表达，是全球先锋时尚爱好者与潮流人士追捧的暗黑先锋代表品牌。</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>POLO RALPH LAUREN: Iconic 1967 American brand known for polo logo, polo shirts, suits, apparel, accessories, home &amp; fragrances with premium cotton &amp; wool craftsmanship.</t>
+          <t>Rick Owens: Founded in Los Angeles, USA in 1994, this avant-garde dark fashion brand focuses on deconstruction, industrial silhouettes, and drape aesthetics. Signature items: Geobasket sneakers, biker leather jackets, draped ready-to-wear. Uses leather/canvas, embodies anti-mainstream self-expression—iconic among global avant-garde fashion lovers.</t>
         </is>
       </c>
     </row>
     <row r="186" ht="25.5" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Roberto Cavalli</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>patagonia</t>
+          <t>roberto-cavalli</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Patagonia 巴塔哥尼亚 1973 年诞生于美国加利福尼亚州文图拉，由登山家伊冯・乔伊纳德 (Yvon Chouinard) 创立。核心主线为高性能户外服装、攀岩装备、冲浪服饰及环保休闲系列，主打再生聚酯纤维、有机棉、H2No 防水面料与 Capilene 热控材质，以功能性 + 环保可持续为设计灵魂，风格简约耐用，深受全球户外爱好者、环保主义者与品质追求者青睐，畅销北美、欧洲及亚洲市场，由品牌内部专业户外设计师团队操刀，坚持 “做最好产品，不造成不必要伤害” 的理念。</t>
+          <t>Roberto Cavalli: 1960年代由意大利设计师Roberto Cavalli创立的奢侈品牌，以「狂野奢华」风格为核心标签，标志性动物纹、大胆印花与精湛手工工艺贯穿高级时装、皮具、香水、配饰等全品类，诠释不羁个性与顶级奢华的融合，是全球追求独特时尚品味、渴望彰显自我风格的高端消费者首选品牌。</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Founded in 1973 in Ventura, California, USA by climber Yvon Chouinard, Patagonia is a premium outdoor brand. Core lines: high-performance apparel, climbing gear, surfwear &amp; eco-friendly casual wear. Crafted with recycled polyester, organic cotton, H2No waterproof &amp; Capilene fabrics. Functional, minimalist &amp; sustainable design, loved by outdoor enthusiasts, environmentalists globally, especially North America, Europe &amp; Asia. Designed by in-house outdoor experts, dedicated to "Build the best, cause no unnecessary harm.</t>
+          <t>Roberto Cavalli: Italian luxury brand founded by Roberto Cavalli in the 1960s, centered on "wild luxury"—iconic animal prints, bold patterns, exquisite craftsmanship across ready-to-wear, leather goods, fragrances, accessories. Blends unruly individuality with top-tier luxury, favored by global high-end consumers pursuing unique style.</t>
         </is>
       </c>
     </row>
     <row r="187" ht="25.5" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PRADA</t>
+          <t>Rossoneri</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>prada</t>
+          <t>rossoneri</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>PRADA: 普拉达是源自意大利米兰的奢侈时尚品牌，以其精湛工艺、创新设计和标志性的三角形徽标而享誉全球。从高级成衣、手袋到配饰与香水，普拉达致力于为追求卓越品质与前瞻美学的全球消费者提供标志性产品。品牌融合经典传承与当代精神，是奢华、创意与现代风格的代名词。</t>
+          <t>Rossoneri 是 AC 米兰官方生活方式品牌，源于1899 年英国创始人Herbert Kilpin创立的红黑军团。由俱乐部设计团队操刀，主营球衣、帽衫、T 恤、配饰等，风格融合意式足球文化与街头潮流，标志性红黑配色与魔鬼队徽极具辨识度。采用100% 精梳棉、聚酯纤维运动面料等优质材质，透气舒适、耐穿易洗。风靡全球足球与潮流圈，尤其在欧洲、南美及亚洲，是球迷彰显信仰与时尚态度的首选，诠释 “Milanismo” 精神。</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>PRADA: PRADA, a luxury fashion house from Milan, Italy, is globally renowned for its exquisite craftsmanship, innovative design, and iconic triangle logo. Offering ready-to-wear, handbags, accessories, and fragrances, PRADA delivers signature pieces that blend heritage with contemporary style for those seeking卓越品质 and前瞻美学.</t>
+          <t>Rossoneri AC Milan’s official lifestyle brand, founded by Herbert Kilpin in 1899 (the Rossoneri). Designed by the club’s team, offers jerseys, hoodies, tees, accessories. Blends Italian football culture with streetwear; iconic red-black &amp; devil emblem stand out. Uses premium 100% combed cotton, polyester sport fabrics—breathable, comfy, durable. Popular globally (Europe, S. America, Asia); fans’ top choice for faith &amp; style, embodying “Milanismo.”</t>
         </is>
       </c>
     </row>
     <row r="188" ht="25.5" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PROJECT CAPRI</t>
+          <t>Saint Michael</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>project-capri</t>
-        </is>
-      </c>
-      <c r="C188"/>
-      <c r="D188"/>
+          <t>saint-michael</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Saint Michael由日本设计师细川雄太 (Yuta Hosokawa)与美国艺术家Cali Thornhill DeWitt于2020 年创立，细川负责服装制作，Cali 主理平面设计。主营重磅卫衣、印花 T 恤、水洗牛仔与棒球夹克，风格融合日式复古工艺、美式街头文化与宗教符号，标志性做旧水洗与开裂印花极具辨识度。采用420g 精梳棉、重磅牛仔布等优质材质，手工做旧处理每件独一无二。风靡日美欧潮流圈，受明星与潮流博主追捧，是高端复古街头品牌标杆。</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Saint Michael: Co-founded by Yuta Hosokawa &amp; Cali Thornhill DeWitt (2020). Hosokawa crafts, DeWitt designs graphics. Heavyweight hoodies, tees, denim, jackets. Fusing Japanese vintage craft, American street, religious symbols. Iconic distressed washes, cracked prints; 420g combed cotton, premium denim. Unique hand-distressing. Trendy Japan/US/Europe, celebrity-loved premium retro streetwear.</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="25.5" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PUMA</t>
+          <t>Salvatore Ferragamo</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>puma</t>
+          <t>salvatore-ferragamo</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>PUMA: 1948年由鲁道夫·达斯勒在德国创立，全球知名运动品牌，产品系列涵盖运动鞋、服装及配件，经典款包括PUMA Suede和RS系列，采用高性能材质与环保面料，工艺精湛，功能注重舒适与支撑，风格融合运动与街头潮流。</t>
+          <t>Salvatore Ferragamo由萨尔瓦多・菲拉格慕于1927 年在意大利佛罗伦萨创立，被誉为 "明星鞋匠"。现任创意总监Maximilian Davis，主营鞋履、皮具、成衣、配饰与香水，标志性 Gancini logo 与 Vara 蝴蝶结鞋款闻名。风格融合意式永恒优雅与现代设计，坚持传统手工与创新结构，采用托斯卡纳小牛皮、鳄鱼皮等顶级材质，每双鞋经超 300 道工序。风靡欧美亚，美日中为核心市场，是意大利奢华时尚标杆。</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>PUMA: Founded 1948 Germany by Rudolf Dassler. Global sportswear brand for shoes, apparel &amp; accessories. Iconic PUMA Suede &amp; RS series. High-performance &amp; eco materials. Crafted for comfort, support &amp; street-style fusion.</t>
+          <t>Salvatore Ferragamo: Luxury Italian shoes &amp; leather goods since 1927, "shoemaker to the stars." Iconic Gancini logo, Vara bow. Handcrafted with premium materials, 300+ steps. Global fashion benchmark.</t>
         </is>
       </c>
     </row>
     <row r="190" ht="25.5" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RALPH LAUREN</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ralph-lauren</t>
+          <t>sampdoria</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>RALPH LAUREN：拉夫劳伦是美国标志性的奢侈生活方式品牌，以其经典的Polo衫、精致剪裁的服装、优雅的配饰以及永恒的美式风格而闻名于世。该品牌融合了卓越的工艺、高端品质与休闲优雅，为追求卓越生活品味的消费者提供从服装到家居的全方位奢华体验。</t>
+          <t>Sampdoria: 意大利热那亚的职业足球俱乐部，1946年由桑普达雷内塞和安德雷亚·多利亚两支球队合并成立，主场为路易吉·费拉里斯球场，以标志性蓝白条纹球衣著称，昵称“Blucerchiati（蓝环队）”。队史斩获1次意甲冠军（1990-91赛季）、4次意大利杯冠军及1次欧洲优胜者杯亚军，是意大利足坛兼具历史底蕴与地域辨识度的传统劲旅。</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>RALPH LAUREN: Iconic American luxury lifestyle brand renowned for classic Polo shirts, tailored clothing, elegant accessories, and timeless style, offering premium craftsmanship and sophisticated living.</t>
+          <t>Sampdoria: Genoa Italian football club founded 1946. Blue-white stripes, nicknamed Blucerchiati. 1 Serie A, 4 Coppa Italia, 1 UEFA Cup Winners' Cup runner-up. Traditional powerhouse.</t>
         </is>
       </c>
     </row>
     <row r="191" ht="25.5" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RB LEIPZIG</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>rb-leipzig</t>
+          <t>santos</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>RB LEIPZIG: 2009年成立的德国足球俱乐部，以红牛竞技场为主场，队服采用红白蓝三色设计，采用高性能面料工艺，功能运动专业，风格现代活力，代表球员有蒂莫·维尔纳和达尼·奥尔莫。</t>
+          <t>Santos，巴西桑托斯足球俱乐部生活方式品牌，1912 年由鲁道夫・阿劳霍创立，主营球衣、帽衫、T 恤等，标志性白色底色配黑红细节，采用透气聚酯纤维、精梳棉，风靡巴西及全球足球圈。</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>RB Leipzig: German football club founded in 2009, home at Red Bull Arena. Red-white-blue kits with high-performance fabric, modern, energetic style. Key players: Timo Werner, Dani Olmo.</t>
+          <t>SantosSantos: Brazilian football lifestyle brand founded 1912 by Rudolf Araújo, specializing in jerseys, hoodies, tees. Iconic white with black-red details, breathable polyester &amp; combed cotton, popular in Brazil &amp; global football circles.</t>
         </is>
       </c>
     </row>
     <row r="192" ht="25.5" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>READYMADE</t>
+          <t>Score Draw</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>readymade</t>
-        </is>
-      </c>
-      <c r="C192"/>
-      <c r="D192"/>
+          <t>score-draw</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Score Draw 由Michael Roy Phillips于2002 年 9 月在英国创立，是全球领先官方复古足球服饰品牌。主营官方授权复古球衣、训练服及周边，与 40 余家俱乐部和足协合作，复刻 50 余年超 600 款经典款式。设计团队经精密考证，忠于原版细节，风格为复古经典、怀旧情怀。采用正宗聚酯纤维，透气舒适，还原当年穿着体验。风靡欧洲、北美、澳洲足球圈，深受全球球迷与复古潮流爱好者追捧，是足球文化收藏首选。</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Score Draw: Leading official retro football apparel since 2002 UK. Licensed vintage jerseys, training wear with 40+ clubs, 600+ classic styles. Authentic polyester comfort. Popular globally, top for football culture.</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="25.5" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>REAL MADRID</t>
+          <t>Sicko</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>real-madrid</t>
+          <t>sicko</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>REAL MADRID: 皇家马德里足球俱乐部成立于1902年，是全球最著名的足球俱乐部之一，以其纯白战袍、辉煌历史和顶级球星闻名，主场为伯纳乌球场，代表荣誉包括14次欧冠冠军，风格高贵传奇。</t>
+          <t>Sicko（全称 Sicko Born From Pain）由美国潮流先锋Ian Connor于2018 年创立，本人担任设计师，洛杉矶限量生产。主营重磅卫衣、印花 T 恤、限定配饰，标志性 “Born From Pain” 标语与婴儿头像 Logo 源自 Björk 专辑封面，融合街头文化与个人艺术表达。采用400g + 精梳棉、透气聚酯纤维等优质面料，手工印花工艺提升质感。风靡全球潮流圈，尤受欧美亚千禧一代追捧，是高街街头与限量收藏的热门选择。</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>REAL MADRID: Founded 1902, iconic football club famed for pure white kits, legendary history, top stars, Bernabéu Stadium, 14 UEFA Champions League titles, noble and epic style.</t>
+          <t>Sicko Born From Pain: Ian Connor's 2018 LA limited streetwear. Iconic 'Born From Pain' logo, heavy hoodies, tees, accessories. 400g+ combed cotton, manual print. Global millennial favorite for high-street fashion.</t>
         </is>
       </c>
     </row>
     <row r="194" ht="25.5" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>REVENGE</t>
+          <t>Snapdragon</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>revenge</t>
-        </is>
-      </c>
-      <c r="C194"/>
-      <c r="D194"/>
+          <t>snapdragon</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Snapdragon: 高通（Qualcomm）旗下全球知名移动处理器品牌，专注为智能手机、平板、笔记本及IoT智能设备提供高性能低功耗芯片解决方案，覆盖旗舰（8系列）、中高端（7系列）至主流（6系列）全产品线，核心优势包含5G高速连接、AI智能加速、Adreno图形渲染及Hexagon音频/计算技术，是三星、小米、OPPO等众多品牌旗舰机型的核心处理器选择，持续推动智能设备的体验升级与技术创新。</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Snapdragon: Qualcomm's flagship mobile processor for smartphones, tablets, &amp; IoT. Features 5G, AI, Adreno GPU, Hexagon tech. Powers top brands like Samsung, Xiaomi, OPPO.</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="25.5" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Represent</t>
+          <t>Sp5der</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>represent</t>
+          <t>sp5der</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Represent（瑞普雷森特）2011 年诞生于英国大曼彻斯特郡霍里奇，由 George Heaton 与 Michael Heaton 兄弟创立。核心主线涵盖奢华街头服饰、Owners Club 基础系列、247 性能系列及 Dusk 靴、Alpha 鞋、Reptor 运动鞋等鞋履，主打优质精梳棉、有机羊毛、意大利皮革与高弹技术面料，风格融合英伦传统、现代奢华与街头能量，兼具剪裁考究与技术细节，深受全球时尚爱好者、明星名人与品质追求者青睐，畅销欧美亚市场，由创始人 George Heaton 担任创意总监、Michael Heaton 负责平面设计的内部团队操刀，坚持极致工艺与不懈精进的品牌理念。</t>
+          <t>Sp5der: 美国街头潮牌，由说唱歌手Young Thug创立，以标志性蜘蛛元素为核心设计语言，主打卫衣、T恤、棒球帽等潮流单品，风格融合嘻哈文化与街头时尚，版型宽松舒适且注重细节工艺，深受全球年轻潮流爱好者追捧，是街头文化穿搭的热门选择。</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Founded in 2011 in Horwich, Greater Manchester, UK by brothers George &amp; Michael Heaton, Represent is a luxury streetwear brand. Core lines: premium apparel, Owners Club essentials, 247 performance wear, Dusk boots, Alpha &amp; Reptor sneakers. Crafted with combed cotton, organic wool, Italian leather &amp; technical fabrics. British heritage meets modern luxury street style, loved by global fashion enthusiasts, celebrities; popular in Europe, Americas &amp; Asiarepresentclothing.ltd. Designed by in-house team led by Creative Director George Heaton, focused on meticulous craftsmanship.</t>
+          <t>Sp5der: Young Thug's streetwear brand. Iconic spider designs, hip-hop style, hoodies, tees, caps. Loose fit, detailed craftsmanship. Globally loved by youth culture.</t>
         </is>
       </c>
     </row>
     <row r="196" ht="25.5" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>RHUDE</t>
+          <t>Ss Lazio</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>rhude</t>
-        </is>
-      </c>
-      <c r="C196"/>
-      <c r="D196"/>
+          <t>ss-lazio</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Ss Lazio: 意大利罗马老牌职业足球俱乐部，1900年成立，主场为罗马奥林匹克体育场，征战意甲联赛。曾斩获意甲冠军、意大利杯冠军等荣誉，队服以经典天蓝色与白色为主色调，拥有悠久历史与深厚球迷文化，是意甲联赛的传统劲旅之一。</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Ss Lazio: A renowned professional football club from Rome, Italy, founded in 1900. It competes in Serie A, plays at Stadio Olimpico Rome, and has won Serie A &amp; Coppa Italia titles. Its classic sky-blue &amp; white kits, long history, and strong fan culture make it a traditional Serie A powerhouse.</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="25.5" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>RICK OWENS</t>
+          <t>Ssc Napoli</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>rick-owens</t>
+          <t>ssc-napoli</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>RICK OWENS：瑞克·欧文斯是来自美国的前卫时尚品牌，以其标志性的暗黑哥特美学、建筑感剪裁和颠覆性设计而闻名。该品牌专注于高品质皮革、不对称轮廓及中性化服饰，融合了叛逆精神与奢华质感，为追求独特个性与极致工艺的消费者提供鞋履、服装和配饰。</t>
+          <t>Ssc Napoli: 1926年成立的意大利甲级联赛传统豪门足球俱乐部，主场为迭戈·阿曼多·马拉多纳球场，以激情进攻风格闻名足坛，曾多次夺得意甲冠军、意大利杯冠军等荣誉，蓝白间条队服是其标志性视觉符号，拥有全球狂热的“tifosi”球迷群体，是意甲赛场极具影响力的劲旅之一。</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>RICK OWENS: Avant-garde dark luxury brand since 1994, known for Geobasket sneakers, lamb leather jackets, and innovative leather/cotton/linen designs.</t>
+          <t>Ssc Napoli: Founded in 1926, Serie A club with passionate attacking football, multiple championships, iconic blue-white stripes, and global tifosi fans.</t>
         </is>
       </c>
     </row>
     <row r="198" ht="25.5" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ROBERTO CAVALLI</t>
+          <t>Starboy</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>roberto-cavalli</t>
+          <t>starboy</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>ROBERTO CAVALLI: 意大利奢侈品牌，由 Roberto Cavalli 于 1970 年代创立，以其狂野的动物纹印花、大胆用色和性感设计闻名，产品涵盖服饰、泳装、太阳镜及家居用品，风格奢华奔放，充满激情与自由精神。</t>
+          <t>Starboy（星男孩）由加拿大流行天王The Weeknd于2016 年随同名专辑推出，本人担任创意主导。主营T 恤、连帽衫、夹克、配饰等街头潮流单品，标志性几何黑豹 Logo、暗黑霓虹美学与 "XO" 标识极具辨识度。风格融合高街奢华与街头反叛，以黑、白、红为主色调，剪裁简约利落。采用重磅精梳棉、透气聚酯纤维等优质材质，舒适耐穿。风靡全球年轻群体，尤在欧美、亚洲及澳洲，是潮流穿搭与音乐文化收藏的热门选择。</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ROBERTO CAVALLI: Italian luxury brand known for wild animal prints, bold colors, and sensual designs in apparel, swimwear, sunglasses, and home decor.</t>
+          <t>Starboy: Streetwear by The Weeknd. Iconic panther logo, XO, dark neon aesthetics. High-end streetwear blend in black/white/red. Premium fabrics for global trendsetters.</t>
         </is>
       </c>
     </row>
     <row r="199" ht="25.5" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ROSSONERI</t>
+          <t>Stone Island</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>rossoneri</t>
-        </is>
-      </c>
-      <c r="C199"/>
-      <c r="D199"/>
+          <t>stone-island</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Stone Island: 1982年由Massimo Osti创立于意大利的高端机能服饰品牌，以实验性面料研发与创新工艺为核心特色，标志性技术涵盖热粘合无缝工艺、成衣染色等，产品覆盖机能外套、卫衣、休闲裤等品类，完美融合户外实用功能与都市时尚风格，始终致力于将科技材质与美学设计深度结合，是全球机能风爱好者与高端时尚消费者的首选品牌。</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Stone Island: Founded in Italy by Massimo Osti in 1982, a high-end functional apparel brand focusing on experimental fabric R&amp;D &amp; innovative techniques (heat-bonded seamless, garment dyeing). Products include functional jackets, hoodies, casual pants, blending outdoor utility with urban style, integrating tech materials &amp; aesthetic design—top choice for global functional fashion lovers &amp; high-end consumers.</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="25.5" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SAINT MICHAEL</t>
+          <t>Stray</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>saint-michael</t>
+          <t>stray</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>SAINT MICHAEL: 日本潮流品牌，由宫下贵裕于2020年创立，以其独特的做旧复古风格和高端街头服饰设计闻名。产品涵盖牛仔外套、卫衣、T恤及配饰，采用重磅棉质、水洗牛仔布等材质，注重细节与工艺，风格前卫不羁。</t>
+          <t>Stray（Stray Rats）由Julian Consuegra于2010 年在美国迈阿密创立，后迁至纽约。创始人亲任设计师，主营印花 T 恤、卫衣、帽子及配饰，标志性 90 年代复古图案与朋克元素融合，致敬硬核音乐与街头文化。采用重磅精梳棉、透气聚酯纤维，手工丝网印刷工艺提升质感。风靡全球潮流圈，尤在欧美、日本及东南亚，是高街穿搭与收藏的热门选择，常与 New Balance 等品牌联名。</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>SAINT MICHAEL: Japanese avant-garde streetwear by Takahiro Miyashita. Known for distressed vintage aesthetics, heavyweight cotton &amp; denim. Rebel style.</t>
+          <t>Stray Rats: 2010 Miami streetwear by Julian Consuegra. 90s retro punk prints on tees, hoodies, hats. Honors hardcore music, street culture. Heavyweight cotton, polyester, hand-screen printing. Global trend, high-street, New Balance collabs.</t>
         </is>
       </c>
     </row>
     <row r="201" ht="25.5" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO</t>
+          <t>Stussy</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>salvatore-ferragamo</t>
+          <t>stussy</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO: 1927年由Salvatore Ferragamo创立的意大利奢侈品牌，以精湛制鞋工艺和优雅设计闻名，产品系列包括鞋履、手袋、丝巾及配饰，经典产品有Vara蝴蝶结鞋和Gancini标志单品，采用优质皮革与丝绸材质，工艺细腻，风格奢华经典。</t>
+          <t>Stussy: 1980年由Shawn Stussy创立于美国加州的传奇街头服饰品牌，以标志性手写体LOGO、融合冲浪、滑板与嘻哈文化的设计内核著称，经典产品线覆盖T恤、卫衣、棒球帽等潮流单品，风格主打复古街头与西海岸随性美学，长期引领全球青年潮流文化，是街头时尚爱好者心中的“复古街头符号”级品牌。</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO: Italian luxury brand since 1927, renowned for exquisite footwear, elegant design, leather goods, scarves, and iconic Vara bow shoes &amp; Gancini motifs.</t>
+          <t>Stussy: Founded in California, USA in 1980 by Shawn Stussy, iconic streetwear with signature handwritten logo, fuses surfing, skateboarding &amp; hip-hop. Classics (tees, hoodies, baseball caps) feature retro street &amp; West Coast casual aesthetics, leading global youth fashion—an iconic retro street symbol for streetwear lovers.</t>
         </is>
       </c>
     </row>
     <row r="202" ht="25.5" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SAMPDORIA</t>
+          <t>Supreme</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>sampdoria</t>
+          <t>supreme</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>SAMPDORIA: 意大利桑普多利亚足球俱乐部官方品牌,1946年创立于热那亚,主营球迷服装与周边产品,经典蓝环设计,采用透气涤纶材质,工艺精湛,功能舒适,风格运动激情。</t>
+          <t>Supreme: 1994年创立于美国纽约曼哈顿的标志性街头潮流品牌，以经典红色Box Logo、高频跨界联名（涵盖Nike、Louis Vuitton等顶尖品牌）及限量发售机制闻名，产品覆盖卫衣、T恤、滑板、配件等品类，深度绑定青年文化与反主流精神，是全球潮流爱好者追求的「街头圣品」符号。</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>SAMPDORIA: Italian football club Sampdoria Genoa 1946, official fan wear &amp; merchandise with classic blue ring design, breathable polyester, crafted for comfort &amp; sport passion.</t>
+          <t>Supreme: Iconic streetwear brand founded in Manhattan, NYC (1994), known for classic red Box Logo, frequent collabs (Nike, Louis Vuitton), limited releases, products (hoodies, tees, skateboards, accessories), tied to youth culture &amp; anti-mainstream spirit—global streetwear icon for enthusiasts.</t>
         </is>
       </c>
     </row>
     <row r="203" ht="25.5" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>Saint Laurent</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>santos</t>
-        </is>
-      </c>
-      <c r="C203"/>
-      <c r="D203"/>
+          <t>Saint Laurent</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Saint Laurent: 1961年由伊夫·圣罗兰（Yves Saint Laurent）创立的法国奢侈品牌，以先锋叛逆的法式酷感风格横扫时尚界，核心覆盖高级时装、成衣、皮具（如Niki包、LouLou包）、鞋履、美妆及香水等品类。品牌标志性元素包括YSL字母标识、Monogram图案，以及打破性别边界的经典吸烟装（Le Smoking）——首次将男性西装剪裁融入女装，重塑时尚规则。从秀场级设计到日常奢华单品，Saint Laurent始终融合优雅与街头感，是全球潮流爱好者追崇的“酷感奢华”代表，持续传递“打破传统、定义自我”的品牌精神。</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Saint Laurent: French luxury brand founded 1961 by Yves Saint Laurent, famed for avant-garde rebellious French cool. Covers haute couture, ready-to-wear, leather goods (Niki, LouLou bags), footwear, beauty, fragrances. Iconic YSL monogram, genderless Le Smoking tuxedo (redefined fashion with men’s tailoring in women’s wear). Blends elegance &amp; streetwear, a “cool luxury” icon conveying “break tradition, define self” spirit.</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="25.5" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SCORE DRAW</t>
+          <t>So Paulo</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>score-draw</t>
-        </is>
-      </c>
-      <c r="C204"/>
-      <c r="D204"/>
+          <t>so-paulo</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>São Paulo（圣保罗足球俱乐部）1930 年由 Firmiano de Morais Pinto Filho 等创立，德国设计师 Walter Ostrich 设计队徽，主营官方球衣、训练服、休闲服饰及配饰，由 New Balance 等品牌操刀设计，标志性白底色配红黑横条纹，象征圣保罗市旗与俱乐部 “信仰、希望、慈善” 理念。采用透气聚酯纤维、AEROREADY 速干面料，舒适耐穿，风靡巴西及全球足球圈，是南美足坛顶级豪门标志性服饰。</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>São Paulo: Founded 1930, São Paulo FC iconic white/red/black stripes symbolize city flag &amp; "faith, hope, charity". New Balance kits/apparel with AEROREADY fabric. Top South American football club.</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="25.5" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SICKO</t>
+          <t>The North Face</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>sicko</t>
-        </is>
-      </c>
-      <c r="C205"/>
-      <c r="D205"/>
+          <t>the-north-face</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>The North Face: 1966年创立于美国旧金山，全球专业户外装备领导品牌，专注研发高性能登山、徒步、滑雪等场景装备，经典产品涵盖Summit系列专业冲锋衣、MCMURDO保暖羽绒服、VECTIV轻量化登山鞋等，核心技术搭载Gore-Tex®防水透气膜、Responsible Down Standard认证鹅绒填充及TNF Apex™耐磨面料，兼顾极端环境适应性与日常机能需求，为专业户外爱好者与城市轻户外人群提供耐用、环保的装备选择，风格融合硬核功能性与经典户外美学。</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>The North Face: Founded in San Francisco, USA (1966), global leading pro outdoor gear brand. Specializes in high-performance mountaineering, hiking, skiing gear—signature products: Summit Series hardshells, MCMURDO down jackets, VECTIV hiking shoes. Features Gore-Tex® membranes, RDS-certified down, TNF Apex™ fabrics. Balances extreme adaptability &amp; daily function for pros/urban light outdoor users, blending hardcore functionality with classic outdoor aesthetics.</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="25.5" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SNAPDRAGON</t>
+          <t>Thug Club</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>snapdragon</t>
+          <t>thug-club</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>SNAPDRAGON: 高通公司旗下移动计算平台品牌，以其强大的性能和能效比著称，广泛应用于高端智能手机和平板电脑等移动设备，为用户提供流畅的使用体验和出色的图形处理能力。</t>
+          <t>Thug Club 由Thug Min与Jiyool Kwon于2018 年在韩国首尔梨泰院创立。主打宽松 T 恤、美式夹克、做旧牛仔及铆钉配饰，融合嘻哈、机车文化与反叛街头风。采用高品质棉料与耐用牛仔，质感硬朗。风靡全球潮流圈，获 A$AP Rocky、SZA 等明星追捧，是韩系街头潮流代表品牌。</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>SNAPDRAGON: Qualcomm's premium mobile platform for high-end smartphones &amp; tablets, delivering powerful performance, energy efficiency &amp; superior graphics for seamless user experiences.</t>
+          <t>Thug Club: Seoul-based streetwear since 2018. Oversized tees, vintage denim, &amp; rebel biker style. Premium cotton &amp; hard-wearing fabrics. Worn by A$AP Rocky, SZA.</t>
         </is>
       </c>
     </row>
     <row r="207" ht="25.5" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SP5DER</t>
+          <t>Tom Ford</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>sp5der</t>
+          <t>tom-ford</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>SP5DER：SP5DER品牌是您值得信赖的跨境电商伙伴，专注于提供创新与高品质的时尚产品。我们致力于将前沿设计与卓越性能相结合，为全球消费者带来独特的在线购物体验。探索SP5DER，发现更多时尚可能性。</t>
+          <t>Tom Ford: 2005年由美国设计师Tom Ford创立的高端奢侈品牌，以性感奢华、现代先锋的风格著称，产品线覆盖美妆（经典Lip Color口红、Black Orchid香水）、高级成衣、皮具、眼镜及腕表等领域，甄选丝绒、小羊皮、稀有香原料等顶级材质，工艺精湛，精准契合全球追求品质与独特个性的高端消费者需求，是奢华时尚与创新设计的标志性代表。</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>SP5DER: Innovative, high-quality fashion brand merging cutting-edge design with performance for a unique global e-commerce shopping experience.</t>
+          <t>Tom Ford: Founded by American designer Tom Ford in 2005, a high-end luxury brand celebrated for sexy luxury &amp; modern avant-garde style. Product lines include beauty (iconic Lip Color lipstick, Black Orchid perfume), ready-to-wear, leather goods, eyewear &amp; watches. Uses premium materials (velvet, lambskin, rare fragrance ingredients) with exquisite craftsmanship, catering to global high-end consumers seeking quality &amp; unique personality. An iconic symbol of luxury fashion &amp; innovative design.</t>
         </is>
       </c>
     </row>
     <row r="208" ht="25.5" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SS LAZIO</t>
+          <t>Tommy Hilfiger</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ss-lazio</t>
+          <t>tommy-hilfiger</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>SS LAZIO: 1900年成立于意大利罗马的传奇足球俱乐部，以其天蓝色球衣和雄鹰标志闻名，提供官方正品球衣、训练装备及潮流服饰，采用高性能透气材质，工艺精湛，风格融合运动精神与意大利时尚，代表忠诚与激情。</t>
+          <t>Tommy Hilfiger: 1985年由同名设计师Tommy Hilfiger创立的美国经典休闲时尚品牌，以标志性红白蓝三色logo、预ppy（预科生）风格及高品质棉质面料为核心特色，产品覆盖男装、女装、童装、配饰与香水，融合美式复古底蕴与现代简约设计，打造日常百搭且具高端休闲感的服饰单品，是全球追求经典时尚、舒适质感人群的首选品牌之一。</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>SS LAZIO: Founded 1900 Rome, legendary Italian football club. Iconic sky-blue jersey &amp; eagle emblem. Official kits, training gear &amp; fashion. High-performance breathable fabric, crafted with excellence. Blends sport spirit with Italian style, representing loyalty &amp; passion.</t>
+          <t>Tommy Hilfiger: Founded in 1985 by its eponymous designer, this iconic American casual fashion brand boasts signature red-white-blue logo, preppy style, and premium cotton fabrics. It offers apparel (men, women, kids), accessories, and fragrances, blending American retro roots with modern minimalist design for versatile high-end casual pieces—top choice for classic fashion &amp; comfort seekers.</t>
         </is>
       </c>
     </row>
     <row r="209" ht="25.5" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SSC NAPOLI</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ssc-napoli</t>
+          <t>tottenham-hotspur</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>SSC NAPOLI: 意大利知名足球俱乐部品牌，推出运动服饰与周边产品，融合经典蓝白配色与高性能面料，工艺精湛，设计时尚，为球迷和运动爱好者提供兼具团队精神与舒适功能的休闲运动装备。</t>
+          <t>Tottenham Hotspur: 1882年成立于伦敦的英超足球俱乐部，主场为托特纳姆热刺球场，以进攻足球与青训体系闻名。经典白色球衣与公鸡标志传承百年，现代风格融合激烈比赛与卓越球员培养，吸引全球球迷关注。</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>SSC NAPOLI: Italian football club's sportswear &amp; gear with classic blue-white design, high-performance fabrics, stylish and comfortable for fans.</t>
+          <t>Tottenham Hotspur: London Premier League club since 1882, attacking football and youth academy, iconic white kit with cockerel emblem, modern play and player development, global fans.</t>
         </is>
       </c>
     </row>
     <row r="210" ht="25.5" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>STARBOY</t>
+          <t>Trapstar</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>starboy</t>
-        </is>
-      </c>
-      <c r="C210"/>
-      <c r="D210"/>
+          <t>trapstar</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Trapstar: 2005年由Mikey Trapstar、Lee Trapstar与Will Trapstar创立于英国伦敦，是扎根街头文化与trap音乐精神的潮流品牌。以标志性星型LOGO、反光材质及军事风剪裁为核心设计符号，产品覆盖卫衣、夹克、配饰等街头单品，曾与Nike、Puma等品牌推出联名系列，深受追求个性表达、热爱街头亚文化与音乐的年轻群体喜爱。</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Trapstar: Founded in London, UK (2005) by Mikey, Lee &amp; Will Trapstar, a streetwear brand rooted in street culture &amp; trap music spirit. Core design: signature star logo, reflective materials, military cuts. Offers hoodies, jackets, accessories. Collaborated with Nike, Puma. Loved by self-expressive young fans of street subculture &amp; music.</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="25.5" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>STONE ISLAND</t>
+          <t>Travis Scott</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>stone-island</t>
+          <t>travis-scott</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>STONE ISLAND: 探索意大利奢华机能服饰品牌STONE ISLAND，以其标志性的罗盘臂章、创新的面料研发与染色技术闻名。从防风夹克到高科技针织衫，STONE ISLAND 服饰融合前沿科技与意式设计，为追求功能与风格的都市探索者打造持久耐用的高品质服装。立即选购经典系列与最新单品，体验机能美学的独特魅力。</t>
+          <t>Travis Scott: 美国知名说唱歌手、音乐制作人兼时尚设计师，以其独特音乐风格和跨界联名系列在全球潮流界备受瞩目。品牌产品涵盖联名鞋款、街头服饰及配饰，采用创新设计、优质材质和标志性元素，融合嘻哈文化与高端时尚，风格前卫。经典合作如Travis Scott x Nike Air Jordan系列，深受年轻消费者和收藏家喜爱，推动全球潮流文化发展。</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>STONE ISLAND: Italian luxury techwear with iconic compass badge. Innovative fabric &amp; dye tech for durable, stylish urban gear. Shop classic &amp; new collections.</t>
+          <t>Travis Scott: Renowned rapper and designer. Iconic Travis Scott x Nike Air Jordan collaborations. Streetwear, sneakers, and accessories. Merging hip-hop with high-fashion innovation.</t>
         </is>
       </c>
     </row>
     <row r="212" ht="25.5" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>STRAY</t>
+          <t>True Religion</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>stray</t>
-        </is>
-      </c>
-      <c r="C212"/>
-      <c r="D212"/>
+          <t>true-religion</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>True Religion: 2002年创立于美国的高端牛仔品牌，以标志性马蹄形（Horseshoe）缝线设计、顶级牛仔布材质及精湛水洗工艺闻名，主打男士/女士牛仔裤、牛仔外套及休闲服饰，融合美式复古与街头潮流风格，是追求个性与高品质牛仔单品的消费者首选品牌。</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>True Religion: Founded in the US in 2002, a high-end denim brand renowned for iconic Horseshoe stitching, premium denim, and exquisite wash techniques. Offers men’s/women’s jeans, denim jackets, casual apparel, blending American retro with streetwear—top choice for consumers seeking individuality &amp; high-quality denim.</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="25.5" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>STUSSY</t>
+          <t>Umbro</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>stussy</t>
+          <t>umbro</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>STUSSY：Stussy 是源自美国加州的街头潮流品牌，由 Shawn Stussy 于 1980 年代创立。品牌以其标志性的手写签名 logo 和冲浪、滑板、嘻哈文化融合的独特风格而闻名。Stussy 提供高品质的 T 恤、帽衫、帽子及配饰，深受全球青年文化爱好者的追捧，代表着原创、自由与地道的街头精神。</t>
+          <t>Umbro: 1924年创立于英国的专业足球运动装备品牌，以标志性双钻石LOGO著称，深耕足球领域近百年，曾长期为英格兰国家队等顶级球队提供球衣装备。产品覆盖专业足球衣、训练服、足球鞋及配件，融合英伦经典设计与运动科技，专注为球员与球迷打造兼具性能与复古质感的足球装备，传承纯粹足球精神。</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>STUSSY: Original California streetwear brand founded by Shawn Stussy. Known for iconic signature logo, surf, skate, hip-hop culture, and premium tees, hoodies, and accessories.</t>
+          <t>Umbro: Founded in 1924 in England, iconic double diamond logo. Professional football gear, kits, footwear &amp; accessories. Merges classic British design with sport tech for players &amp; fans, honoring pure football heritage.</t>
         </is>
       </c>
     </row>
     <row r="214" ht="25.5" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SUPREME</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>supreme</t>
-        </is>
-      </c>
+          <t>UGG</t>
+        </is>
+      </c>
+      <c r="B214"/>
       <c r="C214" t="inlineStr">
         <is>
-          <t>ECCO: ECCO 是源自丹麦的全球知名鞋履及皮具品牌，以其卓越的舒适度、创新科技与北欧简约设计而闻名。品牌致力于使用优质皮革和环保工艺，为全球消费者提供从正装鞋、休闲鞋到户外运动鞋的全系列高品质产品，满足日常穿着与专业需求。
-Samsonite: Samsonite 是全球领先的旅行箱包品牌，以其坚固耐用、创新设计和卓越安全性著称。品牌产品涵盖拉杆箱、背包、商务包等，采用先进材料与科技，为商务人士和旅行者提供可靠且时尚的出行解决方案，守护每一段旅程。
-TUMI: TUMI 是源自美国的高端旅行、商务及生活方式品牌，以其精湛工艺、功能性设计和耐用材质备受推崇。品牌核心的弹道尼龙系列产品尤为知名，为全球旅行者和专业人士提供兼具优雅外观与卓越实用性的箱包、配件及服饰。
-LEGO: LEGO 是来自丹麦的全球知名玩具品牌，以其标志性的乐高积木系统激发各年龄段儿童的创造力、想象力与学习能力。通过主题套装、电子游戏及影视作品，乐高致力于通过“在玩乐中学习和发展”的理念，为家庭带来无尽的建造乐趣。
-Waterpik: Waterpik 是口腔护理领域的创新领导者，以其高效的水牙线（冲牙器）产品而闻名全球。品牌产品通过脉冲水流技术，能有效清除牙缝和牙龈线下的食物残渣与牙菌斑，是传统牙线的重要补充，助力用户实现更彻底的口腔清洁和牙龈健康。</t>
+          <t>UGG: 源自澳大利亚的经典保暖鞋服品牌，以标志性羊皮毛一体雪地靴闻名，核心产品涵盖Classic Short经典短靴、Cozy Slide拖鞋及羊毛外套等，采用优质美利奴羊毛与天然皮革材质，主打“温暖不厚重、舒适又时尚”的设计理念，满足冬季保暖及日常休闲穿搭需求，是全球注重质感与舒适度的消费者首选的保暖时尚品牌。</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>SUPREMESUPREME: Explore the latest Supreme collaborations and limited-edition streetwear. Renowned for unique designs, premium materials, and iconic Box Logo. Shop now for clothing, accessories, and skate gear.</t>
+          <t>UGGUGG: Australian brand iconic for sheepskin boots, Classic Short, Cozy Slide, and wool coats. Made with Merino wool and leather for warm, comfortable, stylish winter and casual wear.</t>
         </is>
       </c>
     </row>
     <row r="215" ht="25.5" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Saint Laurent</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Saint Laurent</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Saint Laurent: 1961年由Yves Saint Laurent创立的法国奢侈品牌，以现代优雅设计闻名，产品系列包括时装、手袋、鞋履及配饰，经典产品有Sac de Jour手袋和Tribute高跟鞋，采用顶级皮革与金属材质，工艺精湛，风格融合经典与前卫，展现奢华时尚魅力。</t>
+          <t>Valencia: （因未提供该品牌的具体中文描述信息，无法生成符合要求的SEO优化品牌描述。）</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Saint Laurent: French luxury brand since 1961, known for modern elegance in fashion, handbags, footwear, and accessories. Features iconic Sac de Jour and Tribute heels with premium leather and metal craftsmanship.</t>
+          <t>Valencia: Due to the lack of specific Chinese description of the brand, we cannot generate a compliant SEO-optimized brand description.</t>
         </is>
       </c>
     </row>
     <row r="216" ht="25.5" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>SÃO PAULO</t>
+          <t>Valentino</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>so-paulo</t>
-        </is>
-      </c>
-      <c r="C216"/>
-      <c r="D216"/>
+          <t>valentino</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Valentino: 1960年由Valentino Garavani创立的意大利顶级奢侈品牌，以高级时装、皮具、鞋履、配饰及美妆为核心产品线，标志性元素包括VLogo标识、Rockstud铆钉系列与经典Valentino Red（华伦天奴红），风格融合奢华、浪漫与经典，凭借精湛工艺与独特设计，成为全球追求高端时尚品味人群的首选品牌之一。</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Valentino: Founded 1960 by Valentino Garavani, Italian luxury house for haute couture, leather goods, accessories. Iconic VLogo, Rockstuds, Valentino Red. Fusion of luxury, romantic, timeless Italian craftsmanship.</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="25.5" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>THE NORTH FACE</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>the-north-face</t>
+          <t>vans</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>THE NORTH FACE：探索永不停止。The North Face 是源自美国的顶尖户外运动品牌，为全球探险家与户外爱好者提供高性能装备。从专业登山服饰、保暖羽绒服到耐用背包与帐篷，我们采用尖端科技面料，致力于应对极端气候与严苛环境。无论是征服世界之巅，还是探索城市近郊，The North Face 产品皆以卓越的防护性、舒适度与耐用性，助力每一次突破极限的旅程。我们坚信，探索的精神存在于每个人心中。</t>
+          <t>Vans: 1966年由Paul Van Doren等创立于美国加州，全球街头潮流与滑板文化的标志性品牌，以“Off The Wall”的自由叛逆精神为内核。经典产品涵盖Authentic、Old Skool、Sk8-Hi等帆布/麂皮滑板鞋款，标志性棋盘格图案、侧边条纹设计深入人心，融合耐用工艺与青年创意表达，成为滑板运动、街头时尚及亚文化群体的核心选择。</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>THE NORTH FACE: Never Stop Exploring. The North Face delivers high-performance outdoor gear for global explorers. Using advanced fabric technology, our professional登山 apparel, insulated jackets, durable packs, and tents protect against extreme conditions. Empowering every journey from summits to city outskirts.</t>
+          <t>Vans: Iconic skate/streetwear brand since 1966, "Off The Wall" spirit. Durable canvas/suede shoes: Authentic, Old Skool, Sk8-Hi. Signature checkerboard &amp; side stripe for youth culture.</t>
         </is>
       </c>
     </row>
     <row r="218" ht="25.5" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>THUG CLUB</t>
+          <t>Vasco Da Gama</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>thug-club</t>
+          <t>vasco-da-gama</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>THUG CLUB: 创立于2017年的中国街头潮牌，融合嘻哈文化与运动精神，产品涵盖oversize卫衣、印花T恤、工装裤及限定联名款，采用高磅数棉料与做旧工艺，以标志性骷髅字母logo和黑橙撞色设计诠释叛逆不羁的街头美学。</t>
+          <t>Vasco Da Gama: （由于未提供该品牌的中文描述内容，无法生成符合要求的SEO优化品牌描述。）</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>THUG CLUB: China streetwear brand since 2017. Merges hip-hop with sport spirit, features oversized hoodies, graphic tees, cargo pants &amp; collabs. Heavyweight cotton, vintage washes. Rebel aesthetic with iconic skull logo and black-orange contrast.</t>
+          <t>Vasco Da Gama: (Due to the lack of Chinese description of the brand, we cannot generate a compliant SEO-optimized brand description.)</t>
         </is>
       </c>
     </row>
     <row r="219" ht="25.5" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>TOM FORD</t>
+          <t>Versace</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>tom-ford</t>
+          <t>versace</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>TOM FORD: 1994年由汤姆·福特创立的美国奢侈品牌，以高级时装、香水和美妆产品闻名，经典产品包括黑管唇膏和 oud wood 香水，采用奢华材质与精湛工艺，风格性感现代，尽显高端魅力。</t>
+          <t>Versace: 1978年由詹尼·范思哲（Gianni Versace）创立于意大利米兰的奢华时尚品牌，以标志性美杜莎头像、巴洛克印花及大胆撞色为核心视觉符号，涵盖高级时装、成衣、皮具、鞋履、配饰、香水与家居系列，风格融合意大利复古奢华与性感张扬，凭借精湛工艺与先锋设计成为全球红毯、名流及时尚爱好者追捧的高端时尚象征，诠释“致命诱惑”的品牌精神。</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>TOM FORD: Luxury American brand since 1994 for high-end fashion, perfumes, and makeup. Known for iconic lipsticks and Oud Wood fragrance with exquisite craftsmanship and sensual modern elegance.</t>
+          <t>Versace: Italian luxury fashion since 1978, iconic Medusa &amp; Baroque prints, bold colors. Haute couture, accessories, perfumes. Style: retro luxury meets sexy flamboyance. High-end for red carpets, celebrities. Spirit: fatal attraction.</t>
         </is>
       </c>
     </row>
     <row r="220" ht="25.5" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>TOMMY HILFIGER</t>
+          <t>Vetements</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>tommy-hilfiger</t>
+          <t>vetements</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>TOMMY HILFIGER:
-1985年由汤米·希尔费格创立的美国休闲服饰品牌，产品系列涵盖男装、女装、童装及配饰，经典产品包括标志性红白蓝Logo衬衫和学院风夹克，采用棉质、丹宁等舒适材质，工艺精致，风格经典美式休闲，兼具时尚与实用性。</t>
+          <t>Vetements: 2014年由Demna Gvasalia与Guram Gvasalia创立于法国的高端街头服饰品牌，以解构主义设计、oversize版型及标志性标语印花为核心特色，融合街头文化与高级时装美学，推出卫衣、外套、配饰等系列单品，曾与Reebok、Juicy Couture等品牌联名，深受追求个性潮流与先锋风格的时尚爱好者喜爱。</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>TOMMY HILFIGER: American classic leisurewear since 1985, iconic red-white-blue logo shirts, collegiate jackets, premium cotton denim comfort.</t>
+          <t>Vetements: French high-end streetwear brand founded 2014, known for deconstructivist designs, oversize fits, slogan prints. Merges street culture with high fashion. Offers hoodies, jackets, accessories. Collaborations with Reebok, Juicy Couture. Loved by avant-garde fashion enthusiasts.</t>
         </is>
       </c>
     </row>
     <row r="221" ht="25.5" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>TOTTENHAM HOTSPUR</t>
+          <t>Vicinity</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>tottenham-hotspur</t>
+          <t>vicinity</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>TOTTENHAM HOTSPUR:  
-托特纳姆热刺足球俱乐部成立于1882年，是英格兰足球超级联赛的知名球队，主场为托特纳姆热刺球场。球队经典产品包括主场白色球衣及复古训练服，采用高性能透气材质与先进工艺，功能舒适耐用，风格经典与现代融合，代表拼搏与激情。</t>
+          <t>Vicinity 是源自澳大利亚的轻奢休闲街头品牌，由本土设计师团队于2015 年创立。主营都市休闲卫衣、简约衬衫、百搭裤装及轻户外穿搭，坚持本土原创设计。风格主打极简通勤、轻户外休闲，利落百搭适配日常。采用优质纯棉、透气梭织、环保再生面料，舒适亲肤。风靡澳新、欧美及亚太地区，是都市轻休闲穿搭的热门选择。</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>TOTTENHAM HOTSPUR: Premier League club since 1882. Classic white jerseys &amp; retro training gear with high-performance, breathable fabrics for comfort and durability.</t>
+          <t>Vicinity: Australian luxury casual streetwear since 2015. Local designers craft urban essentials, minimalist commute to light outdoor styles. Premium cotton, breathable woven, eco fabrics. Popular in Australia, NZ, US, EU, Asia-Pacific.</t>
         </is>
       </c>
     </row>
     <row r="222" ht="25.5" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>TRAPSTAR</t>
+          <t>(Vivi)VivienneWestwood</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>trapstar</t>
+          <t>VivienneWestwood</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>TRAPSTAR：英国潮牌TRAPSTAR以叛逆精神与街头文化为核心，融合音乐、艺术与时尚，打造标志性的徽标设计与前卫服饰。其产品涵盖服装、配饰及联名系列，以大胆图形与地下美学诠释当代青年态度，是全球街头潮流爱好者彰显个性的热门选择。</t>
+          <t>VivienneWestwood: 1971年由英国设计师Vivienne Westwood创立，时尚品牌以朋克和反叛风格著称，产品系列包括服装、配饰、珠宝及鞋履，经典元素有土星标志、格子图案和夸张剪裁，采用皮革、面料等多样材质，工艺创新独特，风格前卫叛逆，融合时尚与艺术，深受全球潮流人士喜爱。</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>TRAPSTAR: UK streetwear brand fusing rebellion, music, and art. Known for iconic logos, bold graphics, and underground aesthetic in apparel and accessories. A global symbol of youth attitude.</t>
+          <t>Vivienne Westwood: Punk rebellious fashion brand since 1971, offering clothing, accessories, jewelry, footwear with Saturn logo, tartan patterns, exaggerated cuts. Uses leather, fabrics, innovative avant-garde style fusing fashion and art, loved globally.</t>
         </is>
       </c>
     </row>
     <row r="223" ht="25.5" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>TRAVIS SCOTT</t>
+          <t>Vlone</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>travis-scott</t>
+          <t>vlone</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>TRAVIS SCOTT: Travis Scott 是风靡全球的潮流文化品牌，由美国著名音乐人、时尚偶像特拉维斯·斯科特创立。品牌以其标志性的迷幻美学、大胆设计和音乐节联名系列而闻名，产品涵盖潮流服饰、鞋履及配饰。它融合了街头文化与高端时尚，代表了年轻一代的叛逆精神与创造力，深受全球潮流爱好者与收藏家的追捧。</t>
+          <t>Vlone: 由A$AP Rocky与A$AP Bari共同创立的美国街头潮流品牌，以标志性V字Logo、“Live Vlone, Die Vlone”核心标语为识别，融合嘻哈文化与叛逆精神，主打T恤、卫衣、帽款及配件等单品，凭借街头感设计与社群共鸣，成为全球潮流爱好者追捧的街头文化符号。</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>TRAVIS SCOTT: Travis Scott, a global trendsetter brand by the iconic artist, fuses streetwear with high fashion. Known for its psychedelic aesthetic, bold designs, and festival collaborations in apparel, footwear, and accessories. Embodies youth rebellion and creativity.</t>
+          <t>Vlone: Streetwear brand by A$AP Rocky &amp; Bari. Iconic V logo, "Live Vlone, Die Vlone" mantra. Hip-hop infused, rebellious essentials – tees, hoodies, caps. A global street culture symbol.</t>
         </is>
       </c>
     </row>
     <row r="224" ht="25.5" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>TRUE RELIGION</t>
+          <t>Yeezy</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>true-religion</t>
+          <t>yeezy</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>TRUE RELIGION: 2002年由Jeff Lubell创立的美国牛仔品牌，以标志性马蹄标志和优质牛仔服饰闻名，产品系列包括牛仔裤、上衣和配饰，采用高品质牛仔布和独特洗水工艺，风格融合复古与奢华，舒适耐穿。</t>
+          <t>Yeezy: 由美国创作歌手坎耶·维斯特（Kanye West）创立的全球街头潮流标杆品牌，以“椰子鞋”系列奠定潮流地位，核心鞋款融合Boost缓震科技、大地色系极简设计与街头基因，标志性产品如Yeezy Boost 350 V2、Yeezy 500等成为sneaker文化符号，主打“舒适与先锋时尚兼具”的理念，覆盖鞋履、服饰等品类，是街头美学与高端运动属性结合的代表，深受潮流爱好者与收藏家追捧。</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>TRUE RELIGION: Iconic American denim brand since 2002, renowned for premium jeans, tops &amp; accessories with signature horseshoe logo. Luxury vintage style, superior comfort &amp; durability.</t>
+          <t>Yeezy: Global streetwear icon founded by U.S. artist Kanye West. Core styles (Yeezy Boost 350 V2, 500) feature Boost cushioning, earth-tone minimal design &amp; street DNA—sneaker culture symbols. Blends street aesthetics with high-end sport, offering footwear/apparel for comfort &amp; avant-garde fashion, sought after by streetwear fans &amp; collectors.</t>
         </is>
       </c>
     </row>
     <row r="225" ht="25.5" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>True Religion</t>
+          <t>Yora</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>True-Religion</t>
+          <t>yora</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>True Religion: 2002年由Jeff Lubell创立的美国高端牛仔品牌，以标志性马蹄标和V形缝合闻名，产品系列包括牛仔裤、服装及配饰，经典产品有Super T牛仔裤，采用优质丹宁和皮革材质，工艺精湛，功能舒适耐用，风格复古奢华。</t>
+          <t>Yora 是德国波恩可持续街头服饰品牌，由本土设计师团队于2018 年创立。主营重磅 T 恤、宽松卫衣、立体剪裁裤装及环保配饰，坚持原创设计与青年艺术家合作。风格主打极简街头、可持续时尚，标志性环保认证标识醒目。采用GOTS 认证有机棉、OEKO-TEX 100 环保面料，植物基油墨印花，全系列 PETA 素食认证。风靡德奥、北欧及欧美潮流圈，是环保街头穿搭热门之选。</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>True Religion: Luxury denim brand since 2002, iconic horseshoe logo, premium jeans like Super T, V-stitch details, retro style with comfort and durability.</t>
+          <t>Yora: Sustainable streetwear from Bonn, 2018. Heavy tees, loose hoodies, tailored pants, eco accessories. Minimalist style, artist collaborations. GOTS organic cotton, OEKO-TEX, plant-based ink. PETA vegan certified. Popular in DACH, Nordic, EU/US.</t>
         </is>
       </c>
     </row>
     <row r="226" ht="25.5" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>UMBRO</t>
+          <t>Yves Saint Laurent</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>umbro</t>
+          <t>yves-saint-laurent</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>UMBRO: 1924年由英国汉弗莱斯兄弟创立，专注足球运动装备的品牌，产品系列包括专业足球鞋、运动服装及训练配件，经典产品有Speciali足球鞋和钻石双菱形标志系列，采用高性能合成材质，工艺注重细节与耐用性，功能突出透气与灵活性，风格经典运动兼具现代时尚。</t>
+          <t>Yves Saint Laurent: 1961年由伊夫·圣罗兰（Yves Saint Laurent）与皮埃尔·贝尔热（Pierre Bergé）创立的法国高端奢侈品牌，以先锋设计、性别流动美学与法式优雅著称，核心业务覆盖高级时装、美妆、皮具、香水及配饰。经典产品包括标志性“鸦片（Opium）”香水、Monogram帆布手袋、“自由之水（Libre）”香水与“高能腮红（Power Blush）”，融合艺术感与奢华质感，是全球时尚爱好者追捧的奢华符号，诠释“时尚是一种态度”的品牌理念。</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>UMBRO: Since 1924, UK's iconic football brand. Performance soccer cleats, apparel &amp; training gear. Classic Speciali boots &amp; diamond logo series. Durable, breathable &amp; flexible.</t>
+          <t>Yves Saint Laurent: Founded in 1961 by Yves Saint Laurent &amp; Pierre Bergé, French luxury brand known for avant-garde design, gender-fluid aesthetics, French elegance. Core: haute couture, beauty, leather goods, fragrances, accessories. Icons: Opium fragrance, Monogram handbags, Libre perfume, Power Blush. Blends artistry &amp; luxury, sought-after by global fashion lovers, embodies “Fashion is an attitude.”</t>
         </is>
       </c>
     </row>
     <row r="227" ht="25.5" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>UGG</t>
-        </is>
-      </c>
-      <c r="B227"/>
+          <t>Zara</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>zara</t>
+        </is>
+      </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>UGG: 作为全球知名的澳大利亚羊皮靴品牌，UGG以其舒适、保暖与经典设计而闻名。我们精选优质羊皮，打造出四季皆宜的鞋履、服饰与配饰，为追求自然舒适生活方式的消费者提供高品质选择。探索UGG系列，体验从脚底升起的温暖与时尚。</t>
+          <t>Zara: 1975年创立于西班牙的快时尚领导品牌，隶属于Inditex集团，以“快速反应”供应链模式著称，产品覆盖男女装、童装及配饰，风格紧跟全球潮流、时尚百搭，兼具高性价比与前沿设计，是年轻群体追求即时时尚的核心选择。</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>UGG: Australian sheepskin boots brand globally renowned for comfort, warmth, and classic design. We craft premium sheepskin into year-round footwear, apparel, and accessories for a natural, comfortable lifestyle.</t>
+          <t>Zara: Spanish fast-fashion leader since 1975. Features trendy, versatile apparel &amp; accessories for all, offering high-style designs at great value through its agile supply chain.</t>
         </is>
       </c>
     </row>
     <row r="228" ht="25.5" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>Zwball</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>zwball</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>VALENCIA: 1996年创立的西班牙时尚品牌，以现代简约设计闻名，产品涵盖女装、配饰及家居用品，经典系列包括刺绣连衣裙和手工编织包，采用天然棉麻材质与传统工艺，风格优雅自然，兼具舒适性与艺术感。</t>
+          <t>ZWOBALL 由日本DropFlava团队于2013 年创立，专注自由式足球装备。创始人亲任设计，主营足球、训练服、花式球鞋及配件，标志性流线型 Logo 与动感街头元素鲜明。风格融合运动活力与潮流个性，适配花式足球与日常穿搭。采用耐磨橡胶、透气聚酯纤维、弹力氨纶，耐用回弹佳。风靡日本、欧美及亚洲足球圈，是自由式足球爱好者的热门选择。</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>VALENCIA: Spanish fashion brand since 1996, known for modern minimalist design. Features embroidered dresses, handwoven bags, and home goods using natural cotton/linen with traditional craftsmanship. Elegant, natural, and artfully comfortable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" ht="25.5" customHeight="1">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>VALENTINO</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>valentino</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>VALENTINO: 华伦天奴是意大利奢侈时尚品牌，以其高级定制、精湛工艺和标志性铆钉元素闻名。品牌融合经典优雅与当代设计，提供包括女装、男装、配饰及香氛在内的全线产品，致力于为全球时尚爱好者打造彰显个性与品味的奢华体验。</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>VALENTINO: Explore luxury Italian fashion with haute couture gowns, elegant handbags &amp; iconic rockstud shoes. Shop ready-to-wear &amp; accessories. Global shipping.</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" ht="25.5" customHeight="1">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>VANS</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>vans</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>VANS: 1966年由保罗·范·多伦创立的美国经典运动品牌，以滑板鞋和街头服饰闻名，产品系列包括休闲鞋、服装及配件，经典款有Old Skool和Authentic，采用帆布和麂皮材质，工艺扎实，功能舒适耐用，风格叛逆复古。</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>VANS: Since 1966 by Paul Van Doren. Classic American skate &amp; streetwear brand for sneakers, apparel &amp; accessories. Famous for Old Skool &amp; Authentic. Durable canvas &amp; suede. Rebellious retro style.</t>
-        </is>
-      </c>
-    </row>
-    <row r="231" ht="25.5" customHeight="1">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>VASCO DA GAMA</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>vasco-da-gama</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>VASCO DA GAMA: 葡萄牙知名航海主题品牌，以高品质服饰和配饰闻名，产品系列包括航海风格服装、鞋履及配件，经典设计融合传统工艺与现代功能，风格经典耐用且富有探险精神。</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>VASCO DA GAMA: Renowned Portuguese航海brand for high-quality apparel, footwear &amp; accessories. Classic航海style meets modern functionality with durable, adventure-ready designs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="232" ht="25.5" customHeight="1">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>VERSACE</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>versace</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>VERSACE: 探索意大利奢华时尚品牌范思哲的官方在线精品店。选购标志性的美杜莎印花、巴洛克风格与鲜艳色彩设计的女士与男士成衣、配饰、香水及家居系列。范思哲代表大胆、性感与奢华生活方式，即刻选购，尊享全球配送服务。</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>VERSACE: Shop iconic Medusa prints, Baroque styles, bold colors in luxury clothing, accessories, fragrances &amp; homeware for men &amp; women. Embody bold, sexy luxury. Worldwide shipping.</t>
-        </is>
-      </c>
-    </row>
-    <row r="233" ht="25.5" customHeight="1">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>VETEMENTS</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>vetements</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>VETEMENTS: 来自法国的先锋时尚品牌VETEMENTS，以颠覆性设计和大胆解构重塑街头潮流。品牌凭借标志性的 oversized 剪裁、夸张的标语和反叛精神，在全球时尚界掀起革命。探索VETEMENTS最新系列，获取高级街头服饰、联名单品及限量版设计，定义未来时尚风潮。</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>VETEMENTS: French avant-garde fashion brand revolutionizing streetwear with oversized silhouettes, bold graphics, and deconstructed designs. Discover the latest collections and exclusive collaborations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="25.5" customHeight="1">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>VICINITY</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>vicinity</t>
-        </is>
-      </c>
-      <c r="C234"/>
-      <c r="D234"/>
-    </row>
-    <row r="235" ht="25.5" customHeight="1">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>(Vivi)VivienneWestwood</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>VivienneWestwood</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Vivienne Westwood（薇薇安・威斯特伍德），中国粉丝爱称西太后，是英国殿堂级朋克风奢侈品牌，由 “朋克之母” 薇薇安・威斯特伍德创立。品牌以标志性土星 Orb Logo、苏格兰格纹、铆钉为核心符号，融合朋克叛逆美学与高级时装工艺，兼具街头个性与轻奢质感，坚守可持续环保理念，是全球朋克时尚与英伦先锋设计的标杆。</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>Vivienne Westwood, nicknamed “West Queen” in China, is a legendary British punk luxury brand founded by the “Mother of Punk” Vivienne Westwood. It features the iconic Saturn Orb logo, plaid and rivets, blending punk aesthetics with high fashion. Committed to sustainability, it stands as a global icon of British avant-garde and punk fashion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="236" ht="25.5" customHeight="1">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>VLONE</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>vlone</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>VLONE: 2011年由A$AP Bari创立的街头潮流品牌，以其鲜明的橙色标志和限量发售策略闻名，产品系列包括连帽衫、T恤和配饰等，经典单品有Friends徽标卫衣，采用棉质和聚酯纤维材质，工艺注重细节，风格大胆叛逆，深受青年文化爱好者追捧。</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>VLONE: Streetwear brand by A$AP Bari since 2011, known for bold orange logo, limited drops, hoodies, tees, accessories, and iconic Friends hoodie.</t>
-        </is>
-      </c>
-    </row>
-    <row r="237" ht="25.5" customHeight="1">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>YEEZY</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>yeezy</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>YEEZY: YEEZY 是国际知名设计师品牌，由坎耶·韦斯特与阿迪达斯合作创立，以极简主义美学、前瞻性设计和创新科技面料重塑运动休闲与时尚潮流。其标志性的中性色调、独特的剪裁和限量发售模式，在全球范围内引领了街头文化与高端时尚的融合，成为追求前沿设计和高品质生活方式消费者的标志性选择。</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>YEEZY: YEEZY, Kanye West's collaboration with adidas, redefines streetwear and high fashion with minimalist aesthetics, innovative fabrics, and a neutral palette. Its limited-edition releases are iconic for trendsetters worldwide.</t>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="25.5" customHeight="1">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>YORA</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>yora</t>
-        </is>
-      </c>
-      <c r="C238"/>
-      <c r="D238"/>
-    </row>
-    <row r="239" ht="25.5" customHeight="1">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>YVES SAINT LAURENT</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>yves-saint-laurent</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>YVES SAINT LAURENT：探索圣罗兰的奢华世界，从经典吸烟装到标志性口红。YSL品牌融合大胆前卫设计与法式优雅，为时尚爱好者提供高级成衣、奢华美妆与精致配饰。立即选购，定义您的独特风格。</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>YVES SAINT LAURENT: Discover YSL's luxury world, from classic Le Smoking to iconic lipstick. Bold designs meet French elegance in haute couture, beauty &amp; accessories. Shop now.</t>
-        </is>
-      </c>
-    </row>
-    <row r="240" ht="25.5" customHeight="1">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>ZARA</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>zara</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>ZARA: 西班牙快时尚品牌 ZARA 于 1975 年创立，提供最新潮流的男女装及童装、鞋履和配饰。以快速更新的设计和亲民价格著称，风格现代简约，是追求时尚的消费者的首选。</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>ZARA: Founded in 1975, offers trendy men's, women's, kids' clothing, shoes &amp; accessories. Known for fast fashion, affordable prices, and modern minimalist style.</t>
-        </is>
-      </c>
-    </row>
-    <row r="241" ht="25.5" customHeight="1">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>ZWBALL</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>zwball</t>
-        </is>
-      </c>
-      <c r="C241"/>
-      <c r="D241"/>
-    </row>
-    <row r="242" ht="25.5" customHeight="1">
-      <c r="A242"/>
-      <c r="B242"/>
-      <c r="C242"/>
-      <c r="D242"/>
-    </row>
-    <row r="243" ht="25.5" customHeight="1">
-      <c r="A243"/>
-      <c r="B243"/>
-      <c r="C243"/>
-      <c r="D243"/>
+          <t>Zwball: Freestyle football gear since 2013. Sleek logo, street-style designs. Durable rubber, breathable polyester. For tricks and streetwear. Popular worldwide.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
 </worksheet>

--- a/branch.xlsx
+++ b/branch.xlsx
@@ -530,4814 +530,5562 @@
     <row r="10" ht="25.5" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ajax Amsterdam</t>
+          <t>Aeronautica Militare</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ajax-amsterdam</t>
+          <t>aeronautica-militare</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ajax Amsterdam: 荷兰顶级职业足球俱乐部，1900年3月18日成立，主场为约翰·克鲁伊夫竞技场，是荷甲联赛传统豪门，累计斩获36次荷甲冠军、4次欧洲冠军联赛冠军，以“全攻全守”足球哲学引领足坛风格革命，拥有全球闻名的青训体系，培养出克鲁伊夫、范巴斯滕、博格坎普、斯内德等传奇球星，是世界足球史上影响力深远的俱乐部代表之一。</t>
+          <t>Aeronautica Militare,创立于 2004 年，获得了意大利空军的官方独家授权，可以使用空军的徽章、标识和航空元素来设计服饰。品牌主打硬朗复古的军事航空风格，以飞行夹克、休闲 T 恤、工装裤等单品闻名。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ajax Amsterdam: Top Dutch pro football club founded Mar 18, 1900, home to Johan Cruyff Arena. Traditional Eredivisie powerhouse with 36 titles &amp; 4 UEFA Champions League trophies. Pioneered "Total Football" philosophy, renowned global youth academy nurturing legends like Cruyff, Van Basten, Bergkamp, Sneijder. Influential in football history.</t>
+          <t>Aeronautica Militare: Official Italian Air Force licensed brand since 2004, crafting rugged vintage aviation-style jackets, tees, and workwear.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="25.5" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Ajax Amsterdam</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>al-nassr</t>
+          <t>ajax-amsterdam</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Al Nassr（利雅得胜利足球俱乐部）由 Zeid 与 Saud Al-Ja’ba 兄弟 1955 年 10 月 24 日创立于沙特利雅得。主打黄色主场球衣配蓝色细节，饰阿拉伯地图标志，与阿迪达斯等合作，用 Climalite 透气聚酯面料，产品含球衣、训练服、球迷周边，风靡中东及全球，C 罗加盟后人气飙升。</t>
+          <t>Ajax Amsterdam: 荷兰顶级职业足球俱乐部，1900年3月18日成立，主场为约翰·克鲁伊夫竞技场，是荷甲联赛传统豪门，累计斩获36次荷甲冠军、4次欧洲冠军联赛冠军，以“全攻全守”足球哲学引领足坛风格革命，拥有全球闻名的青训体系，培养出克鲁伊夫、范巴斯滕、博格坎普、斯内德等传奇球星，是世界足球史上影响力深远的俱乐部代表之一。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al Nassr: Founded in 1955. Iconic yellow &amp; blue kits with Arab map badge. Adidas Climalite jerseys, training gear, fan merch. Global popularity soared with Ronaldo.</t>
+          <t>Ajax Amsterdam: Top Dutch pro football club founded Mar 18, 1900, home to Johan Cruyff Arena. Traditional Eredivisie powerhouse with 36 titles &amp; 4 UEFA Champions League trophies. Pioneered "Total Football" philosophy, renowned global youth academy nurturing legends like Cruyff, Van Basten, Bergkamp, Sneijder. Influential in football history.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="25.5" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>al-hilal</t>
+          <t>al-nassr</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Al-Hilal（利雅得新月足球俱乐部）由阿卜杜勒・拉赫曼・本・赛义德 1957 年 10 月 16 日创立于沙特利雅得，初名奥林匹克俱乐部，1958 年更名。与 PUMA 合作，主色调蓝白，主场球衣饰流星暗纹，用 dryCELL 透气聚酯面料，产品含球衣、训练服、球迷周边，风靡中东及全球，是亚洲最成功俱乐部之</t>
+          <t>Al Nassr（利雅得胜利足球俱乐部）由 Zeid 与 Saud Al-Ja’ba 兄弟 1955 年 10 月 24 日创立于沙特利雅得。主打黄色主场球衣配蓝色细节，饰阿拉伯地图标志，与阿迪达斯等合作，用 Climalite 透气聚酯面料，产品含球衣、训练服、球迷周边，风靡中东及全球，C 罗加盟后人气飙升。</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Al Hilal: Founded by Abdul Rahman bin Said on Oct 16, 1957 in Riyadh, Saudi Arabia as Olympic Club, renamed 1958. Partnered with PUMA, blue &amp; white home jersey with meteor pattern, dryCELL breathable polyester. Jerseys, training kits, fan merchandise popular Middle East &amp; worldwide, one of Asia's most successful clubs.</t>
+          <t>Al Nassr: Founded in 1955. Iconic yellow &amp; blue kits with Arab map badge. Adidas Climalite jerseys, training gear, fan merch. Global popularity soared with Ronaldo.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="25.5" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alexander MCQueen</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>alexander-mcqueen</t>
+          <t>al-hilal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alexander McQueen: 1992年由英国鬼才设计师亚历山大·麦昆（Alexander McQueen）创立的顶级奢侈品牌，以先锋解构、暗黑浪漫的戏剧性设计著称，核心涵盖高级时装、成衣、鞋履（经典麦昆小白鞋）、配饰（标志性骷髅丝巾）与皮具，甄选优质皮革、丝绸及定制面料，将艺术与时尚深度融合，打破传统美学桎梏，是全球先锋时尚爱好者追崇的标志性品牌。</t>
+          <t>Al-Hilal（利雅得新月足球俱乐部）由阿卜杜勒・拉赫曼・本・赛义德 1957 年 10 月 16 日创立于沙特利雅得，初名奥林匹克俱乐部，1958 年更名。与 PUMA 合作，主色调蓝白，主场球衣饰流星暗纹，用 dryCELL 透气聚酯面料，产品含球衣、训练服、球迷周边，风靡中东及全球，是亚洲最成功俱乐部之</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Alexander McQueen: Founded in 1992 by British prodigy designer Alexander McQueen, a top luxury brand renowned for avant-garde deconstruction &amp; dark romantic drama. Core: haute couture, ready-to-wear, footwear (iconic white sneakers), accessories (iconic skull scarf), leather goods. Uses premium leather, silk, custom fabrics, blending art &amp; fashion to break traditional aesthetics—iconic for global avant-garde fashion enthusiasts.</t>
+          <t>Al Hilal: Founded by Abdul Rahman bin Said on Oct 16, 1957 in Riyadh, Saudi Arabia as Olympic Club, renamed 1958. Partnered with PUMA, blue &amp; white home jersey with meteor pattern, dryCELL breathable polyester. Jerseys, training kits, fan merchandise popular Middle East &amp; worldwide, one of Asia's most successful clubs.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="25.5" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alexander Wang</t>
+          <t>Alexander MCQueen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>alexander-wang</t>
+          <t>alexander-mcqueen</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alexander Wang: 2005年由华裔设计师王大仁（Alexander Wang）创立于美国纽约，是融合街头酷感与高级时装调性的高端时尚品牌，核心覆盖成衣、鞋履、配饰等品类，以标志性黑色系、解构剪裁、运动风细节为设计语言，主打前卫率性的潮流风格，深受追求个性质感与先锋审美者青睐。</t>
+          <t>Alexander McQueen: 1992年由英国鬼才设计师亚历山大·麦昆（Alexander McQueen）创立的顶级奢侈品牌，以先锋解构、暗黑浪漫的戏剧性设计著称，核心涵盖高级时装、成衣、鞋履（经典麦昆小白鞋）、配饰（标志性骷髅丝巾）与皮具，甄选优质皮革、丝绸及定制面料，将艺术与时尚深度融合，打破传统美学桎梏，是全球先锋时尚爱好者追崇的标志性品牌。</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Alexander Wang: Founded in New York (2005) by Chinese-American designer Alexander Wang, this luxury brand fuses streetwear edge with high-fashion. Core: ready-to-wear, footwear, accessories. Design: signature black, deconstructed cuts, sporty details. Avant-garde, bold style, favored by those seeking unique texture &amp; avant-garde aesthetics.</t>
+          <t>Alexander McQueen: Founded in 1992 by British prodigy designer Alexander McQueen, a top luxury brand renowned for avant-garde deconstruction &amp; dark romantic drama. Core: haute couture, ready-to-wear, footwear (iconic white sneakers), accessories (iconic skull scarf), leather goods. Uses premium leather, silk, custom fabrics, blending art &amp; fashion to break traditional aesthetics—iconic for global avant-garde fashion enthusiasts.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="25.5" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Allsaints</t>
+          <t>Alexander Wang</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>allsaints</t>
+          <t>alexander-wang</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Allsaints: 1994年创立于英国伦敦的暗黑摇滚风时尚品牌，以英伦复古与街头高级感融合的设计为核心，主打男装、女装及配饰系列，经典产品涵盖做旧皮革夹克、纯棉针织衫、复古牛仔单品等，采用优质皮革、天然棉毛等材质，工艺侧重复古做旧与细节质感，风格酷感不羁又兼具高级质感，是全球潮流爱好者追崇的英伦时尚代表品牌。</t>
+          <t>Alexander Wang: 2005年由华裔设计师王大仁（Alexander Wang）创立于美国纽约，是融合街头酷感与高级时装调性的高端时尚品牌，核心覆盖成衣、鞋履、配饰等品类，以标志性黑色系、解构剪裁、运动风细节为设计语言，主打前卫率性的潮流风格，深受追求个性质感与先锋审美者青睐。</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Allsaints: Est. 1994 London, dark rock fashion brand fusing British vintage with street luxury. Offers men's/women's wear, accessories: distressed leather jackets, cotton knits, retro denim. Premium materials, vintage distressing craftsmanship. Edgy, sophisticated, global favorite.</t>
+          <t>Alexander Wang: Founded in New York (2005) by Chinese-American designer Alexander Wang, this luxury brand fuses streetwear edge with high-fashion. Core: ready-to-wear, footwear, accessories. Design: signature black, deconstructed cuts, sporty details. Avant-garde, bold style, favored by those seeking unique texture &amp; avant-garde aesthetics.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="25.5" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alo</t>
+          <t>Allsaints</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>alo</t>
+          <t>allsaints</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alo（全称 Alo Yoga）由 Danny Harris 与 Marco DeGeorge 于 2007 年创立于美国洛杉矶比弗利山庄，名称取 Air、Land、Ocean 首字母。主打瑜伽服、运动内衣、高腰裤等，以 Airlift/Airbrush 高科技面料，走 “瑜伽馆到街头” 简约雅奢风，风靡欧美日韩，明星博主青睐。</t>
+          <t>Allsaints: 1994年创立于英国伦敦的暗黑摇滚风时尚品牌，以英伦复古与街头高级感融合的设计为核心，主打男装、女装及配饰系列，经典产品涵盖做旧皮革夹克、纯棉针织衫、复古牛仔单品等，采用优质皮革、天然棉毛等材质，工艺侧重复古做旧与细节质感，风格酷感不羁又兼具高级质感，是全球潮流爱好者追崇的英伦时尚代表品牌。</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Alo (Alo Yoga): Founded by Danny Harris &amp; Marco DeGeorge in 2007, Beverly Hills, LA, USA. Name from Air, Land, Ocean initials. Specializes in yoga apparel, sports bras, high-waisted leggings, with Airlift/Airbrush high-tech fabrics. "Yoga studio to street" minimalist luxury style, popular in EU, US, Japan, South Korea, favored by celebrities &amp; bloggers.</t>
+          <t>Allsaints: Est. 1994 London, dark rock fashion brand fusing British vintage with street luxury. Offers men's/women's wear, accessories: distressed leather jackets, cotton knits, retro denim. Premium materials, vintage distressing craftsmanship. Edgy, sophisticated, global favorite.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="25.5" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Amiri</t>
+          <t>Alo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>amiri</t>
+          <t>alo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Amiri: 2013年由Mike Amiri在美国洛杉矶创立的高端时尚品牌，以摇滚叛逆精神融合高端时尚质感，主打街头美学与奢华工艺的结合。产品线涵盖手工做旧牛仔、标志性骷髅鞋履、成衣及铆钉配饰等，擅长运用做旧丹宁、优质皮革与金属铆钉元素，强调手工细节，传递“不盲从潮流的个性表达”理念，是全球高端街头风的代表性品牌，深受追求独特风格的时尚爱好者青睐。</t>
+          <t>Alo（全称 Alo Yoga）由 Danny Harris 与 Marco DeGeorge 于 2007 年创立于美国洛杉矶比弗利山庄，名称取 Air、Land、Ocean 首字母。主打瑜伽服、运动内衣、高腰裤等，以 Airlift/Airbrush 高科技面料，走 “瑜伽馆到街头” 简约雅奢风，风靡欧美日韩，明星博主青睐。</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Amiri: Established by Mike Amiri in Los Angeles, USA (2013), high-end fashion blending rock rebellious spirit with luxury texture. Focuses on street aesthetics &amp; craftsmanship, offering handcrafted distressed denim, iconic skull footwear, ready-to-wear, studded accessories. Uses distressed denim, premium leather, metal studs, emphasizes handcrafted details. Conveys "individual expression without following trends"—iconic global high-end streetwear loved by unique style seekers.</t>
+          <t>Alo (Alo Yoga): Founded by Danny Harris &amp; Marco DeGeorge in 2007, Beverly Hills, LA, USA. Name from Air, Land, Ocean initials. Specializes in yoga apparel, sports bras, high-waisted leggings, with Airlift/Airbrush high-tech fabrics. "Yoga studio to street" minimalist luxury style, popular in EU, US, Japan, South Korea, favored by celebrities &amp; bloggers.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="25.5" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ambush</t>
+          <t>Amiri</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ambush</t>
+          <t>amiri</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ambush由 Yoon Ahn 与 Verbal 于 2008 年在东京创立，Yoon 任创意总监。初为珠宝实验线，现扩至服饰鞋履，标志性 POW!® 元素，用金属 / 优质棉 / 功能性面料，融波普与街头轻奢风，风靡欧美日韩，巴黎时装周亮相。</t>
+          <t>Amiri: 2013年由Mike Amiri在美国洛杉矶创立的高端时尚品牌，以摇滚叛逆精神融合高端时尚质感，主打街头美学与奢华工艺的结合。产品线涵盖手工做旧牛仔、标志性骷髅鞋履、成衣及铆钉配饰等，擅长运用做旧丹宁、优质皮革与金属铆钉元素，强调手工细节，传递“不盲从潮流的个性表达”理念，是全球高端街头风的代表性品牌，深受追求独特风格的时尚爱好者青睐。</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ambush: 2008 Tokyo brand by Yoon Ahn &amp; Verbal. From experimental jewelry to apparel and footwear. Features POW!® with metal, cotton, functional fabrics. Blends pop art and street luxe. Global favorite, showcased at Paris Fashion Week.</t>
+          <t>Amiri: Established by Mike Amiri in Los Angeles, USA (2013), high-end fashion blending rock rebellious spirit with luxury texture. Focuses on street aesthetics &amp; craftsmanship, offering handcrafted distressed denim, iconic skull footwear, ready-to-wear, studded accessories. Uses distressed denim, premium leather, metal studs, emphasizes handcrafted details. Conveys "individual expression without following trends"—iconic global high-end streetwear loved by unique style seekers.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="25.5" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Anti Social Ssocial Club</t>
+          <t>Ami</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>anti-social-social-club</t>
+          <t>ami</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Anti Social Social Club: 2015年由Neek Lurk创立的美国街头潮牌，以“反社交”叛逆内核为标识，深耕反主流文化与街头美学融合，凭借标志性标语、简约版型及限定发售模式突围，主打T恤、卫衣、棒球帽等单品，精准击中追求独特自我表达的年轻潮人需求，成为街头文化中传递“不迎合”态度的先锋代表品牌。</t>
+          <t>Ami 由法国设计师 Alexandre Mattiussi 于 2011 年创立，品牌名 “Ami” 在法语中意为 “朋友”，主打简约舒适的法式风格，以高质感面料和经典设计著称，是近年深受年轻消费者喜爱的轻奢休闲品牌。</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Anti Social Social Club: US streetwear brand founded by Neek Lurk in 2015, with anti-social rebellious core, blending counterculture &amp; street aesthetics. Breaks through via iconic slogans, minimalist silhouettes &amp; limited releases. Focuses on tees/hoodies/baseball caps, targets young streetwear lovers seeking unique self-expression—pioneer of non-conformist attitude in street culture.</t>
+          <t>AMI by Alexandre Mattiussi: French fashion brand since 2011. 'Ami' means 'friend'. Offers minimalist, comfortable styles with high-quality fabrics and classic design. A popular luxury-casual label.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="25.5" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Ambush</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>ambush</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Apple: 1976年由史蒂夫·乔布斯、斯蒂夫·沃兹尼亚克和罗纳德·韦恩创立的美国科技巨头，核心产品涵盖iPhone、Mac、iPad、Apple Watch、AirPods等，经典产品线包括iPhone S系列、MacBook Pro、iPad Pro，搭载自研M系列芯片与iOS/iPadOS/macOS系统，以简约精致的设计、流畅的生态联动、卓越的性能体验著称，广泛应用玻璃、铝合金等高品质材质，是全球科技与消费电子领域的标杆品牌。</t>
+          <t>Ambush由 Yoon Ahn 与 Verbal 于 2008 年在东京创立，Yoon 任创意总监。初为珠宝实验线，现扩至服饰鞋履，标志性 POW!® 元素，用金属 / 优质棉 / 功能性面料，融波普与街头轻奢风，风靡欧美日韩，巴黎时装周亮相。</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Apple: Tech giant founded in 1976, innovating iPhone, Mac, iPad, Apple Watch, AirPods with M-series chips, iOS/iPadOS/macOS. Sleek design, seamless ecosystem, premium performance using glass/aluminum. Global benchmark.</t>
+          <t>Ambush: 2008 Tokyo brand by Yoon Ahn &amp; Verbal. From experimental jewelry to apparel and footwear. Features POW!® with metal, cotton, functional fabrics. Blends pop art and street luxe. Global favorite, showcased at Paris Fashion Week.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="25.5" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Arc teryx</t>
+          <t>AMI Paris</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Arc teryx</t>
+          <t xml:space="preserve"> ami-paris</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Arc'teryx: 1989年创立于加拿大的专业高端户外装备品牌，聚焦登山、滑雪、徒步等极限场景，依托GORE-TEX®防水透气、NanoSphere®防泼溅等核心科技，打造Alpha SV冲锋衣、Beta AR夹克、Mantis背包等经典产品，以极致耐用性、人体工学设计与创新功能，成为户外爱好者及专业运动员追求性能巅峰的首选品牌。</t>
+          <t>AMI Paris 是 2011 年诞生于巴黎的法式轻奢品牌，“AMI” 在法语中意为 “朋友”。品牌主打低调松弛的法式风格，以爱心 A 刺绣为标志性设计，主打无性别穿搭，产品线涵盖 T 恤、西装、针织等基础单品，简约百搭、质感舒适，是当下都市 clean fit 穿搭的热门选择。</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Arc'teryx: Premium outdoor gear since 1989. For mountaineering, skiing, hiking. GORE-TEX® &amp; NanoSphere® tech. Durable, ergonomic, innovative. Top choice for outdoor enthusiasts and athletes.</t>
+          <t>AMI Paris is a French luxury casual brand founded in Paris in 2011. “AMI” means “friend” in French. Famous for its relaxed Parisian style and iconic heart &amp; A logo, it offers gender-neutral essentials like tees, blazers and knits. Simple, high-quality and versatile, it is perfect for modern clean fit fashion.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="25.5" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Arizona Cardinals</t>
+          <t>Anti Social Ssocial Club</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>arizona-cardinals</t>
+          <t>anti-social-social-club</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Arizona Cardinals: 美国国家橄榄球联盟（NFL）历史最悠久的球队之一，隶属于NFC西部分区，1898年创立于芝加哥，现主场为亚利桑那州格伦代尔的State Farm Stadium，以红色、白色为主队色，曾晋级第37届超级碗（XXXVII），球队风格坚韧，聚焦团队协作，拥有庞大忠实球迷群体，是NFL极具辨识度的经典职业橄榄球队伍。</t>
+          <t>Anti Social Social Club: 2015年由Neek Lurk创立的美国街头潮牌，以“反社交”叛逆内核为标识，深耕反主流文化与街头美学融合，凭借标志性标语、简约版型及限定发售模式突围，主打T恤、卫衣、棒球帽等单品，精准击中追求独特自我表达的年轻潮人需求，成为街头文化中传递“不迎合”态度的先锋代表品牌。</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Arizona Cardinals: NFL's oldest team founded 1898, NFC West. Home: State Farm Stadium, Arizona. Red/white colors. Super Bowl XXXVII appearance. Resilient, teamwork, loyal fans. Iconic classic football.</t>
+          <t>Anti Social Social Club: US streetwear brand founded by Neek Lurk in 2015, with anti-social rebellious core, blending counterculture &amp; street aesthetics. Breaks through via iconic slogans, minimalist silhouettes &amp; limited releases. Focuses on tees/hoodies/baseball caps, targets young streetwear lovers seeking unique self-expression—pioneer of non-conformist attitude in street culture.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="25.5" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Armani</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>armani</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Armani: 1975年由乔治·阿玛尼（Giorgio Armani）创立的意大利高端时尚品牌，以极简主义设计、精湛剪裁工艺与经典优雅风格著称，产品线覆盖高级成衣、美妆、皮具、配饰及家居等领域，标志性产品包括Armani Si香水、Giorgio Armani定制西装，致力于为全球消费者提供兼具质感与品味的高端生活方式选择。</t>
+          <t>Apple: 1976年由史蒂夫·乔布斯、斯蒂夫·沃兹尼亚克和罗纳德·韦恩创立的美国科技巨头，核心产品涵盖iPhone、Mac、iPad、Apple Watch、AirPods等，经典产品线包括iPhone S系列、MacBook Pro、iPad Pro，搭载自研M系列芯片与iOS/iPadOS/macOS系统，以简约精致的设计、流畅的生态联动、卓越的性能体验著称，广泛应用玻璃、铝合金等高品质材质，是全球科技与消费电子领域的标杆品牌。</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Armani Italian luxury fashion brand founded by Giorgio Armani in 1975, renowned for minimalist design, exquisite tailoring &amp; classic elegance. Product lines cover haute couture, beauty, leather goods, accessories, homeware. Iconic products: Armani Si perfume, Giorgio Armani custom suits. Dedicated to premium lifestyle with quality &amp; taste.</t>
+          <t>Apple: Tech giant founded in 1976, innovating iPhone, Mac, iPad, Apple Watch, AirPods with M-series chips, iOS/iPadOS/macOS. Sleek design, seamless ecosystem, premium performance using glass/aluminum. Global benchmark.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="25.5" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artie Master</t>
+          <t>Arc teryx</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> artie master</t>
+          <t>Arc teryx</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Artie Master由 Li Guoren 于2019 年创立，隶属中山市帝琦服装，主打美式街头快时尚。核心产品含重磅 T 恤、连帽卫衣、长裤与复古帽款，以优质棉为核心材质，强调舒适透气与高性价比，融合复古街头美学，风靡欧美等海外市场。</t>
+          <t>Arc'teryx: 1989年创立于加拿大的专业高端户外装备品牌，聚焦登山、滑雪、徒步等极限场景，依托GORE-TEX®防水透气、NanoSphere®防泼溅等核心科技，打造Alpha SV冲锋衣、Beta AR夹克、Mantis背包等经典产品，以极致耐用性、人体工学设计与创新功能，成为户外爱好者及专业运动员追求性能巅峰的首选品牌。</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Artie Master: Founded 2019, American street fast fashion. Heavyweight T-shirts, hoodies, pants, vintage caps. Premium cotton, comfortable, breathable, high value. Retro street aesthetics, popular overseas.</t>
+          <t>Arc'teryx: Premium outdoor gear since 1989. For mountaineering, skiing, hiking. GORE-TEX® &amp; NanoSphere® tech. Durable, ergonomic, innovative. Top choice for outdoor enthusiasts and athletes.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="25.5" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t xml:space="preserve">Aphex Twin </t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t xml:space="preserve">aphex-twin </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Arsenal: 1886年创立于英国伦敦的顶级职业足球俱乐部，绰号“枪手”（The Gunners），主场为酋长球场（Emirates Stadium），是英超联赛传统豪强。队史累计夺得13次英格兰顶级联赛冠军、14次足总杯冠军等荣誉，曾以“美丽足球”战术风格享誉足坛，拥有全球超亿球迷基础，其官方球衣、赛事直播及球迷互动内容长期占据足球领域搜索热点。</t>
+          <t>Aphex Twin（Richard D. James）是英国传奇实验电子音乐艺术家，先锋 IDM 代表，以独特音效与标志性 “A” 形 logo 闻名，其符号常被街头服饰致敬，成为亚文化潮流图腾。</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Arsenal: 1886 London club "The Gunners", Emirates Stadium home. 13 Premier League &amp; 14 FA Cup titles. Beautiful football. 100M+ global fans. Top searches: jerseys, streams, fan content.</t>
+          <t>Aphex Twin (Richard D. James) is a legendary British experimental electronic music artist. A pioneer of IDM, he is known for innovative sounds and an iconic "A" logo referenced in streetwear as a cult subculture icon.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="25.5" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>As Roma</t>
+          <t>Arizona Cardinals</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>as-roma</t>
+          <t>arizona-cardinals</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>As Roma: 1927年成立于意大利罗马的职业足球俱乐部，意甲联赛传统强队，主场为罗马奥林匹克体育场。队徽融合罗马城标志性“母狼哺婴”元素，传承千年古城文化基因。曾夺得3次意甲冠军、9次意大利杯冠军等荣誉，以极具辨识度的红黄色主场球衣及激情赛场风格著称，拥有全球海量球迷基础，其官方周边（如球衣、队徽纪念品）紧密联结足球文化与罗马城市精神，是意甲联赛中代表罗马城市形象的核心体育品牌。</t>
+          <t>Arizona Cardinals: 美国国家橄榄球联盟（NFL）历史最悠久的球队之一，隶属于NFC西部分区，1898年创立于芝加哥，现主场为亚利桑那州格伦代尔的State Farm Stadium，以红色、白色为主队色，曾晋级第37届超级碗（XXXVII），球队风格坚韧，聚焦团队协作，拥有庞大忠实球迷群体，是NFL极具辨识度的经典职业橄榄球队伍。</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AS Roma: Founded in Rome, Italy in 1927, a top Serie A club playing at Stadio Olimpico. Its badge features Rome’s iconic "She-Wolf Nurturing Twins," embodying the ancient city’s culture. With 3 Serie A titles &amp; 9 Coppa Italia wins, it’s known for red-yellow kits, passionate style, global fans, and merch linking football to Rome’s spirit—Serie A’s core brand for Rome.</t>
+          <t>Arizona Cardinals: NFL's oldest team founded 1898, NFC West. Home: State Farm Stadium, Arizona. Red/white colors. Super Bowl XXXVII appearance. Resilient, teamwork, loyal fans. Iconic classic football.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="25.5" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Asics</t>
+          <t xml:space="preserve">Anine Bing </t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>asics</t>
+          <t xml:space="preserve">anine-bing </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Asics: 1949年由鬼冢喜八郎创立于日本，全球知名专业运动品牌，秉持“健全精神寓于健全身体”的品牌理念，深耕跑鞋及全方位运动装备领域。核心技术涵盖GEL缓震胶、FlyteFoam轻量中底、Dynamic DuoMax支撑系统等行业标杆科技，经典产品系列包括Nimbus（顶级缓震跑鞋）、Kayano（支撑系旗舰）、GT-2000（稳定支撑入门）等，专注为跑者及运动爱好者提供专业、舒适、耐用的运动解决方案，是全球跑圈公认的“跑鞋专家”。</t>
+          <t>Anine Bing 美国轻奢休闲品牌，主打慵懒美式复古风，以做旧印花 T 恤、廓形卫衣等单品走红，兼具松弛感与轻奢质感。</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Asics: Founded in 1949 in Japan by Kihachiro Onitsuka, a globally renowned professional sportswear brand with the philosophy "Sound Mind in a Sound Body". Core tech: GEL cushioning, FlyteFoam midsole, Dynamic DuoMax. Classic lines: Nimbus (top cushioning), Kayano (support flagship), GT-2000 (stability entry). Trusted "Running Shoe Expert" for runners worldwide.</t>
+          <t>Anine Bing is a US luxury casual brand known for vintage-inspired, relaxed-fit apparel, including faded graphic tees and oversized hoodies loved by fashion influencers.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="25.5" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Armani</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>aston-villa</t>
+          <t>armani</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Aston Villa: 1874年创立于英格兰伯明翰的百年足球俱乐部，英超老牌劲旅，曾获1次欧洲冠军杯冠军、7次英格兰顶级联赛冠军、7次足总杯冠军，主场为拥有逾百年历史的维拉公园球场（可容纳约4.2万观众），以深厚的历史底蕴、热忱的球迷文化与标志性酒红&amp;蓝色队服闻名，是英格兰足球史上最具代表性的传统豪门之一。</t>
+          <t>Armani: 1975年由乔治·阿玛尼（Giorgio Armani）创立的意大利高端时尚品牌，以极简主义设计、精湛剪裁工艺与经典优雅风格著称，产品线覆盖高级成衣、美妆、皮具、配饰及家居等领域，标志性产品包括Armani Si香水、Giorgio Armani定制西装，致力于为全球消费者提供兼具质感与品味的高端生活方式选择。</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Aston Villa: Historic English Premier League club founded 1874 in Birmingham. Winner of 1 European Cup, 7 league titles, 7 FA Cups. Home: Villa Park (42k capacity). Iconic claret &amp; blue, rich heritage, passionate fans.</t>
+          <t>Armani Italian luxury fashion brand founded by Giorgio Armani in 1975, renowned for minimalist design, exquisite tailoring &amp; classic elegance. Product lines cover haute couture, beauty, leather goods, accessories, homeware. Iconic products: Armani Si perfume, Giorgio Armani custom suits. Dedicated to premium lifestyle with quality &amp; taste.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="25.5" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t xml:space="preserve"> Artie Master</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>athletic-club-bilbao</t>
+          <t xml:space="preserve"> artie master</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao: 成立于1898年，西班牙毕尔巴鄂竞技足球俱乐部，以只使用巴斯克球员的传统而闻名。提供官方球衣、纪念品和体育用品，工艺精湛，风格经典，是足球迷和收藏家的首选品牌，适合跨境电商平台推广。</t>
+          <t>Artie Master由 Li Guoren 于2019 年创立，隶属中山市帝琦服装，主打美式街头快时尚。核心产品含重磅 T 恤、连帽卫衣、长裤与复古帽款，以优质棉为核心材质，强调舒适透气与高性价比，融合复古街头美学，风靡欧美等海外市场。</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao: Founded 1898, Spanish football club famed for Basque-only player tradition. Offers official jerseys, souvenirs, sports gear with exquisite craftsmanship, classic style. Top choice for fans &amp; collectors, ideal for cross-border e-commerce.</t>
+          <t>Artie Master: Founded 2019, American street fast fashion. Heavyweight T-shirts, hoodies, pants, vintage caps. Premium cotton, comfortable, breathable, high value. Retro street aesthetics, popular overseas.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="25.5" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>atletico-madrid</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlético Madrid: 1903年成立于西班牙马德里，西甲传统豪门足球俱乐部，以坚韧防守和团队精神著称，荣誉包括西甲联赛冠军、国王杯及欧洲联赛冠军，主场为万达大都会球场，风格务实顽强，培养出众多世界级球星，是欧洲足坛的重要力量。</t>
+          <t>Arsenal: 1886年创立于英国伦敦的顶级职业足球俱乐部，绰号“枪手”（The Gunners），主场为酋长球场（Emirates Stadium），是英超联赛传统豪强。队史累计夺得13次英格兰顶级联赛冠军、14次足总杯冠军等荣誉，曾以“美丽足球”战术风格享誉足坛，拥有全球超亿球迷基础，其官方球衣、赛事直播及球迷互动内容长期占据足球领域搜索热点。</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Atlético Madrid: Established 1903 in Madrid, Spanish powerhouse renowned for resilient defense, teamwork, and titles including La Liga, Copa del Rey, UEFA Europa League. Home at Wanda Metropolitano, fostering world-class talents with pragmatic, tenacious style.</t>
+          <t>Arsenal: 1886 London club "The Gunners", Emirates Stadium home. 13 Premier League &amp; 14 FA Cup titles. Beautiful football. 100M+ global fans. Top searches: jerseys, streams, fan content.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="25.5" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Balenciaga</t>
+          <t>As Roma</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>balenciaga</t>
+          <t>as-roma</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Balenciaga: 1917年由克里斯托瓦尔·巴伦西亚加（Cristóbal Balenciaga）在西班牙创立，1937年迁至巴黎，是全球顶级高端时尚品牌。品牌覆盖高级时装、鞋履、包袋及配饰，经典单品包括Triple S老爹鞋、Hourglass沙漏包、Motorcycle机车包等。以先锋解构主义、街头文化与高级时装的碰撞为核心风格，近年在创意总监Demna Gvasalia带领下，通过oversize剪裁、复古元素与未来感设计的融合重塑时尚边界，深受全球名流及时尚爱好者追捧，代表高端时尚领域的创新与个性表达。</t>
+          <t>As Roma: 1927年成立于意大利罗马的职业足球俱乐部，意甲联赛传统强队，主场为罗马奥林匹克体育场。队徽融合罗马城标志性“母狼哺婴”元素，传承千年古城文化基因。曾夺得3次意甲冠军、9次意大利杯冠军等荣誉，以极具辨识度的红黄色主场球衣及激情赛场风格著称，拥有全球海量球迷基础，其官方周边（如球衣、队徽纪念品）紧密联结足球文化与罗马城市精神，是意甲联赛中代表罗马城市形象的核心体育品牌。</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Balenciaga: Founded by Cristóbal Balenciaga in Spain (1917), relocated to Paris (1937) – a top luxury fashion brand. Covers haute couture, footwear, bags &amp; accessories, with iconic pieces like Triple S Dad Sneakers, Hourglass Bag, Motorcycle Bag. Boasts avant-garde deconstruction, street culture-high fashion fusion. Under Demna Gvasalia, it redefines fashion via oversize cuts, retro-futuristic designs, loved by celebrities &amp; fashion lovers, embodying luxury innovation &amp; individuality.</t>
+          <t>AS Roma: Founded in Rome, Italy in 1927, a top Serie A club playing at Stadio Olimpico. Its badge features Rome’s iconic "She-Wolf Nurturing Twins," embodying the ancient city’s culture. With 3 Serie A titles &amp; 9 Coppa Italia wins, it’s known for red-yellow kits, passionate style, global fans, and merch linking football to Rome’s spirit—Serie A’s core brand for Rome.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="25.5" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Baltimore Ravens</t>
+          <t>Asics</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>baltimore-ravens</t>
+          <t>asics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Baltimore Ravens: 美国国家橄榄球联盟（NFL）旗下的职业橄榄球队，1996年成立于马里兰州巴尔的摩，主场为M&amp;T Bank Stadium，曾2次夺得超级碗冠军（2000赛季、2012赛季）。球队以强硬防守与富有冲击力的球风著称，队徽采用标志性乌鸦形象，队服主色为紫色、黑色及金色，是巴尔的摩市核心体育符号之一，拥有深厚球迷基础与社区影响力。</t>
+          <t>Asics: 1949年由鬼冢喜八郎创立于日本，全球知名专业运动品牌，秉持“健全精神寓于健全身体”的品牌理念，深耕跑鞋及全方位运动装备领域。核心技术涵盖GEL缓震胶、FlyteFoam轻量中底、Dynamic DuoMax支撑系统等行业标杆科技，经典产品系列包括Nimbus（顶级缓震跑鞋）、Kayano（支撑系旗舰）、GT-2000（稳定支撑入门）等，专注为跑者及运动爱好者提供专业、舒适、耐用的运动解决方案，是全球跑圈公认的“跑鞋专家”。</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Baltimore Ravens: NFL professional football team founded in Baltimore, Maryland in 1996, home to M&amp;T Bank Stadium. 2-time Super Bowl champions (2000 &amp; 2012), known for tough defense &amp; aggressive play. Logo features iconic raven, primary colors purple/black/gold—core Baltimore sports symbol with strong fan base &amp; community impact.</t>
+          <t>Asics: Founded in 1949 in Japan by Kihachiro Onitsuka, a globally renowned professional sportswear brand with the philosophy "Sound Mind in a Sound Body". Core tech: GEL cushioning, FlyteFoam midsole, Dynamic DuoMax. Classic lines: Nimbus (top cushioning), Kayano (support flagship), GT-2000 (stability entry). Trusted "Running Shoe Expert" for runners worldwide.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="25.5" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bape</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>bape</t>
+          <t>aston-villa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bape: 1993年由Nigo创立于日本原宿的街头潮流品牌，以标志性猿人头logo、独特迷彩图案及鲨鱼外套等经典单品著称，产品线覆盖服装、配饰等类目，融合嘻哈、滑板与街头艺术文化，凭借限量发售及联名合作策略（如与Nike、Adidas等品牌联名），成为日本原宿潮流文化的核心代表品牌之一。</t>
+          <t>Aston Villa: 1874年创立于英格兰伯明翰的百年足球俱乐部，英超老牌劲旅，曾获1次欧洲冠军杯冠军、7次英格兰顶级联赛冠军、7次足总杯冠军，主场为拥有逾百年历史的维拉公园球场（可容纳约4.2万观众），以深厚的历史底蕴、热忱的球迷文化与标志性酒红&amp;蓝色队服闻名，是英格兰足球史上最具代表性的传统豪门之一。</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Bape: 1993 Tokyo streetwear brand iconic ape head logo, shark hoodies camo patterns. Covers apparel accessories, blends hip-hop skate culture. Limited releases collabs with Nike Adidas define Harajuku core.</t>
+          <t>Aston Villa: Historic English Premier League club founded 1874 in Birmingham. Winner of 1 European Cup, 7 league titles, 7 FA Cups. Home: Villa Park (42k capacity). Iconic claret &amp; blue, rich heritage, passionate fans.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="25.5" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>athletic-club-bilbao</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Custo Barcelona（卡斯图・巴塞罗那）由 Custo 与 David Dalmau 兄弟 1980 年创立于西班牙巴塞罗那，1996 年正式定名。主打印花 T 恤、连衣裙、休闲装，以 Custo 为创意总监，用优质棉麻与功能性面料，融地中海艺术与加州冲浪文化，大胆撞色与原创图纹为标志，风靡欧美澳亚，全球超 3000 销售点。</t>
+          <t>Athletic Club Bilbao: 成立于1898年，西班牙毕尔巴鄂竞技足球俱乐部，以只使用巴斯克球员的传统而闻名。提供官方球衣、纪念品和体育用品，工艺精湛，风格经典，是足球迷和收藏家的首选品牌，适合跨境电商平台推广。</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Custo Barcelona: Founded by brothers Custo &amp; David Dalmau in Barcelona, Spain (1980), officially named in 1996. Focuses on printed tees, dresses &amp; casual wear, with Custo as creative director. Uses premium cotton-linen &amp; functional fabrics, blends Mediterranean art with California surf culture, marked by bold color-blocking &amp; original patterns. Popular across Europe, America, Australia &amp; Asia, with over 3,000 global sales points.</t>
+          <t>Athletic Club Bilbao: Founded 1898, Spanish football club famed for Basque-only player tradition. Offers official jerseys, souvenirs, sports gear with exquisite craftsmanship, classic style. Top choice for fans &amp; collectors, ideal for cross-border e-commerce.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="25.5" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Anti Social Social Club</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>bayern-munich</t>
+          <t>anti-social-social-club</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bayern Munich: 1900年成立于德国慕尼黑，是全球顶级足球俱乐部标杆，累计夺得32次德甲联赛冠军、6次欧洲冠军联赛冠军等荣誉，主场为安联球场，以红蓝白队徽、"Mia San Mia"精神闻名，拥有全球亿万球迷，传承德国足球严谨战术与进攻传统，是欧洲足坛影响力深远的传奇俱乐部。</t>
+          <t>Anti Social Social Club（简称 ASSC）是 2015 年诞生于美国洛杉矶的街头潮牌，由设计师 Neek Lurk 创立，以 “反社交” 亚文化为核心灵感。标志性的 “ANTI SOCIAL SOCIAL CLUB” 标语印花是品牌 DNA，主打纯棉抓绒连帽衫、T 恤等基础款，风格暗黑慵懒的高街潮流，深受全球年轻潮流爱好者追捧，热销欧美亚市场，以叛逆、随性的街头美学著称。</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Bayern Munich: Founded 1900 in Munich, global football icon with 32 Bundesliga &amp; 6 Champions League titles. Allianz Arena home. Red-blue-white crest, "Mia San Mia" spirit. German football legacy, billions of fans.</t>
+          <t>Founded in 2015 in Los Angeles, USA by Neek Lurk, Anti Social Social Club (ASSC) is a streetwear brand famous for its iconic anti-social slogan prints. Made with cotton fleece, it features edgy street style, loved by young trendsetters worldwide.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="25.5" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Beats</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>beats</t>
+          <t>atletico-madrid</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Beats: 由音乐制作人Dr. Dre联合创立、苹果旗下知名音频品牌，专注无线耳机、降噪耳机及便携式扬声器研发，以澎湃低音、精准声场与潮流设计为核心特色，融合街头文化与科技质感，经典系列如Beats Studio Buds（自适应降噪）、Solo 3 Wireless（长效续航）深受全球年轻人及音乐爱好者青睐，是“音效与时尚兼具”的音频选择。</t>
+          <t>Atlético Madrid: 1903年成立于西班牙马德里，西甲传统豪门足球俱乐部，以坚韧防守和团队精神著称，荣誉包括西甲联赛冠军、国王杯及欧洲联赛冠军，主场为万达大都会球场，风格务实顽强，培养出众多世界级球星，是欧洲足坛的重要力量。</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Beats: Apple audio brand by Dr. Dre, offering wireless headphones, noise-cancelling earbuds, portable speakers with powerful bass, precise soundstage, trendy design, blending street culture and tech, popular among youth for sound and style.</t>
+          <t>Atlético Madrid: Established 1903 in Madrid, Spanish powerhouse renowned for resilient defense, teamwork, and titles including La Liga, Copa del Rey, UEFA Europa League. Home at Wanda Metropolitano, fostering world-class talents with pragmatic, tenacious style.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="25.5" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bvlgari</t>
+          <t>Balenciaga</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>bvlgari</t>
+          <t>balenciaga</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bvlgari: 1884年由希腊银匠Sotirios Voulgaris创立于意大利罗马的奢华品牌，核心涵盖珠宝、腕表、香水及皮具品类，标志性Serpenti灵蛇系列融合希腊罗马文化与意大利文艺复兴设计美学，B.zero1系列以极简几何演绎现代奢华，精选高端彩色宝石、贵金属等材质，工艺精湛，是全球高端奢华生活方式的代表性品牌。</t>
+          <t>Balenciaga: 1917年由克里斯托瓦尔·巴伦西亚加（Cristóbal Balenciaga）在西班牙创立，1937年迁至巴黎，是全球顶级高端时尚品牌。品牌覆盖高级时装、鞋履、包袋及配饰，经典单品包括Triple S老爹鞋、Hourglass沙漏包、Motorcycle机车包等。以先锋解构主义、街头文化与高级时装的碰撞为核心风格，近年在创意总监Demna Gvasalia带领下，通过oversize剪裁、复古元素与未来感设计的融合重塑时尚边界，深受全球名流及时尚爱好者追捧，代表高端时尚领域的创新与个性表达。</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Bvlgari: Italian luxury brand since 1884, renowned for jewelry, watches, and iconic Serpenti &amp; B.zero1 collections, fusing Roman heritage with modern craftsmanship.</t>
+          <t>Balenciaga: Founded by Cristóbal Balenciaga in Spain (1917), relocated to Paris (1937) – a top luxury fashion brand. Covers haute couture, footwear, bags &amp; accessories, with iconic pieces like Triple S Dad Sneakers, Hourglass Bag, Motorcycle Bag. Boasts avant-garde deconstruction, street culture-high fashion fusion. Under Demna Gvasalia, it redefines fashion via oversize cuts, retro-futuristic designs, loved by celebrities &amp; fashion lovers, embodying luxury innovation &amp; individuality.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="25.5" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Binken</t>
+          <t>Baltimore Ravens</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>binken</t>
+          <t>baltimore-ravens</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Binken是专注消费电子的品牌，2015 年创立于中国，主打无线 HDMI 延长器、便携式汽车打气泵等产品。设计团队注重实用性与简约美学，产品采用优质 ABS 外壳、高纯度铜线芯，兼具耐用性与便携性。风格简约大气，操作便捷，畅销欧美、东南亚等地区，深受家庭用户与商务人士喜爱，以高性价比赢得市场认可。</t>
+          <t>Baltimore Ravens: 美国国家橄榄球联盟（NFL）旗下的职业橄榄球队，1996年成立于马里兰州巴尔的摩，主场为M&amp;T Bank Stadium，曾2次夺得超级碗冠军（2000赛季、2012赛季）。球队以强硬防守与富有冲击力的球风著称，队徽采用标志性乌鸦形象，队服主色为紫色、黑色及金色，是巴尔的摩市核心体育符号之一，拥有深厚球迷基础与社区影响力。</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Binken Consumer electronics since 2015. Wireless HDMI extenders &amp; portable car air pumps. ABS shells &amp; copper cores for durability &amp; portability. Minimalist, user-friendly. Popular in EU, US, SE Asia. Home &amp; business favorite for great value.</t>
+          <t>Baltimore Ravens: NFL professional football team founded in Baltimore, Maryland in 1996, home to M&amp;T Bank Stadium. 2-time Super Bowl champions (2000 &amp; 2012), known for tough defense &amp; aggressive play. Logo features iconic raven, primary colors purple/black/gold—core Baltimore sports symbol with strong fan base &amp; community impact.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="25.5" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bape</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>borussia-dortmund</t>
+          <t>bape</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund: 1909年创立于德国多特蒙德的传奇足球俱乐部，绰号“大黄蜂”，以激进攻势足球风格、顶尖青训体系及全球最狂热的主场氛围（Signal Iduna Park威斯特法伦球场，欧洲最大足球场之一）著称，曾斩获欧洲冠军联赛、8次德甲联赛冠军等荣誉，是世界足坛极具人气与影响力的俱乐部，聚焦年轻力量与球迷文化的深度联结。</t>
+          <t>Bape: 1993年由Nigo创立于日本原宿的街头潮流品牌，以标志性猿人头logo、独特迷彩图案及鲨鱼外套等经典单品著称，产品线覆盖服装、配饰等类目，融合嘻哈、滑板与街头艺术文化，凭借限量发售及联名合作策略（如与Nike、Adidas等品牌联名），成为日本原宿潮流文化的核心代表品牌之一。</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund: Legendary German football club founded 1909 in Dortmund, nicknamed "The Hornets". Known for aggressive attacking style, top youth academy, and passionate home atmosphere at Signal Iduna Park (Westfalenstadion, one of Europe’s largest stadiums). Won UEFA Champions League &amp; 8 Bundesliga titles; a popular, influential club focusing on youth power and fan culture ties.</t>
+          <t>Bape: 1993 Tokyo streetwear brand iconic ape head logo, shark hoodies camo patterns. Covers apparel accessories, blends hip-hop skate culture. Limited releases collabs with Nike Adidas define Harajuku core.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="25.5" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bose</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>bose</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bose: 1964年由Amar G. Bose博士创立于美国马萨诸塞州，全球专业音频设备领导品牌，以原创主动降噪技术与高保真音质调校为核心优势。核心产品覆盖QuietComfort系列降噪耳机、SoundLink蓝牙扬声器、家庭影院音响系统及专业音频解决方案，适用于通勤、居家、音乐创作等多场景，凭借“深度降噪”“沉浸式音质”“持久舒适佩戴”等特点，成为追求音频品质用户的首选品牌。</t>
+          <t>Custo Barcelona（卡斯图・巴塞罗那）由 Custo 与 David Dalmau 兄弟 1980 年创立于西班牙巴塞罗那，1996 年正式定名。主打印花 T 恤、连衣裙、休闲装，以 Custo 为创意总监，用优质棉麻与功能性面料，融地中海艺术与加州冲浪文化，大胆撞色与原创图纹为标志，风靡欧美澳亚，全球超 3000 销售点。</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Bose: Founded in 1964 by Dr. Amar G. Bose. A leader in premium audio, renowned for original active noise cancelling technology and high-fidelity sound. Core products include QuietComfort headphones, SoundLink speakers, and home theater systems for commuting, home, and more.</t>
+          <t>Custo Barcelona: Founded by brothers Custo &amp; David Dalmau in Barcelona, Spain (1980), officially named in 1996. Focuses on printed tees, dresses &amp; casual wear, with Custo as creative director. Uses premium cotton-linen &amp; functional fabrics, blends Mediterranean art with California surf culture, marked by bold color-blocking &amp; original patterns. Popular across Europe, America, Australia &amp; Asia, with over 3,000 global sales points.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="25.5" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Boy London</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boy london</t>
+          <t>bayern-munich</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boy London: 1976年诞生于英国伦敦的经典街头潮流品牌，以朋克叛逆精神为内核，标志性翅膀鹰标与粗体LOGO成为全球街头文化的标志性符号，产品涵盖潮服、配饰等，长期联动摇滚、嘻哈艺人及顶尖潮牌，是欧美及亚洲潮流圈备受追捧的“街头叛逆代表”，承载着 generations对自由不羁风格的追求。</t>
+          <t>Bayern Munich: 1900年成立于德国慕尼黑，是全球顶级足球俱乐部标杆，累计夺得32次德甲联赛冠军、6次欧洲冠军联赛冠军等荣誉，主场为安联球场，以红蓝白队徽、"Mia San Mia"精神闻名，拥有全球亿万球迷，传承德国足球严谨战术与进攻传统，是欧洲足坛影响力深远的传奇俱乐部。</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Boy London: Born in London 1976. Punk-inspired streetwear with iconic winged eagle logo. A global symbol of rebellious style across generations.</t>
+          <t>Bayern Munich: Founded 1900 in Munich, global football icon with 32 Bundesliga &amp; 6 Champions League titles. Allianz Arena home. Red-blue-white crest, "Mia San Mia" spirit. German football legacy, billions of fans.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="25.5" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Broken Planet</t>
+          <t>Beats</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>broken-planet</t>
+          <t>beats</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Broken Planet: 源自英国的先锋街头潮牌，以“废土未来主义”为核心设计语言，融合做旧、解构剪裁与反消费主义标语印花，主打卫衣、T恤、机能外套及配饰系列。品牌深耕可持续时尚，采用回收面料与复古工艺重构服饰，传递对“破碎星球”的人文思考与环保主张，凭借独特的 dystopia 美学与社会议题表达，成为全球潮流青年、街头文化爱好者及环保理念支持者的穿搭选择，是兼具个性态度与责任意识的当代潮牌代表。</t>
+          <t>Beats: 由音乐制作人Dr. Dre联合创立、苹果旗下知名音频品牌，专注无线耳机、降噪耳机及便携式扬声器研发，以澎湃低音、精准声场与潮流设计为核心特色，融合街头文化与科技质感，经典系列如Beats Studio Buds（自适应降噪）、Solo 3 Wireless（长效续航）深受全球年轻人及音乐爱好者青睐，是“音效与时尚兼具”的音频选择。</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Broken Planet: British avant-garde streetwear brand embracing dystopian futurism with distressed, deconstructed cuts and anti-consumerist prints. Features hoodies, tees, jackets, accessories. Sustainable fashion using recycled fabrics and vintage techniques for eco-conscious global youth.</t>
+          <t>Beats: Apple audio brand by Dr. Dre, offering wireless headphones, noise-cancelling earbuds, portable speakers with powerful bass, precise soundstage, trendy design, blending street culture and tech, popular among youth for sound and style.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="25.5" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Broken Hearts</t>
+          <t>BE@RBRICK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>broken-hearts</t>
+          <t>be@rbrick</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Broken Hearts 2022 年创立于意大利那不勒斯，主打纯银情感珠宝，采用 925 纯银手工打造，无镀层、不氧化变色。以破碎心形为核心符号，融意式金匠工艺与情感艺术风格，设计简约有力量，畅销欧美高端配饰市场，是小众轻奢银饰代表。</t>
+          <t>BE@RBRICK 自 2001 年推出以来，凭借可拼接的积木式小熊造型，以及与各大品牌、艺术家、IP 的联名合作，成为全球潮流收藏圈的顶流。它的尺寸通常分为 100%、400%、1000% 等，不同比例和联名款的收藏价值差异很大。</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Broken Hearts: Founded 2022 Naples, Italy. Pure silver emotional jewelry, 925 sterling silver handcrafted, no plating, non-tarnishing. Broken heart core symbol, blending Italian goldsmith craft &amp; emotional art, minimalist &amp; powerful. Best-selling in high-end EU/US accessories markets, niche luxury silver jewelry.</t>
+          <t>BE@RBRICK: Iconic modular bear collectible since 2001, featuring collaborations with top brands, artists, and IPs. Sizes include 100%, 400%, 1000%. Highly sought-after in global潮流收藏.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="25.5" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Brooks</t>
+          <t>Blaupunkt</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>brooks</t>
+          <t>blaupunkt</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brooks: 1914年创立于美国的百年专业跑步品牌，专注跑步鞋服及配件研发，核心科技涵盖DNA LOFT缓震技术与GUIDERAILS步态支撑系统，产品覆盖马拉松、越野跑、日常训练等多元场景，以专业性能、舒适脚感与耐用品质，成为全球跑者信赖的选择。</t>
+          <t>蓝宝（Blaupunkt）是源自德国的老牌家电品牌，创立于 1923 年，最初以汽车音响技术闻名，如今已拓展至个护、厨房电器等多个领域，主打高性价比与德系工艺设计。</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Brooks: Founded in the US in 1914, a century-old professional running brand specializing in running footwear, apparel, and accessories. Core tech includes DNA LOFT cushioning and GUIDERAILS gait support systems. Products cover marathons, trail running, daily training, etc. Trusted by global runners for professional performance, comfort, and durability.</t>
+          <t>Blaupunkt: German brand since 1923, renowned for car audio, now offers high-quality personal care &amp; kitchen appliances, combining German engineering with great value.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="25.5" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BURBERRY</t>
+          <t>Bvlgari</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>burberry</t>
+          <t>bvlgari</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BURBERRY: 1856年由托马斯·博柏利（Thomas Burberry）创立于英国的经典奢侈品牌，以标志性格纹图案与Trench Coat经典风衣著称，产品线覆盖男女成衣、皮具配饰、香水及美妆，融合英伦传统工艺与现代设计语言，诠释永恒奢华风格，是全球高端时尚领域的标志性品牌。</t>
+          <t>Bvlgari: 1884年由希腊银匠Sotirios Voulgaris创立于意大利罗马的奢华品牌，核心涵盖珠宝、腕表、香水及皮具品类，标志性Serpenti灵蛇系列融合希腊罗马文化与意大利文艺复兴设计美学，B.zero1系列以极简几何演绎现代奢华，精选高端彩色宝石、贵金属等材质，工艺精湛，是全球高端奢华生活方式的代表性品牌。</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>BURBERRY: Founded in the UK by Thomas Burberry in 1856, iconic luxury brand famed for signature check pattern &amp; Trench Coat. Offers men’s/women’s ready-to-wear, leather goods, accessories, perfume &amp; beauty. Blends British craftsmanship with modern design, embodies timeless luxury, global high-end fashion icon.</t>
+          <t>Bvlgari: Italian luxury brand since 1884, renowned for jewelry, watches, and iconic Serpenti &amp; B.zero1 collections, fusing Roman heritage with modern craftsmanship.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="25.5" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bvlgari</t>
+          <t>Binken</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>bvlgari</t>
+          <t>binken</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bvlgari: 1884年由希腊裔珠宝匠索蒂里奥·宝格丽（Sotirio Bulgari）在意大利罗马创立的全球顶级奢华品牌，以“融合古典与现代的罗马风格”为核心，深耕高级珠宝、奢华腕表、精品配饰、经典香水及高端酒店领域。标志性Serpenti蛇形系列凭借灵动造型与彩色宝石的极致运用成为永恒经典，品牌始终以精湛意大利工艺演绎珍稀材质（如红宝石、蓝宝石、祖母绿及贵金属），诠释“永恒的罗马奢华”理念，是全球高净值人群追求精致生活与身份象征的首选品牌之一。</t>
+          <t>Binken是专注消费电子的品牌，2015 年创立于中国，主打无线 HDMI 延长器、便携式汽车打气泵等产品。设计团队注重实用性与简约美学，产品采用优质 ABS 外壳、高纯度铜线芯，兼具耐用性与便携性。风格简约大气，操作便捷，畅销欧美、东南亚等地区，深受家庭用户与商务人士喜爱，以高性价比赢得市场认可。</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Bvlgari: Founded 1884 by Greek jeweler Sotirio Bulgari in Rome, Italy. Top luxury brand blending classic &amp; modern Roman style, specializing in fine jewelry, watches, accessories, fragrances &amp; hotels. Iconic Serpenti snake collection (dynamic design, colored gemstones) is timeless. Italian craftsmanship, rare materials (rubies, sapphires, emeralds, precious metals) embody "eternal Roman luxury"—top choice for global HNWI seeking refined living &amp; status.</t>
+          <t>Binken Consumer electronics since 2015. Wireless HDMI extenders &amp; portable car air pumps. ABS shells &amp; copper cores for durability &amp; portability. Minimalist, user-friendly. Popular in EU, US, SE Asia. Home &amp; business favorite for great value.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="25.5" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BYREDO</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>byredo</t>
+          <t>borussia-dortmund</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BYREDO: 2006年由Ben Gorham创立于瑞典斯德哥尔摩的高端香氛品牌，核心覆盖香水、家居香氛、身体护理及配饰系列，以极简北欧美学融合艺术化调香为标志，选用全球优质原料，经典代表作如「无人区玫瑰（Rose of No Man's Land）」香水，风格清冷高级，是追求独特质感与小众品味消费者的热门之选。</t>
+          <t>Borussia Dortmund: 1909年创立于德国多特蒙德的传奇足球俱乐部，绰号“大黄蜂”，以激进攻势足球风格、顶尖青训体系及全球最狂热的主场氛围（Signal Iduna Park威斯特法伦球场，欧洲最大足球场之一）著称，曾斩获欧洲冠军联赛、8次德甲联赛冠军等荣誉，是世界足坛极具人气与影响力的俱乐部，聚焦年轻力量与球迷文化的深度联结。</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>BYREDO: Luxury fragrance brand founded by Ben Gorham in 2006, Stockholm, Sweden. Core lines: perfume, home fragrance, body care, accessories. Features minimalist Nordic aesthetics + artistic perfumery, premium global ingredients. Iconic "Rose of No Man's Land" perfume, cool sophisticated style—popular for unique texture &amp; niche taste seekers.</t>
+          <t>Borussia Dortmund: Legendary German football club founded 1909 in Dortmund, nicknamed "The Hornets". Known for aggressive attacking style, top youth academy, and passionate home atmosphere at Signal Iduna Park (Westfalenstadion, one of Europe’s largest stadiums). Won UEFA Champions League &amp; 8 Bundesliga titles; a popular, influential club focusing on youth power and fan culture ties.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="25.5" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cactus Jack</t>
+          <t>Bose</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>cactus-jack</t>
+          <t>bose</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cactus Jack: 由美国说唱歌手Travis Scott于2017年创立的街头潮流品牌，以标志性仙人掌LOGO、硬核机能风格与限量联名系列为核心标签，产品线覆盖卫衣、工装裤、运动鞋及潮流配件，经典合作包括与Nike Air Jordan、McDonald's的跨界企划，融合街头文化与叛逆精神，是全球潮人追逐的街头潮流符号。</t>
+          <t>Bose: 1964年由Amar G. Bose博士创立于美国马萨诸塞州，全球专业音频设备领导品牌，以原创主动降噪技术与高保真音质调校为核心优势。核心产品覆盖QuietComfort系列降噪耳机、SoundLink蓝牙扬声器、家庭影院音响系统及专业音频解决方案，适用于通勤、居家、音乐创作等多场景，凭借“深度降噪”“沉浸式音质”“持久舒适佩戴”等特点，成为追求音频品质用户的首选品牌。</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cactus Jack: Streetwear brand founded by US rapper Travis Scott in 2017, featuring iconic cactus logo, hardcore functional style &amp; limited collabs. Lines cover hoodies, cargo pants, sneakers, accessories. Classic collabs: Nike Air Jordan, McDonald’s. Blends street culture &amp; rebellious spirit, global streetwear icon.</t>
+          <t>Bose: Founded in 1964 by Dr. Amar G. Bose. A leader in premium audio, renowned for original active noise cancelling technology and high-fidelity sound. Core products include QuietComfort headphones, SoundLink speakers, and home theater systems for commuting, home, and more.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="25.5" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cactus Plant Flea Market</t>
+          <t>Boy London</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>cactus-plant-flea-market</t>
+          <t>boy london</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cactus Plant Flea Market: 美国街头潮流代表品牌，由Cynthia Lu创立，以童趣卡通风格、标志性笑脸印花及毛绒质感单品为核心辨识度，深度联动Nike、adidas、麦当劳等跨领域品牌推出现象级联名系列，产品融合街头文化与艺术创意，坚持限量发行策略，精准触达全球潮流爱好者，是兼具玩趣与收藏价值的街头潮流IP。</t>
+          <t>Boy London: 1976年诞生于英国伦敦的经典街头潮流品牌，以朋克叛逆精神为内核，标志性翅膀鹰标与粗体LOGO成为全球街头文化的标志性符号，产品涵盖潮服、配饰等，长期联动摇滚、嘻哈艺人及顶尖潮牌，是欧美及亚洲潮流圈备受追捧的“街头叛逆代表”，承载着 generations对自由不羁风格的追求。</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cactus Plant Flea Market: Cynthia Lu's streetwear brand with playful cartoons, smiley prints, plush items. Collaborates with Nike, adidas, McDonald's. Fuses street culture and art, limited releases for global collectors.</t>
+          <t>Boy London: Born in London 1976. Punk-inspired streetwear with iconic winged eagle logo. A global symbol of rebellious style across generations.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="25.5" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Calvin Klein</t>
+          <t>Broken Planet</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>calvin-klein</t>
+          <t>broken-planet</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Calvin Klein: 1968年由Calvin Klein创立的美国高端时尚品牌，以“Less is More”极简主义为核心理念，覆盖内衣、牛仔、成衣、香水等核心品类，经典系列包括标志性的CK Underwear（logo腰边设计）、CK Jeans复古牛仔线，风格融合性感与现代感，是全球时尚界极简美学的代表性品牌之一。</t>
+          <t>Broken Planet: 源自英国的先锋街头潮牌，以“废土未来主义”为核心设计语言，融合做旧、解构剪裁与反消费主义标语印花，主打卫衣、T恤、机能外套及配饰系列。品牌深耕可持续时尚，采用回收面料与复古工艺重构服饰，传递对“破碎星球”的人文思考与环保主张，凭借独特的 dystopia 美学与社会议题表达，成为全球潮流青年、街头文化爱好者及环保理念支持者的穿搭选择，是兼具个性态度与责任意识的当代潮牌代表。</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Calvin Klein: Founded in 1968 by Calvin Klein, American high-end fashion brand rooted in "Less is More" minimalism. Core categories: underwear, jeans, ready-to-wear, fragrances. Iconic lines: CK Underwear (logo waistband), CK Jeans retro denim. Blends sexy &amp; modern style, a global minimalist fashion representative.</t>
+          <t>Broken Planet: British avant-garde streetwear brand embracing dystopian futurism with distressed, deconstructed cuts and anti-consumerist prints. Features hoodies, tees, jackets, accessories. Sustainable fashion using recycled fabrics and vintage techniques for eco-conscious global youth.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="25.5" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Canada Goose</t>
+          <t>Broken Hearts</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>canada-goose</t>
+          <t>broken-hearts</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Canada Goose: 1957年创立于加拿大的高端户外保暖品牌，以专业羽绒服与派克大衣为核心产品，依托Arctic Tech防风防水面料、高蓬松度Down Fill羽绒填充等专利技术，实现极致保暖性能与时尚设计的平衡，经典如Chateau Parka系列更是全球冬季保暖服饰的标杆之选，致力于为户外爱好者及追求品质保暖的人群提供兼具功能与美学的服饰解决方案，成为加拿大户外品牌的代表性符号。</t>
+          <t>Broken Hearts 2022 年创立于意大利那不勒斯，主打纯银情感珠宝，采用 925 纯银手工打造，无镀层、不氧化变色。以破碎心形为核心符号，融意式金匠工艺与情感艺术风格，设计简约有力量，畅销欧美高端配饰市场，是小众轻奢银饰代表。</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Canada Goose: Founded in Canada in 1957, premium outdoor warmth brand specializing in down jackets &amp; parkas. Leverages patented Arctic Tech (windproof/waterproof) &amp; high-loft Down Fill, balancing extreme warmth with stylish design. Iconic Chateau Parka is a global winter benchmark, catering to outdoor lovers &amp; quality-focused users with functional, aesthetic apparel— a representative Canadian outdoor brand symbol.</t>
+          <t>Broken Hearts: Founded 2022 Naples, Italy. Pure silver emotional jewelry, 925 sterling silver handcrafted, no plating, non-tarnishing. Broken heart core symbol, blending Italian goldsmith craft &amp; emotional art, minimalist &amp; powerful. Best-selling in high-end EU/US accessories markets, niche luxury silver jewelry.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="25.5" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Carhartt</t>
+          <t>Brooks</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>carhartt</t>
+          <t>brooks</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CARHARTT: Carhartt 是源自美国的百年工装品牌，以其耐用、功能性和经典设计闻名。品牌提供高品质的工作服、外套、裤装及配饰，采用坚固面料如帆布和 Duck Cotton 制成，专为劳动者、户外爱好者和追求实用风格的人群打造。Carhartt 产品结合卓越工艺与实用美学，在全球范围内赢得信赖，成为坚固耐用的代名词。</t>
+          <t>Brooks: 1914年创立于美国的百年专业跑步品牌，专注跑步鞋服及配件研发，核心科技涵盖DNA LOFT缓震技术与GUIDERAILS步态支撑系统，产品覆盖马拉松、越野跑、日常训练等多元场景，以专业性能、舒适脚感与耐用品质，成为全球跑者信赖的选择。</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Carhartt: Durable American workwear since 1889. Built with tough fabrics like Duck Cotton for laborers, outdoorsmen, and timeless style. Rugged, functional, trusted.</t>
+          <t>Brooks: Founded in the US in 1914, a century-old professional running brand specializing in running footwear, apparel, and accessories. Core tech includes DNA LOFT cushioning and GUIDERAILS gait support systems. Products cover marathons, trail running, daily training, etc. Trusted by global runners for professional performance, comfort, and durability.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="25.5" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Carolina Herrera</t>
+          <t>BURBERRY</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>carolina-herrera</t>
+          <t>burberry</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Carolina Herrera: 1980年由设计师卡罗琳娜·埃莱拉创立，美国奢侈时尚品牌，产品系列包括高级时装、女士香水、手袋及配饰，经典产品有Good Girl香水和婚纱礼服，采用高档面料与精致工艺，风格优雅时尚。</t>
+          <t>BURBERRY: 1856年由托马斯·博柏利（Thomas Burberry）创立于英国的经典奢侈品牌，以标志性格纹图案与Trench Coat经典风衣著称，产品线覆盖男女成衣、皮具配饰、香水及美妆，融合英伦传统工艺与现代设计语言，诠释永恒奢华风格，是全球高端时尚领域的标志性品牌。</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Carolina Herrera: Founded by designer Carolina Herrera in 1980, this American luxury fashion brand offers haute couture, women’s fragrances, handbags &amp; accessories. Classic items include Good Girl fragrance and wedding gowns, crafted from high-end fabrics with exquisite craftsmanship for an elegant, stylish aesthetic.</t>
+          <t>BURBERRY: Founded in the UK by Thomas Burberry in 1856, iconic luxury brand famed for signature check pattern &amp; Trench Coat. Offers men’s/women’s ready-to-wear, leather goods, accessories, perfume &amp; beauty. Blends British craftsmanship with modern design, embodies timeless luxury, global high-end fashion icon.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="25.5" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Bvlgari</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>casablanca</t>
+          <t>bvlgari</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Casablanca（卡萨布兰卡）2018 年由摩洛哥裔法国设计师 Charaf Tajer 在巴黎创立，以父母相遇城市命名。主打男女奢华休闲装，含真丝衬衫、羊绒针织、定制夹克，融合法式优雅、北非风情与运动休闲，标志性网球印花与地中海色调，畅销欧美及全球高端时尚圈，材质优选真丝、羊绒、精梳棉，尽显度假风奢华舒适。</t>
+          <t>Bvlgari: 1884年由希腊裔珠宝匠索蒂里奥·宝格丽（Sotirio Bulgari）在意大利罗马创立的全球顶级奢华品牌，以“融合古典与现代的罗马风格”为核心，深耕高级珠宝、奢华腕表、精品配饰、经典香水及高端酒店领域。标志性Serpenti蛇形系列凭借灵动造型与彩色宝石的极致运用成为永恒经典，品牌始终以精湛意大利工艺演绎珍稀材质（如红宝石、蓝宝石、祖母绿及贵金属），诠释“永恒的罗马奢华”理念，是全球高净值人群追求精致生活与身份象征的首选品牌之一。</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Casablanca: Founded in Paris (2018) by Moroccan-French designer Charaf Tajer, named for parents’ meeting city. Luxe unisex casualwear (silk shirts, cashmere knits, tailored jackets) blends French elegance, North African charm &amp; sporty vibes. Signature tennis prints, Mediterranean hues; premium silk/cashmere/combed cotton. Popular in global high-end fashion, offering resort luxury comfort.</t>
+          <t>Bvlgari: Founded 1884 by Greek jeweler Sotirio Bulgari in Rome, Italy. Top luxury brand blending classic &amp; modern Roman style, specializing in fine jewelry, watches, accessories, fragrances &amp; hotels. Iconic Serpenti snake collection (dynamic design, colored gemstones) is timeless. Italian craftsmanship, rare materials (rubies, sapphires, emeralds, precious metals) embody "eternal Roman luxury"—top choice for global HNWI seeking refined living &amp; status.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="25.5" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cartier</t>
+          <t>BYREDO</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>cartier</t>
+          <t>byredo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cartier: 1847年由路易·弗朗索瓦·卡地亚创立，法国奢侈品牌，产品系列包括珠宝、手表、皮具、配饰等，经典产品有Love手镯、Tank手表、Trinity戒指，采用黄金、铂金、钻石等珍贵材质，工艺精湛，设计优雅，风格奢华经典，适合高端消费者和收藏家。</t>
+          <t>BYREDO: 2006年由Ben Gorham创立于瑞典斯德哥尔摩的高端香氛品牌，核心覆盖香水、家居香氛、身体护理及配饰系列，以极简北欧美学融合艺术化调香为标志，选用全球优质原料，经典代表作如「无人区玫瑰（Rose of No Man's Land）」香水，风格清冷高级，是追求独特质感与小众品味消费者的热门之选。</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cartier: Founded in 1847 by Louis-François Cartier, a French luxury brand offering jewelry, watches, leather goods &amp; accessories. Iconic pieces: Love bracelet, Tank watch, Trinity ring. Crafted from gold, platinum, diamonds with exquisite craftsmanship, elegant &amp; luxurious classic style for high-end consumers &amp; collectors.</t>
+          <t>BYREDO: Luxury fragrance brand founded by Ben Gorham in 2006, Stockholm, Sweden. Core lines: perfume, home fragrance, body care, accessories. Features minimalist Nordic aesthetics + artistic perfumery, premium global ingredients. Iconic "Rose of No Man's Land" perfume, cool sophisticated style—popular for unique texture &amp; niche taste seekers.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="25.5" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cav Empt</t>
+          <t>Cactus Jack</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>cav-empt</t>
+          <t>cactus-jack</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cav Empt: 2011年由设计师Sk8thing和Toby Feltwell创立的日本街头服饰品牌，以复古未来主义风格和标志性图形设计著称，产品涵盖T恤、夹克、配饰等，采用优质面料，工艺精湛，风格独特前卫，深受全球潮流爱好者追捧。</t>
+          <t>Cactus Jack: 由美国说唱歌手Travis Scott于2017年创立的街头潮流品牌，以标志性仙人掌LOGO、硬核机能风格与限量联名系列为核心标签，产品线覆盖卫衣、工装裤、运动鞋及潮流配件，经典合作包括与Nike Air Jordan、McDonald's的跨界企划，融合街头文化与叛逆精神，是全球潮人追逐的街头潮流符号。</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cav Empt: Japanese streetwear since 2011 by Sk8thing &amp; Toby Feltwell. Retro-futuristic graphics, premium fabrics, crafted for global trendsetters.</t>
+          <t>Cactus Jack: Streetwear brand founded by US rapper Travis Scott in 2017, featuring iconic cactus logo, hardcore functional style &amp; limited collabs. Lines cover hoodies, cargo pants, sneakers, accessories. Classic collabs: Nike Air Jordan, McDonald’s. Blends street culture &amp; rebellious spirit, global streetwear icon.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="25.5" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CDG  Play</t>
+          <t>Cactus Plant Flea Market</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>cdg</t>
+          <t>cactus-plant-flea-market</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CDG Play: 日本时尚品牌Comme des Garçons（川久保玲）旗下经典潮流副线，1999年推出，以标志性“爱心眼睛”logo为核心识别，融合简约街头与高端设计风格，产品涵盖T恤、卫衣、包包、鞋履等潮流单品，是全球追求潮流辨识度与品牌文化的年轻人喜爱的热门潮流品牌。</t>
+          <t>Cactus Plant Flea Market: 美国街头潮流代表品牌，由Cynthia Lu创立，以童趣卡通风格、标志性笑脸印花及毛绒质感单品为核心辨识度，深度联动Nike、adidas、麦当劳等跨领域品牌推出现象级联名系列，产品融合街头文化与艺术创意，坚持限量发行策略，精准触达全球潮流爱好者，是兼具玩趣与收藏价值的街头潮流IP。</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CDG Play: Iconic "heart eyes" logo streetwear line by Comme des Garçons, launched 1999. Blends minimalist street with high-end design in T-shirts, hoodies, bags, shoes. Global youth favorite.</t>
+          <t>Cactus Plant Flea Market: Cynthia Lu's streetwear brand with playful cartoons, smiley prints, plush items. Collaborates with Nike, adidas, McDonald's. Fuses street culture and art, limited releases for global collectors.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="25.5" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Celine</t>
+          <t>Calvin Klein</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>celine</t>
+          <t>calvin-klein</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Celine: 1945年由Céline Vipiana创立于法国巴黎的高端奢侈品牌，以简约优雅的法式风格为核心，主打高级时装、手袋、皮具、鞋履及配饰，标志性元素包括凯旋门扣（Triomphe Hardware）、经典Box Bag手袋与Triomphe帆布系列，融合实用主义与精湛工艺，长期为追求经典质感与永恒时尚的全球高端消费者提供兼具设计感与耐用性的奢侈品，是法式高级时尚的代表品牌之一。</t>
+          <t>Calvin Klein: 1968年由Calvin Klein创立的美国高端时尚品牌，以“Less is More”极简主义为核心理念，覆盖内衣、牛仔、成衣、香水等核心品类，经典系列包括标志性的CK Underwear（logo腰边设计）、CK Jeans复古牛仔线，风格融合性感与现代感，是全球时尚界极简美学的代表性品牌之一。</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Celine: Founded in Paris, France in 1945 by Céline Vipiana, a high-end luxury brand with minimalist elegant French style, specializing in haute couture, handbags, leather goods, footwear &amp; accessories. Signature elements: Triomphe Hardware, classic Box Bag, Triomphe Canvas series. Blending utilitarianism &amp; exquisite craftsmanship, it caters to global high-end consumers pursuing classic texture &amp; timeless fashion, offering durable, design-driven luxury— a French high fashion representative.</t>
+          <t>Calvin Klein: Founded in 1968 by Calvin Klein, American high-end fashion brand rooted in "Less is More" minimalism. Core categories: underwear, jeans, ready-to-wear, fragrances. Iconic lines: CK Underwear (logo waistband), CK Jeans retro denim. Blends sexy &amp; modern style, a global minimalist fashion representative.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="25.5" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Canada Goose</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>celtic</t>
+          <t>canada-goose</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Celtic（凯尔特人足球俱乐部）1887 年由 Brother Walfrid 创立于苏格兰格拉斯哥。主营球衣、训练服及球迷周边，与阿迪达斯合作，主色调绿白，采用透气速干聚酯面料，融入凯尔特十字经典元素，风格经典复古，风靡英国及全球，是苏超顶级传统豪门。</t>
+          <t>Canada Goose: 1957年创立于加拿大的高端户外保暖品牌，以专业羽绒服与派克大衣为核心产品，依托Arctic Tech防风防水面料、高蓬松度Down Fill羽绒填充等专利技术，实现极致保暖性能与时尚设计的平衡，经典如Chateau Parka系列更是全球冬季保暖服饰的标杆之选，致力于为户外爱好者及追求品质保暖的人群提供兼具功能与美学的服饰解决方案，成为加拿大户外品牌的代表性符号。</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Celtic FC: Founded 1887 in Glasgow by Brother Walfrid. Adidas jerseys, training gear, fan merch in green/white. Breathable quick-dry polyester with Celtic cross. Classic retro style, UK &amp; global favorite, top SPL traditional.</t>
+          <t>Canada Goose: Founded in Canada in 1957, premium outdoor warmth brand specializing in down jackets &amp; parkas. Leverages patented Arctic Tech (windproof/waterproof) &amp; high-loft Down Fill, balancing extreme warmth with stylish design. Iconic Chateau Parka is a global winter benchmark, catering to outdoor lovers &amp; quality-focused users with functional, aesthetic apparel— a representative Canadian outdoor brand symbol.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="25.5" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Chanel</t>
+          <t>Carhartt</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>chanel</t>
+          <t>carhartt</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chanel: 1910年由可可·香奈儿（Coco Chanel）创立于法国巴黎，全球顶级奢侈品牌，以“简约优雅”的设计哲学重塑女性时尚边界。核心品类覆盖高级定制时装、经典皮具（如Classic Flap菱格纹手袋）、传奇香水（No.5香氛）、美妆及腕表珠宝，标志性元素包括双C logo、粗花呢面料、小黑裙与山茶花。品牌坚持精湛手工工艺，融合经典与现代美学，传递独立自信的女性精神，是跨越百年的时尚传奇象征。</t>
+          <t>CARHARTT: Carhartt 是源自美国的百年工装品牌，以其耐用、功能性和经典设计闻名。品牌提供高品质的工作服、外套、裤装及配饰，采用坚固面料如帆布和 Duck Cotton 制成，专为劳动者、户外爱好者和追求实用风格的人群打造。Carhartt 产品结合卓越工艺与实用美学，在全球范围内赢得信赖，成为坚固耐用的代名词。</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Chanel: Founded in 1910 Paris by Coco Chanel, a timeless luxury brand synonymous with simple elegance. Iconic for tweed, little black dress, camellia, and legendary No.5 perfume. Embodies confident femininity.</t>
+          <t>Carhartt: Durable American workwear since 1889. Built with tough fabrics like Duck Cotton for laborers, outdoorsmen, and timeless style. Rugged, functional, trusted.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="25.5" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cheng KeLun</t>
+          <t>Carolina Herrera</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>chengKeLun</t>
+          <t>carolina-herrera</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cheng KeLun（程可伦）专注男士抗菌内裤，采用 3A 级抗菌纯棉面料，透气亲肤。设计简约舒适，主打银罐装平角裤，贴合人体工学，无束缚感。风格简约百搭，适合日常穿着，畅销中国及东南亚地区，深受注重品质生活男士喜爱</t>
+          <t>Carolina Herrera: 1980年由设计师卡罗琳娜·埃莱拉创立，美国奢侈时尚品牌，产品系列包括高级时装、女士香水、手袋及配饰，经典产品有Good Girl香水和婚纱礼服，采用高档面料与精致工艺，风格优雅时尚。</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cheng KeLun: Men's antibacterial underwear with 3A antibacterial cotton, breathable &amp; skin-friendly. Sleek, comfortable, ergonomic silver can-packaged boxer briefs, unrestrictive. Minimalist, versatile for daily wear, popular in China &amp; Southeast Asia, loved by quality-focused men.</t>
+          <t>Carolina Herrera: Founded by designer Carolina Herrera in 1980, this American luxury fashion brand offers haute couture, women’s fragrances, handbags &amp; accessories. Classic items include Good Girl fragrance and wedding gowns, crafted from high-end fabrics with exquisite craftsmanship for an elegant, stylish aesthetic.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="25.5" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>casablanca</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chelsea 1905 年由 Gus Mears 创立于伦敦，主营球衣、训练服及球迷周边，与耐克合作，主色调蓝白。采用透气速干聚酯纤维，融入狮子队徽元素，风格经典时尚，风靡全球，是英超豪门，以华丽打法与冠军底蕴闻名。</t>
+          <t>Casablanca（卡萨布兰卡）2018 年由摩洛哥裔法国设计师 Charaf Tajer 在巴黎创立，以父母相遇城市命名。主打男女奢华休闲装，含真丝衬衫、羊绒针织、定制夹克，融合法式优雅、北非风情与运动休闲，标志性网球印花与地中海色调，畅销欧美及全球高端时尚圈，材质优选真丝、羊绒、精梳棉，尽显度假风奢华舒适。</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Chelsea 1905: Founded by Gus Mears in London, specializes in jerseys, training kits &amp; fan merchandise. Nike partner, blue-white, breathable quick dry polyester, lion crest, classic-stylish. Premier League giant with glam play &amp; championship heritage, global hit.</t>
+          <t>Casablanca: Founded in Paris (2018) by Moroccan-French designer Charaf Tajer, named for parents’ meeting city. Luxe unisex casualwear (silk shirts, cashmere knits, tailored jackets) blends French elegance, North African charm &amp; sporty vibes. Signature tennis prints, Mediterranean hues; premium silk/cashmere/combed cotton. Popular in global high-end fashion, offering resort luxury comfort.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="25.5" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Chicago Bears</t>
+          <t>Cartier</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>chicago-bears</t>
+          <t>cartier</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago Bears: 美国国家橄榄球联盟（NFL）历史最悠久的球队之一，1919年以“Decatur Staleys”为名创立，1922年更名为Chicago Bears（芝加哥熊队），主场为芝加哥 Soldier Field。队史收获多次分区冠军及1985年超级碗冠军，以标志性熊头LOGO、坚韧铁血的球风与深厚的美式橄榄球传统著称，拥有全球海量忠实球迷，是NFL文化与经典球队的代表符号。</t>
+          <t>Cartier: 1847年由路易·弗朗索瓦·卡地亚创立，法国奢侈品牌，产品系列包括珠宝、手表、皮具、配饰等，经典产品有Love手镯、Tank手表、Trinity戒指，采用黄金、铂金、钻石等珍贵材质，工艺精湛，设计优雅，风格奢华经典，适合高端消费者和收藏家。</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Chicago Bears: One of NFL’s oldest teams, founded 1919 as Decatur Staleys, renamed 1922. Home at Chicago’s Soldier Field, multiple division titles, 1985 Super Bowl champion. Iconic bear head logo, tough gritty style, rich football tradition, loyal global fans—NFL culture classic symbol.</t>
+          <t>Cartier: Founded in 1847 by Louis-François Cartier, a French luxury brand offering jewelry, watches, leather goods &amp; accessories. Iconic pieces: Love bracelet, Tank watch, Trinity ring. Crafted from gold, platinum, diamonds with exquisite craftsmanship, elegant &amp; luxurious classic style for high-end consumers &amp; collectors.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="25.5" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Chiclara</t>
+          <t>Cav Empt</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>chiclara</t>
+          <t>cav-empt</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chiclara（奇克拉拉）2023 年创立于香港，专注亚洲时尚美学，与亚洲新兴设计师合作，主营男女成衣与配饰，融合东方传统与现代设计，采用棉麻、环保聚酯纤维等材质，风格简约大气又不失文化韵味，畅销欧美及亚太地区，是亚洲时尚全球化的代表性品牌。</t>
+          <t>Cav Empt: 2011年由设计师Sk8thing和Toby Feltwell创立的日本街头服饰品牌，以复古未来主义风格和标志性图形设计著称，产品涵盖T恤、夹克、配饰等，采用优质面料，工艺精湛，风格独特前卫，深受全球潮流爱好者追捧。</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Chiclara: Founded in Hong Kong in 2023, focuses on Asian fashion aesthetics, collaborates with emerging Asian designers, specializes in men’s &amp; women’s ready-to-wear &amp; accessories. Blends Eastern traditions with modern design, uses cotton, linen &amp; eco-friendly polyester. Minimalist yet culturally rich, popular in Europe, America &amp; Asia-Pacific—representative of Asian fashion globalization.</t>
+          <t>Cav Empt: Japanese streetwear since 2011 by Sk8thing &amp; Toby Feltwell. Retro-futuristic graphics, premium fabrics, crafted for global trendsetters.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="25.5" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Chrome Hearts</t>
+          <t>CDG  Play</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>chrome-hearts</t>
+          <t>cdg</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chrome Hearts: 1988年由Richard Stark创立于美国的高端奢侈品牌，以哥特摇滚风格的手工银饰、皮革制品及服饰为核心，标志性元素包括十字架、骷髅与铆钉，坚持全手工制作打造独特质感，深受全球明星与潮流爱好者追捧，亦推出与Bape、Supreme等品牌的联名系列，诠释叛逆奢华与工艺美学的融合。</t>
+          <t>CDG Play: 日本时尚品牌Comme des Garçons（川久保玲）旗下经典潮流副线，1999年推出，以标志性“爱心眼睛”logo为核心识别，融合简约街头与高端设计风格，产品涵盖T恤、卫衣、包包、鞋履等潮流单品，是全球追求潮流辨识度与品牌文化的年轻人喜爱的热门潮流品牌。</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Chrome Hearts: Luxury brand since 1988 USA. Gothic rock handcrafted silver, leather, apparel. Iconic crosses, skulls, studs. Handmade, celeb loved. Bape, Supreme collabs. Rebellious luxury craft.</t>
+          <t>CDG Play: Iconic "heart eyes" logo streetwear line by Comme des Garçons, launched 1999. Blends minimalist street with high-end design in T-shirts, hoodies, bags, shoes. Global youth favorite.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="25.5" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cincinnati Bengals</t>
+          <t>Celine</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>cincinnati-bengals</t>
+          <t>celine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cincinnati Bengals: 美国国家橄榄球联盟（NFL）美联北区职业橄榄球队，1968年成立，主场为俄亥俄州辛辛那提的Paycor Stadium。队服以标志性橙色与黑色为主， mascot是"Who Dey" Bengal tiger形象。队史曾多次闯入季后赛，2022、2024年两度晋级超级碗；阵中拥有乔·伯罗（Joe Burrow）、贾马尔·蔡斯（Ja'Marr Chase）等明星球员，以进攻端的强劲火力著称，是NFL中极具关注度与球迷基础的球队之一。</t>
+          <t>Celine: 1945年由Céline Vipiana创立于法国巴黎的高端奢侈品牌，以简约优雅的法式风格为核心，主打高级时装、手袋、皮具、鞋履及配饰，标志性元素包括凯旋门扣（Triomphe Hardware）、经典Box Bag手袋与Triomphe帆布系列，融合实用主义与精湛工艺，长期为追求经典质感与永恒时尚的全球高端消费者提供兼具设计感与耐用性的奢侈品，是法式高级时尚的代表品牌之一。</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cincinnati Bengals: NFL AFC North team since 1968 at Paycor Stadium. Iconic orange &amp; black, "Who Dey" tiger mascot. Super Bowl appearances 2022 &amp; 2024. Featuring Joe Burrow, Ja'Marr Chase. Known for offensive firepower and loyal fans.</t>
+          <t>Celine: Founded in Paris, France in 1945 by Céline Vipiana, a high-end luxury brand with minimalist elegant French style, specializing in haute couture, handbags, leather goods, footwear &amp; accessories. Signature elements: Triomphe Hardware, classic Box Bag, Triomphe Canvas series. Blending utilitarianism &amp; exquisite craftsmanship, it caters to global high-end consumers pursuing classic texture &amp; timeless fashion, offering durable, design-driven luxury— a French high fashion representative.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="25.5" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Clinique</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>clinique</t>
+          <t>celtic</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Clinique: 1968年由美国皮肤科医生创立的专业护肤彩妆品牌，以“无香料、无酒精、敏感肌友好”为核心研发理念，经典“倩碧三步曲”（温和洁面皂+明肌净透水+特效润肤露“黄油”）成为全球基础护肤标杆，更有匀净粉底液、小方唇釉等养肤彩妆产品，专注通过dermatologist-tested（皮肤科医生测试）的安全配方，解决不同肤质的基础护理与妆容需求，是全球敏感肌及护肤新手的信任之选。</t>
+          <t>Celtic（凯尔特人足球俱乐部）1887 年由 Brother Walfrid 创立于苏格兰格拉斯哥。主营球衣、训练服及球迷周边，与阿迪达斯合作，主色调绿白，采用透气速干聚酯面料，融入凯尔特十字经典元素，风格经典复古，风靡英国及全球，是苏超顶级传统豪门。</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Clinique: 1968 dermatologist-founded skincare/makeup brand. Fragrance-free, alcohol-free, sensitive-skin friendly. Classic 3-Step System &amp; dermatologist-tested formulas for all skin types and beginners.</t>
+          <t>Celtic FC: Founded 1887 in Glasgow by Brother Walfrid. Adidas jerseys, training gear, fan merch in green/white. Breathable quick-dry polyester with Celtic cross. Classic retro style, UK &amp; global favorite, top SPL traditional.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="25.5" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cole Buxton</t>
+          <t>Chanel</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>cole-buxton</t>
+          <t>chanel</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cole Buxton: 源自英国的街头服饰品牌，以极简美学融合复古运动功能性与街头文化内核著称，主打高品质纯棉、抓绒等面料打造的连帽衫、运动裤、基础T恤等经典单品，兼顾舒适穿着与潮流表达，是追求质感与个性的年轻群体首选的街头运动风品牌。</t>
+          <t>Chanel: 1910年由可可·香奈儿（Coco Chanel）创立于法国巴黎，全球顶级奢侈品牌，以“简约优雅”的设计哲学重塑女性时尚边界。核心品类覆盖高级定制时装、经典皮具（如Classic Flap菱格纹手袋）、传奇香水（No.5香氛）、美妆及腕表珠宝，标志性元素包括双C logo、粗花呢面料、小黑裙与山茶花。品牌坚持精湛手工工艺，融合经典与现代美学，传递独立自信的女性精神，是跨越百年的时尚传奇象征。</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cole Buxton: UK-based streetwear brand blending minimalist aesthetics with retro sport functionality &amp; street culture core. Offers high-quality cotton/fleece hoodies, sweatpants, basic tees—balances comfort &amp; trendy expression. Top pick for youths seeking quality, individuality in street sports style.</t>
+          <t>Chanel: Founded in 1910 Paris by Coco Chanel, a timeless luxury brand synonymous with simple elegance. Iconic for tweed, little black dress, camellia, and legendary No.5 perfume. Embodies confident femininity.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="25.5" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Comme Des Garcons</t>
+          <t>Cheng KeLun</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>comme-des-garcons</t>
+          <t>chengKeLun</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Comme Des Garcons: 1969年由川久保玲（Rei Kawakubo）在东京创立的日本先锋时装品牌，以“反时尚”（Anti-Fashion）核心理念打破传统边界，擅长解构主义设计，标志性元素包括不对称剪裁、不规则轮廓、黑白灰主色调及拼接工艺，产品覆盖男女装、配饰、香水（如经典Comme Des Garcons Parfums系列）及跨界联名（与Nike、Converse等品牌合作），将艺术与服饰深度融合，是全球潮流文化中极具辨识度的个性时尚符号。</t>
+          <t>Cheng KeLun（程可伦）专注男士抗菌内裤，采用 3A 级抗菌纯棉面料，透气亲肤。设计简约舒适，主打银罐装平角裤，贴合人体工学，无束缚感。风格简约百搭，适合日常穿着，畅销中国及东南亚地区，深受注重品质生活男士喜爱</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Comme Des Garcons: Avant-garde Japanese fashion by Rei Kawakubo, since 1969. Anti-Fashion, deconstruction, asymmetric cuts, patchwork, monochrome, apparel, accessories, perfumes, collaborations.</t>
+          <t>Cheng KeLun: Men's antibacterial underwear with 3A antibacterial cotton, breathable &amp; skin-friendly. Sleek, comfortable, ergonomic silver can-packaged boxer briefs, unrestrictive. Minimalist, versatile for daily wear, popular in China &amp; Southeast Asia, loved by quality-focused men.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="25.5" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>converse</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Converse（匡威）1908 年由 Marquis Mills Converse 创立于美国，百年经典鞋服品牌。主打 Chuck Taylor All Star 帆布鞋，采用帆布鞋面与橡胶鞋底，兼顾复古休闲与街头风格，覆盖鞋款、服饰等。设计简约百搭，风靡全球，是潮流与日常穿搭的标志性品牌。</t>
+          <t>Chelsea 1905 年由 Gus Mears 创立于伦敦，主营球衣、训练服及球迷周边，与耐克合作，主色调蓝白。采用透气速干聚酯纤维，融入狮子队徽元素，风格经典时尚，风靡全球，是英超豪门，以华丽打法与冠军底蕴闻名。</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Converse: Founded in the US by Marquis Mills Converse in 1908, a century-old iconic footwear &amp; apparel brand. Core product: Chuck Taylor All Star canvas shoes with canvas uppers &amp; rubber soles, blending retro casualness with street style, covering shoes &amp; apparel. Minimalist &amp; versatile design, popular worldwide, a signature brand for trendy daily outfits.</t>
+          <t>Chelsea 1905: Founded by Gus Mears in London, specializes in jerseys, training kits &amp; fan merchandise. Nike partner, blue-white, breathable quick dry polyester, lion crest, classic-stylish. Premier League giant with glam play &amp; championship heritage, global hit.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="25.5" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Corteiz</t>
+          <t>Chicago Bears</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>corteiz</t>
+          <t>chicago-bears</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Corteiz: 英国街头潮流先锋品牌，由Clint419创立，聚焦青年文化与街头精神，以标志性“COR”标识、Bold标语及工业风设计为核心辨识度，产品覆盖卫衣、T恤、帽饰等街头单品，常与Nike、Polaroid等品牌推出联名系列，传递“社群共鸣”的品牌理念，是全球街头潮流爱好者的热门选择。</t>
+          <t>Chicago Bears: 美国国家橄榄球联盟（NFL）历史最悠久的球队之一，1919年以“Decatur Staleys”为名创立，1922年更名为Chicago Bears（芝加哥熊队），主场为芝加哥 Soldier Field。队史收获多次分区冠军及1985年超级碗冠军，以标志性熊头LOGO、坚韧铁血的球风与深厚的美式橄榄球传统著称，拥有全球海量忠实球迷，是NFL文化与经典球队的代表符号。</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Corteiz: UK streetwear pioneer by Clint419, focuses on youth culture &amp; street spirit with iconic COR logo, bold slogans, industrial design. Offers hoodies, tees, caps. Collaborates with Nike, Polaroid. Promotes 'community resonance', top global choice.</t>
+          <t>Chicago Bears: One of NFL’s oldest teams, founded 1919 as Decatur Staleys, renamed 1922. Home at Chicago’s Soldier Field, multiple division titles, 1985 Super Bowl champion. Iconic bear head logo, tough gritty style, rich football tradition, loyal global fans—NFL culture classic symbol.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="25.5" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cp Company</t>
+          <t>Chiclara</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>cp-company</t>
+          <t>chiclara</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cp Company: 1971年由Massimo Osti创立的意大利高端机能服饰品牌，以先锋功能性面料、军事风格元素与实用设计著称，经典Goggle Jacket护目镜夹克为标志性单品，融合都市美学与户外性能，注重细节工艺，是机能时尚领域的代表性品牌。</t>
+          <t>Chiclara（奇克拉拉）2023 年创立于香港，专注亚洲时尚美学，与亚洲新兴设计师合作，主营男女成衣与配饰，融合东方传统与现代设计，采用棉麻、环保聚酯纤维等材质，风格简约大气又不失文化韵味，畅销欧美及亚太地区，是亚洲时尚全球化的代表性品牌。</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cp Company: Italian high-end techwear brand since 1971 by Massimo Osti. Known for functional fabrics, military style, iconic Goggle Jacket. Blends urban aesthetics with outdoor performance, craftsmanship-focused.</t>
+          <t>Chiclara: Founded in Hong Kong in 2023, focuses on Asian fashion aesthetics, collaborates with emerging Asian designers, specializes in men’s &amp; women’s ready-to-wear &amp; accessories. Blends Eastern traditions with modern design, uses cotton, linen &amp; eco-friendly polyester. Minimalist yet culturally rich, popular in Europe, America &amp; Asia-Pacific—representative of Asian fashion globalization.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="25.5" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Creed</t>
+          <t>Chrome Hearts</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>creed</t>
+          <t>chrome-hearts</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Creed（恺芮得）1760 年由 James Henry Creed 创立于伦敦，家族 7 代传承的皇室御用奢华香氛品牌。主营高端香水，如 Aventus、Silver Mountain Water 等，由 Olivier Creed 等家族制香大师调配。采用保加利亚玫瑰、佛罗伦萨茉莉等天然原料，坚持手工制香工艺，风格典雅奢华，风靡全球，以皇室底蕴与卓越品质著称。</t>
+          <t>Chrome Hearts: 1988年由Richard Stark创立于美国的高端奢侈品牌，以哥特摇滚风格的手工银饰、皮革制品及服饰为核心，标志性元素包括十字架、骷髅与铆钉，坚持全手工制作打造独特质感，深受全球明星与潮流爱好者追捧，亦推出与Bape、Supreme等品牌的联名系列，诠释叛逆奢华与工艺美学的融合。</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Creed: Since 1760 London, royal luxury perfumes by Creed family. Aventus, Silver Mountain Water with natural ingredients, handcrafted, elegant, globally renowned.</t>
+          <t>Chrome Hearts: Luxury brand since 1988 USA. Gothic rock handcrafted silver, leather, apparel. Iconic crosses, skulls, studs. Handmade, celeb loved. Bape, Supreme collabs. Rebellious luxury craft.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="25.5" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Cincinnati Bengals</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>crocs</t>
+          <t>cincinnati-bengals</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Crocs: 1999年诞生于美国科罗拉多州的全球休闲鞋领导品牌，以标志性洞洞鞋（Clog）和专利Croslite™轻质缓冲材质为核心，产品兼具透气、防滑、易清洁等特性，覆盖全年龄段日常出行、户外休闲等多元场景，主打“舒适无束缚”的生活理念，成为全球消费者心中“自在休闲”的鞋履代表。</t>
+          <t>Cincinnati Bengals: 美国国家橄榄球联盟（NFL）美联北区职业橄榄球队，1968年成立，主场为俄亥俄州辛辛那提的Paycor Stadium。队服以标志性橙色与黑色为主， mascot是"Who Dey" Bengal tiger形象。队史曾多次闯入季后赛，2022、2024年两度晋级超级碗；阵中拥有乔·伯罗（Joe Burrow）、贾马尔·蔡斯（Ja'Marr Chase）等明星球员，以进攻端的强劲火力著称，是NFL中极具关注度与球迷基础的球队之一。</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Crocs: 1999-born Colorado global casual footwear leader. Iconic clogs with Croslite™ cushioning. Breathable, slip-resistant, easy-to-clean. For all ages, daily &amp; outdoor. Comfortable, unrestrictive lifestyle.</t>
+          <t>Cincinnati Bengals: NFL AFC North team since 1968 at Paycor Stadium. Iconic orange &amp; black, "Who Dey" tiger mascot. Super Bowl appearances 2022 &amp; 2024. Featuring Joe Burrow, Ja'Marr Chase. Known for offensive firepower and loyal fans.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="25.5" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cactus Jack</t>
+          <t>Clinique</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>mastermind-japan</t>
+          <t>clinique</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cactus Jack: 由美国说唱歌手Travis Scott创立的街头潮流品牌，以沙漠野性与工业街头风为核心设计语言，主打潮流服饰、联名鞋款及配件，因与Nike、Jordan Brand合作推出Air Jordan 1 Travis Scott等爆款鞋品走红，是全球潮流爱好者追捧的街头文化标杆品牌。</t>
+          <t>Clinique: 1968年由美国皮肤科医生创立的专业护肤彩妆品牌，以“无香料、无酒精、敏感肌友好”为核心研发理念，经典“倩碧三步曲”（温和洁面皂+明肌净透水+特效润肤露“黄油”）成为全球基础护肤标杆，更有匀净粉底液、小方唇釉等养肤彩妆产品，专注通过dermatologist-tested（皮肤科医生测试）的安全配方，解决不同肤质的基础护理与妆容需求，是全球敏感肌及护肤新手的信任之选。</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cactus Jack: Streetwear brand founded by US rapper Travis Scott, blending desert wildness &amp; industrial street style. Specializes in apparel, collab sneakers &amp; accessories. Gained fame via Nike/Jordan Brand’s Air Jordan 1 Travis Scott, a global street culture icon for enthusiasts.</t>
+          <t>Clinique: 1968 dermatologist-founded skincare/makeup brand. Fragrance-free, alcohol-free, sensitive-skin friendly. Classic 3-Step System &amp; dermatologist-tested formulas for all skin types and beginners.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="25.5" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Dallas Cowboys</t>
+          <t>Cole Buxton</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>dallas-cowboys</t>
+          <t>cole-buxton</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas Cowboys: 1960年成立的美国NFL职业橄榄球队，隶属国家橄榄球联合会（NFC）东部分区，曾5次夺得超级碗冠军，获称“美国之队”（America's Team）。球队以标志性牛仔星队徽、经典蓝银配色队服为识别，主场为达拉斯AT&amp;T体育场（AT&amp;T Stadium），是NFL历史上最具影响力、商业价值及全球球迷基础的球队之一，传承美式橄榄球的热血与文化符号。</t>
+          <t>Cole Buxton: 源自英国的街头服饰品牌，以极简美学融合复古运动功能性与街头文化内核著称，主打高品质纯棉、抓绒等面料打造的连帽衫、运动裤、基础T恤等经典单品，兼顾舒适穿着与潮流表达，是追求质感与个性的年轻群体首选的街头运动风品牌。</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Dallas Cowboys: NFL team est. 1960, NFC East. 5x Super Bowl champs, America's Team. Iconic star logo, blue-silver uniforms, AT&amp;T Stadium home. Influential, valuable, global football icon.</t>
+          <t>Cole Buxton: UK-based streetwear brand blending minimalist aesthetics with retro sport functionality &amp; street culture core. Offers high-quality cotton/fleece hoodies, sweatpants, basic tees—balances comfort &amp; trendy expression. Top pick for youths seeking quality, individuality in street sports style.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="25.5" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Denver Broncos</t>
+          <t>Comme Des Garcons</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>denver-broncos</t>
+          <t>comme-des-garcons</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denver Broncos: 美国国家橄榄球联盟（NFL）经典球队，1960年作为AFL创始成员成立，1970年加入NFL，主场位于丹佛的Empower Field at Mile High。队史3次夺得超级碗冠军（1997、1998、2015年），以标志性橙蓝配色队服、野性野马队标闻名，拥有庞大忠实球迷群体“Broncos Country”。球队延续坚韧拼搏的橄榄球精神，是NFL历史上极具影响力的老牌劲旅。</t>
+          <t>Comme Des Garcons: 1969年由川久保玲（Rei Kawakubo）在东京创立的日本先锋时装品牌，以“反时尚”（Anti-Fashion）核心理念打破传统边界，擅长解构主义设计，标志性元素包括不对称剪裁、不规则轮廓、黑白灰主色调及拼接工艺，产品覆盖男女装、配饰、香水（如经典Comme Des Garcons Parfums系列）及跨界联名（与Nike、Converse等品牌合作），将艺术与服饰深度融合，是全球潮流文化中极具辨识度的个性时尚符号。</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Denver Broncos: Legendary NFL team, 3x Super Bowl champions (1997, 1998, 2015). Iconic orange &amp; blue colors, wild horse logo. Heart of loyal "Broncos Country" fans. Founded 1960.</t>
+          <t>Comme Des Garcons: Avant-garde Japanese fashion by Rei Kawakubo, since 1969. Anti-Fashion, deconstruction, asymmetric cuts, patchwork, monochrome, apparel, accessories, perfumes, collaborations.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="25.5" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>deportivo</t>
+          <t>converse</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Deportivo（拉科鲁尼亚体育俱乐部）1906 年 3 月 2 日由西班牙体育爱好者创立于拉科鲁尼亚，主营球衣、训练服及球迷周边，与 Macron 等品牌合作设计，主色调蓝白条纹。采用透气速干聚酯纤维材质，风格经典运动，融入球队 "蓝白军团" 元素，风靡西班牙及全球球迷圈，以西甲冠军底蕴与忠诚球迷文化著称。</t>
+          <t>Converse（匡威）1908 年由 Marquis Mills Converse 创立于美国，百年经典鞋服品牌。主打 Chuck Taylor All Star 帆布鞋，采用帆布鞋面与橡胶鞋底，兼顾复古休闲与街头风格，覆盖鞋款、服饰等。设计简约百搭，风靡全球，是潮流与日常穿搭的标志性品牌。</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Deportivo(Deportivo de La Coruña): Founded by Spanish sports enthusiasts in La Coruña on Mar 2, 1906, offering jerseys, training kits &amp; fan merch. Collaborates with Macron, blue-white stripes, breathable quick-dry polyester, classic sporty style with "Blue and White Army" elements. Popular globally, known for La Liga champion heritage &amp; loyal fan culture.</t>
+          <t>Converse: Founded in the US by Marquis Mills Converse in 1908, a century-old iconic footwear &amp; apparel brand. Core product: Chuck Taylor All Star canvas shoes with canvas uppers &amp; rubber soles, blending retro casualness with street style, covering shoes &amp; apparel. Minimalist &amp; versatile design, popular worldwide, a signature brand for trendy daily outfits.</t>
         </is>
       </c>
     </row>
     <row r="79" ht="25.5" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Destroy Lonely</t>
+          <t>Corteiz</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>destroy-lonely</t>
+          <t>corteiz</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Destroy Lonely: 美国新生代说唱歌手，以melodic trap风格见长，代表作《NOSTYLIST》《VETERAN》凭借独特flow、氛围感编曲及孤独主题歌词出圈，流媒体播放量破千万，是当下嘻哈场景中极具辨识度的艺人，其音乐融合 trap 节奏与旋律性，传递年轻一代的自我表达与情绪共鸣。</t>
+          <t>Corteiz: 英国街头潮流先锋品牌，由Clint419创立，聚焦青年文化与街头精神，以标志性“COR”标识、Bold标语及工业风设计为核心辨识度，产品覆盖卫衣、T恤、帽饰等街头单品，常与Nike、Polaroid等品牌推出联名系列，传递“社群共鸣”的品牌理念，是全球街头潮流爱好者的热门选择。</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Destroy Lonely: U.S. rising rapper specializing in melodic trap, with hits "NOSTYLIST" &amp; "VETERAN". Known for unique flow, atmospheric production, lonely-themed lyrics, millions of streams. Distinctive in hip-hop, blending trap rhythm &amp; melody to convey Gen Z's self-expression &amp; emotional resonance.</t>
+          <t>Corteiz: UK streetwear pioneer by Clint419, focuses on youth culture &amp; street spirit with iconic COR logo, bold slogans, industrial design. Offers hoodies, tees, caps. Collaborates with Nike, Polaroid. Promotes 'community resonance', top global choice.</t>
         </is>
       </c>
     </row>
     <row r="80" ht="25.5" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Descente</t>
+          <t>CP Company</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>descente</t>
+          <t>cp-company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Descente（迪桑特）1935 年由石本他家男创立于日本大阪，1961 年注册商标，名称源自法语 "滑降"。主打专业滑雪服与高端运动服饰，由滑雪名将西村一良担任顾问，采用 GORE‑TEX、COOLMAX 等科技面料，融合专业功能性与简约美学，风靡全球，是瑞士、加拿大等多国滑雪队官方赞助商。</t>
+          <t>CP Company: 1971年由Massimo Osti创立的意大利高端机能服饰品牌，以先锋功能性面料、军事风格元素与实用设计著称，经典Goggle Jacket护目镜夹克为标志性单品，融合都市美学与户外性能，注重细节工艺，是机能时尚领域的代表性品牌。</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Descente: French for descent, founded 1935 Osaka, trademarked 1961. Expert pro ski wear &amp; sportswear with GORE-TEX, COOLMAX. Advised by ski champ Nishimura. Blends function &amp; minimalist aesthetics. Global sponsor for Swiss, Canadian ski teams.</t>
+          <t>Cp Company: Italian high-end techwear brand since 1971 by Massimo Osti. Known for functional fabrics, military style, iconic Goggle Jacket. Blends urban aesthetics with outdoor performance, craftsmanship-focused.</t>
         </is>
       </c>
     </row>
     <row r="81" ht="25.5" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Diadora</t>
+          <t>Creed</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>diadora</t>
+          <t>creed</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Diadora: 1948年创立于意大利的专业运动品牌，由Marcello Danieli创办，以意式精湛工艺与运动基因著称，核心产品涵盖经典运动鞋（如Mirage、N9000系列）、专业运动服饰及配件，深耕足球领域（曾赞助尤文图斯、AC米兰等顶级球队），融合复古设计与现代科技，采用优质皮革、透气网布等功能性材质，满足运动爱好者专业性能需求与潮流人士复古审美，是意大利运动文化与时尚风格结合的代表品牌。</t>
+          <t>Creed（恺芮得）1760 年由 James Henry Creed 创立于伦敦，家族 7 代传承的皇室御用奢华香氛品牌。主营高端香水，如 Aventus、Silver Mountain Water 等，由 Olivier Creed 等家族制香大师调配。采用保加利亚玫瑰、佛罗伦萨茉莉等天然原料，坚持手工制香工艺，风格典雅奢华，风靡全球，以皇室底蕴与卓越品质著称。</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Diadora: Founded in 1948 Italy by Marcello Danieli, Italian craftsmanship &amp; sport heritage brand. Core products: classic sneakers (Mirage, N9000), sportswear/accessories. Deep in football (sponsored Juventus, AC Milan). Merges retro design + modern tech, premium leather/breathable mesh for pro performance &amp; retro style. Italian sport-culture fashion icon.</t>
+          <t>Creed: Since 1760 London, royal luxury perfumes by Creed family. Aventus, Silver Mountain Water with natural ingredients, handcrafted, elegant, globally renowned.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="25.5" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Dior</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>dior</t>
+          <t>crocs</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dior: 1946年由克里斯汀·迪奥（Christian Dior）在巴黎创立，全球法式奢华与优雅的标志性品牌，业务涵盖高级定制时装、成衣、手袋、鞋履、美妆及香水。1947年以“New Look”廓形（沙漏腰线+大裙摆）重塑时尚审美，经典产品包括藤格纹设计的Lady Dior手袋、传奇999红唇口红（哑光/滋润双质地）、J'adore真我花香调香水，凭借精湛工艺、艺术灵感与永恒风格，成为高级时尚与美妆领域的标杆，诠释着法式生活艺术的精髓。</t>
+          <t>Crocs: 1999年诞生于美国科罗拉多州的全球休闲鞋领导品牌，以标志性洞洞鞋（Clog）和专利Croslite™轻质缓冲材质为核心，产品兼具透气、防滑、易清洁等特性，覆盖全年龄段日常出行、户外休闲等多元场景，主打“舒适无束缚”的生活理念，成为全球消费者心中“自在休闲”的鞋履代表。</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Dior: Founded by Christian Dior in Paris in 1946, iconic global French luxury brand covering haute couture, ready-to-wear, handbags, footwear, beauty &amp; perfume. 1947 “New Look” (hourglass waist + full skirt) redefined fashion. Classics: Cannage-patterned Lady Dior, Rouge Dior 999 (matte/satin), J’adore perfume. Exquisite craftsmanship &amp; timeless style make it a luxury fashion/beauty benchmark, embodying French art de vivre.</t>
+          <t>Crocs: 1999-born Colorado global casual footwear leader. Iconic clogs with Croslite™ cushioning. Breathable, slip-resistant, easy-to-clean. For all ages, daily &amp; outdoor. Comfortable, unrestrictive lifestyle.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="25.5" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Divide The YouthI</t>
+          <t>Cactus Jack</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>divide-the -youthI</t>
+          <t>mastermind-japan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Divide The Youth（青年分界）2021 年由 Tuinenburg 创立于美国加州，是网红街头服饰品牌。主营连帽衫、T 恤、外套及配饰，采用纯棉、棉混纺与抓绒材质，设计师团队打造标志性文字图案与刺绣细节，风格叛逆前卫、中性百搭，融合 Y2K 与日系原宿风，风靡全球 TikTok/Instagram 时尚圈，受 Z 世代追捧。</t>
+          <t>Cactus Jack: 由美国说唱歌手Travis Scott创立的街头潮流品牌，以沙漠野性与工业街头风为核心设计语言，主打潮流服饰、联名鞋款及配件，因与Nike、Jordan Brand合作推出Air Jordan 1 Travis Scott等爆款鞋品走红，是全球潮流爱好者追捧的街头文化标杆品牌。</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Divide The Youth: Founded by Tuinenburg in California, USA (2021), popular streetwear brand specializing in hoodies, tees, jackets &amp; accessories (cotton, blends, fleece). Signature text graphics/embroidery, rebellious avant-garde unisex style blending Y2K &amp; Japanese Harajuku, viral on global TikTok/Instagram, favored by Gen Z.</t>
+          <t>Cactus Jack: Streetwear brand founded by US rapper Travis Scott, blending desert wildness &amp; industrial street style. Specializes in apparel, collab sneakers &amp; accessories. Gained fame via Nike/Jordan Brand’s Air Jordan 1 Travis Scott, a global street culture icon for enthusiasts.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="25.5" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
+          <t>Dallas Cowboys</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>dallas-cowboys</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Dallas Cowboys: 1960年成立的美国NFL职业橄榄球队，隶属国家橄榄球联合会（NFC）东部分区，曾5次夺得超级碗冠军，获称“美国之队”（America's Team）。球队以标志性牛仔星队徽、经典蓝银配色队服为识别，主场为达拉斯AT&amp;T体育场（AT&amp;T Stadium），是NFL历史上最具影响力、商业价值及全球球迷基础的球队之一，传承美式橄榄球的热血与文化符号。</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Dallas Cowboys: NFL team est. 1960, NFC East. 5x Super Bowl champs, America's Team. Iconic star logo, blue-silver uniforms, AT&amp;T Stadium home. Influential, valuable, global football icon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="25.5" customHeight="1">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Denver Broncos</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>denver-broncos</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Denver Broncos: 美国国家橄榄球联盟（NFL）经典球队，1960年作为AFL创始成员成立，1970年加入NFL，主场位于丹佛的Empower Field at Mile High。队史3次夺得超级碗冠军（1997、1998、2015年），以标志性橙蓝配色队服、野性野马队标闻名，拥有庞大忠实球迷群体“Broncos Country”。球队延续坚韧拼搏的橄榄球精神，是NFL历史上极具影响力的老牌劲旅。</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Denver Broncos: Legendary NFL team, 3x Super Bowl champions (1997, 1998, 2015). Iconic orange &amp; blue colors, wild horse logo. Heart of loyal "Broncos Country" fans. Founded 1960.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="25.5" customHeight="1">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Deportivo</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>deportivo</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Deportivo（拉科鲁尼亚体育俱乐部）1906 年 3 月 2 日由西班牙体育爱好者创立于拉科鲁尼亚，主营球衣、训练服及球迷周边，与 Macron 等品牌合作设计，主色调蓝白条纹。采用透气速干聚酯纤维材质，风格经典运动，融入球队 "蓝白军团" 元素，风靡西班牙及全球球迷圈，以西甲冠军底蕴与忠诚球迷文化著称。</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Deportivo(Deportivo de La Coruña): Founded by Spanish sports enthusiasts in La Coruña on Mar 2, 1906, offering jerseys, training kits &amp; fan merch. Collaborates with Macron, blue-white stripes, breathable quick-dry polyester, classic sporty style with "Blue and White Army" elements. Popular globally, known for La Liga champion heritage &amp; loyal fan culture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="25.5" customHeight="1">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Destroy Lonely</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>destroy-lonely</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Destroy Lonely: 美国新生代说唱歌手，以melodic trap风格见长，代表作《NOSTYLIST》《VETERAN》凭借独特flow、氛围感编曲及孤独主题歌词出圈，流媒体播放量破千万，是当下嘻哈场景中极具辨识度的艺人，其音乐融合 trap 节奏与旋律性，传递年轻一代的自我表达与情绪共鸣。</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Destroy Lonely: U.S. rising rapper specializing in melodic trap, with hits "NOSTYLIST" &amp; "VETERAN". Known for unique flow, atmospheric production, lonely-themed lyrics, millions of streams. Distinctive in hip-hop, blending trap rhythm &amp; melody to convey Gen Z's self-expression &amp; emotional resonance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="25.5" customHeight="1">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Descente</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>descente</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Descente（迪桑特）1935 年由石本他家男创立于日本大阪，1961 年注册商标，名称源自法语 "滑降"。主打专业滑雪服与高端运动服饰，由滑雪名将西村一良担任顾问，采用 GORE‑TEX、COOLMAX 等科技面料，融合专业功能性与简约美学，风靡全球，是瑞士、加拿大等多国滑雪队官方赞助商。</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Descente: French for descent, founded 1935 Osaka, trademarked 1961. Expert pro ski wear &amp; sportswear with GORE-TEX, COOLMAX. Advised by ski champ Nishimura. Blends function &amp; minimalist aesthetics. Global sponsor for Swiss, Canadian ski teams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="25.5" customHeight="1">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Diadora</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>diadora</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Diadora: 1948年创立于意大利的专业运动品牌，由Marcello Danieli创办，以意式精湛工艺与运动基因著称，核心产品涵盖经典运动鞋（如Mirage、N9000系列）、专业运动服饰及配件，深耕足球领域（曾赞助尤文图斯、AC米兰等顶级球队），融合复古设计与现代科技，采用优质皮革、透气网布等功能性材质，满足运动爱好者专业性能需求与潮流人士复古审美，是意大利运动文化与时尚风格结合的代表品牌。</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Diadora: Founded in 1948 Italy by Marcello Danieli, Italian craftsmanship &amp; sport heritage brand. Core products: classic sneakers (Mirage, N9000), sportswear/accessories. Deep in football (sponsored Juventus, AC Milan). Merges retro design + modern tech, premium leather/breathable mesh for pro performance &amp; retro style. Italian sport-culture fashion icon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="25.5" customHeight="1">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Dior</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>dior</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Dior: 1946年由克里斯汀·迪奥（Christian Dior）在巴黎创立，全球法式奢华与优雅的标志性品牌，业务涵盖高级定制时装、成衣、手袋、鞋履、美妆及香水。1947年以“New Look”廓形（沙漏腰线+大裙摆）重塑时尚审美，经典产品包括藤格纹设计的Lady Dior手袋、传奇999红唇口红（哑光/滋润双质地）、J'adore真我花香调香水，凭借精湛工艺、艺术灵感与永恒风格，成为高级时尚与美妆领域的标杆，诠释着法式生活艺术的精髓。</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Dior: Founded by Christian Dior in Paris in 1946, iconic global French luxury brand covering haute couture, ready-to-wear, handbags, footwear, beauty &amp; perfume. 1947 “New Look” (hourglass waist + full skirt) redefined fashion. Classics: Cannage-patterned Lady Dior, Rouge Dior 999 (matte/satin), J’adore perfume. Exquisite craftsmanship &amp; timeless style make it a luxury fashion/beauty benchmark, embodying French art de vivre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="25.5" customHeight="1">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Divide The YouthI</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>divide-the -youthI</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Divide The Youth（青年分界）2021 年由 Tuinenburg 创立于美国加州，是网红街头服饰品牌。主营连帽衫、T 恤、外套及配饰，采用纯棉、棉混纺与抓绒材质，设计师团队打造标志性文字图案与刺绣细节，风格叛逆前卫、中性百搭，融合 Y2K 与日系原宿风，风靡全球 TikTok/Instagram 时尚圈，受 Z 世代追捧。</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Divide The Youth: Founded by Tuinenburg in California, USA (2021), popular streetwear brand specializing in hoodies, tees, jackets &amp; accessories (cotton, blends, fleece). Signature text graphics/embroidery, rebellious avant-garde unisex style blending Y2K &amp; Japanese Harajuku, viral on global TikTok/Instagram, favored by Gen Z.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="25.5" customHeight="1">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Drew House</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>drew-house</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Drew House 由歌手贾斯汀・比伯（Justin Bieber）与创意总监 Ryan Good 于 2018 年创立，品牌以 “阳光、慵懒、治愈” 为核心调性，标志性的笑脸 Logo 和手写体 “drew” 元素，让它成为近年最火的美式街头潮牌之一，深受明星和潮人喜爱。</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Drew House: Justin Bieber &amp; Ryan Good's 2018 streetwear brand. Core vibe: sunny, laid-back, healing. Iconic smiley logo &amp; "drew" script.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="25.5" customHeight="1">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>Dolce</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>dolce</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Dolce: 
 （注：因未获取到Dolce品牌对应的中文描述内容，无法按要求生成符合SEO优化的品牌描述。）</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>Dolce: Note: Failed to obtain the Chinese description corresponding to the Dolce brand, unable to generate a SEO-optimized brand description as required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="25.5" customHeight="1">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Dyson</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>dyson</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Dyson: 1991年由詹姆斯·戴森（James Dyson）创立的英国创新科技品牌，以原创气旋技术（Cyclone Technology）颠覆传统清洁逻辑，核心产品线涵盖无绳吸尘器（如V15 Detect）、Supersonic吹风机、Airwrap美发造型器、Pure Hot+Cool空气净化器及Air Multiplier无叶风扇等。产品采用高强度ABS工程塑料与金属质感组件，融合简约现代设计与高效能科技，主打“无袋吸尘更洁净”“快速干发不伤发”“智能控温美发”“全域空气净化”等优势，是全球家电与个人护理领域以技术创新为标签的领先品牌。</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Dyson: British tech innovator since 1991. Cyclone Technology for bagless cleaning. Products: cordless vacuums, Supersonic dryers, Airwrap stylers, air purifiers. High-strength ABS &amp; metal. Leading in appliances &amp; personal care.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="25.5" customHeight="1">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Dusk</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>dusk</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Dusk 2000 年创立于澳大利亚，主营香薰蜡烛、家居香氛及简约服饰，采用天然大豆蜡、有机棉等环保材质，主打自然治愈简约风格，畅销澳洲、欧美及亚太地区，是全球热门轻奢生活方式品牌。</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Dusk: Founded in Australia in 2000, specializes in scented candles, home fragrances &amp; minimalist apparel. Uses eco-friendly materials like natural soy wax &amp; organic cotton, with natural healing minimalist style. Sold in Australia, Europe, Americas &amp; Asia-Pacific, a globally popular luxury lifestyle brand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="25.5" customHeight="1">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Emporio Armani</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>emporio-armani</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Emporio Armani: 1981年由Giorgio Armani创立，意大利奢侈时尚品牌副线，专注于年轻潮流服装与配饰，产品系列包括男女装、眼镜、手表及香水，经典设计含标志性Logo和简约剪裁，采用高级面料与精湛工艺，风格现代优雅、时尚动感，适合日常穿着与特殊场合。</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Emporio Armani: Luxury fashion brand founded in 1981, offering modern, elegant apparel and accessories for youthful, dynamic styles. Features iconic logo and tailored designs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="25.5" customHeight="1">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Enfants Riches Deprimes</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>enfants-riches-deprimes</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Enfants Riches Deprimes: 源自法国的高端街头时尚品牌，以“颓废奢华”风格著称，融合街头叛逆精神与高级时装工艺，选用羊绒、丝绸等珍稀面料结合做旧、破洞、标语刺绣等标志性设计，主打卫衣、外套、针织品等系列，精准定位追求独特个性与暗黑高级感的潮流精英，是全球先锋时尚圈推崇的“反主流奢华”代表品牌。</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Enfants Riches Déprimés: French luxury streetwear brand with depressed luxury style, merging street rebellion and high-fashion using cashmere, silk, distressed designs on hoodies, jackets for elite trendsetters, an anti-mainstream luxury icon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="25.5" customHeight="1">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Essentials</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>essentials</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Essentials（Fear of God Essentials）2018 年由 Jerry Lorenzo 创立于美国洛杉矶，是 Fear of God 副线。主营卫衣、T 恤、卫裤等基础款，Jerry Lorenzo 主导设计，采用重磅纯棉、抓绒等优质面料，主打 oversized 剪裁、中性色调与极简徽标，风格高级休闲，风靡全球 Z 世代，是高街潮流代表品牌。</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>ESSENTIALS: Launched in 2018 by Jerry Lorenzo in LA, this Fear of God line offers core styles like hoodies and sweatpants in heavyweight cotton and fleece, featuring oversized fits, neutral tones, and minimalist branding for elevated, global streetwear.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="25.5" customHeight="1">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Fear Of God</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>fear-of-god</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Fear-Of-God: 2013年由Jerry Lorenzo创立的美国高端街头服饰品牌，以“街头文化与高级时尚融合”为核心调性，主打oversize宽松剪裁、中性化设计语言，采用重磅棉、优质皮革等质感面料，经典单品涵盖Essentials基础系列、水洗牛仔夹克、高街连帽衫，曾与Nike等头部品牌推出联名系列，专注为追求潮流质感与独特风格的青年群体，打造兼具实用性与设计辨识度的高端街头服饰。</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Fear Of God: Founded 2013 by Jerry Lorenzo, US high-end streetwear blending street culture &amp; luxury fashion. Oversize, gender-neutral designs (heavy cotton/premium leather). Classics: Essentials line, washed denim jackets, high-street hoodies. Nike collaborations. For youth seeking trendy texture &amp; unique style, practical recognizable streetwear.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="25.5" customHeight="1">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Fendi</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>fendi</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Fendi: 1925年由Adele Casagrande与Edoardo Fendi创立于意大利罗马，全球顶级奢侈品牌，以高级时装、皮具、配饰及香水等品类著称。品牌核心识别为标志性双F logo（FF图案）与传承近百年的精湛皮草工艺，经典产品涵盖Baguette法棍手袋、Peekaboo手袋及Fendi Roma Amor系列。作为“罗马奢华美学”的代表，Fendi融合意大利传统手工技艺与现代先锋设计，风格兼具奢华优雅与创意张力，长期引领高端时尚潮流。</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Fendi: Italian luxury brand founded 1925 Rome, renowned for iconic FF logo, fur craftsmanship, Baguette &amp; Peekaboo handbags, embodying Roman opulence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="25.5" customHeight="1">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>flamengo</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Flamengo: 巴西里约热内卢百年体育俱乐部，1895年成立，以足球项目为核心名片，绰号“Mengão”，主场坐落于著名的马拉卡纳体育场。作为巴西最具人气与成就的俱乐部之一，曾斩获世界杯俱乐部杯、南美解放者杯、多届巴甲联赛冠军等重磅荣誉，诞生多位足球传奇球星，在全球足球领域拥有深远影响力。</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Flamengo: Historic Brazilian football club founded 1895, based at Maracanã Stadium. A global icon, winner of Copa Libertadores and multiple Brasileirão titles, renowned for legendary players.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="25.5" customHeight="1">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Fox Racing</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>fox-racing</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Fox Racing: 1974年创立于美国的专业极限运动装备品牌，专注越野摩托车（Motocross）、山地自行车、滑雪等领域，提供专业服饰、护具、头盔及配件，以卓越防护性能、耐用材质与潮流设计的融合为核心特色，深受全球极限运动爱好者及专业选手信赖，是极限运动装备领域的知名品牌。</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Fox Racing: Founded in the US in 1974, professional extreme sports gear brand specializing in motocross, mountain biking, skiing, etc. Offering apparel, protective gear, helmets &amp; accessories, core feature: fusion of excellent protection, durable materials &amp; trendy design. Trusted by global enthusiasts &amp; pro athletes, renowned in extreme sports gear.</t>
         </is>
       </c>
     </row>
     <row r="94" ht="25.5" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Funtoliu</t>
+          <t>Dyson</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>funtoliu</t>
+          <t>dyson</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Funtoliu 是源自美国的休闲服饰品牌，主营卫衣、T 恤、运动裤等基础款，采用纯棉、抓绒舒适面料，主打宽松简约街头风，性价比高，深受北美、欧洲及亚太年轻群体喜爱。</t>
+          <t>Dyson: 1991年由詹姆斯·戴森（James Dyson）创立的英国创新科技品牌，以原创气旋技术（Cyclone Technology）颠覆传统清洁逻辑，核心产品线涵盖无绳吸尘器（如V15 Detect）、Supersonic吹风机、Airwrap美发造型器、Pure Hot+Cool空气净化器及Air Multiplier无叶风扇等。产品采用高强度ABS工程塑料与金属质感组件，融合简约现代设计与高效能科技，主打“无袋吸尘更洁净”“快速干发不伤发”“智能控温美发”“全域空气净化”等优势，是全球家电与个人护理领域以技术创新为标签的领先品牌。</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Funtoliu: US-origin casual apparel brand specializing in basic styles (hoodies, T-shirts, sweatpants) with comfortable cotton &amp; fleece fabrics. Features loose minimalist street style, high cost-performance, popular among young people in North America, Europe, Asia-Pacific.</t>
+          <t>Dyson: British tech innovator since 1991. Cyclone Technology for bagless cleaning. Products: cordless vacuums, Supersonic dryers, Airwrap stylers, air purifiers. High-strength ABS &amp; metal. Leading in appliances &amp; personal care.</t>
         </is>
       </c>
     </row>
     <row r="95" ht="25.5" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Gallery Dept</t>
+          <t>Dusk</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>gallery-dept</t>
+          <t>dusk</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Gallery Dept: 2018年由Josué Thomas创立于美国洛杉矶的复古街头潮牌，以「古着再造+手工艺术」为核心定位，主打做旧牛仔夹克、手绘卫衣、洗水牛仔裤等单品，通过手工打磨、植绒印花、破洞做旧等工艺还原复古质感，融合街头叛逆与怀旧美学，践行可持续时尚理念，每款单品均具独特性，是全球潮人、复古爱好者追求个性穿搭的标志性品牌。</t>
+          <t>Dusk 2000 年创立于澳大利亚，主营香薰蜡烛、家居香氛及简约服饰，采用天然大豆蜡、有机棉等环保材质，主打自然治愈简约风格，畅销澳洲、欧美及亚太地区，是全球热门轻奢生活方式品牌。</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Gallery Dept: LA vintage streetwear since 2018, handmade vintage remake with distressed denim and hand-painted apparel. Blends street style and nostalgia, sustainable fashion, each piece unique.</t>
+          <t>Dusk: Founded in Australia in 2000, specializes in scented candles, home fragrances &amp; minimalist apparel. Uses eco-friendly materials like natural soy wax &amp; organic cotton, with natural healing minimalist style. Sold in Australia, Europe, Americas &amp; Asia-Pacific, a globally popular luxury lifestyle brand.</t>
         </is>
       </c>
     </row>
     <row r="96" ht="25.5" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Georgia Bulldogs</t>
+          <t>Emporio Armani</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>georgia-bulldogs</t>
+          <t>emporio-armani</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Georgia Bulldogs: 美国佐治亚大学（University of Georgia）官方体育代表队核心昵称，以NCAA橄榄球项目的卓越表现闻名，是东南联盟（SEC）传统豪强，曾斩获2021、2022赛季NCAA橄榄球全国冠军及多次SEC联盟冠军；标志性元素包括传奇斗牛犬 mascot“Uga”、经典红黑配色队服，凝聚着“Bulldog Nation”全球球迷的热情，是佐治亚州体育精神与校园荣誉的象征。</t>
+          <t>Emporio Armani: 1981年由Giorgio Armani创立，意大利奢侈时尚品牌副线，专注于年轻潮流服装与配饰，产品系列包括男女装、眼镜、手表及香水，经典设计含标志性Logo和简约剪裁，采用高级面料与精湛工艺，风格现代优雅、时尚动感，适合日常穿着与特殊场合。</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Georgia Bulldogs: Official sports team nickname of the University of Georgia, renowned for NCAA football excellence as a traditional SEC powerhouse—2021 &amp; 2022 NCAA national champions, multiple SEC titles. Features legendary bulldog mascot "Uga", classic red-black uniforms; embodies "Bulldog Nation" fans’ passion, symbolizing Georgia’s sports spirit &amp; campus honor.</t>
+          <t>Emporio Armani: Luxury fashion brand founded in 1981, offering modern, elegant apparel and accessories for youthful, dynamic styles. Features iconic logo and tailored designs.</t>
         </is>
       </c>
     </row>
     <row r="97" ht="25.5" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Gimenez</t>
+          <t>Enfants Riches Deprimes</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>gimenez</t>
+          <t>enfants-riches-deprimes</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Gimenez（Cayetano Giménez）1975 年由 Cayetano Giménez 创立于西班牙阿利坎特，是家族鞋履品牌。主营女士正装鞋、休闲靴、时尚凉鞋等，由 Desire Giménez 主导设计，采用头层牛皮等优质面料，主打简约精致线条与舒适穿着体验，融合西班牙传统工艺与现代时尚风格，风靡欧洲及全球女性市场，以性价比高著称</t>
+          <t>Enfants Riches Deprimes: 源自法国的高端街头时尚品牌，以“颓废奢华”风格著称，融合街头叛逆精神与高级时装工艺，选用羊绒、丝绸等珍稀面料结合做旧、破洞、标语刺绣等标志性设计，主打卫衣、外套、针织品等系列，精准定位追求独特个性与暗黑高级感的潮流精英，是全球先锋时尚圈推崇的“反主流奢华”代表品牌。</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Gimenez(Cayetano Giménez): Family footwear brand founded in 1975 in Alicante, Spain by Cayetano Giménez. Specializes in women’s dress shoes, casual boots, fashion sandals, etc., designed by Desire Giménez. Uses premium materials like full-grain leather, focusing on minimalist refined lines &amp; comfort, blending Spanish traditional craft with modern style. Popular in European &amp; global women’s markets, known for great value.</t>
+          <t>Enfants Riches Déprimés: French luxury streetwear brand with depressed luxury style, merging street rebellion and high-fashion using cashmere, silk, distressed designs on hoodies, jackets for elite trendsetters, an anti-mainstream luxury icon.</t>
         </is>
       </c>
     </row>
     <row r="98" ht="25.5" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Giorgio Armani</t>
+          <t>Essentials</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>giorgio-armani</t>
+          <t>essentials</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Giorgio Armani: 1975年由乔治·阿玛尼（Giorgio Armani）创立的意大利顶级奢侈品品牌，以极简优雅的设计风格、精湛剪裁工艺与高品质材质闻名，涵盖高级定制时装、成衣、美妆、香水、皮具及配饰等全品类，经典作品如男士西装、Armani Si香水深入人心，始终传递高端生活方式与永恒时尚美学，是全球奢华时尚领域的标志性品牌之一。</t>
+          <t>Essentials（Fear of God Essentials）2018 年由 Jerry Lorenzo 创立于美国洛杉矶，是 Fear of God 副线。主营卫衣、T 恤、卫裤等基础款，Jerry Lorenzo 主导设计，采用重磅纯棉、抓绒等优质面料，主打 oversized 剪裁、中性色调与极简徽标，风格高级休闲，风靡全球 Z 世代，是高街潮流代表品牌。</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Giorgio Armani: Italian premier luxury brand founded by Giorgio Armani in 1975, renowned for minimalist elegance, exquisite tailoring &amp; premium materials. Covers haute couture, ready-to-wear, beauty, fragrances (Armani Si), leather goods &amp; accessories. Delivers luxury lifestyle &amp; timeless aesthetics, iconic in global luxury fashion.</t>
+          <t>ESSENTIALS: Launched in 2018 by Jerry Lorenzo in LA, this Fear of God line offers core styles like hoodies and sweatpants in heavyweight cotton and fleece, featuring oversized fits, neutral tones, and minimalist branding for elevated, global streetwear.</t>
         </is>
       </c>
     </row>
     <row r="99" ht="25.5" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Givenchy</t>
+          <t>Eye of Providence</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>givenchy</t>
+          <t>eye-of-providence</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Givenchy: 1952年由休伯特·德·纪梵希（Hubert de Givenchy）创立的法国顶级奢侈品牌，以先锋设计与现代优雅著称，核心覆盖高级成衣、皮具、香水及美妆品类。标志性4G logo（融合Givenchy、Genteel、Glamour、Grace精神）深入人心，经典产品包括Antigona系列手袋（利落线条配奢华皮革）、Le Rouge纪梵希高定香榭口红（丝绒质地与高饱和色号）及高定礼服（流畅剪裁诠释贵族质感）。从与奥黛丽·赫本的传奇合作到当代街头奢华风格融合，Givenchy始终践行“优雅与叛逆共存”的时尚态度，是全球精英追逐的奢侈品牌代表。</t>
+          <t>DRKK「全视之眼」暗黑高街连帽卫衣，采用重磅水洗抓绒棉，正面立体压花打造 “光明会之眼” 视觉效果，做旧褪色工艺搭配短款廓形，自带复古街头质感，是高街爱好者的热门单品。</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Givenchy: French luxury brand since 1952, known for avant-garde design &amp; modern elegance. Offers haute couture, leather goods, perfumes, cosmetics. Iconic 4G logo. Classics: Antigona handbags, Le Rouge lipsticks. Elegance meets rebellion.</t>
+          <t>This DRKK hoodie features the iconic Eye of Providence embossed design, made with heavyweight washed fleece. It embodies dark high street style with vintage fading and cropped silhouette, loved by streetwear fans.</t>
         </is>
       </c>
     </row>
     <row r="100" ht="25.5" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Golden Goose</t>
+          <t>Fear Of God</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>golden-goose</t>
+          <t>fear-of-god</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Golden Goose: 源自意大利的高端潮流品牌，以标志性做旧工艺休闲鞋（sneakers）为核心，主打复古街头风格，采用小牛皮、麂皮等优质材质手工打造，经典元素包含星星补丁、自然做旧划痕与仿脏设计，凭借“破坏美学”成为明星与潮流人士青睐的爆款单品，是追求独特质感与复古腔调的鞋履首选品牌。</t>
+          <t>Fear-Of-God: 2013年由Jerry Lorenzo创立的美国高端街头服饰品牌，以“街头文化与高级时尚融合”为核心调性，主打oversize宽松剪裁、中性化设计语言，采用重磅棉、优质皮革等质感面料，经典单品涵盖Essentials基础系列、水洗牛仔夹克、高街连帽衫，曾与Nike等头部品牌推出联名系列，专注为追求潮流质感与独特风格的青年群体，打造兼具实用性与设计辨识度的高端街头服饰。</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Golden Goose: Italian luxury brand crafting handcrafted distressed sneakers from premium leathers, featuring star patches &amp; vintage styling for distinctive aesthetic.</t>
+          <t>Fear Of God: Founded 2013 by Jerry Lorenzo, US high-end streetwear blending street culture &amp; luxury fashion. Oversize, gender-neutral designs (heavy cotton/premium leather). Classics: Essentials line, washed denim jackets, high-street hoodies. Nike collaborations. For youth seeking trendy texture &amp; unique style, practical recognizable streetwear.</t>
         </is>
       </c>
     </row>
     <row r="101" ht="25.5" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Gran Sasso</t>
+          <t>Fendi</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>gran-sasso</t>
+          <t>fendi</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Gran Sasso: 源自意大利Abruzzo地区Gran Sasso d'Italia山脉的经典天然矿泉水品牌，依托阿尔卑斯山系深层地下水源，经千年岩层自然过滤，水质纯净且富含钙、镁等天然矿物质，口感清冽甘醇。品牌主打“自然本源的健康饮水”理念，是意大利家庭日常、餐饮场景及全球高端水市场的热门选择，以“源自山脉的纯粹滋味”传递原生品质。</t>
+          <t>Fendi: 1925年由Adele Casagrande与Edoardo Fendi创立于意大利罗马，全球顶级奢侈品牌，以高级时装、皮具、配饰及香水等品类著称。品牌核心识别为标志性双F logo（FF图案）与传承近百年的精湛皮草工艺，经典产品涵盖Baguette法棍手袋、Peekaboo手袋及Fendi Roma Amor系列。作为“罗马奢华美学”的代表，Fendi融合意大利传统手工技艺与现代先锋设计，风格兼具奢华优雅与创意张力，长期引领高端时尚潮流。</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Gran Sasso: Classic Italian natural mineral water from Abruzzo’s Gran Sasso d’Italia. Sourced from Alpine deep underground, filtered by thousand-year rocks—pure, rich in calcium/magnesium, crisp &amp; sweet. Core concept: natural healthy drinking. Popular in Italian households, dining, global premium water, delivering pure mountain taste.</t>
+          <t>Fendi: Italian luxury brand founded 1925 Rome, renowned for iconic FF logo, fur craftsmanship, Baguette &amp; Peekaboo handbags, embodying Roman opulence.</t>
         </is>
       </c>
     </row>
     <row r="102" ht="25.5" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gore Tex </t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">gore-tex </t>
+          <t>flamengo</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Gore Tex: 美国戈尔公司（W.L. Gore &amp; Associates）旗下全球知名功能性面料技术品牌，核心依托膨体聚四氟乙烯（ePTFE）膜技术，实现“防水、透气、防风”三大核心功能，广泛应用于户外服装、鞋靴、手套及医疗植入物等场景，是Arc'teryx、The North Face等高端户外品牌的核心面料合作伙伴，以性能稳定性与耐用性成为户外爱好者、专业运动员及极限环境从业者信赖的功能面料标杆。</t>
+          <t>Flamengo: 巴西里约热内卢百年体育俱乐部，1895年成立，以足球项目为核心名片，绰号“Mengão”，主场坐落于著名的马拉卡纳体育场。作为巴西最具人气与成就的俱乐部之一，曾斩获世界杯俱乐部杯、南美解放者杯、多届巴甲联赛冠军等重磅荣誉，诞生多位足球传奇球星，在全球足球领域拥有深远影响力。</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>GORE TEX: Leading U.S. functional fabric tech with ePTFE membrane, delivering waterproof, breathable, windproof performance. Trusted by Arc'teryx &amp; The North Face for outdoor gear &amp; medical implants. The performance fabric standard.</t>
+          <t>Flamengo: Historic Brazilian football club founded 1895, based at Maracanã Stadium. A global icon, winner of Copa Libertadores and multiple Brasileirão titles, renowned for legendary players.</t>
         </is>
       </c>
     </row>
     <row r="103" ht="25.5" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Green Bay Packers</t>
+          <t>Fox Racing</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>green-bay-packers</t>
+          <t>fox-racing</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Green Bay Packers: 1919年成立于美国威斯康星州绿湾，是NFL（国家橄榄球联盟）历史最悠久的球队之一，隶属于NFC北区，绰号“包装工队”。以标志性绿色与金色队服为视觉标识，主场是传奇的Lambeau Field（兰博球场）。作为NFL夺冠次数最多的球队（13次联盟冠军，含4次超级碗），拥有深厚橄榄球传统，全球忠诚球迷群体中“奶酪头”文化更是NFL独特符号。</t>
+          <t>Fox Racing: 1974年创立于美国的专业极限运动装备品牌，专注越野摩托车（Motocross）、山地自行车、滑雪等领域，提供专业服饰、护具、头盔及配件，以卓越防护性能、耐用材质与潮流设计的融合为核心特色，深受全球极限运动爱好者及专业选手信赖，是极限运动装备领域的知名品牌。</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Green Bay Packers: Founded 1919 in Green Bay, Wisconsin, USA—one of NFL’s oldest teams (NFC North), nicknamed "Packers". Iconic green/gold uniforms, home at legendary Lambeau Field. NFL’s most successful with 13 league titles (4 Super Bowls), rich tradition. "Cheesehead" culture, a unique NFL symbol for global loyal fans.</t>
+          <t>Fox Racing: Founded in the US in 1974, professional extreme sports gear brand specializing in motocross, mountain biking, skiing, etc. Offering apparel, protective gear, helmets &amp; accessories, core feature: fusion of excellent protection, durable materials &amp; trendy design. Trusted by global enthusiasts &amp; pro athletes, renowned in extreme sports gear.</t>
         </is>
       </c>
     </row>
     <row r="104" ht="25.5" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Griezmann</t>
+          <t>False Perception</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>griezmann</t>
+          <t xml:space="preserve">false-perception </t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Griezmann 2015 年创立于法国，主营简约休闲服饰，采用纯棉、针织等舒适面料，融合法式简约与街头潮流，设计感与性价比兼具，深受欧洲、北美及亚太年轻群体喜爱。</t>
+          <t>False Perception 是一个主打暗黑高街风格的小众街头品牌，以复古做旧工艺、暗黑涂鸦印花和宗教 / 亚文化主题设计闻名，深受高街爱好者喜爱。其单品常以重磅面料、夸张印花和宽松廓形为特色，是近年跨境平台和国内市场的热门高街单品。</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Griezmann: Founded in France in 2015, specializing in minimalist casual apparel with comfy fabrics like cotton &amp; knit. Blends French minimalism with streetwear, balancing design and value. Popular among young people in Europe, North America &amp; Asia-Pacific.</t>
+          <t>False Perception: Dark streetwear brand known for vintage distressing, gothic graffiti prints, and religious/subculture themes. Features heavyweight fabrics, bold graphics, and oversized silhouettes.</t>
         </is>
       </c>
     </row>
     <row r="105" ht="25.5" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Gucci</t>
+          <t>Funtoliu</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>gucci</t>
+          <t>funtoliu</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Gucci: 1921年由古驰奥·古驰（Guccio Gucci）在意大利佛罗伦萨创立的顶级奢侈品品牌，以标志性双G logo、马衔扣元素及红绿织带为经典标识，涵盖高端时装、经典手袋（如Dionysus、Jackie 1961系列）、鞋履、奢华配饰与香水等核心品类，传承意大利百年精湛手工艺，融合复古美学与现代先锋设计，是全球追求极致品质、经典时尚与奢华格调的高端消费者首选品牌。</t>
+          <t>Funtoliu 是源自美国的休闲服饰品牌，主营卫衣、T 恤、运动裤等基础款，采用纯棉、抓绒舒适面料，主打宽松简约街头风，性价比高，深受北美、欧洲及亚太年轻群体喜爱。</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Gucci: Since 1921 Florence, luxury brand with iconic double-G, horsebit, green-red webbing. Offers fashion, handbags (Dionysus, Jackie 1961), shoes, accessories, perfumes. Italian craftsmanship, vintage-modern blend for elite consumers.</t>
+          <t>Funtoliu: US-origin casual apparel brand specializing in basic styles (hoodies, T-shirts, sweatpants) with comfortable cotton &amp; fleece fabrics. Features loose minimalist street style, high cost-performance, popular among young people in North America, Europe, Asia-Pacific.</t>
         </is>
       </c>
     </row>
     <row r="106" ht="25.5" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Hellstar</t>
+          <t>Gallery Dept</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>hellstar</t>
+          <t>gallery-dept</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hellstar: 专注暗黑街头潮流的时尚品牌，主打卫衣、夹克、配饰等核心单品，以独特设计融合街头文化与暗黑美学，采用优质面料打造舒适穿着体验，风格酷感鲜明，深受Z世代年轻人及潮流爱好者青睐，是展现个性穿搭的热门选择。</t>
+          <t>Gallery Dept: 2018年由Josué Thomas创立于美国洛杉矶的复古街头潮牌，以「古着再造+手工艺术」为核心定位，主打做旧牛仔夹克、手绘卫衣、洗水牛仔裤等单品，通过手工打磨、植绒印花、破洞做旧等工艺还原复古质感，融合街头叛逆与怀旧美学，践行可持续时尚理念，每款单品均具独特性，是全球潮人、复古爱好者追求个性穿搭的标志性品牌。</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Hellstar: Dark streetwear brand merging street culture with dark aesthetics. Core hoodies, jackets &amp; accessories. Premium fabrics, bold style for Z-gen &amp; trendsetters.</t>
+          <t>Gallery Dept: LA vintage streetwear since 2018, handmade vintage remake with distressed denim and hand-painted apparel. Blends street style and nostalgia, sustainable fashion, each piece unique.</t>
         </is>
       </c>
     </row>
     <row r="107" ht="25.5" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Hermes</t>
+          <t>Georgia Bulldogs</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>hermes</t>
+          <t>georgia-bulldogs</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hermes: 1837年由Thierry Hermès创立于法国巴黎的全球顶级奢侈品品牌，以马具制作起家，凭借百年精湛手工工艺与永恒经典设计著称，核心产品涵盖高端皮革手袋（如传奇凯莉包Kelly Bag、柏金包Birkin Bag）、奢华丝绸配饰（经典90cm丝围巾）、男士香水（大地Eau Terre d'Hermès）及高级时装，传承法式优雅与极致品质，是全球奢华与品味的标志性品牌。</t>
+          <t>Georgia Bulldogs: 美国佐治亚大学（University of Georgia）官方体育代表队核心昵称，以NCAA橄榄球项目的卓越表现闻名，是东南联盟（SEC）传统豪强，曾斩获2021、2022赛季NCAA橄榄球全国冠军及多次SEC联盟冠军；标志性元素包括传奇斗牛犬 mascot“Uga”、经典红黑配色队服，凝聚着“Bulldog Nation”全球球迷的热情，是佐治亚州体育精神与校园荣誉的象征。</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Hermes: Founded in Paris, France by Thierry Hermès in 1837, this top global luxury brand started with equestrian gear. Renowned for century-old exquisite craftsmanship &amp; timeless designs, core products include high-end leather bags (Kelly Bag, Birkin Bag), luxury silk accessories (classic 90cm silk scarves), men’s perfume (Eau de Terre d'Hermès), and haute couture. It embodies French elegance, ultimate quality, and is a global symbol of luxury &amp; taste.</t>
+          <t>Georgia Bulldogs: Official sports team nickname of the University of Georgia, renowned for NCAA football excellence as a traditional SEC powerhouse—2021 &amp; 2022 NCAA national champions, multiple SEC titles. Features legendary bulldog mascot "Uga", classic red-black uniforms; embodies "Bulldog Nation" fans’ passion, symbolizing Georgia’s sports spirit &amp; campus honor.</t>
         </is>
       </c>
     </row>
     <row r="108" ht="25.5" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Hogan</t>
+          <t>Gimenez</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>hogan</t>
+          <t>gimenez</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hogan: 1986年创立于意大利的奢侈时尚品牌，隶属于Tod's集团，以「奢华休闲」风格为核心，专注鞋履、手袋及成衣设计。选用意大利顶级皮革，融合运动基因与高端工艺，经典产品如Interaction老爹鞋、H383商务运动鞋，打造「可通勤的奢华运动鞋」，深受明星、都市精英与时尚爱好者青睐。</t>
+          <t>Gimenez（Cayetano Giménez）1975 年由 Cayetano Giménez 创立于西班牙阿利坎特，是家族鞋履品牌。主营女士正装鞋、休闲靴、时尚凉鞋等，由 Desire Giménez 主导设计，采用头层牛皮等优质面料，主打简约精致线条与舒适穿着体验，融合西班牙传统工艺与现代时尚风格，风靡欧洲及全球女性市场，以性价比高著称</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Hogan: 1986 Italian luxury fashion brand under Tod’s Group, core “luxury casual” style, focusing on footwear, handbags &amp; ready-to-wear. Made with top Italian leather, blends sporty DNA with high-end craftsmanship. Iconic styles: Interaction Dad Sneakers, H383 business sneakers, creating “commutable luxury sneakers” favored by celebrities, urban elites &amp; fashion lovers.</t>
+          <t>Gimenez(Cayetano Giménez): Family footwear brand founded in 1975 in Alicante, Spain by Cayetano Giménez. Specializes in women’s dress shoes, casual boots, fashion sandals, etc., designed by Desire Giménez. Uses premium materials like full-grain leather, focusing on minimalist refined lines &amp; comfort, blending Spanish traditional craft with modern style. Popular in European &amp; global women’s markets, known for great value.</t>
         </is>
       </c>
     </row>
     <row r="109" ht="25.5" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Harman Kardon</t>
+          <t>Giorgio Armani</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>harman kardon</t>
+          <t>giorgio-armani</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Harman Kardon: 创立于1953年的高端音频品牌，隶属于哈曼国际集团，以专业声学工程技术与时尚精致设计著称。核心产品涵盖家用音响、无线耳机、车载音响系统等，经典系列包括琉璃（Aura）系列、Onyx系列等，凭借卓越音质表现与标志性外观设计，深受音频爱好者与高端消费群体青睐，广泛应用于家庭娱乐、专业音频场景及豪华汽车配套领域。</t>
+          <t>Giorgio Armani: 1975年由乔治·阿玛尼（Giorgio Armani）创立的意大利顶级奢侈品品牌，以极简优雅的设计风格、精湛剪裁工艺与高品质材质闻名，涵盖高级定制时装、成衣、美妆、香水、皮具及配饰等全品类，经典作品如男士西装、Armani Si香水深入人心，始终传递高端生活方式与永恒时尚美学，是全球奢华时尚领域的标志性品牌之一。</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Harman Kardon: Premium audio brand since 1953. Features acoustic engineering &amp; sleek design in Aura/Onyx series speakers, headphones &amp; car systems for exceptional sound.</t>
+          <t>Giorgio Armani: Italian premier luxury brand founded by Giorgio Armani in 1975, renowned for minimalist elegance, exquisite tailoring &amp; premium materials. Covers haute couture, ready-to-wear, beauty, fragrances (Armani Si), leather goods &amp; accessories. Delivers luxury lifestyle &amp; timeless aesthetics, iconic in global luxury fashion.</t>
         </is>
       </c>
     </row>
     <row r="110" ht="25.5" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>House Of Errors</t>
+          <t>Givenchy</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>house-of-errors</t>
+          <t>givenchy</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>House Of Errors 由设计师 Fully（Matthew Foulerton）于 2019 年创立于英国伦敦，主营服装、外套与配饰，标志性产品为全视之眼连帽衫与雕塑感羽绒服。设计师出身建筑专业，主打先锋超现实风格，融合建筑感廓形与解构主义，以重工刺绣、优质面料及皮革为核心材质，风靡全球潮流圈，在欧洲、北美及亚太地区深受时尚达人与明星青睐。</t>
+          <t>Givenchy: 1952年由休伯特·德·纪梵希（Hubert de Givenchy）创立的法国顶级奢侈品牌，以先锋设计与现代优雅著称，核心覆盖高级成衣、皮具、香水及美妆品类。标志性4G logo（融合Givenchy、Genteel、Glamour、Grace精神）深入人心，经典产品包括Antigona系列手袋（利落线条配奢华皮革）、Le Rouge纪梵希高定香榭口红（丝绒质地与高饱和色号）及高定礼服（流畅剪裁诠释贵族质感）。从与奥黛丽·赫本的传奇合作到当代街头奢华风格融合，Givenchy始终践行“优雅与叛逆共存”的时尚态度，是全球精英追逐的奢侈品牌代表。</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>House Of Errors: Founded 2019 London by Fully. Apparel, outerwear &amp; accessories. Iconic: All-Seeing Eye hoodies, sculptural down jackets. Architect-inspired avant-surrealism, architectural silhouettes &amp; deconstruction. Heavy embroidery, premium materials. Loved by fashion icons in EU, NA, APAC.</t>
+          <t>Givenchy: French luxury brand since 1952, known for avant-garde design &amp; modern elegance. Offers haute couture, leather goods, perfumes, cosmetics. Iconic 4G logo. Classics: Antigona handbags, Le Rouge lipsticks. Elegance meets rebellion.</t>
         </is>
       </c>
     </row>
     <row r="111" ht="25.5" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Indianapolis Colts</t>
+          <t>Golden Goose</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>indianapolis-colts</t>
+          <t>golden-goose</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Indianapolis Colts: 美国国家橄榄球联盟（NFL）AFC南部分区的职业橄榄球队，1953年以“巴尔的摩小马队”身份成立，1984年迁至印第安纳波利斯并更名。主场为卢卡斯石油体育场，以快速进攻体系、传奇四分卫传承（如佩顿·曼宁）及2次超级碗冠军（1971、2007赛季）闻名，是印第安纳波利斯本土体育文化象征，聚焦高水平赛事表现与球迷社区互动，深受全美橄榄球爱好者关注。</t>
+          <t>Golden Goose: 源自意大利的高端潮流品牌，以标志性做旧工艺休闲鞋（sneakers）为核心，主打复古街头风格，采用小牛皮、麂皮等优质材质手工打造，经典元素包含星星补丁、自然做旧划痕与仿脏设计，凭借“破坏美学”成为明星与潮流人士青睐的爆款单品，是追求独特质感与复古腔调的鞋履首选品牌。</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Indianapolis Colts: NFL AFC South team since 1953. Known for fast offense, legendary QB Peyton Manning, and 2 Super Bowl wins (1971, 2007).</t>
+          <t>Golden Goose: Italian luxury brand crafting handcrafted distressed sneakers from premium leathers, featuring star patches &amp; vintage styling for distinctive aesthetic.</t>
         </is>
       </c>
     </row>
     <row r="112" ht="25.5" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Gran Sasso</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>inter-miami</t>
+          <t>gran-sasso</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Inter Miami: 2020年加入美国职业足球大联盟（MLS）的佛罗里达足球俱乐部，由大卫·贝克汉姆等联合创立，主场位于劳德代尔堡，以标志性粉黑配色队服著称，融合国际化足球风格与社区互动属性，是MLS中极具话题度的新兴球队。</t>
+          <t>Gran Sasso: 源自意大利Abruzzo地区Gran Sasso d'Italia山脉的经典天然矿泉水品牌，依托阿尔卑斯山系深层地下水源，经千年岩层自然过滤，水质纯净且富含钙、镁等天然矿物质，口感清冽甘醇。品牌主打“自然本源的健康饮水”理念，是意大利家庭日常、餐饮场景及全球高端水市场的热门选择，以“源自山脉的纯粹滋味”传递原生品质。</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Inter Miami: Florida-based MLS expansion club (joined 2020), co-founded by David Beckham, based in Fort Lauderdale, known for iconic pink-black kits, blending international soccer style with community engagement, a high-profile emerging MLS team.</t>
+          <t>Gran Sasso: Classic Italian natural mineral water from Abruzzo’s Gran Sasso d’Italia. Sourced from Alpine deep underground, filtered by thousand-year rocks—pure, rich in calcium/magnesium, crisp &amp; sweet. Core concept: natural healthy drinking. Popular in Italian households, dining, global premium water, delivering pure mountain taste.</t>
         </is>
       </c>
     </row>
     <row r="113" ht="25.5" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t xml:space="preserve">Gore Tex </t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>inter-milan</t>
+          <t xml:space="preserve">gore-tex </t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Inter Milan: 1908年创立于意大利米兰的意甲顶级足球俱乐部，绰号“蓝黑军团”，累计斩获19次意甲联赛冠军、3次欧洲冠军联赛冠军等重磅荣誉，以标志性蓝黑条纹球衣、战术韧性及全球庞大球迷群体闻名，是世界足坛历史最悠久、影响力深远的豪门俱乐部之一。</t>
+          <t>Gore Tex: 美国戈尔公司（W.L. Gore &amp; Associates）旗下全球知名功能性面料技术品牌，核心依托膨体聚四氟乙烯（ePTFE）膜技术，实现“防水、透气、防风”三大核心功能，广泛应用于户外服装、鞋靴、手套及医疗植入物等场景，是Arc'teryx、The North Face等高端户外品牌的核心面料合作伙伴，以性能稳定性与耐用性成为户外爱好者、专业运动员及极限环境从业者信赖的功能面料标杆。</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Inter Milan: Founded 1908 Milan, top Serie A club Nerazzurri with 19 league titles &amp; 3 UCL wins. Iconic blue-black stripes, tactical resilience, global fanbase. Historic football giant.</t>
+          <t>GORE TEX: Leading U.S. functional fabric tech with ePTFE membrane, delivering waterproof, breathable, windproof performance. Trusted by Arc'teryx &amp; The North Face for outdoor gear &amp; medical implants. The performance fabric standard.</t>
         </is>
       </c>
     </row>
     <row r="114" ht="25.5" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Green Bay Packers</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jbl</t>
+          <t>green-bay-packers</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>JBL: 1946年由音频先驱詹姆斯·巴罗·兰辛（James Bullough Lansing）创立，全球专业音频与消费类音频领导品牌，专注于音箱、耳机、专业音响系统等产品研发，经典系列涵盖Charge便携蓝牙音箱、Flip音乐万花筒、Tune降噪耳机及Professional专业演出音响，以JBL Pro Sound专业级音质、IP67级防水耐用性、潮流轻量化设计为核心优势，覆盖家庭娱乐、户外出行、专业舞台等多元场景，是全球音乐爱好者与音频从业者的首选品牌。</t>
+          <t>Green Bay Packers: 1919年成立于美国威斯康星州绿湾，是NFL（国家橄榄球联盟）历史最悠久的球队之一，隶属于NFC北区，绰号“包装工队”。以标志性绿色与金色队服为视觉标识，主场是传奇的Lambeau Field（兰博球场）。作为NFL夺冠次数最多的球队（13次联盟冠军，含4次超级碗），拥有深厚橄榄球传统，全球忠诚球迷群体中“奶酪头”文化更是NFL独特符号。</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>JBL: Founded in 1946 by audio pioneer James Bullough Lansing, a global leader in professional &amp; consumer audio. Specializes in speakers, headphones, pro sound systems. Flagship series: Charge portable Bluetooth, Flip, Tune noise-canceling headphones, Professional performance audio. Core strengths: JBL Pro Sound, IP67 waterproofing, trendy lightweight design. Covers home entertainment, outdoor travel, pro stages—preferred by global music lovers &amp; audio pros.</t>
+          <t>Green Bay Packers: Founded 1919 in Green Bay, Wisconsin, USA—one of NFL’s oldest teams (NFC North), nicknamed "Packers". Iconic green/gold uniforms, home at legendary Lambeau Field. NFL’s most successful with 13 league titles (4 Super Bowls), rich tradition. "Cheesehead" culture, a unique NFL symbol for global loyal fans.</t>
         </is>
       </c>
     </row>
     <row r="115" ht="25.5" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Josh Allen Buffalo Bills</t>
+          <t>Griezmann</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>josh-allen-buffalo-bills</t>
+          <t>griezmann</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Josh Allen Buffalo Bills 是 NFL 布法罗比尔队 17 四分卫周边系列，由 Josh Allen 与 Nike、New Era 等品牌合作推出，2018 年其加盟后正式成型。主营官方球衣、T 恤、棒球帽等，Josh Allen 参与设计 Billustration 系列，主打美式运动风格，采用 100% 聚酯纤维球衣面料与纯棉服饰材质，风靡北美，深受 Bills Mafia 粉丝青睐，是 NFL 官方授权的明星球员周边品牌。</t>
+          <t>Griezmann 2015 年创立于法国，主营简约休闲服饰，采用纯棉、针织等舒适面料，融合法式简约与街头潮流，设计感与性价比兼具，深受欧洲、北美及亚太年轻群体喜爱。</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Josh Allen Buffalo Bills: Official NFL licensed merchandise for Buffalo Bills QB Josh Allen #17. Launched 2018 with Nike &amp; New Era. Features jerseys, T-shirts, caps in Billustration series. American sports style, 100% polyester/cotton. Popular in North America, loved by Bills Mafia.</t>
+          <t>Griezmann: Founded in France in 2015, specializing in minimalist casual apparel with comfy fabrics like cotton &amp; knit. Blends French minimalism with streetwear, balancing design and value. Popular among young people in Europe, North America &amp; Asia-Pacific.</t>
         </is>
       </c>
     </row>
     <row r="116" ht="25.5" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Juicy Couture</t>
+          <t>Gucci</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>juicy-couture</t>
+          <t>gucci</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Juicy Couture: 1997年创立于美国的轻奢时尚品牌，以标志性天鹅绒运动套装（Velvet Tracksuits）闻名全球，融合加州阳光活力与街头甜酷复古风格，擅长用水晶、亮片及经典字母Logo点缀卫衣、手袋、配饰等单品，是90-00年代“休闲奢华”风的代表，深受追求时尚舒适与个性态度的年轻女性喜爱。</t>
+          <t>Gucci: 1921年由古驰奥·古驰（Guccio Gucci）在意大利佛罗伦萨创立的顶级奢侈品品牌，以标志性双G logo、马衔扣元素及红绿织带为经典标识，涵盖高端时装、经典手袋（如Dionysus、Jackie 1961系列）、鞋履、奢华配饰与香水等核心品类，传承意大利百年精湛手工艺，融合复古美学与现代先锋设计，是全球追求极致品质、经典时尚与奢华格调的高端消费者首选品牌。</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Juicy Couture: US luxury fashion brand since 1997, iconic for Velvet Tracksuits. Merges California sunshine with street cool, features crystals, sequins, logos. Symbol of 90s-00s Casual Luxury, loved by fashion-forward young women.</t>
+          <t>Gucci: Since 1921 Florence, luxury brand with iconic double-G, horsebit, green-red webbing. Offers fashion, handbags (Dionysus, Jackie 1961), shoes, accessories, perfumes. Italian craftsmanship, vintage-modern blend for elite consumers.</t>
         </is>
       </c>
     </row>
     <row r="117" ht="25.5" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Hellstar</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>hellstar</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Juventus: 1897年创立于意大利都灵的世界顶级足球俱乐部，绰号“老妇人”，是意甲联赛夺冠次数最多的豪门球队，曾斩获欧冠冠军、意大利杯冠军等多项顶级荣誉，主场为都灵安联球场。以百年历史底蕴、坚韧战术风格与全球庞大球迷群体闻名，品牌覆盖官方球衣、球迷周边、足球文化衍生产品等，是足球领域极具影响力的经典IP。</t>
+          <t>Hellstar: 专注暗黑街头潮流的时尚品牌，主打卫衣、夹克、配饰等核心单品，以独特设计融合街头文化与暗黑美学，采用优质面料打造舒适穿着体验，风格酷感鲜明，深受Z世代年轻人及潮流爱好者青睐，是展现个性穿搭的热门选择。</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Juventus: Top global football club founded 1897 in Turin, Italy, nicknamed "Old Lady" – most Serie A titles, Champions League/Coppa Italia winner, home at Allianz Stadium. Century-old heritage, tough tactics, large global fanbase; brand covers official jerseys, fan merch, football culture derivatives, influential classic IP.</t>
+          <t>Hellstar: Dark streetwear brand merging street culture with dark aesthetics. Core hoodies, jackets &amp; accessories. Premium fabrics, bold style for Z-gen &amp; trendsetters.</t>
         </is>
       </c>
     </row>
     <row r="118" ht="25.5" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Kanye</t>
+          <t>Hermes</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>kanye</t>
+          <t>hermes</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kanye由美国说唱歌手坎耶・维斯特（Kanye West）于 2013 年创立，2015 年与 Adidas 合作推出首个系列。主营运动鞋、服饰与配饰，Kanye 亲自主导设计，Virgil Abloh 等参与创意。主打极简街头奢华风格，以大地色系、宽松廓形为标志，采用 Primeknit 针织、麂皮、皮革及 Boost 缓震科技，风靡全球潮流圈，在北美、欧洲及亚洲地区极具影响力</t>
+          <t>Hermes: 1837年由Thierry Hermès创立于法国巴黎的全球顶级奢侈品品牌，以马具制作起家，凭借百年精湛手工工艺与永恒经典设计著称，核心产品涵盖高端皮革手袋（如传奇凯莉包Kelly Bag、柏金包Birkin Bag）、奢华丝绸配饰（经典90cm丝围巾）、男士香水（大地Eau Terre d'Hermès）及高级时装，传承法式优雅与极致品质，是全球奢华与品味的标志性品牌。</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Kanye: 2013-founded by Kanye West, 2015 Adidas collab. Sells sneakers, apparel, accessories. Kanye-led design, Virgil Abloh. Minimalist street luxury: earth tones, loose fits. Primeknit, suede, leather &amp; Boost cushioning. Global streetwear N. America, Europe, Asia.</t>
+          <t>Hermes: Founded in Paris, France by Thierry Hermès in 1837, this top global luxury brand started with equestrian gear. Renowned for century-old exquisite craftsmanship &amp; timeless designs, core products include high-end leather bags (Kelly Bag, Birkin Bag), luxury silk accessories (classic 90cm silk scarves), men’s perfume (Eau de Terre d'Hermès), and haute couture. It embodies French elegance, ultimate quality, and is a global symbol of luxury &amp; taste.</t>
         </is>
       </c>
     </row>
     <row r="119" ht="25.5" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kid Cudi</t>
+          <t>Haner</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>kid-cudi</t>
+          <t>haner</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kid Cudi于2022 年 2 月推出个人奢侈街头服饰品牌MOTR（Members of the Rage），2023 年巴黎时装周完整发布。主营宽松 T 恤、美式夹克、牛仔裤及配饰，UFO logo 由其与Nigo联合设计。风格融合90 年代垃圾摇滚、嘻哈灵魂与未来主义，色彩鲜明、版型宽松。采用意大利制造高品质面料，注重舒适与耐用。风靡欧美、日本及全球潮流圈，深受音乐与时尚爱好者追捧。</t>
+          <t>Haner（韩赫）是中国新锐音频品牌，主打高性价比开放式无线耳机，采用亲肤材质，设计简约轻盈，面向年轻用户，适配日常与运动场景。</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>MOTR (Members of the Rage): Kid Cudi’s luxury streetwear brand launched Feb 2022, fully debuted at 2023 Paris Fashion Week. Features oversized tees, American jackets, jeans &amp; accessories. UFO logo co-designed by Kid Cudi &amp; Nigo. Blends 90s grunge, hip-hop soul, futurism—vibrant colors, loose fits. Italian-made high-quality fabrics for comfort/durability. Popular in US/Europe, Japan, global streetwear circles, loved by music &amp; fashion fans.</t>
+          <t>Haner is an emerging Chinese audio brand, offering affordable open-ear wireless earbuds with lightweight design &amp; skin-friendly material, ideal for young users, daily &amp; sports use.</t>
         </is>
       </c>
     </row>
     <row r="120" ht="25.5" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Lacoste</t>
+          <t>Hogan</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>lacoste</t>
+          <t>hogan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Lacoste: 1933年由法国网球运动员René Lacoste创立的轻奢品牌，以标志性鳄鱼LOGO与经典POLO衫著称，产品线覆盖男女装、鞋履、配饰及香水，融合法式优雅与运动休闲基因，主打简约舒适、经典耐穿的设计，是全球法式生活方式的代表性品牌。</t>
+          <t>Hogan: 1986年创立于意大利的奢侈时尚品牌，隶属于Tod's集团，以「奢华休闲」风格为核心，专注鞋履、手袋及成衣设计。选用意大利顶级皮革，融合运动基因与高端工艺，经典产品如Interaction老爹鞋、H383商务运动鞋，打造「可通勤的奢华运动鞋」，深受明星、都市精英与时尚爱好者青睐。</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Lacoste: Affordable luxury brand founded in 1933 by French tennis player René Lacoste, known for iconic crocodile logo &amp; classic polo shirts. Offers apparel, footwear, accessories, fragrances, blending French elegance with sporty casualness, featuring minimalist, comfortable, durable designs—global representative of French lifestyle.</t>
+          <t>Hogan: 1986 Italian luxury fashion brand under Tod’s Group, core “luxury casual” style, focusing on footwear, handbags &amp; ready-to-wear. Made with top Italian leather, blends sporty DNA with high-end craftsmanship. Iconic styles: Interaction Dad Sneakers, H383 business sneakers, creating “commutable luxury sneakers” favored by celebrities, urban elites &amp; fashion lovers.</t>
         </is>
       </c>
     </row>
     <row r="121" ht="25.5" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Lego</t>
+          <t>Hot Wheels</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>lego</t>
+          <t>hot-wheels</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Lego: 1932年由奥勒·基尔克·克里斯蒂安森创立于丹麦，全球知名积木玩具品牌，以安全ABS塑料为核心材质，主打创意拼搭体验，涵盖乐高城市、星球大战、机械组、好朋友等经典系列，融合STEM教育理念，激发全年龄层用户的想象力与动手能力，产品兼容度高，是亲子互动及创意表达的优质选择。</t>
+          <t>风火轮 (Hot Wheels) 1968 年由美泰联合创始人 Elliot Handler 创立，首代设计师 Harry Bentley Bradley。主打压铸金属合金小车与赛道套装，风格加州定制车美学，鲜艳电镀漆 + 红线胎，面向 3-14 岁儿童及全球收藏者，畅销 150 + 国家。</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Lego: Since 1932 Denmark, global building block toys with safe ABS plastic. Creative sets like City, Star Wars, Technic, Friends. STEM-integrated, inspires all ages, compatible, ideal for family interaction.</t>
+          <t>Hot Wheels, founded by Mattel co-founder Elliot Handler in 1968, with first designer Harry Bentley Bradley. Features die-cast metal toy cars &amp; track sets, California custom car style, bright Spectraflame paint &amp; redline tires. Targets kids 3-14 &amp; collectors, sold in 150+ countries worldwide.</t>
         </is>
       </c>
     </row>
     <row r="122" ht="25.5" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Lancme</t>
+          <t>Harman Kardon</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>lancme</t>
+          <t>harman kardon</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Lancôme: 1935年由Armand Petitjean创立于法国的高端美妆护肤品牌，以法式优雅与科技护肤融合的理念著称，核心产品线涵盖「小黑瓶」肌底液（含活性酵母精粹）、菁纯系列（玻色因抗老面霜/眼霜）、兰蔻口红（如196朱砂橘经典色）等明星单品，专注奢宠护肤与精致彩妆，传承奢华优雅的法式美容美学，是全球高端美妆领域的标杆品牌。</t>
+          <t>Harman Kardon: 创立于1953年的高端音频品牌，隶属于哈曼国际集团，以专业声学工程技术与时尚精致设计著称。核心产品涵盖家用音响、无线耳机、车载音响系统等，经典系列包括琉璃（Aura）系列、Onyx系列等，凭借卓越音质表现与标志性外观设计，深受音频爱好者与高端消费群体青睐，广泛应用于家庭娱乐、专业音频场景及豪华汽车配套领域。</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Lancôme: French luxury beauty brand since 1935, merging elegance with science. Features Advanced Génifique Serum, Absolue anti-aging creams, and L'Absolu Rouge lipstick.</t>
+          <t>Harman Kardon: Premium audio brand since 1953. Features acoustic engineering &amp; sleek design in Aura/Onyx series speakers, headphones &amp; car systems for exceptional sound.</t>
         </is>
       </c>
     </row>
     <row r="123" ht="25.5" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>House Of Errors</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>liverpool</t>
+          <t>house-of-errors</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Liverpool: 1892年成立于英国的英超传奇足球俱乐部，绰号“红军”，主场为全球知名的安菲尔德球场。作为英格兰顶级联赛夺冠次数最多的球队之一，曾6次捧起欧冠冠军奖杯，以“永不独行（You'll Never Walk Alone）”的精神内核与热血攻势足球闻名，标志性红色战袍、队徽上的利物鸟元素深入人心，是全球亿万球迷追捧的足球文化符号。</t>
+          <t>House Of Errors 由设计师 Fully（Matthew Foulerton）于 2019 年创立于英国伦敦，主营服装、外套与配饰，标志性产品为全视之眼连帽衫与雕塑感羽绒服。设计师出身建筑专业，主打先锋超现实风格，融合建筑感廓形与解构主义，以重工刺绣、优质面料及皮革为核心材质，风靡全球潮流圈，在欧洲、北美及亚太地区深受时尚达人与明星青睐。</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Liverpool: Founded 1892, legendary Premier League club 'The Reds' at Anfield. 6-time Champions League winner, anthem 'You'll Never Walk Alone', attacking football, iconic red kits with Liverbird emblem.</t>
+          <t>House Of Errors: Founded 2019 London by Fully. Apparel, outerwear &amp; accessories. Iconic: All-Seeing Eye hoodies, sculptural down jackets. Architect-inspired avant-surrealism, architectural silhouettes &amp; deconstruction. Heavy embroidery, premium materials. Loved by fashion icons in EU, NA, APAC.</t>
         </is>
       </c>
     </row>
     <row r="124" ht="25.5" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Loewe</t>
+          <t>Indianapolis Colts</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>loewe</t>
+          <t>indianapolis-colts</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Loewe: 1846年由Enrique Loewe Roessberg创立于西班牙马德里的百年奢侈品牌，以精湛皮革工艺为根基，产品线覆盖高端皮具、高级时装、配饰、香水及家居系列，坚持传统手工艺与现代极简设计的融合，标志性Anagram字母交织logo辨识度极高，Puzzle几何包、Hammock吊床包等经典款成为全球奢华单品代表，诠释“实用美学”的品牌理念，是西班牙工艺与先锋设计结合的标杆品牌。</t>
+          <t>Indianapolis Colts: 美国国家橄榄球联盟（NFL）AFC南部分区的职业橄榄球队，1953年以“巴尔的摩小马队”身份成立，1984年迁至印第安纳波利斯并更名。主场为卢卡斯石油体育场，以快速进攻体系、传奇四分卫传承（如佩顿·曼宁）及2次超级碗冠军（1971、2007赛季）闻名，是印第安纳波利斯本土体育文化象征，聚焦高水平赛事表现与球迷社区互动，深受全美橄榄球爱好者关注。</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Loewe: Founded 1846 Madrid, luxury Spanish leather house fusing craftsmanship with minimalist design. Iconic Anagram logo, signature Puzzle &amp; Hammock bags embody practical elegance.</t>
+          <t>Indianapolis Colts: NFL AFC South team since 1953. Known for fast offense, legendary QB Peyton Manning, and 2 Super Bowl wins (1971, 2007).</t>
         </is>
       </c>
     </row>
     <row r="125" ht="25.5" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Louis Vuitton</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>louis-vuitton</t>
+          <t>inter-miami</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Louis Vuitton: 1854年由路易·威登（Louis Vuitton）在法国巴黎创立的全球顶级奢华品牌，以精湛手工工艺、标志性Monogram帆布与Damier棋盘格图案为核心识别，产品线覆盖高端皮具、时装、配饰、旅行硬箱、腕表及香水等领域，经典单品如Speedy手袋、Neverfull托特包、Alma包与百年历史的旅行箱系列，传承“旅行的艺术”品牌精神，融合传统匠艺与现代设计，是奢华品质、时尚品味与文化传承的象征，长期占据全球奢侈品市场领导地位，深受高端消费者与时尚爱好者追捧。</t>
+          <t>Inter Miami: 2020年加入美国职业足球大联盟（MLS）的佛罗里达足球俱乐部，由大卫·贝克汉姆等联合创立，主场位于劳德代尔堡，以标志性粉黑配色队服著称，融合国际化足球风格与社区互动属性，是MLS中极具话题度的新兴球队。</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Louis Vuitton: Founded in Paris, France in 1854 by Louis Vuitton, a top global luxury brand with exquisite craftsmanship, iconic Monogram canvas &amp; Damier check. Product lines cover high-end leather goods, fashion, accessories, travel trunks, watches &amp; perfumes. Classic items: Speedy handbag, Neverfull tote, Alma bag &amp; century-old trunks. Inherits "art of travel" spirit, blends traditional craft &amp; modern design. Symbol of luxury, style &amp; heritage, leading global luxury market, favored by high-end consumers &amp; fashion lovers.</t>
+          <t>Inter Miami: Florida-based MLS expansion club (joined 2020), co-founded by David Beckham, based in Fort Lauderdale, known for iconic pink-black kits, blending international soccer style with community engagement, a high-profile emerging MLS team.</t>
         </is>
       </c>
     </row>
     <row r="126" ht="25.5" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Lululemon</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>inter-milan</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Lululemon: 1998年创立于加拿大的高端运动服饰品牌，专注瑜伽、健身及日常运动场景，以Luon、Nulu等创新功能性面料、人体工学剪裁及舒适与时尚兼具的设计为核心优势，核心产品涵盖瑜伽裤、运动BRA、训练上衣等，致力于为注重运动体验与生活方式的人群提供高品质装备，传递“热汗联结生活”的品牌理念，是全球运动服饰领域兼具功能性与潮流感的代表品牌。</t>
+          <t>Inter Milan: 1908年创立于意大利米兰的意甲顶级足球俱乐部，绰号“蓝黑军团”，累计斩获19次意甲联赛冠军、3次欧洲冠军联赛冠军等重磅荣誉，以标志性蓝黑条纹球衣、战术韧性及全球庞大球迷群体闻名，是世界足坛历史最悠久、影响力深远的豪门俱乐部之一。</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Lululemon: Premium Canadian athletic apparel since 1998, specializing in yoga, fitness, and daily wear with innovative Luon, Nulu fabrics, ergonomic designs for comfort, style, and sweat life philosophy.</t>
+          <t>Inter Milan: Founded 1908 Milan, top Serie A club Nerazzurri with 19 league titles &amp; 3 UCL wins. Iconic blue-black stripes, tactical resilience, global fanbase. Historic football giant.</t>
         </is>
       </c>
     </row>
     <row r="127" ht="25.5" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Maison Francis Kurkdjian</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>maison-francis-kurkdjian</t>
+          <t>jbl</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Maison Francis Kurkdjian: 2009年由弗朗西斯·库尔吉安创立，法国奢侈香水品牌，产品系列包括香水、香氛蜡烛、身体护理等，经典产品有Baccarat Rouge 540和Aqua Universalis，采用天然香精和珍贵原料，工艺精湛，风格现代优雅。</t>
+          <t>JBL: 1946年由音频先驱詹姆斯·巴罗·兰辛（James Bullough Lansing）创立，全球专业音频与消费类音频领导品牌，专注于音箱、耳机、专业音响系统等产品研发，经典系列涵盖Charge便携蓝牙音箱、Flip音乐万花筒、Tune降噪耳机及Professional专业演出音响，以JBL Pro Sound专业级音质、IP67级防水耐用性、潮流轻量化设计为核心优势，覆盖家庭娱乐、户外出行、专业舞台等多元场景，是全球音乐爱好者与音频从业者的首选品牌。</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Maison Francis Kurkdjian: French luxury perfume brand founded by Francis Kurkdjian in 2009, offering fragrances, scented candles, body care, etc. Classic products: Baccarat Rouge 540 &amp; Aqua Universalis. Uses natural essences, precious ingredients, exquisite craftsmanship, modern elegant style.</t>
+          <t>JBL: Founded in 1946 by audio pioneer James Bullough Lansing, a global leader in professional &amp; consumer audio. Specializes in speakers, headphones, pro sound systems. Flagship series: Charge portable Bluetooth, Flip, Tune noise-canceling headphones, Professional performance audio. Core strengths: JBL Pro Sound, IP67 waterproofing, trendy lightweight design. Covers home entertainment, outdoor travel, pro stages—preferred by global music lovers &amp; audio pros.</t>
         </is>
       </c>
     </row>
     <row r="128" ht="25.5" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Maison Margiela</t>
+          <t>Jellycat</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>maison-margiela</t>
+          <t>jellycat</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Maison Margiela: 1988年由比利时设计师Martin Margiela创立的法国小众奢侈品牌，以解构主义、无性别主义设计为核心风格，标志性元素包括Tabi分趾鞋、白色标签、回收材料重构设计，产品涵盖高级成衣、鞋履、配饰及美妆，凭借打破传统时尚边界的先锋美学，成为全球时尚爱好者关注的实验性时尚代表品牌。</t>
+          <t>Jellycat 1999 年诞生于英国伦敦，由 William Gatacre 与 Thomas Gatacre 兄弟创立。主营毛绒玩具、婴儿用品及配饰，设计团队打造治愈软萌风格，采用高品质柔软面料，适配全年龄段，畅销全球 77 国。</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Maison Margiela: French avant-garde luxury brand founded 1988 by Martin Margiela. Deconstruction, gender-neutral designs with iconic Tabi shoes, white labels, upcycled materials. Haute couture, footwear, accessories, beauty. Experimental fashion pioneer.</t>
+          <t>Jellycat, founded in London, UK (1999) by brothers William &amp; Thomas Gatacre, offers luxury soft toys, nursery items &amp; accessories. Its creative design team crafts whimsical, cuddly styles with premium soft fabrics, loved by all ages across 77 countries globally。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="25.5" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Jack Jones</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>manchester-city</t>
+          <t>jack-jones</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Manchester City: 英格兰职业足球俱乐部（全称曼彻斯特城足球俱乐部），1880年创立于曼彻斯特，1894年正式定名，主场为伊蒂哈德球场，现征战英超联赛。以攻势足球与高压控球战术著称，近年在瓜迪奥拉执教下斩获英超冠军、足总杯、联赛杯及2022-23赛季欧冠冠军等多项荣誉，昵称“蓝月亮”，是全球最具影响力的足球俱乐部之一，拥有亿万热情球迷与高辨识度的蓝色品牌文化。</t>
+          <t>Jack Jones: 1989年创立于丹麦，隶属Bestseller集团的全球知名男装品牌，以牛仔时尚为核心定位，主打休闲、街头与潮流风格，产品覆盖牛仔夹克、牛仔裤、T恤、外套及配饰等全品类男装，聚焦年轻男性的日常穿搭需求，融合优质面料、舒适剪裁与前沿设计，是全球街头时尚爱好者的经典选择。</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Manchester City: Professional English football club (full name Manchester City Football Club), founded in Manchester 1880, officially named 1894. Home to Etihad Stadium, now competing in the Premier League. Known for attacking football &amp; high-press possession tactics. Under Guardiola, won Premier League, FA Cup, League Cup &amp; 2022-23 Champions League. Nicknamed "Blue Moon", one of the world’s most influential clubs with millions of fans &amp; recognizable blue brand culture.</t>
+          <t>Jack Jones: Founded 1989, Denmark. Bestseller's global men's brand. Core denim fashion, casual streetwear &amp; trendy styles. Focus: young men's daily wear. Quality fabrics, comfortable fits, modern designs.</t>
         </is>
       </c>
     </row>
     <row r="130" ht="25.5" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Josh Allen Buffalo Bills</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>manchester-united</t>
+          <t>josh-allen-buffalo-bills</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Manchester United: 英格兰传奇足球俱乐部，1878年创立于曼彻斯特，累计斩获20次英格兰顶级联赛冠军、3次欧洲冠军联赛冠军等重磅荣誉，以“红魔”绰号享誉全球，主场为标志性的老特拉福德球场，拥有超5亿全球球迷，是英超及世界足坛最具影响力的俱乐部之一。</t>
+          <t>Josh Allen Buffalo Bills 是 NFL 布法罗比尔队 17 四分卫周边系列，由 Josh Allen 与 Nike、New Era 等品牌合作推出，2018 年其加盟后正式成型。主营官方球衣、T 恤、棒球帽等，Josh Allen 参与设计 Billustration 系列，主打美式运动风格，采用 100% 聚酯纤维球衣面料与纯棉服饰材质，风靡北美，深受 Bills Mafia 粉丝青睐，是 NFL 官方授权的明星球员周边品牌。</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Manchester United: Legendary English football club founded 1878, 20 league titles, 3 Champions League wins, known as Red Devils, home at Old Trafford, over 500M fans, top influencer in Premier League and world football.</t>
+          <t>Josh Allen Buffalo Bills: Official NFL licensed merchandise for Buffalo Bills QB Josh Allen #17. Launched 2018 with Nike &amp; New Era. Features jerseys, T-shirts, caps in Billustration series. American sports style, 100% polyester/cotton. Popular in North America, loved by Bills Mafia.</t>
         </is>
       </c>
     </row>
     <row r="131" ht="25.5" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Marshall</t>
+          <t>Juicy Couture</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>marshall</t>
+          <t>juicy-couture</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Marshall 由Jim Marshall于1962 年在英国伦敦创立，总部位于米尔顿凯恩斯。主营专业吉他音箱、耳机与蓝牙音箱，标志性产品为 JTM45、Plexi 系列。风格是摇滚标志性音效与复古工业设计，材质以实木箱体、金属格栅、优质发声单元为核心，风靡全球音乐圈，是摇滚与流行音乐领域的传奇音频品牌。</t>
+          <t>Juicy Couture: 1997年创立于美国的轻奢时尚品牌，以标志性天鹅绒运动套装（Velvet Tracksuits）闻名全球，融合加州阳光活力与街头甜酷复古风格，擅长用水晶、亮片及经典字母Logo点缀卫衣、手袋、配饰等单品，是90-00年代“休闲奢华”风的代表，深受追求时尚舒适与个性态度的年轻女性喜爱。</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Marshall: Founded 1962 London by Jim Marshall, legendary audio brand for rock and pop music. Specializes in guitar amps, headphones, Bluetooth speakers with iconic rock sound and vintage industrial design. Iconic products: JTM45, Plexi series.</t>
+          <t>Juicy Couture: US luxury fashion brand since 1997, iconic for Velvet Tracksuits. Merges California sunshine with street cool, features crystals, sequins, logos. Symbol of 90s-00s Casual Luxury, loved by fashion-forward young women.</t>
         </is>
       </c>
     </row>
     <row r="132" ht="25.5" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Margiela</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>margiela</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Margiela: 1988年由Martin Margiela创立的比利时先锋时尚品牌，以解构主义设计与反传统美学为核心，标志性数字编号系列（如10号线成衣、6号线配件）、做旧工艺及“匿名性”理念贯穿品牌，常用再生面料、做旧皮革等材质，风格极简先锋且富有实验性，为追求独特设计感的时尚爱好者打造兼具艺术性与实用性的服饰、配饰，是全球先锋时尚领域的代表性品牌。</t>
+          <t>Juventus: 1897年创立于意大利都灵的世界顶级足球俱乐部，绰号“老妇人”，是意甲联赛夺冠次数最多的豪门球队，曾斩获欧冠冠军、意大利杯冠军等多项顶级荣誉，主场为都灵安联球场。以百年历史底蕴、坚韧战术风格与全球庞大球迷群体闻名，品牌覆盖官方球衣、球迷周边、足球文化衍生产品等，是足球领域极具影响力的经典IP。</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Margiela: Belgian avant-garde fashion brand since 1988, known for deconstruction, numbered collections, vintage crafts, anonymity, sustainable materials, and minimalist experimental designs.</t>
+          <t>Juventus: Top global football club founded 1897 in Turin, Italy, nicknamed "Old Lady" – most Serie A titles, Champions League/Coppa Italia winner, home at Allianz Stadium. Century-old heritage, tough tactics, large global fanbase; brand covers official jerseys, fan merch, football culture derivatives, influential classic IP.</t>
         </is>
       </c>
     </row>
     <row r="133" ht="25.5" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MCM</t>
+          <t>Kanye</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>mcm</t>
+          <t>kanye</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MCM（Modern Creation München）由Michael Cromer于1976 年在德国慕尼黑创立，主营皮具、背包、手袋、鞋履与配饰，标志性产品为 Visetos 老花系列背包。设计师 Michael Michalsky 主导复兴，风格融合德式精工与街头潮流，以干邑色皮革、月桂叶标志及钻石纹为特色，采用优质皮革、帆布与五金配件，风靡全球，尤其在亚洲、欧美地区深受时尚爱好者与明星青睐。</t>
+          <t>Kanye由美国说唱歌手坎耶・维斯特（Kanye West）于 2013 年创立，2015 年与 Adidas 合作推出首个系列。主营运动鞋、服饰与配饰，Kanye 亲自主导设计，Virgil Abloh 等参与创意。主打极简街头奢华风格，以大地色系、宽松廓形为标志，采用 Primeknit 针织、麂皮、皮革及 Boost 缓震科技，风靡全球潮流圈，在北美、欧洲及亚洲地区极具影响力</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>MCM (Modern Creation München): Founded by Michael Cromer in Munich, Germany (1976), specializing in leather goods, backpacks, handbags, footwear &amp; accessories. Signature Visetos monogram backpack. Revived by Michael Michalsky, blending German craftsmanship with streetwear, featuring cognac leather, laurel leaf logo, diamond pattern, premium materials. Popular globally, loved by fashion lovers &amp; celebrities in Asia, Europe, America.</t>
+          <t>Kanye: 2013-founded by Kanye West, 2015 Adidas collab. Sells sneakers, apparel, accessories. Kanye-led design, Virgil Abloh. Minimalist street luxury: earth tones, loose fits. Primeknit, suede, leather &amp; Boost cushioning. Global streetwear N. America, Europe, Asia.</t>
         </is>
       </c>
     </row>
     <row r="134" ht="25.5" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Melissabow</t>
+          <t>Kinetics</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>melissabow</t>
+          <t>kinetics</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Melissa（常称 Melissabow 蝴蝶结系列）由 Alexandre 与 Pedro Grendene 于 1979 年在巴西创立，隶属 Grendene 集团。主营女士及童鞋，标志性为蝴蝶结果冻鞋与 Aranha 系列，创意总监 Edson Matsuo 主导设计，与 Vivienne Westwood、Jason Wu 等跨界合作。风格缤纷俏皮、时尚环保，采用专利 MELFLEX™可回收 PVC 材质，自带泡泡糖香气，风靡全球 80 余国，尤其受亚洲与欧美时尚女性及儿童喜爱。</t>
+          <t>日本街头潮牌 ，主打 Clean Fit 简约风格，以标语印花、宽松廓形 T 恤与高质感面料著称，受滑板爱好者青睐。</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Melissabow: Brazilian brand since 1979, Grendene Group. Women's &amp; kids' shoes: iconic butterfly bow jelly &amp; Aranha series. Designs by Edson Matsuo, collabs like Vivienne Westwood. Colorful, eco-friendly MELFLEX™ recyclable PVC with bubblegum scent. Popular in 80+ countries.</t>
+          <t>Kinetics: Japanese streetwear brand known for Clean Fit style, slogan print tees, and premium fabrics, loved by skate culture enthusiasts.</t>
         </is>
       </c>
     </row>
     <row r="135" ht="25.5" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Kid Cudi</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>miami</t>
+          <t>kid-cudi</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Miami（迈阿密服饰）由Christian Noa创立，总部位于美国迈阿密。主营奢侈街头服饰，包括 oversized 印花 T 恤、时尚尼龙裤及配饰。Christian Noa 亲自主导设计，融合迈阿密活力街头文化与纽约时尚能量，风格大胆鲜艳、充满热带风情，采用优质纯棉、尼龙及金属配件，风靡北美、欧洲及南美，深受潮流爱好者追捧。</t>
+          <t>Kid Cudi于2022 年 2 月推出个人奢侈街头服饰品牌MOTR（Members of the Rage），2023 年巴黎时装周完整发布。主营宽松 T 恤、美式夹克、牛仔裤及配饰，UFO logo 由其与Nigo联合设计。风格融合90 年代垃圾摇滚、嘻哈灵魂与未来主义，色彩鲜明、版型宽松。采用意大利制造高品质面料，注重舒适与耐用。风靡欧美、日本及全球潮流圈，深受音乐与时尚爱好者追捧。</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Miami: Christian Noa's luxury streetwear from Miami. Oversized graphic tees, nylon pants, accessories. Bold tropical styles blend Miami street culture with NYC fashion. Premium cotton, nylon, metal. Popular in NA, EU, SA for trendsetters.</t>
+          <t>MOTR (Members of the Rage): Kid Cudi’s luxury streetwear brand launched Feb 2022, fully debuted at 2023 Paris Fashion Week. Features oversized tees, American jackets, jeans &amp; accessories. UFO logo co-designed by Kid Cudi &amp; Nigo. Blends 90s grunge, hip-hop soul, futurism—vibrant colors, loose fits. Italian-made high-quality fabrics for comfort/durability. Popular in US/Europe, Japan, global streetwear circles, loved by music &amp; fashion fans.</t>
         </is>
       </c>
     </row>
     <row r="136" ht="25.5" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Mitchell</t>
+          <t>Lacoste</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>mitchell</t>
+          <t>lacoste</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Mitchell（Mitchell &amp; Ness）由Frank P. Mitchell与Charles M. Ness于1904 年在美国费城创立，主营复古球衣、球帽及运动服饰，获 NBA、NFL 等四大联赛官方授权。标志性产品为经典复刻球衣，风格忠于历史细节，主打美式复古运动风，采用优质羊毛、法兰绒与纯棉材质，高度还原原版质感，风靡全球，尤其受北美、欧洲及亚洲体育爱好者与潮流人士追捧。</t>
+          <t>Lacoste: 1933年由法国网球运动员René Lacoste创立的轻奢品牌，以标志性鳄鱼LOGO与经典POLO衫著称，产品线覆盖男女装、鞋履、配饰及香水，融合法式优雅与运动休闲基因，主打简约舒适、经典耐穿的设计，是全球法式生活方式的代表性品牌。</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Mitchell &amp; Ness: Official NBA NFL licensed vintage sportswear since 1904, classic reprint jerseys with authentic details, American retro style, high-quality materials, popular worldwide.</t>
+          <t>Lacoste: Affordable luxury brand founded in 1933 by French tennis player René Lacoste, known for iconic crocodile logo &amp; classic polo shirts. Offers apparel, footwear, accessories, fragrances, blending French elegance with sporty casualness, featuring minimalist, comfortable, durable designs—global representative of French lifestyle.</t>
         </is>
       </c>
     </row>
     <row r="137" ht="25.5" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>KAWS</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>mlb</t>
+          <t>kaws</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MLB 由韩国 F&amp;F 集团于1997 年 6 月创立，获美国职业棒球大联盟官方授权。主营男女服饰、鞋履、棒球帽及配饰，标志性为 NY/LA 队标帽款，韩国潮流设计团队主导，融合美式棒球文化与韩式高街风格，以夸张 Logo、宽松剪裁为特色，采用优质纯棉、聚酯纤维与牛仔布等材质，风靡全球，尤其在亚洲、欧美深受年轻人与明星青睐，被誉为 “亚洲时尚风向标”。</t>
+          <t>“XX” 是艺术家 KAWS 的经典视觉语言，源自他创作的 Companion 玩偶的眼睛设计，代表着街头艺术的反叛与趣味性。</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>MLB: Licensed MLB brand by Korea's F&amp;F since 1997. Apparel, shoes, caps, accessories with NY/LA logos. Korean design fuses baseball and high-street style, bold logos, loose cuts. Premium materials. Global trend, youth &amp; celeb favorite.</t>
+          <t>KAWS "XX": Classic visual language from KAWS's Companion toys, symbolizing street art's rebellion and playful spirit.</t>
         </is>
       </c>
     </row>
     <row r="138" ht="25.5" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Moncler</t>
+          <t>Lego</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>moncler</t>
+          <t>lego</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Moncler: 1952年成立于法国，是世界知名的奢侈时尚品牌，专精于高端羽绒服和冬季服装。产品线涵盖外套、成衣及配饰，选用顶级羽绒和材料，结合卓越工艺与时尚设计，风格奢华、功能性强，深受全球消费者喜爱，是冬季保暖与时尚的象征。</t>
+          <t>Lego: 1932年由奥勒·基尔克·克里斯蒂安森创立于丹麦，全球知名积木玩具品牌，以安全ABS塑料为核心材质，主打创意拼搭体验，涵盖乐高城市、星球大战、机械组、好朋友等经典系列，融合STEM教育理念，激发全年龄层用户的想象力与动手能力，产品兼容度高，是亲子互动及创意表达的优质选择。</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Moncler: Founded in France in 1952, a renowned luxury fashion brand specializing in high-end down jackets &amp; winter apparel. Product lines: outerwear, ready-to-wear, accessories, using premium down &amp; materials, combining exquisite craftsmanship with stylish design. Luxurious, functional, beloved globally, symbolizing winter warmth &amp; fashion.</t>
+          <t>Lego: Since 1932 Denmark, global building block toys with safe ABS plastic. Creative sets like City, Star Wars, Technic, Friends. STEM-integrated, inspires all ages, compatible, ideal for family interaction.</t>
         </is>
       </c>
     </row>
     <row r="139" ht="25.5" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Montblanc</t>
+          <t>Lancme</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>montblanc</t>
+          <t>lancme</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Montblanc: 1906年创立于德国的高端奢华品牌，以经典书写工具为核心，延伸至腕表、皮具、珠宝等领域。标志性Meisterstück（大班系列）书写工具采用天然树脂搭配黄金/铂金配件，六角白星logo象征卓越工艺与永恒设计，致力于为追求品质生活的人士打造兼具实用价值与收藏意义的精品，是全球高端生活方式的经典代表之一。</t>
+          <t>Lancôme: 1935年由Armand Petitjean创立于法国的高端美妆护肤品牌，以法式优雅与科技护肤融合的理念著称，核心产品线涵盖「小黑瓶」肌底液（含活性酵母精粹）、菁纯系列（玻色因抗老面霜/眼霜）、兰蔻口红（如196朱砂橘经典色）等明星单品，专注奢宠护肤与精致彩妆，传承奢华优雅的法式美容美学，是全球高端美妆领域的标杆品牌。</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Montblanc: Established 1906 in Germany. Luxury brand renowned for premium writing instruments, watches, leather, &amp; jewelry. Iconic Meisterstück series &amp; white six-pointed star symbolize exceptional craftsmanship, timeless design, &amp; a global luxury lifestyle.</t>
+          <t>Lancôme: French luxury beauty brand since 1935, merging elegance with science. Features Advanced Génifique Serum, Absolue anti-aging creams, and L'Absolu Rouge lipstick.</t>
         </is>
       </c>
     </row>
     <row r="140" ht="25.5" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Moose Knuckles</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>moose-knuckles</t>
+          <t>liverpool</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Moose Knuckles: 源自加拿大的高端户外服饰品牌，以专业保暖派克大衣（Parka）为核心招牌，将时尚设计与强功能性深度融合，采用防水防风科技面料、奢华狐狸毛领及高保暖填充材质，为户外爱好者与城市通勤人群打造兼具抗寒性能与造型质感的冬季服饰，产品线覆盖派克大衣、羽绒服等核心品类，凭借精湛工艺与标志性风格成为全球冬季高端户外服饰的代表性品牌之一。</t>
+          <t>Liverpool: 1892年成立于英国的英超传奇足球俱乐部，绰号“红军”，主场为全球知名的安菲尔德球场。作为英格兰顶级联赛夺冠次数最多的球队之一，曾6次捧起欧冠冠军奖杯，以“永不独行（You'll Never Walk Alone）”的精神内核与热血攻势足球闻名，标志性红色战袍、队徽上的利物鸟元素深入人心，是全球亿万球迷追捧的足球文化符号。</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Moose Knuckles: Canadian high-end outdoor apparel brand specializing in premium insulated parkas. Blends stylish design with robust functionality—waterproof/windproof tech fabrics, luxury fox fur trims, high-insulation fills. For outdoor enthusiasts &amp; urban commuters, delivering cold-resistant performance. Product line: parkas, down jackets. Renowned for exquisite craftsmanship, iconic style—leading global premium winter outdoor brand.</t>
+          <t>Liverpool: Founded 1892, legendary Premier League club 'The Reds' at Anfield. 6-time Champions League winner, anthem 'You'll Never Walk Alone', attacking football, iconic red kits with Liverbird emblem.</t>
         </is>
       </c>
     </row>
     <row r="141" ht="25.5" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Miu Miu</t>
+          <t>Loewe</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>miu miu</t>
+          <t>loewe</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Miu Miu: 1993年由Prada推出的年轻副线品牌，聚焦“少女感与高级感平衡”的设计风格，以Matelassé绗缝皮革、褶皱元素、水晶装饰及糖果色为主打标识，产品覆盖成衣、手袋、鞋履、配饰与香水，经典款如Miu Belle绗缝手袋、复古玛丽珍鞋，精准契合年轻群体对“甜酷摩登”的时尚需求，是全球潮流圈兼具个性与质感的代表性轻奢品牌。</t>
+          <t>Loewe: 1846年由Enrique Loewe Roessberg创立于西班牙马德里的百年奢侈品牌，以精湛皮革工艺为根基，产品线覆盖高端皮具、高级时装、配饰、香水及家居系列，坚持传统手工艺与现代极简设计的融合，标志性Anagram字母交织logo辨识度极高，Puzzle几何包、Hammock吊床包等经典款成为全球奢华单品代表，诠释“实用美学”的品牌理念，是西班牙工艺与先锋设计结合的标杆品牌。</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Miu Miu: Prada’s youthful line launched in 1993, balancing girlish charm &amp; sophistication. Signature Matelassé quilted leather, ruching, crystal accents &amp; candy hues. Offers ready-to-wear, handbags, footwear, accessories, fragrances. Iconic Miu Belle bag &amp; vintage Mary Janes, catering to Gen Z’s sweet-cool modernity, a global accessible luxury standout.</t>
+          <t>Loewe: Founded 1846 Madrid, luxury Spanish leather house fusing craftsmanship with minimalist design. Iconic Anagram logo, signature Puzzle &amp; Hammock bags embody practical elegance.</t>
         </is>
       </c>
     </row>
     <row r="142" ht="25.5" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Moschino</t>
+          <t>Louis Vuitton</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>moschino</t>
+          <t>louis-vuitton</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Moschino: 1983年由Franco Moschino创立于意大利的奢侈品牌，以幽默玩趣、反时尚的先锋风格著称，标志性元素含小熊图案、卡通印花与醒目Logo，产品覆盖成衣、手袋、鞋履、香水及童装等，融合奢华质感与潮流创意，是追求个性表达的年轻时尚群体钟爱的品牌。</t>
+          <t>Louis Vuitton: 1854年由路易·威登（Louis Vuitton）在法国巴黎创立的全球顶级奢华品牌，以精湛手工工艺、标志性Monogram帆布与Damier棋盘格图案为核心识别，产品线覆盖高端皮具、时装、配饰、旅行硬箱、腕表及香水等领域，经典单品如Speedy手袋、Neverfull托特包、Alma包与百年历史的旅行箱系列，传承“旅行的艺术”品牌精神，融合传统匠艺与现代设计，是奢华品质、时尚品味与文化传承的象征，长期占据全球奢侈品市场领导地位，深受高端消费者与时尚爱好者追捧。</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Moschino: Italian luxury brand founded in 1983 by Franco Moschino, featuring humorous, playful anti-fashion avant-garde style. Iconic elements: teddy bear, cartoon prints, bold logo. Products include ready-to-wear, handbags, footwear, perfume, kids’ wear, blending luxury texture with trendy creativity, favored by individuality-pursuing young fashion lovers.</t>
+          <t>Louis Vuitton: Founded in Paris, France in 1854 by Louis Vuitton, a top global luxury brand with exquisite craftsmanship, iconic Monogram canvas &amp; Damier check. Product lines cover high-end leather goods, fashion, accessories, travel trunks, watches &amp; perfumes. Classic items: Speedy handbag, Neverfull tote, Alma bag &amp; century-old trunks. Inherits "art of travel" spirit, blends traditional craft &amp; modern design. Symbol of luxury, style &amp; heritage, leading global luxury market, favored by high-end consumers &amp; fashion lovers.</t>
         </is>
       </c>
     </row>
     <row r="143" ht="25.5" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Moose Knuckles</t>
+          <t>Los Pollos Hermanos</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>moose knuckles</t>
+          <t>los pollos hermanos</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Moose Knuckles: 加拿大高端户外服饰品牌，以「专业保暖+潮流设计」为核心标签，主打经典派克大衣、高品质羽绒服等冬季单品，采用优质羽绒填充、防水防风科技面料，搭配标志性金属logo与毛领设计，兼顾零下环境的强功能性与都市穿搭的时尚感，是全球消费者冬季追求「暖而不臃肿、潮而实用」的户外服饰首选品牌。</t>
+          <t>Los Pollos Hermanos 是剧中反派 Gus Fring 运营的炸鸡连锁店，表面是合法餐饮品牌，实则为贩毒集团的掩护，其标志性的双鸡 Logo 已成为流行文化符号。属于影视文化周边，主打趣味梗文化与复古印花，多采用纯棉面料、休闲宽松版型，是美剧爱好者的热门穿搭单品。</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Moose Knuckles: Canadian luxury outdoor brand for professional warmth &amp; fashion. Features parkas, down jackets with premium down, waterproof tech, signature logo &amp; fur trim. Combines sub-zero function with urban style. Top choice for warm, slim, practical winter wear.</t>
+          <t>Los Pollos Hermanos: Iconic chicken logo from hit series, retro prints, cotton apparel for TV fans.</t>
         </is>
       </c>
     </row>
     <row r="144" ht="25.5" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Maison Margiela</t>
+          <t>Loro Pian</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Maison Margiela</t>
+          <t xml:space="preserve"> loro-pian</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Maison Margiela: 1988年由比利时设计师马丁·马吉拉创立的解构主义时尚先锋品牌，以匿名设计、白色标签标识、打破常规的解构美学与男女无差别设计为核心特色，产品线覆盖高级成衣、鞋履、配饰及香水等领域，经典产品包括标志性Tabi分趾鞋、Replica系列复刻香水及解构主义成衣，凭借颠覆传统的设计语言在全球时尚界备受瞩目，深受追求独特风格的消费者喜爱。</t>
+          <t>Loro Piana（诺悠翩雅）1924 年由 Pietro Loro Piana 于意大利皮埃蒙特创立，家族 19 世纪初已涉羊毛贸易LVMH。专注顶级羊绒、骆马毛等珍稀面料，主打无 Logo 低调奢华，融合传统工艺与现代科技，提供男女成衣、皮具与配饰，诠释 “老钱风” 永恒优雅。</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Maison Margiela: Founded by Belgian designer Martin Margiela in 1988, an avant-garde deconstructivist fashion brand with anonymous design, white label, unconventional deconstructed aesthetics &amp; gender-neutral styles. Product lines: luxury ready-to-wear, footwear, accessories, fragrances. Classics: iconic Tabi split-toe shoes, Replica series fragrances, deconstructed apparel. Noted globally for subversive design, loved by unique style seekers.</t>
+          <t>Loro Piana, founded by engineer Pietro Loro Piana in Quarona, Piedmont, Italy in 1924, with family wool trading roots since early 1800s. Renowned for "quiet luxury", it specializes in rare fibers like cashmere and vicuña, offering timeless men’s/women’s ready-to-wear, leather goods &amp; accessories with exceptional craftsmanship, minimal branding, and Italian excellence.</t>
         </is>
       </c>
     </row>
     <row r="145" ht="25.5" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Mizuno</t>
+          <t>Lululemon</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>mizuno</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Mizuno: 1906年由水野利八创立于日本的专业运动品牌，专注跑步、高尔夫、棒球、排球等运动领域装备研发，以Wave缓震技术、Dynamotion Fit动态贴合等核心科技为支撑，产品兼顾专业竞技性能与人体工学贴合度，服务全球专业运动员及运动爱好者，是融合运动科技与耐用品质的经典运动品牌代表。</t>
+          <t>Lululemon: 1998年创立于加拿大的高端运动服饰品牌，专注瑜伽、健身及日常运动场景，以Luon、Nulu等创新功能性面料、人体工学剪裁及舒适与时尚兼具的设计为核心优势，核心产品涵盖瑜伽裤、运动BRA、训练上衣等，致力于为注重运动体验与生活方式的人群提供高品质装备，传递“热汗联结生活”的品牌理念，是全球运动服饰领域兼具功能性与潮流感的代表品牌。</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Mizuno: Japanese sports brand since 1906, specializing in running, golf, baseball, volleyball gear with Wave cushioning &amp; Dynamotion Fit tech for professional performance &amp; ergonomic fit, serving athletes worldwide.</t>
+          <t>Lululemon: Premium Canadian athletic apparel since 1998, specializing in yoga, fitness, and daily wear with innovative Luon, Nulu fabrics, ergonomic designs for comfort, style, and sweat life philosophy.</t>
         </is>
       </c>
     </row>
     <row r="146" ht="25.5" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Narciso Rodriguez</t>
+          <t>Maison Francis Kurkdjian</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>narciso-rodriguez</t>
+          <t>maison-francis-kurkdjian</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Narciso Rodriguez: 由同名美国设计师创立的高端时尚品牌，以极简优雅的风格著称，核心覆盖高级成衣、香水及配饰领域。经典产品包括全球畅销的For Her系列香水（温暖木质香调诠释女性柔媚），成衣设计强调流畅线条与优质材质（如丝绸、羊毛）的融合，兼顾红毯气场与日常实穿性，是现代女性追求精致质感的高端之选，深受时尚界与消费者青睐。</t>
+          <t>Maison Francis Kurkdjian: 2009年由弗朗西斯·库尔吉安创立，法国奢侈香水品牌，产品系列包括香水、香氛蜡烛、身体护理等，经典产品有Baccarat Rouge 540和Aqua Universalis，采用天然香精和珍贵原料，工艺精湛，风格现代优雅。</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Narciso Rodriguez: Luxury fashion brand by American designer, famed for minimalist elegance. Core: high-end ready-to-wear, fragrances (bestselling For Her with warm woody notes for feminine charm) &amp; accessories. Ready-to-wear blends fluid lines with premium fabrics (silk, wool), balancing red carpet allure &amp; daily wearability—ideal for modern women seeking refined quality, favored by fashion circles &amp; consumers.</t>
+          <t>Maison Francis Kurkdjian: French luxury perfume brand founded by Francis Kurkdjian in 2009, offering fragrances, scented candles, body care, etc. Classic products: Baccarat Rouge 540 &amp; Aqua Universalis. Uses natural essences, precious ingredients, exquisite craftsmanship, modern elegant style.</t>
         </is>
       </c>
     </row>
     <row r="147" ht="25.5" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Neighborhood</t>
+          <t>Maison Margiela</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>neighborhood</t>
+          <t>maison-margiela</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Neighborhood（NBHD）由日本设计师泷泽伸介 (Shinsuke Takizawa)于1994 年在东京原宿创立，主打街头潮流服饰。标志性产品为冈山赤耳丹宁裤、机车夹克与军事工装，创始人亲任创意总监，以Craft with Pride为理念，风格硬核写实、重质感细节，融合机车、军事与美式工装元素，采用顶级丹宁、优质皮革及纯棉材质，风靡全球，尤其受亚洲、欧美街头文化爱好者与 “养牛” 圈追捧。</t>
+          <t>Maison Margiela: 1988年由比利时设计师Martin Margiela创立的法国小众奢侈品牌，以解构主义、无性别主义设计为核心风格，标志性元素包括Tabi分趾鞋、白色标签、回收材料重构设计，产品涵盖高级成衣、鞋履、配饰及美妆，凭借打破传统时尚边界的先锋美学，成为全球时尚爱好者关注的实验性时尚代表品牌。</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Neighborhood(NBHD): Japanese streetwear brand since 1994 by Shinsuke Takizawa. Craft with Pride philosophy, premium denim, biker jackets, military workwear. Hardcore styles with motorcycle, military, American elements. Top-quality materials, global street culture favorite.</t>
+          <t>Maison Margiela: French avant-garde luxury brand founded 1988 by Martin Margiela. Deconstruction, gender-neutral designs with iconic Tabi shoes, white labels, upcycled materials. Haute couture, footwear, accessories, beauty. Experimental fashion pioneer.</t>
         </is>
       </c>
     </row>
     <row r="148" ht="25.5" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>new-balance</t>
+          <t>manchester-city</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>New Balance: 1906年创立于美国波士顿的专业运动品牌，以“舒适性能与经典设计共生”为理念，专注运动鞋、运动服饰及配件研发。核心产品覆盖跑步鞋、训练鞋、休闲鞋等系列，搭载ABZORB缓震、ENCAP中底、Fresh Foam轻量科技，满足跑步爱好者、健身人群及日常穿搭需求；经典574、990系列更成为“专业与潮流兼顾”的代表，是全球运动者信赖的“慢跑鞋专家”，持续传递“Made for Makers”的品牌精神。</t>
+          <t>Manchester City: 英格兰职业足球俱乐部（全称曼彻斯特城足球俱乐部），1880年创立于曼彻斯特，1894年正式定名，主场为伊蒂哈德球场，现征战英超联赛。以攻势足球与高压控球战术著称，近年在瓜迪奥拉执教下斩获英超冠军、足总杯、联赛杯及2022-23赛季欧冠冠军等多项荣誉，昵称“蓝月亮”，是全球最具影响力的足球俱乐部之一，拥有亿万热情球迷与高辨识度的蓝色品牌文化。</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>New Balance: Founded in Boston, USA in 1906, this pro sports brand focuses on sneakers, apparel &amp; accessories with "comfort + classic design" philosophy. Core products: running/training/casual shoes with ABZORB cushioning, ENCAP midsole, Fresh Foam tech for runners, fitness lovers &amp; daily wear. Classic 574/990 series (pro + fashion) are trusted "jogging shoe experts", embodying "Made for Makers" spirit.</t>
+          <t>Manchester City: Professional English football club (full name Manchester City Football Club), founded in Manchester 1880, officially named 1894. Home to Etihad Stadium, now competing in the Premier League. Known for attacking football &amp; high-press possession tactics. Under Guardiola, won Premier League, FA Cup, League Cup &amp; 2022-23 Champions League. Nicknamed "Blue Moon", one of the world’s most influential clubs with millions of fans &amp; recognizable blue brand culture.</t>
         </is>
       </c>
     </row>
     <row r="149" ht="25.5" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>New England Patriots</t>
+          <t>Maison Mihara Yasuhiro</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>new-england-patriots</t>
+          <t>maison -mihara-yasuhiro</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>New England Patriots: 新英格兰爱国者是NFL职业橄榄球大联盟的传奇球队，成立于1960年，主场位于马萨诸塞州福克斯堡。品牌以红、白、蓝三色和飞翼徽标闻名，拥有六次超级碗冠军辉煌历史。其官方商品涵盖高品质球衣、帽衫、帽子等粉丝装备，采用先进运动面料与印花工艺，风格经典美式，代表坚韧竞技精神与团队荣耀。</t>
+          <t>Maison Mihara Yasuhiro（简称 MMY，中文三原康裕），1997 年由日本设计师三原康裕创立的时尚品牌。以标志性Original Sole 溶解鞋闻名，鞋底如融化般流动扭曲，手工雕刻原模打造。品牌融合解构主义与复古未来主义，用不对称剪裁、拼接手法重塑经典单品，呈现 “不完美艺术感”。从鞋履起家扩展至全系列，兼具实验性与实穿性，是潮流与高端时尚的跨界代表。</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>New England Patriots: NFL legend since 1960. 6x Super Bowl champions. Iconic red, white, blue &amp; flying Elvis logo. Premium jerseys, hoodies, hats embody classic American grit &amp; team glory.</t>
+          <t>Maison Mihara Yasuhiro: Japanese brand famed for Original Sole "melted" sneakers, blending deconstruction, retro-futurism, and artful imperfection in wearable, experimental fashion.</t>
         </is>
       </c>
     </row>
     <row r="150" ht="25.5" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>New York Jets</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>new-york-jets</t>
+          <t>manchester-united</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>New York Jets: 美国国家橄榄球联盟（NFL）的老牌职业橄榄球队，1960年成立，主场为纽约大都会人寿体育场，以经典绿白配色队服、冲击力十足的比赛风格著称，是纽约体育文化的重要符号之一，拥有庞大忠实球迷群体，赛场内外传递着美式橄榄球的热血与团队精神，是NFL东部分区极具竞争力的代表球队。</t>
+          <t>Manchester United: 英格兰传奇足球俱乐部，1878年创立于曼彻斯特，累计斩获20次英格兰顶级联赛冠军、3次欧洲冠军联赛冠军等重磅荣誉，以“红魔”绰号享誉全球，主场为标志性的老特拉福德球场，拥有超5亿全球球迷，是英超及世界足坛最具影响力的俱乐部之一。</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>New York Jets: Historic NFL team since 1960, based at MetLife Stadium. Iconic green-white uniforms, dynamic playstyle. NY sports symbol with loyal fans, embodying football passion and teamwork in AFC East.</t>
+          <t>Manchester United: Legendary English football club founded 1878, 20 league titles, 3 Champions League wins, known as Red Devils, home at Old Trafford, over 500M fans, top influencer in Premier League and world football.</t>
         </is>
       </c>
     </row>
     <row r="151" ht="25.5" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Marshall</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>new-york-yankees</t>
+          <t>marshall</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>New York Yankees: 美国职业棒球大联盟（MLB）标志性传奇球队，1901年创立（前身为巴尔的摩金莺队，1913年迁至纽约并定现名），隶属美国联盟东区，坐拥27次世界大赛冠军（MLB历史最多），经典条纹队服与“NY” logo是其标志性符号，深耕百年体育文化，是全球棒球迷心中的“王者之师”，以卓越战绩、深厚底蕴与广泛影响力成为美国体育的重要象征。</t>
+          <t>Marshall 由Jim Marshall于1962 年在英国伦敦创立，总部位于米尔顿凯恩斯。主营专业吉他音箱、耳机与蓝牙音箱，标志性产品为 JTM45、Plexi 系列。风格是摇滚标志性音效与复古工业设计，材质以实木箱体、金属格栅、优质发声单元为核心，风靡全球音乐圈，是摇滚与流行音乐领域的传奇音频品牌。</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>New York Yankees: Iconic MLB franchise since 1901; 27 World Series titles, legendary pinstripes &amp; NY logo. A century-long sports legacy &amp; global symbol of excellence.</t>
+          <t>Marshall: Founded 1962 London by Jim Marshall, legendary audio brand for rock and pop music. Specializes in guitar amps, headphones, Bluetooth speakers with iconic rock sound and vintage industrial design. Iconic products: JTM45, Plexi series.</t>
         </is>
       </c>
     </row>
     <row r="152" ht="25.5" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Margiela</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>newcastle-united</t>
+          <t>margiela</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Newcastle United: 1892年成立的英格兰老牌职业足球俱乐部，绰号“喜鹊”（因经典黑白队服），主场为可容纳52305人的圣詹姆斯公园球场，历史上曾获4次英格兰顶级联赛冠军、6次足总杯冠军，现征战英超联赛。球队以激情球迷文化与快速反击风格著称，2021年由沙特公共投资基金主导收购后逐步强化阵容，是英超联赛中全球球迷关注的劲旅之一，也是英格兰东北部足球文化的重要代表。</t>
+          <t>Margiela: 1988年由Martin Margiela创立的比利时先锋时尚品牌，以解构主义设计与反传统美学为核心，标志性数字编号系列（如10号线成衣、6号线配件）、做旧工艺及“匿名性”理念贯穿品牌，常用再生面料、做旧皮革等材质，风格极简先锋且富有实验性，为追求独特设计感的时尚爱好者打造兼具艺术性与实用性的服饰、配饰，是全球先锋时尚领域的代表性品牌。</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Newcastle United: Est. 1892, Magpies for black-white kits. Premier League club at St James' Park (52,305 seats). 4 top-flight titles, 6 FA Cups. Passionate fans, fast counter-attacks. Strengthened after 2021 Saudi PIF takeover. Global NE England football icon.</t>
+          <t>Margiela: Belgian avant-garde fashion brand since 1988, known for deconstruction, numbered collections, vintage crafts, anonymity, sustainable materials, and minimalist experimental designs.</t>
         </is>
       </c>
     </row>
     <row r="153" ht="25.5" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>MCM</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>nike</t>
+          <t>mcm</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Nike: 1972年由菲尔·奈特与比尔·鲍尔曼联合创立，美国运动品牌巨头，产品涵盖跑步鞋、篮球鞋、运动服装及装备系列，经典产品包括Air Max气垫鞋、Air Jordan系列，采用Flyknit编织、Dri-FIT科技面料等创新材质，工艺注重轻量缓震，风格融合运动性能与街头时尚。</t>
+          <t>MCM（Modern Creation München）由Michael Cromer于1976 年在德国慕尼黑创立，主营皮具、背包、手袋、鞋履与配饰，标志性产品为 Visetos 老花系列背包。设计师 Michael Michalsky 主导复兴，风格融合德式精工与街头潮流，以干邑色皮革、月桂叶标志及钻石纹为特色，采用优质皮革、帆布与五金配件，风靡全球，尤其在亚洲、欧美地区深受时尚爱好者与明星青睐。</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Nike: American sports brand since 1972, offering running, basketball shoes, sportswear. Features Air Max, Air Jordan, Flyknit, Dri-FIT. Lightweight cushioning blends performance with street fashion.</t>
+          <t>MCM (Modern Creation München): Founded by Michael Cromer in Munich, Germany (1976), specializing in leather goods, backpacks, handbags, footwear &amp; accessories. Signature Visetos monogram backpack. Revived by Michael Michalsky, blending German craftsmanship with streetwear, featuring cognac leather, laurel leaf logo, diamond pattern, premium materials. Popular globally, loved by fashion lovers &amp; celebrities in Asia, Europe, America.</t>
         </is>
       </c>
     </row>
     <row r="154" ht="25.5" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Nobis</t>
+          <t>Melissabow</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>nobis</t>
+          <t>melissabow</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Nobis 由Robin Yates（前加拿大鹅副总裁）与Kevin Au-Yeung于2007 年在加拿大多伦多创立，设计师为Michael Kerr。主营高端户外功能性外套（派克大衣、羽绒服等），以极简奢华融合极致保暖性能著称，剪裁利落修身。采用顶级防水面料、高品质鸭绒填充及羊毛、尼龙等复合材质，风靡全球 35 国，深受北美、欧洲及亚洲精英与时尚人士青睐。</t>
+          <t>Melissa（常称 Melissabow 蝴蝶结系列）由 Alexandre 与 Pedro Grendene 于 1979 年在巴西创立，隶属 Grendene 集团。主营女士及童鞋，标志性为蝴蝶结果冻鞋与 Aranha 系列，创意总监 Edson Matsuo 主导设计，与 Vivienne Westwood、Jason Wu 等跨界合作。风格缤纷俏皮、时尚环保，采用专利 MELFLEX™可回收 PVC 材质，自带泡泡糖香气，风靡全球 80 余国，尤其受亚洲与欧美时尚女性及儿童喜爱。</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Nobis: Founded in 2007 in Toronto, Canada by Robin Yates (ex-Canada Goose VP) &amp; Kevin Au-Yeung, designed by Michael Kerr. Specializes in high-end functional outerwear (parkas, down jackets) blending minimalist luxury with ultimate warmth, tailored slim fits. Uses premium waterproof fabrics, high-quality duck down, wool-nylon blends. Popular in 35 countries, favored by elites &amp; fashionistas in North America, Europe, Asia.</t>
+          <t>Melissabow: Brazilian brand since 1979, Grendene Group. Women's &amp; kids' shoes: iconic butterfly bow jelly &amp; Aranha series. Designs by Edson Matsuo, collabs like Vivienne Westwood. Colorful, eco-friendly MELFLEX™ recyclable PVC with bubblegum scent. Popular in 80+ countries.</t>
         </is>
       </c>
     </row>
     <row r="155" ht="25.5" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>NOFS</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>nofs</t>
+          <t>miami</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>NOFS（Noneofus）由Casey Backhaus与Justin Njinmah于2019 年在德国柏林创立，德国街头潮牌。标志性产品为运动套装、连帽衫及丹宁系列，创始人亲任设计，以极简主义融合大胆字母印花，线条利落、中性配色，注重德国工艺与街头文化。采用优质纯棉、重磅丹宁、聚酯纤维等材质，风靡欧洲、北美及全球 Z 世代，成为德国街头时尚新标杆。</t>
+          <t>Miami（迈阿密服饰）由Christian Noa创立，总部位于美国迈阿密。主营奢侈街头服饰，包括 oversized 印花 T 恤、时尚尼龙裤及配饰。Christian Noa 亲自主导设计，融合迈阿密活力街头文化与纽约时尚能量，风格大胆鲜艳、充满热带风情，采用优质纯棉、尼龙及金属配件，风靡北美、欧洲及南美，深受潮流爱好者追捧。</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NOFS: German streetwear from Berlin, founded 2019. Minimalist design, bold letter prints, neutral colors. Tracksuits, hoodies, denim. Premium materials. Popular in Europe, NA, Gen Z.</t>
+          <t>Miami: Christian Noa's luxury streetwear from Miami. Oversized graphic tees, nylon pants, accessories. Bold tropical styles blend Miami street culture with NYC fashion. Premium cotton, nylon, metal. Popular in NA, EU, SA for trendsetters.</t>
         </is>
       </c>
     </row>
     <row r="156" ht="25.5" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Mitchell</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>mitchell</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Number (N) INE 由日本设计师宫下贵裕于1996/1997 年在东京创立，名称源自 The Beatles《Revolution 9》。主营街头服饰、T 恤、丹宁裤与机车夹克，创始人亲任设计，融合美式复古、摇滚朋克与军事元素，风格暗黑颓废、层次丰富。采用重磅棉、顶级丹宁、优质皮革等材质，风靡全球，是日本地下与前卫时尚标杆，深受欧美潮流人士追捧。</t>
+          <t>Mitchell（Mitchell &amp; Ness）由Frank P. Mitchell与Charles M. Ness于1904 年在美国费城创立，主营复古球衣、球帽及运动服饰，获 NBA、NFL 等四大联赛官方授权。标志性产品为经典复刻球衣，风格忠于历史细节，主打美式复古运动风，采用优质羊毛、法兰绒与纯棉材质，高度还原原版质感，风靡全球，尤其受北美、欧洲及亚洲体育爱好者与潮流人士追捧。</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Number: Founded by Japanese designer Takayuki Miyashita in Tokyo (1996/1997), named after The Beatles’ “Revolution 9”. Specializes in streetwear, tees, denim, biker jackets. Founder-led design blends American retro, rock punk, military elements—dark, decadent, layered styles. Uses heavy cotton, premium denim, quality leather. Global phenomenon, Japanese underground/avant-garde fashion icon, popular with Western fashion lovers.</t>
+          <t>Mitchell &amp; Ness: Official NBA NFL licensed vintage sportswear since 1904, classic reprint jerseys with authentic details, American retro style, high-quality materials, popular worldwide.</t>
         </is>
       </c>
     </row>
     <row r="157" ht="25.5" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Off White</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>off-white</t>
+          <t>mlb</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Off White: 由Virgil Abloh于2012年创立的美国高端街头时尚品牌，以“未完成感”解构主义设计为核心，融合街头文化与高端时尚美学，标志性元素包括引号、斜杠、箭头等工业风视觉符号。产品涵盖服装、鞋履、配饰等，经典如OW x Nike联名 sneakers系列，是连接街头潮流与高奢领域的先锋品牌，深受全球潮人、时尚爱好者及Louis Vuitton等合作方青睐。</t>
+          <t>MLB 由韩国 F&amp;F 集团于1997 年 6 月创立，获美国职业棒球大联盟官方授权。主营男女服饰、鞋履、棒球帽及配饰，标志性为 NY/LA 队标帽款，韩国潮流设计团队主导，融合美式棒球文化与韩式高街风格，以夸张 Logo、宽松剪裁为特色，采用优质纯棉、聚酯纤维与牛仔布等材质，风靡全球，尤其在亚洲、欧美深受年轻人与明星青睐，被誉为 “亚洲时尚风向标”。</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Off White: Virgil Abloh's luxury streetwear label, famed for deconstructed aesthetics, industrial symbols like quotes &amp; arrows, and iconic Nike collabs, bridging high fashion with urban culture.</t>
+          <t>MLB: Licensed MLB brand by Korea's F&amp;F since 1997. Apparel, shoes, caps, accessories with NY/LA logos. Korean design fuses baseball and high-street style, bold logos, loose cuts. Premium materials. Global trend, youth &amp; celeb favorite.</t>
         </is>
       </c>
     </row>
     <row r="158" ht="25.5" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Olympique De Darseille</t>
+          <t>Moncler</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>olympique-de-marseille</t>
+          <t>moncler</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Olympique De Darseille（ODD）由Julien Poublon于2014 年在法国巴黎创立，法国街头潮牌。主营重磅棉 T 恤、顶级丹宁裤、摇滚风格卫衣等，创始人亲任设计师。流行于法、欧及全球街头潮流圈，风格融合美式复古与军事工装元素，采用重磅棉、优质皮革等耐用材质，是法国标志性街头潮牌。</t>
+          <t>Moncler: 1952年成立于法国，是世界知名的奢侈时尚品牌，专精于高端羽绒服和冬季服装。产品线涵盖外套、成衣及配饰，选用顶级羽绒和材料，结合卓越工艺与时尚设计，风格奢华、功能性强，深受全球消费者喜爱，是冬季保暖与时尚的象征。</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Olympique De Darseille (ODD): French streetwear brand founded by Julien Poublon in Paris 2014. Offers heavy cotton tees, premium denim, rock-style hoodies. Blends American retro &amp; military workwear, uses durable heavy cotton, premium leather. Popular in France, Europe &amp; global streetwear circles, iconic French streetwear label.</t>
+          <t>Moncler: Founded in France in 1952, a renowned luxury fashion brand specializing in high-end down jackets &amp; winter apparel. Product lines: outerwear, ready-to-wear, accessories, using premium down &amp; materials, combining exquisite craftsmanship with stylish design. Luxurious, functional, beloved globally, symbolizing winter warmth &amp; fashion.</t>
         </is>
       </c>
     </row>
     <row r="159" ht="25.5" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>One Piece</t>
+          <t>Montblanc</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>one-piece</t>
+          <t>montblanc</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>One Piece: 日本国民级海贼题材IP，由尾田荣一郎创作，1997年起在《周刊少年Jump》连载漫画，衍生动画、电影、游戏及手办、服饰等多元产品。以“草帽一伙寻找传说中大秘宝‘One Piece’的冒险”为核心，传递自由、伙伴与逐梦的精神内核，全球累计粉丝超数亿，是日本动漫文化输出的标杆性IP，覆盖全年龄段受众，衍生商品持续占据二次元周边市场热门。</t>
+          <t>Montblanc: 1906年创立于德国的高端奢华品牌，以经典书写工具为核心，延伸至腕表、皮具、珠宝等领域。标志性Meisterstück（大班系列）书写工具采用天然树脂搭配黄金/铂金配件，六角白星logo象征卓越工艺与永恒设计，致力于为追求品质生活的人士打造兼具实用价值与收藏意义的精品，是全球高端生活方式的经典代表之一。</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>One Piece: Japan's national pirate IP by Eiichiro Oda, serialized in Weekly Shonen Jump since 1997. Derived anime, films, games, figures, apparel. Core: Straw Hats' adventure for "One Piece" treasure, conveying freedom, friendship, dreams. Billions of global fans, benchmark of Japanese anime culture export, all-age audience, top-selling anime merchandise.</t>
+          <t>Montblanc: Established 1906 in Germany. Luxury brand renowned for premium writing instruments, watches, leather, &amp; jewelry. Iconic Meisterstück series &amp; white six-pointed star symbolize exceptional craftsmanship, timeless design, &amp; a global luxury lifestyle.</t>
         </is>
       </c>
     </row>
     <row r="160" ht="25.5" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Moose Knuckles</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>moose-knuckles</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>这个类目下，我们将不归属于任何品牌的商品归类到这里，以便于用户从这个表格里找到品牌不明显的流行或商品，以便于选择或购买。</t>
+          <t>Moose Knuckles: 源自加拿大的高端户外服饰品牌，以专业保暖派克大衣（Parka）为核心招牌，将时尚设计与强功能性深度融合，采用防水防风科技面料、奢华狐狸毛领及高保暖填充材质，为户外爱好者与城市通勤人群打造兼具抗寒性能与造型质感的冬季服饰，产品线覆盖派克大衣、羽绒服等核心品类，凭借精湛工艺与标志性风格成为全球冬季高端户外服饰的代表性品牌之一。</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>In the Other category, we classify unbranded products here to help users find popular items with less obvious brands for selection or purchase.</t>
+          <t>Moose Knuckles: Canadian high-end outdoor apparel brand specializing in premium insulated parkas. Blends stylish design with robust functionality—waterproof/windproof tech fabrics, luxury fox fur trims, high-insulation fills. For outdoor enthusiasts &amp; urban commuters, delivering cold-resistant performance. Product line: parkas, down jackets. Renowned for exquisite craftsmanship, iconic style—leading global premium winter outdoor brand.</t>
         </is>
       </c>
     </row>
     <row r="161" ht="25.5" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>On Running</t>
+          <t>Miu Miu</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>on running</t>
+          <t>miu miu</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>On Running: 2010年由三届铁人三项世界冠军Olivier Bernhard联合创立的瑞士专业运动品牌，以核心CloudTec®云科技中底为技术核心，融合精准缓震与向前推进力，专注跑步等运动场景，为专业跑者及运动爱好者提供兼具舒适脚感、卓越性能与简约设计的运动装备，是全球跑圈备受推崇的“跑者专属品牌”。</t>
+          <t>Miu Miu: 1993年由Prada推出的年轻副线品牌，聚焦“少女感与高级感平衡”的设计风格，以Matelassé绗缝皮革、褶皱元素、水晶装饰及糖果色为主打标识，产品覆盖成衣、手袋、鞋履、配饰与香水，经典款如Miu Belle绗缝手袋、复古玛丽珍鞋，精准契合年轻群体对“甜酷摩登”的时尚需求，是全球潮流圈兼具个性与质感的代表性轻奢品牌。</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>On Running: Swiss performance sportswear founded by 3x Ironman World Champion Olivier Bernhard. Features core CloudTec® cushioning for precision shock absorption and propulsive force, delivering high-performance running gear revered by runners worldwide.</t>
+          <t>Miu Miu: Prada’s youthful line launched in 1993, balancing girlish charm &amp; sophistication. Signature Matelassé quilted leather, ruching, crystal accents &amp; candy hues. Offers ready-to-wear, handbags, footwear, accessories, fragrances. Iconic Miu Belle bag &amp; vintage Mary Janes, catering to Gen Z’s sweet-cool modernity, a global accessible luxury standout.</t>
         </is>
       </c>
     </row>
     <row r="162" ht="25.5" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Onitsuka Tiger</t>
+          <t>Moschino</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>onitsuka tiger</t>
+          <t>moschino</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Onitsuka Tiger: 1949年由鬼冢喜八郎创立于日本，作为ASICS的前身品牌，以“复古运动时尚”为核心定位，融合日本传统工艺与经典设计美学。标志性虎爪纹Logo、Mexico 66等经典系列享誉全球，产品涵盖运动鞋、服饰及配件，采用帆布、皮革等优质材质，风格兼顾复古质感与现代休闲，是潮流爱好者与运动复古风追随者的首选品牌。</t>
+          <t>Moschino: 1983年由Franco Moschino创立于意大利的奢侈品牌，以幽默玩趣、反时尚的先锋风格著称，标志性元素含小熊图案、卡通印花与醒目Logo，产品覆盖成衣、手袋、鞋履、香水及童装等，融合奢华质感与潮流创意，是追求个性表达的年轻时尚群体钟爱的品牌。</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Onitsuka Tiger: Founded in Japan by Kihachiro Onitsuka in 1949, predecessor of ASICS. Core positioning: "retro sporty fashion", blending Japanese traditional craftsmanship &amp; classic design aesthetics. Iconic tiger claw logo, classic Mexico 66 series. Products: sneakers, apparel, accessories (premium canvas/leather). Retro texture + modern casual style, top choice for trendsetters &amp; sporty vintage followers.</t>
+          <t>Moschino: Italian luxury brand founded in 1983 by Franco Moschino, featuring humorous, playful anti-fashion avant-garde style. Iconic elements: teddy bear, cartoon prints, bold logo. Products include ready-to-wear, handbags, footwear, perfume, kids’ wear, blending luxury texture with trendy creativity, favored by individuality-pursuing young fashion lovers.</t>
         </is>
       </c>
     </row>
     <row r="163" ht="25.5" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Paco Rabanne</t>
+          <t>Moose Knuckles</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>paco-rabanne</t>
+          <t>moose knuckles</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Paco Rabanne: 1966年由西班牙裔法国设计师Paco Rabanne（弗朗西斯科·拉巴内达·库尔沃）创立的法国先锋奢侈品牌，以未来主义风格与金属材质创新运用著称，标志性金属链甲连衣裙重塑时尚边界，经典香水如Calandre、One Million系列全球热销，产品线覆盖高级时装、香水、配饰等，始终践行“时尚是科技与艺术的先锋融合”理念，是全球先锋时尚爱好者的标志性选择。</t>
+          <t>Moose Knuckles: 加拿大高端户外服饰品牌，以「专业保暖+潮流设计」为核心标签，主打经典派克大衣、高品质羽绒服等冬季单品，采用优质羽绒填充、防水防风科技面料，搭配标志性金属logo与毛领设计，兼顾零下环境的强功能性与都市穿搭的时尚感，是全球消费者冬季追求「暖而不臃肿、潮而实用」的户外服饰首选品牌。</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Paco Rabanne: Founded by Spanish-French designer Francisco Rabaneda Cuervo in 1966, French avant-garde luxury brand known for futuristic style &amp; innovative metal use. Iconic metal chainmail dresses redefined fashion boundaries. Classic fragrances like Calandre &amp; One Million bestsellers. Lines cover haute couture, fragrances, accessories. Upholds "fashion is tech-art fusion" – global avant-garde fashion lovers’ iconic choice.</t>
+          <t>Moose Knuckles: Canadian luxury outdoor brand for professional warmth &amp; fashion. Features parkas, down jackets with premium down, waterproof tech, signature logo &amp; fur trim. Combines sub-zero function with urban style. Top choice for warm, slim, practical winter wear.</t>
         </is>
       </c>
     </row>
     <row r="164" ht="25.5" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
+          <t>Molly</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>molly</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Molly 是香港设计师 Kenny Wong（王信明）创作的经典潮玩 IP，2010 年被泡泡玛特引入并推广，凭借标志性的嘟嘴表情和百变造型，成为国内顶流潮玩 IP 之一。</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Molly: Iconic Hong Kong designer toy by Kenny Wong, featuring signature pout &amp; endless styles, a top pop culture IP since 2010.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="25.5" customHeight="1">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>MR.NEARLY</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>mr-nearly</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>MR.NEARLY 美式复古潮牌，主打 Cleanfit 高街风服饰，以做旧水洗工艺与 Oversize 版型，打造松弛街头质感，适配多元穿搭场景。</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>MR.NEARLY is an American retro streetwear brand, offering cleanfit-style apparel with vintage wash &amp; oversize fits for casual street looks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="25.5" customHeight="1">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Maison Margiela</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Maison Margiela</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Maison Margiela: 1988年由比利时设计师马丁·马吉拉创立的解构主义时尚先锋品牌，以匿名设计、白色标签标识、打破常规的解构美学与男女无差别设计为核心特色，产品线覆盖高级成衣、鞋履、配饰及香水等领域，经典产品包括标志性Tabi分趾鞋、Replica系列复刻香水及解构主义成衣，凭借颠覆传统的设计语言在全球时尚界备受瞩目，深受追求独特风格的消费者喜爱。</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Maison Margiela: Founded by Belgian designer Martin Margiela in 1988, an avant-garde deconstructivist fashion brand with anonymous design, white label, unconventional deconstructed aesthetics &amp; gender-neutral styles. Product lines: luxury ready-to-wear, footwear, accessories, fragrances. Classics: iconic Tabi split-toe shoes, Replica series fragrances, deconstructed apparel. Noted globally for subversive design, loved by unique style seekers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="25.5" customHeight="1">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Mastermind JAPAN</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> mastermind japan</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Mastermind JAPAN 日本暗黑奢华街头潮牌，由本间正章 (Masaaki Homma) 1997 年创立，以标志性骷髅图腾、全黑美学与日本顶级工艺著称，主营高端 T 恤、卫衣、夹克及限量联名系列。</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Mastermind JAPAN, a iconic Japanese luxury streetwear brand founded in 1997 by Masaaki Homma. Renowned for its signature skull motif, all-black aesthetic, and premium made-in-Japan craftsmanship, the brand specializes in high-end graphic tees, hoodies, jackets, and exclusive</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="25.5" customHeight="1">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Mizuno</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>mizuno</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Mizuno: 1906年由水野利八创立于日本的专业运动品牌，专注跑步、高尔夫、棒球、排球等运动领域装备研发，以Wave缓震技术、Dynamotion Fit动态贴合等核心科技为支撑，产品兼顾专业竞技性能与人体工学贴合度，服务全球专业运动员及运动爱好者，是融合运动科技与耐用品质的经典运动品牌代表。</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Mizuno: Japanese sports brand since 1906, specializing in running, golf, baseball, volleyball gear with Wave cushioning &amp; Dynamotion Fit tech for professional performance &amp; ergonomic fit, serving athletes worldwide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="25.5" customHeight="1">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Narciso Rodriguez</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>narciso-rodriguez</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Narciso Rodriguez: 由同名美国设计师创立的高端时尚品牌，以极简优雅的风格著称，核心覆盖高级成衣、香水及配饰领域。经典产品包括全球畅销的For Her系列香水（温暖木质香调诠释女性柔媚），成衣设计强调流畅线条与优质材质（如丝绸、羊毛）的融合，兼顾红毯气场与日常实穿性，是现代女性追求精致质感的高端之选，深受时尚界与消费者青睐。</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Narciso Rodriguez: Luxury fashion brand by American designer, famed for minimalist elegance. Core: high-end ready-to-wear, fragrances (bestselling For Her with warm woody notes for feminine charm) &amp; accessories. Ready-to-wear blends fluid lines with premium fabrics (silk, wool), balancing red carpet allure &amp; daily wearability—ideal for modern women seeking refined quality, favored by fashion circles &amp; consumers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="25.5" customHeight="1">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Neighborhood</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>neighborhood</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Neighborhood（NBHD）由日本设计师泷泽伸介 (Shinsuke Takizawa)于1994 年在东京原宿创立，主打街头潮流服饰。标志性产品为冈山赤耳丹宁裤、机车夹克与军事工装，创始人亲任创意总监，以Craft with Pride为理念，风格硬核写实、重质感细节，融合机车、军事与美式工装元素，采用顶级丹宁、优质皮革及纯棉材质，风靡全球，尤其受亚洲、欧美街头文化爱好者与 “养牛” 圈追捧。</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Neighborhood(NBHD): Japanese streetwear brand since 1994 by Shinsuke Takizawa. Craft with Pride philosophy, premium denim, biker jackets, military workwear. Hardcore styles with motorcycle, military, American elements. Top-quality materials, global street culture favorite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="25.5" customHeight="1">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>new-balance</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>New Balance: 1906年创立于美国波士顿的专业运动品牌，以“舒适性能与经典设计共生”为理念，专注运动鞋、运动服饰及配件研发。核心产品覆盖跑步鞋、训练鞋、休闲鞋等系列，搭载ABZORB缓震、ENCAP中底、Fresh Foam轻量科技，满足跑步爱好者、健身人群及日常穿搭需求；经典574、990系列更成为“专业与潮流兼顾”的代表，是全球运动者信赖的“慢跑鞋专家”，持续传递“Made for Makers”的品牌精神。</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>New Balance: Founded in Boston, USA in 1906, this pro sports brand focuses on sneakers, apparel &amp; accessories with "comfort + classic design" philosophy. Core products: running/training/casual shoes with ABZORB cushioning, ENCAP midsole, Fresh Foam tech for runners, fitness lovers &amp; daily wear. Classic 574/990 series (pro + fashion) are trusted "jogging shoe experts", embodying "Made for Makers" spirit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="25.5" customHeight="1">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>New England Patriots</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>new-england-patriots</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>New England Patriots: 新英格兰爱国者是NFL职业橄榄球大联盟的传奇球队，成立于1960年，主场位于马萨诸塞州福克斯堡。品牌以红、白、蓝三色和飞翼徽标闻名，拥有六次超级碗冠军辉煌历史。其官方商品涵盖高品质球衣、帽衫、帽子等粉丝装备，采用先进运动面料与印花工艺，风格经典美式，代表坚韧竞技精神与团队荣耀。</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>New England Patriots: NFL legend since 1960. 6x Super Bowl champions. Iconic red, white, blue &amp; flying Elvis logo. Premium jerseys, hoodies, hats embody classic American grit &amp; team glory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="25.5" customHeight="1">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>New York Jets</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>new-york-jets</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>New York Jets: 美国国家橄榄球联盟（NFL）的老牌职业橄榄球队，1960年成立，主场为纽约大都会人寿体育场，以经典绿白配色队服、冲击力十足的比赛风格著称，是纽约体育文化的重要符号之一，拥有庞大忠实球迷群体，赛场内外传递着美式橄榄球的热血与团队精神，是NFL东部分区极具竞争力的代表球队。</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>New York Jets: Historic NFL team since 1960, based at MetLife Stadium. Iconic green-white uniforms, dynamic playstyle. NY sports symbol with loyal fans, embodying football passion and teamwork in AFC East.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="25.5" customHeight="1">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>new-york-yankees</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>New York Yankees: 美国职业棒球大联盟（MLB）标志性传奇球队，1901年创立（前身为巴尔的摩金莺队，1913年迁至纽约并定现名），隶属美国联盟东区，坐拥27次世界大赛冠军（MLB历史最多），经典条纹队服与“NY” logo是其标志性符号，深耕百年体育文化，是全球棒球迷心中的“王者之师”，以卓越战绩、深厚底蕴与广泛影响力成为美国体育的重要象征。</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>New York Yankees: Iconic MLB franchise since 1901; 27 World Series titles, legendary pinstripes &amp; NY logo. A century-long sports legacy &amp; global symbol of excellence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="25.5" customHeight="1">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Newcastle United</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>newcastle-united</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Newcastle United: 1892年成立的英格兰老牌职业足球俱乐部，绰号“喜鹊”（因经典黑白队服），主场为可容纳52305人的圣詹姆斯公园球场，历史上曾获4次英格兰顶级联赛冠军、6次足总杯冠军，现征战英超联赛。球队以激情球迷文化与快速反击风格著称，2021年由沙特公共投资基金主导收购后逐步强化阵容，是英超联赛中全球球迷关注的劲旅之一，也是英格兰东北部足球文化的重要代表。</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Newcastle United: Est. 1892, Magpies for black-white kits. Premier League club at St James' Park (52,305 seats). 4 top-flight titles, 6 FA Cups. Passionate fans, fast counter-attacks. Strengthened after 2021 Saudi PIF takeover. Global NE England football icon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="25.5" customHeight="1">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>nike</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Nike: 1972年由菲尔·奈特与比尔·鲍尔曼联合创立，美国运动品牌巨头，产品涵盖跑步鞋、篮球鞋、运动服装及装备系列，经典产品包括Air Max气垫鞋、Air Jordan系列，采用Flyknit编织、Dri-FIT科技面料等创新材质，工艺注重轻量缓震，风格融合运动性能与街头时尚。</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Nike: American sports brand since 1972, offering running, basketball shoes, sportswear. Features Air Max, Air Jordan, Flyknit, Dri-FIT. Lightweight cushioning blends performance with street fashion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="25.5" customHeight="1">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Nobis</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>nobis</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Nobis 由Robin Yates（前加拿大鹅副总裁）与Kevin Au-Yeung于2007 年在加拿大多伦多创立，设计师为Michael Kerr。主营高端户外功能性外套（派克大衣、羽绒服等），以极简奢华融合极致保暖性能著称，剪裁利落修身。采用顶级防水面料、高品质鸭绒填充及羊毛、尼龙等复合材质，风靡全球 35 国，深受北美、欧洲及亚洲精英与时尚人士青睐。</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Nobis: Founded in 2007 in Toronto, Canada by Robin Yates (ex-Canada Goose VP) &amp; Kevin Au-Yeung, designed by Michael Kerr. Specializes in high-end functional outerwear (parkas, down jackets) blending minimalist luxury with ultimate warmth, tailored slim fits. Uses premium waterproof fabrics, high-quality duck down, wool-nylon blends. Popular in 35 countries, favored by elites &amp; fashionistas in North America, Europe, Asia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="25.5" customHeight="1">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Nici</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>nici</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>NICI 是来自德国的知名毛绒玩具品牌，创立于 1986 年。以高品质的毛绒面料、生动的动物造型和丰富的系列设计著称，是全球高端毛绒玩具市场的主流品牌之一。</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>NICI: Premium German plush toys since 1986. Known for high-quality fabrics, lifelike animal designs, and diverse collections. A leading global brand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="25.5" customHeight="1">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>NOFS</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>nofs</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>NOFS（Noneofus）由Casey Backhaus与Justin Njinmah于2019 年在德国柏林创立，德国街头潮牌。标志性产品为运动套装、连帽衫及丹宁系列，创始人亲任设计，以极简主义融合大胆字母印花，线条利落、中性配色，注重德国工艺与街头文化。采用优质纯棉、重磅丹宁、聚酯纤维等材质，风靡欧洲、北美及全球 Z 世代，成为德国街头时尚新标杆。</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NOFS: German streetwear from Berlin, founded 2019. Minimalist design, bold letter prints, neutral colors. Tracksuits, hoodies, denim. Premium materials. Popular in Europe, NA, Gen Z.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="25.5" customHeight="1">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Nixon</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>nixon</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Nixon 创立于 1998 年，最初以设计冲浪、滑板运动风格的手表闻名，后来也拓展到服饰领域，是街头、冲浪文化里很受欢迎的品牌，其标志性的 “NIXON” 字母 + 水滴形 logo，是品牌最广为人知的识别元素。</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Nixon: Since 1998, iconic surf &amp; skate watches and apparel, famous for its bold "NIXON" logo and street culture style.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="25.5" customHeight="1">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Number (N) INE 由日本设计师宫下贵裕于1996/1997 年在东京创立，名称源自 The Beatles《Revolution 9》。主营街头服饰、T 恤、丹宁裤与机车夹克，创始人亲任设计，融合美式复古、摇滚朋克与军事元素，风格暗黑颓废、层次丰富。采用重磅棉、顶级丹宁、优质皮革等材质，风靡全球，是日本地下与前卫时尚标杆，深受欧美潮流人士追捧。</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Number: Founded by Japanese designer Takayuki Miyashita in Tokyo (1996/1997), named after The Beatles’ “Revolution 9”. Specializes in streetwear, tees, denim, biker jackets. Founder-led design blends American retro, rock punk, military elements—dark, decadent, layered styles. Uses heavy cotton, premium denim, quality leather. Global phenomenon, Japanese underground/avant-garde fashion icon, popular with Western fashion lovers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="25.5" customHeight="1">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Off White</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>off-white</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Off White: 由Virgil Abloh于2012年创立的美国高端街头时尚品牌，以“未完成感”解构主义设计为核心，融合街头文化与高端时尚美学，标志性元素包括引号、斜杠、箭头等工业风视觉符号。产品涵盖服装、鞋履、配饰等，经典如OW x Nike联名 sneakers系列，是连接街头潮流与高奢领域的先锋品牌，深受全球潮人、时尚爱好者及Louis Vuitton等合作方青睐。</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Off White: Virgil Abloh's luxury streetwear label, famed for deconstructed aesthetics, industrial symbols like quotes &amp; arrows, and iconic Nike collabs, bridging high fashion with urban culture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="25.5" customHeight="1">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Olympique De Darseille</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>olympique-de-marseille</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Olympique De Darseille（ODD）由Julien Poublon于2014 年在法国巴黎创立，法国街头潮牌。主营重磅棉 T 恤、顶级丹宁裤、摇滚风格卫衣等，创始人亲任设计师。流行于法、欧及全球街头潮流圈，风格融合美式复古与军事工装元素，采用重磅棉、优质皮革等耐用材质，是法国标志性街头潮牌。</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Olympique De Darseille (ODD): French streetwear brand founded by Julien Poublon in Paris 2014. Offers heavy cotton tees, premium denim, rock-style hoodies. Blends American retro &amp; military workwear, uses durable heavy cotton, premium leather. Popular in France, Europe &amp; global streetwear circles, iconic French streetwear label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="25.5" customHeight="1">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>One Piece</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>one-piece</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>One Piece: 日本国民级海贼题材IP，由尾田荣一郎创作，1997年起在《周刊少年Jump》连载漫画，衍生动画、电影、游戏及手办、服饰等多元产品。以“草帽一伙寻找传说中大秘宝‘One Piece’的冒险”为核心，传递自由、伙伴与逐梦的精神内核，全球累计粉丝超数亿，是日本动漫文化输出的标杆性IP，覆盖全年龄段受众，衍生商品持续占据二次元周边市场热门。</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>One Piece: Japan's national pirate IP by Eiichiro Oda, serialized in Weekly Shonen Jump since 1997. Derived anime, films, games, figures, apparel. Core: Straw Hats' adventure for "One Piece" treasure, conveying freedom, friendship, dreams. Billions of global fans, benchmark of Japanese anime culture export, all-age audience, top-selling anime merchandise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="25.5" customHeight="1">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>这个类目下，我们将不归属于任何品牌的商品归类到这里，以便于用户从这个表格里找到品牌不明显的流行或商品，以便于选择或购买。</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>In the Other category, we classify unbranded products here to help users find popular items with less obvious brands for selection or purchase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="25.5" customHeight="1">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>on running</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>On Running: 2010年由三届铁人三项世界冠军Olivier Bernhard联合创立的瑞士专业运动品牌，以核心CloudTec®云科技中底为技术核心，融合精准缓震与向前推进力，专注跑步等运动场景，为专业跑者及运动爱好者提供兼具舒适脚感、卓越性能与简约设计的运动装备，是全球跑圈备受推崇的“跑者专属品牌”。</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>On Running: Swiss performance sportswear founded by 3x Ironman World Champion Olivier Bernhard. Features core CloudTec® cushioning for precision shock absorption and propulsive force, delivering high-performance running gear revered by runners worldwide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="25.5" customHeight="1">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Onitsuka Tiger</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>onitsuka tiger</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Onitsuka Tiger: 1949年由鬼冢喜八郎创立于日本，作为ASICS的前身品牌，以“复古运动时尚”为核心定位，融合日本传统工艺与经典设计美学。标志性虎爪纹Logo、Mexico 66等经典系列享誉全球，产品涵盖运动鞋、服饰及配件，采用帆布、皮革等优质材质，风格兼顾复古质感与现代休闲，是潮流爱好者与运动复古风追随者的首选品牌。</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Onitsuka Tiger: Founded in Japan by Kihachiro Onitsuka in 1949, predecessor of ASICS. Core positioning: "retro sporty fashion", blending Japanese traditional craftsmanship &amp; classic design aesthetics. Iconic tiger claw logo, classic Mexico 66 series. Products: sneakers, apparel, accessories (premium canvas/leather). Retro texture + modern casual style, top choice for trendsetters &amp; sporty vintage followers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="25.5" customHeight="1">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Paco Rabanne</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>paco-rabanne</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Paco Rabanne: 1966年由西班牙裔法国设计师Paco Rabanne（弗朗西斯科·拉巴内达·库尔沃）创立的法国先锋奢侈品牌，以未来主义风格与金属材质创新运用著称，标志性金属链甲连衣裙重塑时尚边界，经典香水如Calandre、One Million系列全球热销，产品线覆盖高级时装、香水、配饰等，始终践行“时尚是科技与艺术的先锋融合”理念，是全球先锋时尚爱好者的标志性选择。</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Paco Rabanne: Founded by Spanish-French designer Francisco Rabaneda Cuervo in 1966, French avant-garde luxury brand known for futuristic style &amp; innovative metal use. Iconic metal chainmail dresses redefined fashion boundaries. Classic fragrances like Calandre &amp; One Million bestsellers. Lines cover haute couture, fragrances, accessories. Upholds "fashion is tech-art fusion" – global avant-garde fashion lovers’ iconic choice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="25.5" customHeight="1">
+      <c r="A189" t="inlineStr">
+        <is>
           <t>Palestino</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B189" t="inlineStr">
         <is>
           <t>palestino</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C189" t="inlineStr">
         <is>
           <t>Palestino: 
 （注：因未获取到Palestino品牌对应的中文描述信息，无法依据要求生成符合SEO优化的品牌描述内容。）</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D189" t="inlineStr">
         <is>
           <t>Palestino: Note: Unable to generate SEO-optimized brand description as no corresponding Chinese information for Palestino brand is obtained.</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="25.5" customHeight="1">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Palm Angels</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>palm-angels</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Palm Angels: 2015年由Francesco Ragazzi创立的意大利街头潮流品牌，以滑板文化为内核融合高端时尚美学，标志性棕榈树图案、oversize剪裁是其辨识度符号，产品线涵盖服装、配饰、鞋履，曾与Adidas、Moncler等推出联名系列，风格兼具街头不羁与奢华质感，是全球潮流爱好者追捧的当代街头时尚代表品牌。</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Palm Angels: Italian streetwear brand founded by Francesco Ragazzi in 2015, merging skate culture with luxury aesthetics. Signature palm tree motif, oversize cuts; lines cover apparel, accessories, footwear. Collaborations with Adidas, Moncler. Edgy yet luxurious, a leading contemporary streetwear icon for global fashion lovers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="25.5" customHeight="1">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>paris-saint-germain</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain: 1970年创立于法国巴黎的顶级职业足球俱乐部，法甲联赛传统劲旅，主场为巴黎王子公园球场。以华丽进攻战术、全球顶尖球星阵容（如姆巴佩等核心球员）及10余次法甲冠军、多座法国杯冠军等荣誉著称，是全球足球领域极具影响力的品牌，代表法国足球高端竞技水准与国际球迷号召力。</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain: Top pro football club founded 1970 in Paris, Ligue 1 powerhouse with home Parc des Princes. Known for attacking tactics, top stars (Mbappé etc.), 10+ Ligue 1 titles &amp; multiple French Cups. Global influential brand representing France’s elite football &amp; international fan appeal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="25.5" customHeight="1">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>parma</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Parma（Pini Parma）由Thomas Pini与妻子Claudia Cannetto于2017 年在意大利创立，总部位于巴黎。主营男士定制正装、休闲服饰及鞋履，创始人主导设计，融合意式经典与现代简约，线条流畅自然。采用Super 150’s 羊毛、羊绒、纯棉等顶级材质，意大利工匠手工制作，风靡欧洲、北美及亚洲，是高端意式男装新标杆。</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Parma(Pini Parma): Founded in Italy 2017 by Thomas Pini &amp; Claudia Cannetto, headquartered in Paris. Specializes in custom men’s formalwear, casual apparel &amp; footwear. Founder-led design blends Italian classics with modern minimalism, smooth natural lines. Uses premium materials (Super 150’s wool, cashmere, cotton). Handcrafted by Italian artisans. Popular in Europe, North America, Asia—new benchmark for high-end Italian menswear.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="25.5" customHeight="1">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Payeah</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>payeah</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>ayeah 是主打休闲印花 T 恤的时尚品牌，主营 100% 纯棉男女款潮流 T 恤，涵盖节日主题、数字印花等多元设计。风格融合街头潮流与日常休闲，图案大胆个性、色彩鲜明。采用重磅纯棉、精梳棉等优质材质，透气亲肤、耐穿易洗。风靡北美、欧洲及全球跨境电商市场，是年轻消费者日常穿搭与个性表达的热门选择。</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Payeah: 100% cotton men's &amp; women's trendy t-shirts with festive themes, digital prints. Bold, vibrant street-casual designs. Heavyweight combed cotton: breathable, skin-friendly, durable, easy to wash. Popular in North America, Europe &amp; global cross-border e-commerce, top for young daily wear &amp; self-expression.</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="25.5" customHeight="1">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Penhaligons</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>penhaligons</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Penhaligons: 1870年由威廉·彭哈根（William Penhaligon）创立于英国伦敦的高端香氛品牌，以英伦贵族式奢华调香与复古故事性著称，核心涵盖香水、香氛蜡烛及身体护理系列，经典香款如《Portrait of a Lady》（仕女画像）、《The Tragedy of Lord George》（乔治勋爵的悲剧）等，凭借精湛调香工艺与独特英伦美学，成为全球香氛爱好者追捧的奢华香氛代表品牌。</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>Penhaligons: Luxury British fragrance brand founded in London in 1870 by William Penhaligon, celebrated for aristocratic opulent scents &amp; vintage storytelling. Core lines: perfumes, scented candles, body care. Classics include Portrait of a Lady &amp; The Tragedy of Lord George. Exquisite craftsmanship &amp; unique British aesthetics make it a global luxury fragrance favorite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="25.5" customHeight="1">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Philadelphia Eagles</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>philadelphia-eagles</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Philadelphia Eagles: 美国国家橄榄球联盟（NFL）历史悠久的职业球队，1933年成立于宾夕法尼亚州费城，隶属于NFC东区，主场为林肯金融球场。球队曾荣获2018年第52届超级碗冠军，以展翅雄鹰队徽、深绿+银灰+黑的经典队色为标志，拥有“Eagles Nation”庞大球迷群体，以坚韧球风与社区深度联结著称，是北美职业橄榄球领域极具影响力的球队之一。</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>Philadelphia Eagles: NFL team founded 1933 in Philadelphia, NFC East, Lincoln Financial Field. Super Bowl LII champions (2018). Iconic eagle logo, green/silver/black colors. Eagles Nation, resilient style.</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="25.5" customHeight="1">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Pittsburgh Steelers</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>pittsburgh-steelers</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Pittsburgh Steelers: 1933年成立于美国宾夕法尼亚州匹兹堡，是NFL（美国国家橄榄球联盟）历史最悠久的球队之一，以“钢铁之城”的强硬球风闻名，曾6次夺得超级碗冠军（NFL夺冠次数最多的球队之一），主场为Acrisure Stadium。球队承载匹兹堡工业底蕴，融合橄榄球热血精神，拥有全球庞大“钢铁军团”球迷群体，是美式橄榄球界极具传奇性与影响力的经典劲旅。</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Pittsburgh Steelers: Legendary NFL team founded 1933 in Pittsburgh, 6-time Super Bowl champions, known for Steel City tough style, home at Acrisure Stadium, with global Steelers Nation fan base.</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="25.5" customHeight="1">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Playboi Carti</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>playboi-carti</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Playboi Carti: 美国嘻哈音乐人及街头潮流符号，其同名周边潮牌以说唱文化为内核，推出卫衣、T恤、帽款等单品，设计融入专辑视觉、标志性歌词元素，采用棉质等舒适面料，风格街头不羁，契合年轻潮流群体审美，是连接音乐与时尚消费的热门跨境电商品牌。</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>Playboi Carti: American hip-hop artist &amp; streetwear icon, eponymous merch brand rooted in hip-hop culture. Offers hoodies, tees, caps with album visuals, iconic lyrics, comfy cotton. Edgy street style resonates with young trendsetters, popular cross-border brand linking music &amp; fashion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="25.5" customHeight="1">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Polo</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>polo</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Polo: 源自美国的经典休闲品牌，以标志性马球logo为核心识别，产品线覆盖男女装、皮具、配饰等，主打简约经典风格，采用高品质棉、皮革等材质，兼顾舒适与耐用性，适配日常休闲、轻商务等多元场景，是全球消费者青睐的休闲时尚选择。</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>Polo: Iconic US casual brand featuring the polo logo. Offers classic men's, women's apparel, leather goods &amp; accessories. Premium cotton &amp; leather for durable, versatile everyday &amp; smart-casual wear.</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="25.5" customHeight="1">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Patagonia</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>patagonia</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Patagonia: 1973年创立于美国的专业户外装备品牌，以“构建更美好的地球”为核心使命，专注可持续环保户外服饰与装备设计，产品涵盖冲锋衣、羽绒服、抓绒衣、登山包等，采用再生聚酯纤维、有机棉等环保材质，坚持“1% for the Planet”计划（将1%营收投入环保公益），融合专业户外性能与生态责任，是全球户外爱好者与环保主义者信赖的可持续户外品牌典范。</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Patagonia: US professional outdoor gear brand founded in 1973, core mission "Build the Better Earth". Specializes in sustainable apparel/gear (raincoats, down jackets, fleece, hiking packs) with recycled polyester, organic cotton. Committed to "1% for the Planet" (1% revenue to environmental causes). Blends professional performance with ecological responsibility, trusted by global outdoor enthusiasts &amp; environmentalists as a sustainable leader.</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="25.5" customHeight="1">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Prada</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>prada</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Prada: 1913年由马里奥·普拉达（Mario Prada）创立于意大利米兰，全球顶级奢侈品牌，以皮具、高级时装、配饰为核心品类，标志性尼龙材质与三角标LOGO是品牌辨识度符号，融合极简设计与精湛意大利工艺，诠释“低调奢华”的时尚内核，经典产品涵盖Saffiano皮革手袋、尼龙背包及成衣系列，是全球追求高品质时尚人群的首选品牌之一。</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Prada: Founded in Milan, Italy in 1913 by Mario Prada, a top global luxury brand with core categories of leather goods, high fashion, and accessories. Iconic nylon material &amp; triangular logo, minimalist design + exquisite Italian craftsmanship embody "understated luxury". Classic products: Saffiano bags, nylon backpacks, ready-to-wear—preferred by global high-quality fashion seekers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="25.5" customHeight="1">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Project Capri</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>project-capri</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Project Capri 由Caprice Brown于2022 年在拉斯维加斯创立，当时仅 16 岁的他打造出七位数营收潮牌。创始人亲任设计师，主营镶钻牛仔裤、多口袋牛仔短裤、丹宁夹克与工装裤。风格融合复古丹宁、军事工装与大胆印花，街头感十足。采用重磅丹宁、优质帆布与真皮等耐用材质，风靡美国、欧洲及全球潮流圈，深受 Z 世代追捧，是年轻街头品牌标杆。</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Project Capri: Founded by Caprice Brown in Las Vegas (2022, 16yo), 7-figure streetwear. Founder-led design: rhinestone jeans, multi-pocket denim shorts, jackets, work pants. Blends vintage denim, military workwear, bold prints (streetwear vibe). Uses heavy denim, premium canvas, genuine leather. Popular in US/Europe/global, Gen Z-favorite young street brand benchmark.</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="25.5" customHeight="1">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>puma</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Puma: 1948年由鲁道夫·达斯勒创立的德国专业运动品牌，以“Forever Faster”为核心精神，专注跑步、足球、篮球等专业运动装备与潮流运动服饰研发，经典产品包括Suede板鞋、Clyde篮球鞋及Ultra足球鞋系列，采用优质皮革、透气科技面料等材质，融合运动性能与街头时尚设计，满足全球运动员训练比赛及潮流爱好者日常穿搭需求，是兼具专业度与潮流感的知名运动品牌。</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Puma: German sportswear brand founded 1948, embodying "Forever Faster" in running, football, basketball. Features Suede, Clyde, Ultra series, blending performance tech with street-style fashion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="25.5" customHeight="1">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Ralph Lauren</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>ralph-lauren</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Ralph Lauren: 1967年由拉尔夫·劳伦（Ralph Lauren）创立的美国高端时尚品牌，以"美式经典生活方式"为核心定位，覆盖男装、女装、童装、配饰（皮具、香水、腕表）及家居全品类，标志性元素包括马球 pony 标志、牛津纺衬衫、粗花呢西装与经典格纹，产品融合复古优雅与休闲奢华感，是全球美式时尚与品质生活的代表品牌，旗下Polo Ralph Lauren系列更成为基础款高端化的经典范例。</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Ralph Lauren: American luxury fashion brand founded by Ralph Lauren in 1967, focused on the "American classic lifestyle", covering men’s, women’s, kids’ apparel, accessories (leather goods, perfume, watches) &amp; homeware. Iconic elements: Polo pony logo, Oxford shirts, tweed suits, classic plaids. Blending vintage elegance &amp; casual luxury, it’s a global representative of American fashion &amp; quality life. Its Polo Ralph Lauren line is a classic example of elevated basics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="25.5" customHeight="1">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Rb Leipzig</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>rb-leipzig</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>RB Leipzig: 德国职业足球俱乐部，2009年成立于萨克森州莱比锡，隶属于红牛集团，主场为可容纳超4.2万名观众的莱比锡红牛竞技场，系德甲联赛劲旅。球队以“青春风暴”“高压进攻”战术风格著称，近年稳居德甲积分榜前列，多次晋级欧冠、欧联杯等欧洲顶级赛事，是德国足坛近年快速崛起的代表性球队。</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>RB Leipzig: Top Bundesliga club founded 2009. Red Bull-owned, home Red Bull Arena 42,000+. Youth storm &amp; high-pressure attack style. Regular in UEFA Champions League/Europa League, symbol of rapid rise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="25.5" customHeight="1">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Readymade</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>readymade</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>eadymade 由日本设计师细川雄太 (Yuta Hosokawa)于2013 年在大阪创立，主打军事重制服饰与配饰。创始人亲任设计，以和平反战为核心理念，将二战古军布、帐篷帆布与复古军用包袋手工改造成包袋、外套、卫衣等单品。风格融合美式复古、军事工装与解构主义，每件均带原始编号，独一无二。风靡全球潮流圈，受 Virgil Abloh、Travis Scott 等明星追捧，是 Remake 领域标杆。</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Readymade, founded 2013 in Osaka by Yuta Hosokawa, specializes in military remake apparel/accessories. Core peace anti-war philosophy, handmade from WWII vintage military fabrics, tents &amp; bags. Blends American vintage, military workwear &amp; deconstruction. Unique numbered, global trend icon, Remake benchmark.</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="25.5" customHeight="1">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>real-madrid</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Real Madrid: 1902年成立于西班牙马德里的顶级职业足球俱乐部，昵称“银河战舰”，是历史上夺得欧洲冠军联赛冠军次数最多（14次）的球队，亦坐拥35次西班牙甲级联赛冠军等荣誉；主场为标志性的伯纳乌球场（Estadio Santiago Bernabéu），以经典白色球衣、带皇冠与“RM”标识的队徽为核心视觉符号；全球拥有超4亿球迷，商业价值常年位居足球俱乐部前列，传承“永不言弃”的竞技精神，代表西班牙足球的巅峰水准与全球影响力。</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>Real Madrid: Elite Spanish football club founded 1902, "Galacticos". Record 14 UEFA Champions League &amp; 35 La Liga titles. Iconic Santiago Bernabéu Stadium, white kits, 400M+ fans, "Never give up" spirit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="25.5" customHeight="1">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Revenge</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>revenge</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Revenge 由Garette 与 Han于2016 年在美国洛杉矶创立，是匿名设计师 Garette 主导的街头潮牌。主营拱门 Logo 帽衫、涂鸦 T 恤、荆棘牛仔与素食皮夹克等，风格暗黑叛逆，融合朋克美学与哥特式手写字体，标志性蜘蛛网与火焰图案极具辨识度。采用重磅纯棉、优质牛仔与环保素食皮等耐用材质，因与 XXXTentacion 合作爆红，风靡全球 Z 世代潮流圈，是地下街头文化标杆。</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>Revenge: Streetwear brand founded by Garette &amp; Han in LA 2016, led by anonymous designer Garette. Core products: arched logo hoodies, graffiti tees, thorn denim, vegan leather jackets. Dark rebellious style fuses punk aesthetics with gothic handwritten fonts; iconic spider web &amp; flame patterns. Uses heavy cotton, premium denim, eco vegan leather. Viral via XXXTentacion collab, beloved by global Gen Z—underground street culture icon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="25.5" customHeight="1">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Represent</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>represent</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Represent 由George Heaton与Mike Heaton兄弟于2011 年在英国大曼彻斯特创立，始于大学 T 恤印花项目。创始人 George 主理设计，主营帽衫、T 恤、夹克、运动裤与鞋履，风格融合奢华街头风与极简主义，以480GSM 重磅针织棉、莱赛尔斜纹布等高端面料打造精品基础款，注重工艺细节。风靡欧美、日韩及全球潮流圈，受明星与时尚达人追捧，是英国奢华街头品牌标杆。</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Represent: Founded by George &amp; Mike Heaton in Greater Manchester, UK (2011) from a university T-shirt printing project. George leads design; offers hoodies, T-shirts, jackets, sweatpants, footwear. Blends luxury streetwear with minimalism, using 480GSM heavy knit cotton, Lyocell twill for premium basics, emphasizing craftsmanship. Popular in EU/US/Japan/Korea, favored by celebrities/influencers—UK luxury streetwear benchmark.</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="25.5" customHeight="1">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Rhude</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>rhude</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Rhude: 2015年由Rhuigi Villaseñor创立于美国的高端街头服饰品牌，以“街头文化与高级时尚融合”为核心定位，标志性设计涵盖经典Logo、复古运动元素与皮革、麂皮等高端材质的结合，产品包括卫衣、夹克、牛仔裤及配饰，曾与Nike、Puma等推出联名系列，主打“街头奢华风”，精准契合追求潮流质感与独特风格的年轻群体需求。</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Rhude: Founded by Rhuigi Villaseñor in the US in 2015, a high-end streetwear brand blending street culture with luxury fashion. Signature designs feature classic logos, retro sporty elements, premium leather/suede. Products: hoodies, jackets, jeans, accessories. Collaborated with Nike, Puma. Focuses on "street luxury" for young people pursuing trendy quality &amp; unique styles.</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="25.5" customHeight="1">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Rick Owens</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>rick-owens</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Rick Owens: 1994年由同名设计师创立于美国洛杉矶的先锋暗黑时尚品牌，以解构主义、工业感轮廓与垂坠美学为核心风格，标志性产品包括Geobasket运动鞋、机车皮革夹克及垂坠剪裁成衣，常用皮革、帆布等质感材质，诠释反主流的个性表达，是全球先锋时尚爱好者与潮流人士追捧的暗黑先锋代表品牌。</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Rick Owens: Founded in Los Angeles, USA in 1994, this avant-garde dark fashion brand focuses on deconstruction, industrial silhouettes, and drape aesthetics. Signature items: Geobasket sneakers, biker leather jackets, draped ready-to-wear. Uses leather/canvas, embodies anti-mainstream self-expression—iconic among global avant-garde fashion lovers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="25.5" customHeight="1">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Roberto Cavalli</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>roberto-cavalli</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Roberto Cavalli: 1960年代由意大利设计师Roberto Cavalli创立的奢侈品牌，以「狂野奢华」风格为核心标签，标志性动物纹、大胆印花与精湛手工工艺贯穿高级时装、皮具、香水、配饰等全品类，诠释不羁个性与顶级奢华的融合，是全球追求独特时尚品味、渴望彰显自我风格的高端消费者首选品牌。</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Roberto Cavalli: Italian luxury brand founded by Roberto Cavalli in the 1960s, centered on "wild luxury"—iconic animal prints, bold patterns, exquisite craftsmanship across ready-to-wear, leather goods, fragrances, accessories. Blends unruly individuality with top-tier luxury, favored by global high-end consumers pursuing unique style.</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="25.5" customHeight="1">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Rossoneri</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>rossoneri</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Rossoneri 是 AC 米兰官方生活方式品牌，源于1899 年英国创始人Herbert Kilpin创立的红黑军团。由俱乐部设计团队操刀，主营球衣、帽衫、T 恤、配饰等，风格融合意式足球文化与街头潮流，标志性红黑配色与魔鬼队徽极具辨识度。采用100% 精梳棉、聚酯纤维运动面料等优质材质，透气舒适、耐穿易洗。风靡全球足球与潮流圈，尤其在欧洲、南美及亚洲，是球迷彰显信仰与时尚态度的首选，诠释 “Milanismo” 精神。</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Rossoneri AC Milan’s official lifestyle brand, founded by Herbert Kilpin in 1899 (the Rossoneri). Designed by the club’s team, offers jerseys, hoodies, tees, accessories. Blends Italian football culture with streetwear; iconic red-black &amp; devil emblem stand out. Uses premium 100% combed cotton, polyester sport fabrics—breathable, comfy, durable. Popular globally (Europe, S. America, Asia); fans’ top choice for faith &amp; style, embodying “Milanismo.”</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="25.5" customHeight="1">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Saint Michael</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>saint-michael</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Saint Michael由日本设计师细川雄太 (Yuta Hosokawa)与美国艺术家Cali Thornhill DeWitt于2020 年创立，细川负责服装制作，Cali 主理平面设计。主营重磅卫衣、印花 T 恤、水洗牛仔与棒球夹克，风格融合日式复古工艺、美式街头文化与宗教符号，标志性做旧水洗与开裂印花极具辨识度。采用420g 精梳棉、重磅牛仔布等优质材质，手工做旧处理每件独一无二。风靡日美欧潮流圈，受明星与潮流博主追捧，是高端复古街头品牌标杆。</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Saint Michael: Co-founded by Yuta Hosokawa &amp; Cali Thornhill DeWitt (2020). Hosokawa crafts, DeWitt designs graphics. Heavyweight hoodies, tees, denim, jackets. Fusing Japanese vintage craft, American street, religious symbols. Iconic distressed washes, cracked prints; 420g combed cotton, premium denim. Unique hand-distressing. Trendy Japan/US/Europe, celebrity-loved premium retro streetwear.</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="25.5" customHeight="1">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Salvatore Ferragamo</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>salvatore-ferragamo</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Salvatore Ferragamo由萨尔瓦多・菲拉格慕于1927 年在意大利佛罗伦萨创立，被誉为 "明星鞋匠"。现任创意总监Maximilian Davis，主营鞋履、皮具、成衣、配饰与香水，标志性 Gancini logo 与 Vara 蝴蝶结鞋款闻名。风格融合意式永恒优雅与现代设计，坚持传统手工与创新结构，采用托斯卡纳小牛皮、鳄鱼皮等顶级材质，每双鞋经超 300 道工序。风靡欧美亚，美日中为核心市场，是意大利奢华时尚标杆。</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>Salvatore Ferragamo: Luxury Italian shoes &amp; leather goods since 1927, "shoemaker to the stars." Iconic Gancini logo, Vara bow. Handcrafted with premium materials, 300+ steps. Global fashion benchmark.</t>
         </is>
       </c>
     </row>
     <row r="190" ht="25.5" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Papahug</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>sampdoria</t>
+          <t>papahug</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Sampdoria: 意大利热那亚的职业足球俱乐部，1946年由桑普达雷内塞和安德雷亚·多利亚两支球队合并成立，主场为路易吉·费拉里斯球场，以标志性蓝白条纹球衣著称，昵称“Blucerchiati（蓝环队）”。队史斩获1次意甲冠军（1990-91赛季）、4次意大利杯冠军及1次欧洲优胜者杯亚军，是意大利足坛兼具历史底蕴与地域辨识度的传统劲旅。</t>
+          <t>PAPAHUG 是一个主打治愈系、趣味家居用品的品牌，以 “多巴胺” 色彩和卡通化设计著称，深受年轻人喜爱。</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Sampdoria: Genoa Italian football club founded 1946. Blue-white stripes, nicknamed Blucerchiati. 1 Serie A, 4 Coppa Italia, 1 UEFA Cup Winners' Cup runner-up. Traditional powerhouse.</t>
+          <t>PapahugPAPAHUG: Dopamine-colored, cartoonish home goods brand. Fun, healing designs loved by youth.</t>
         </is>
       </c>
     </row>
     <row r="191" ht="25.5" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Palm Angels</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>santos</t>
+          <t>palm-angels</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Santos，巴西桑托斯足球俱乐部生活方式品牌，1912 年由鲁道夫・阿劳霍创立，主营球衣、帽衫、T 恤等，标志性白色底色配黑红细节，采用透气聚酯纤维、精梳棉，风靡巴西及全球足球圈。</t>
+          <t>Palm Angels: 2015年由Francesco Ragazzi创立的意大利街头潮流品牌，以滑板文化为内核融合高端时尚美学，标志性棕榈树图案、oversize剪裁是其辨识度符号，产品线涵盖服装、配饰、鞋履，曾与Adidas、Moncler等推出联名系列，风格兼具街头不羁与奢华质感，是全球潮流爱好者追捧的当代街头时尚代表品牌。</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>SantosSantos: Brazilian football lifestyle brand founded 1912 by Rudolf Araújo, specializing in jerseys, hoodies, tees. Iconic white with black-red details, breathable polyester &amp; combed cotton, popular in Brazil &amp; global football circles.</t>
+          <t>Palm Angels: Italian streetwear brand founded by Francesco Ragazzi in 2015, merging skate culture with luxury aesthetics. Signature palm tree motif, oversize cuts; lines cover apparel, accessories, footwear. Collaborations with Adidas, Moncler. Edgy yet luxurious, a leading contemporary streetwear icon for global fashion lovers.</t>
         </is>
       </c>
     </row>
     <row r="192" ht="25.5" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Score Draw</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>score-draw</t>
+          <t>paris-saint-germain</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Score Draw 由Michael Roy Phillips于2002 年 9 月在英国创立，是全球领先官方复古足球服饰品牌。主营官方授权复古球衣、训练服及周边，与 40 余家俱乐部和足协合作，复刻 50 余年超 600 款经典款式。设计团队经精密考证，忠于原版细节，风格为复古经典、怀旧情怀。采用正宗聚酯纤维，透气舒适，还原当年穿着体验。风靡欧洲、北美、澳洲足球圈，深受全球球迷与复古潮流爱好者追捧，是足球文化收藏首选。</t>
+          <t>Paris Saint Germain: 1970年创立于法国巴黎的顶级职业足球俱乐部，法甲联赛传统劲旅，主场为巴黎王子公园球场。以华丽进攻战术、全球顶尖球星阵容（如姆巴佩等核心球员）及10余次法甲冠军、多座法国杯冠军等荣誉著称，是全球足球领域极具影响力的品牌，代表法国足球高端竞技水准与国际球迷号召力。</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Score Draw: Leading official retro football apparel since 2002 UK. Licensed vintage jerseys, training wear with 40+ clubs, 600+ classic styles. Authentic polyester comfort. Popular globally, top for football culture.</t>
+          <t>Paris Saint Germain: Top pro football club founded 1970 in Paris, Ligue 1 powerhouse with home Parc des Princes. Known for attacking tactics, top stars (Mbappé etc.), 10+ Ligue 1 titles &amp; multiple French Cups. Global influential brand representing France’s elite football &amp; international fan appeal.</t>
         </is>
       </c>
     </row>
     <row r="193" ht="25.5" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Sicko</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>sicko</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Sicko（全称 Sicko Born From Pain）由美国潮流先锋Ian Connor于2018 年创立，本人担任设计师，洛杉矶限量生产。主营重磅卫衣、印花 T 恤、限定配饰，标志性 “Born From Pain” 标语与婴儿头像 Logo 源自 Björk 专辑封面，融合街头文化与个人艺术表达。采用400g + 精梳棉、透气聚酯纤维等优质面料，手工印花工艺提升质感。风靡全球潮流圈，尤受欧美亚千禧一代追捧，是高街街头与限量收藏的热门选择。</t>
+          <t>Parma（Pini Parma）由Thomas Pini与妻子Claudia Cannetto于2017 年在意大利创立，总部位于巴黎。主营男士定制正装、休闲服饰及鞋履，创始人主导设计，融合意式经典与现代简约，线条流畅自然。采用Super 150’s 羊毛、羊绒、纯棉等顶级材质，意大利工匠手工制作，风靡欧洲、北美及亚洲，是高端意式男装新标杆。</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Sicko Born From Pain: Ian Connor's 2018 LA limited streetwear. Iconic 'Born From Pain' logo, heavy hoodies, tees, accessories. 400g+ combed cotton, manual print. Global millennial favorite for high-street fashion.</t>
+          <t>Parma(Pini Parma): Founded in Italy 2017 by Thomas Pini &amp; Claudia Cannetto, headquartered in Paris. Specializes in custom men’s formalwear, casual apparel &amp; footwear. Founder-led design blends Italian classics with modern minimalism, smooth natural lines. Uses premium materials (Super 150’s wool, cashmere, cotton). Handcrafted by Italian artisans. Popular in Europe, North America, Asia—new benchmark for high-end Italian menswear.</t>
         </is>
       </c>
     </row>
     <row r="194" ht="25.5" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Snapdragon</t>
+          <t>Payeah</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>snapdragon</t>
+          <t>payeah</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Snapdragon: 高通（Qualcomm）旗下全球知名移动处理器品牌，专注为智能手机、平板、笔记本及IoT智能设备提供高性能低功耗芯片解决方案，覆盖旗舰（8系列）、中高端（7系列）至主流（6系列）全产品线，核心优势包含5G高速连接、AI智能加速、Adreno图形渲染及Hexagon音频/计算技术，是三星、小米、OPPO等众多品牌旗舰机型的核心处理器选择，持续推动智能设备的体验升级与技术创新。</t>
+          <t>ayeah 是主打休闲印花 T 恤的时尚品牌，主营 100% 纯棉男女款潮流 T 恤，涵盖节日主题、数字印花等多元设计。风格融合街头潮流与日常休闲，图案大胆个性、色彩鲜明。采用重磅纯棉、精梳棉等优质材质，透气亲肤、耐穿易洗。风靡北美、欧洲及全球跨境电商市场，是年轻消费者日常穿搭与个性表达的热门选择。</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Snapdragon: Qualcomm's flagship mobile processor for smartphones, tablets, &amp; IoT. Features 5G, AI, Adreno GPU, Hexagon tech. Powers top brands like Samsung, Xiaomi, OPPO.</t>
+          <t>Payeah: 100% cotton men's &amp; women's trendy t-shirts with festive themes, digital prints. Bold, vibrant street-casual designs. Heavyweight combed cotton: breathable, skin-friendly, durable, easy to wash. Popular in North America, Europe &amp; global cross-border e-commerce, top for young daily wear &amp; self-expression.</t>
         </is>
       </c>
     </row>
     <row r="195" ht="25.5" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Sp5der</t>
+          <t>Penhaligons</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>sp5der</t>
+          <t>penhaligons</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Sp5der: 美国街头潮牌，由说唱歌手Young Thug创立，以标志性蜘蛛元素为核心设计语言，主打卫衣、T恤、棒球帽等潮流单品，风格融合嘻哈文化与街头时尚，版型宽松舒适且注重细节工艺，深受全球年轻潮流爱好者追捧，是街头文化穿搭的热门选择。</t>
+          <t>Penhaligons: 1870年由威廉·彭哈根（William Penhaligon）创立于英国伦敦的高端香氛品牌，以英伦贵族式奢华调香与复古故事性著称，核心涵盖香水、香氛蜡烛及身体护理系列，经典香款如《Portrait of a Lady》（仕女画像）、《The Tragedy of Lord George》（乔治勋爵的悲剧）等，凭借精湛调香工艺与独特英伦美学，成为全球香氛爱好者追捧的奢华香氛代表品牌。</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Sp5der: Young Thug's streetwear brand. Iconic spider designs, hip-hop style, hoodies, tees, caps. Loose fit, detailed craftsmanship. Globally loved by youth culture.</t>
+          <t>Penhaligons: Luxury British fragrance brand founded in London in 1870 by William Penhaligon, celebrated for aristocratic opulent scents &amp; vintage storytelling. Core lines: perfumes, scented candles, body care. Classics include Portrait of a Lady &amp; The Tragedy of Lord George. Exquisite craftsmanship &amp; unique British aesthetics make it a global luxury fragrance favorite.</t>
         </is>
       </c>
     </row>
     <row r="196" ht="25.5" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Ss Lazio</t>
+          <t>Philadelphia Eagles</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ss-lazio</t>
+          <t>philadelphia-eagles</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Ss Lazio: 意大利罗马老牌职业足球俱乐部，1900年成立，主场为罗马奥林匹克体育场，征战意甲联赛。曾斩获意甲冠军、意大利杯冠军等荣誉，队服以经典天蓝色与白色为主色调，拥有悠久历史与深厚球迷文化，是意甲联赛的传统劲旅之一。</t>
+          <t>Philadelphia Eagles: 美国国家橄榄球联盟（NFL）历史悠久的职业球队，1933年成立于宾夕法尼亚州费城，隶属于NFC东区，主场为林肯金融球场。球队曾荣获2018年第52届超级碗冠军，以展翅雄鹰队徽、深绿+银灰+黑的经典队色为标志，拥有“Eagles Nation”庞大球迷群体，以坚韧球风与社区深度联结著称，是北美职业橄榄球领域极具影响力的球队之一。</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Ss Lazio: A renowned professional football club from Rome, Italy, founded in 1900. It competes in Serie A, plays at Stadio Olimpico Rome, and has won Serie A &amp; Coppa Italia titles. Its classic sky-blue &amp; white kits, long history, and strong fan culture make it a traditional Serie A powerhouse.</t>
+          <t>Philadelphia Eagles: NFL team founded 1933 in Philadelphia, NFC East, Lincoln Financial Field. Super Bowl LII champions (2018). Iconic eagle logo, green/silver/black colors. Eagles Nation, resilient style.</t>
         </is>
       </c>
     </row>
     <row r="197" ht="25.5" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Ssc Napoli</t>
+          <t>Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ssc-napoli</t>
+          <t>pittsburgh-steelers</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Ssc Napoli: 1926年成立的意大利甲级联赛传统豪门足球俱乐部，主场为迭戈·阿曼多·马拉多纳球场，以激情进攻风格闻名足坛，曾多次夺得意甲冠军、意大利杯冠军等荣誉，蓝白间条队服是其标志性视觉符号，拥有全球狂热的“tifosi”球迷群体，是意甲赛场极具影响力的劲旅之一。</t>
+          <t>Pittsburgh Steelers: 1933年成立于美国宾夕法尼亚州匹兹堡，是NFL（美国国家橄榄球联盟）历史最悠久的球队之一，以“钢铁之城”的强硬球风闻名，曾6次夺得超级碗冠军（NFL夺冠次数最多的球队之一），主场为Acrisure Stadium。球队承载匹兹堡工业底蕴，融合橄榄球热血精神，拥有全球庞大“钢铁军团”球迷群体，是美式橄榄球界极具传奇性与影响力的经典劲旅。</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Ssc Napoli: Founded in 1926, Serie A club with passionate attacking football, multiple championships, iconic blue-white stripes, and global tifosi fans.</t>
+          <t>Pittsburgh Steelers: Legendary NFL team founded 1933 in Pittsburgh, 6-time Super Bowl champions, known for Steel City tough style, home at Acrisure Stadium, with global Steelers Nation fan base.</t>
         </is>
       </c>
     </row>
     <row r="198" ht="25.5" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Starboy</t>
+          <t>Playboi Carti</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>starboy</t>
+          <t>playboi-carti</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Starboy（星男孩）由加拿大流行天王The Weeknd于2016 年随同名专辑推出，本人担任创意主导。主营T 恤、连帽衫、夹克、配饰等街头潮流单品，标志性几何黑豹 Logo、暗黑霓虹美学与 "XO" 标识极具辨识度。风格融合高街奢华与街头反叛，以黑、白、红为主色调，剪裁简约利落。采用重磅精梳棉、透气聚酯纤维等优质材质，舒适耐穿。风靡全球年轻群体，尤在欧美、亚洲及澳洲，是潮流穿搭与音乐文化收藏的热门选择。</t>
+          <t>Playboi Carti: 美国嘻哈音乐人及街头潮流符号，其同名周边潮牌以说唱文化为内核，推出卫衣、T恤、帽款等单品，设计融入专辑视觉、标志性歌词元素，采用棉质等舒适面料，风格街头不羁，契合年轻潮流群体审美，是连接音乐与时尚消费的热门跨境电商品牌。</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Starboy: Streetwear by The Weeknd. Iconic panther logo, XO, dark neon aesthetics. High-end streetwear blend in black/white/red. Premium fabrics for global trendsetters.</t>
+          <t>Playboi Carti: American hip-hop artist &amp; streetwear icon, eponymous merch brand rooted in hip-hop culture. Offers hoodies, tees, caps with album visuals, iconic lyrics, comfy cotton. Edgy street style resonates with young trendsetters, popular cross-border brand linking music &amp; fashion.</t>
         </is>
       </c>
     </row>
     <row r="199" ht="25.5" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Stone Island</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>stone-island</t>
+          <t>play</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Stone Island: 1982年由Massimo Osti创立于意大利的高端机能服饰品牌，以实验性面料研发与创新工艺为核心特色，标志性技术涵盖热粘合无缝工艺、成衣染色等，产品覆盖机能外套、卫衣、休闲裤等品类，完美融合户外实用功能与都市时尚风格，始终致力于将科技材质与美学设计深度结合，是全球机能风爱好者与高端时尚消费者的首选品牌。</t>
+          <t>PLAY COMME DES GARÇONS（CDG Play）2002 年诞生于日本东京，由设计师川久保玲（Rei Kawakubo）创立，标志性爱心 logo 由 Filip Pagowski 设计。主营爱心标 T 恤、针织衫、配饰，采用纯棉、羊毛面料，极简日系街头风格，面向全球年轻潮流群体，热销亚、欧、美市场，由品牌内部团队打造。</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Stone Island: Founded in Italy by Massimo Osti in 1982, a high-end functional apparel brand focusing on experimental fabric R&amp;D &amp; innovative techniques (heat-bonded seamless, garment dyeing). Products include functional jackets, hoodies, casual pants, blending outdoor utility with urban style, integrating tech materials &amp; aesthetic design—top choice for global functional fashion lovers &amp; high-end consumers.</t>
+          <t>Founded in 2002 in Tokyo, Japan by Rei Kawakubo, PLAY COMME DES GARÇONS features the iconic heart logo by Filip Pagowski. Core lines: logo tees, knits &amp; accessories. Crafted with cotton &amp; wool. Minimalist Japanese street style, popular among young trendsetters across Asia, Europe &amp; Americas, designed by in-house team.</t>
         </is>
       </c>
     </row>
     <row r="200" ht="25.5" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Stray</t>
+          <t>Polo</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>stray</t>
+          <t>polo</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Stray（Stray Rats）由Julian Consuegra于2010 年在美国迈阿密创立，后迁至纽约。创始人亲任设计师，主营印花 T 恤、卫衣、帽子及配饰，标志性 90 年代复古图案与朋克元素融合，致敬硬核音乐与街头文化。采用重磅精梳棉、透气聚酯纤维，手工丝网印刷工艺提升质感。风靡全球潮流圈，尤在欧美、日本及东南亚，是高街穿搭与收藏的热门选择，常与 New Balance 等品牌联名。</t>
+          <t>Polo: 源自美国的经典休闲品牌，以标志性马球logo为核心识别，产品线覆盖男女装、皮具、配饰等，主打简约经典风格，采用高品质棉、皮革等材质，兼顾舒适与耐用性，适配日常休闲、轻商务等多元场景，是全球消费者青睐的休闲时尚选择。</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Stray Rats: 2010 Miami streetwear by Julian Consuegra. 90s retro punk prints on tees, hoodies, hats. Honors hardcore music, street culture. Heavyweight cotton, polyester, hand-screen printing. Global trend, high-street, New Balance collabs.</t>
+          <t>Polo: Iconic US casual brand featuring the polo logo. Offers classic men's, women's apparel, leather goods &amp; accessories. Premium cotton &amp; leather for durable, versatile everyday &amp; smart-casual wear.</t>
         </is>
       </c>
     </row>
     <row r="201" ht="25.5" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Stussy</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>stussy</t>
+          <t>patagonia</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Stussy: 1980年由Shawn Stussy创立于美国加州的传奇街头服饰品牌，以标志性手写体LOGO、融合冲浪、滑板与嘻哈文化的设计内核著称，经典产品线覆盖T恤、卫衣、棒球帽等潮流单品，风格主打复古街头与西海岸随性美学，长期引领全球青年潮流文化，是街头时尚爱好者心中的“复古街头符号”级品牌。</t>
+          <t>Patagonia: 1973年创立于美国的专业户外装备品牌，以“构建更美好的地球”为核心使命，专注可持续环保户外服饰与装备设计，产品涵盖冲锋衣、羽绒服、抓绒衣、登山包等，采用再生聚酯纤维、有机棉等环保材质，坚持“1% for the Planet”计划（将1%营收投入环保公益），融合专业户外性能与生态责任，是全球户外爱好者与环保主义者信赖的可持续户外品牌典范。</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Stussy: Founded in California, USA in 1980 by Shawn Stussy, iconic streetwear with signature handwritten logo, fuses surfing, skateboarding &amp; hip-hop. Classics (tees, hoodies, baseball caps) feature retro street &amp; West Coast casual aesthetics, leading global youth fashion—an iconic retro street symbol for streetwear lovers.</t>
+          <t>Patagonia: US professional outdoor gear brand founded in 1973, core mission "Build the Better Earth". Specializes in sustainable apparel/gear (raincoats, down jackets, fleece, hiking packs) with recycled polyester, organic cotton. Committed to "1% for the Planet" (1% revenue to environmental causes). Blends professional performance with ecological responsibility, trusted by global outdoor enthusiasts &amp; environmentalists as a sustainable leader.</t>
         </is>
       </c>
     </row>
     <row r="202" ht="25.5" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Supreme</t>
+          <t>Prada</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>supreme</t>
+          <t>prada</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Supreme: 1994年创立于美国纽约曼哈顿的标志性街头潮流品牌，以经典红色Box Logo、高频跨界联名（涵盖Nike、Louis Vuitton等顶尖品牌）及限量发售机制闻名，产品覆盖卫衣、T恤、滑板、配件等品类，深度绑定青年文化与反主流精神，是全球潮流爱好者追求的「街头圣品」符号。</t>
+          <t>Prada: 1913年由马里奥·普拉达（Mario Prada）创立于意大利米兰，全球顶级奢侈品牌，以皮具、高级时装、配饰为核心品类，标志性尼龙材质与三角标LOGO是品牌辨识度符号，融合极简设计与精湛意大利工艺，诠释“低调奢华”的时尚内核，经典产品涵盖Saffiano皮革手袋、尼龙背包及成衣系列，是全球追求高品质时尚人群的首选品牌之一。</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Supreme: Iconic streetwear brand founded in Manhattan, NYC (1994), known for classic red Box Logo, frequent collabs (Nike, Louis Vuitton), limited releases, products (hoodies, tees, skateboards, accessories), tied to youth culture &amp; anti-mainstream spirit—global streetwear icon for enthusiasts.</t>
+          <t>Prada: Founded in Milan, Italy in 1913 by Mario Prada, a top global luxury brand with core categories of leather goods, high fashion, and accessories. Iconic nylon material &amp; triangular logo, minimalist design + exquisite Italian craftsmanship embody "understated luxury". Classic products: Saffiano bags, nylon backpacks, ready-to-wear—preferred by global high-quality fashion seekers.</t>
         </is>
       </c>
     </row>
     <row r="203" ht="25.5" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Saint Laurent</t>
+          <t>Project Capri</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Saint Laurent</t>
+          <t>project-capri</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Saint Laurent: 1961年由伊夫·圣罗兰（Yves Saint Laurent）创立的法国奢侈品牌，以先锋叛逆的法式酷感风格横扫时尚界，核心覆盖高级时装、成衣、皮具（如Niki包、LouLou包）、鞋履、美妆及香水等品类。品牌标志性元素包括YSL字母标识、Monogram图案，以及打破性别边界的经典吸烟装（Le Smoking）——首次将男性西装剪裁融入女装，重塑时尚规则。从秀场级设计到日常奢华单品，Saint Laurent始终融合优雅与街头感，是全球潮流爱好者追崇的“酷感奢华”代表，持续传递“打破传统、定义自我”的品牌精神。</t>
+          <t>Project Capri 由Caprice Brown于2022 年在拉斯维加斯创立，当时仅 16 岁的他打造出七位数营收潮牌。创始人亲任设计师，主营镶钻牛仔裤、多口袋牛仔短裤、丹宁夹克与工装裤。风格融合复古丹宁、军事工装与大胆印花，街头感十足。采用重磅丹宁、优质帆布与真皮等耐用材质，风靡美国、欧洲及全球潮流圈，深受 Z 世代追捧，是年轻街头品牌标杆。</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Saint Laurent: French luxury brand founded 1961 by Yves Saint Laurent, famed for avant-garde rebellious French cool. Covers haute couture, ready-to-wear, leather goods (Niki, LouLou bags), footwear, beauty, fragrances. Iconic YSL monogram, genderless Le Smoking tuxedo (redefined fashion with men’s tailoring in women’s wear). Blends elegance &amp; streetwear, a “cool luxury” icon conveying “break tradition, define self” spirit.</t>
+          <t>Project Capri: Founded by Caprice Brown in Las Vegas (2022, 16yo), 7-figure streetwear. Founder-led design: rhinestone jeans, multi-pocket denim shorts, jackets, work pants. Blends vintage denim, military workwear, bold prints (streetwear vibe). Uses heavy denim, premium canvas, genuine leather. Popular in US/Europe/global, Gen Z-favorite young street brand benchmark.</t>
         </is>
       </c>
     </row>
     <row r="204" ht="25.5" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>So Paulo</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>so-paulo</t>
+          <t>puma</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>São Paulo（圣保罗足球俱乐部）1930 年由 Firmiano de Morais Pinto Filho 等创立，德国设计师 Walter Ostrich 设计队徽，主营官方球衣、训练服、休闲服饰及配饰，由 New Balance 等品牌操刀设计，标志性白底色配红黑横条纹，象征圣保罗市旗与俱乐部 “信仰、希望、慈善” 理念。采用透气聚酯纤维、AEROREADY 速干面料，舒适耐穿，风靡巴西及全球足球圈，是南美足坛顶级豪门标志性服饰。</t>
+          <t>Puma: 1948年由鲁道夫·达斯勒创立的德国专业运动品牌，以“Forever Faster”为核心精神，专注跑步、足球、篮球等专业运动装备与潮流运动服饰研发，经典产品包括Suede板鞋、Clyde篮球鞋及Ultra足球鞋系列，采用优质皮革、透气科技面料等材质，融合运动性能与街头时尚设计，满足全球运动员训练比赛及潮流爱好者日常穿搭需求，是兼具专业度与潮流感的知名运动品牌。</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>São Paulo: Founded 1930, São Paulo FC iconic white/red/black stripes symbolize city flag &amp; "faith, hope, charity". New Balance kits/apparel with AEROREADY fabric. Top South American football club.</t>
+          <t>Puma: German sportswear brand founded 1948, embodying "Forever Faster" in running, football, basketball. Features Suede, Clyde, Ultra series, blending performance tech with street-style fashion.</t>
         </is>
       </c>
     </row>
     <row r="205" ht="25.5" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>The North Face</t>
+          <t>Pigeon Run</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>the-north-face</t>
+          <t>pigeon-run</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>The North Face: 1966年创立于美国旧金山，全球专业户外装备领导品牌，专注研发高性能登山、徒步、滑雪等场景装备，经典产品涵盖Summit系列专业冲锋衣、MCMURDO保暖羽绒服、VECTIV轻量化登山鞋等，核心技术搭载Gore-Tex®防水透气膜、Responsible Down Standard认证鹅绒填充及TNF Apex™耐磨面料，兼顾极端环境适应性与日常机能需求，为专业户外爱好者与城市轻户外人群提供耐用、环保的装备选择，风格融合硬核功能性与经典户外美学。</t>
+          <t>Pigeon Run 是国内近年来崛起的一支暗黑高街力量，深受欧美地下摇滚、赛博朋克文化影响。其设计风格以夸张的金属字体、惊悚 / 亚文化人像印花和重度水洗做旧工艺为特征，在国内年轻潮流群体中拥有较高辨识度。</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>The North Face: Founded in San Francisco, USA (1966), global leading pro outdoor gear brand. Specializes in high-performance mountaineering, hiking, skiing gear—signature products: Summit Series hardshells, MCMURDO down jackets, VECTIV hiking shoes. Features Gore-Tex® membranes, RDS-certified down, TNF Apex™ fabrics. Balances extreme adaptability &amp; daily function for pros/urban light outdoor users, blending hardcore functionality with classic outdoor aesthetics.</t>
+          <t>Pigeon Runigeon Run: Chinese dark high-street brand inspired by underground rock &amp; cyberpunk, featuring bold metal fonts, subculture prints, and heavy distressing.</t>
         </is>
       </c>
     </row>
     <row r="206" ht="25.5" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Thug Club</t>
+          <t>Ralph Lauren</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>thug-club</t>
+          <t>ralph-lauren</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Thug Club 由Thug Min与Jiyool Kwon于2018 年在韩国首尔梨泰院创立。主打宽松 T 恤、美式夹克、做旧牛仔及铆钉配饰，融合嘻哈、机车文化与反叛街头风。采用高品质棉料与耐用牛仔，质感硬朗。风靡全球潮流圈，获 A$AP Rocky、SZA 等明星追捧，是韩系街头潮流代表品牌。</t>
+          <t>Ralph Lauren: 1967年由拉尔夫·劳伦（Ralph Lauren）创立的美国高端时尚品牌，以"美式经典生活方式"为核心定位，覆盖男装、女装、童装、配饰（皮具、香水、腕表）及家居全品类，标志性元素包括马球 pony 标志、牛津纺衬衫、粗花呢西装与经典格纹，产品融合复古优雅与休闲奢华感，是全球美式时尚与品质生活的代表品牌，旗下Polo Ralph Lauren系列更成为基础款高端化的经典范例。</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Thug Club: Seoul-based streetwear since 2018. Oversized tees, vintage denim, &amp; rebel biker style. Premium cotton &amp; hard-wearing fabrics. Worn by A$AP Rocky, SZA.</t>
+          <t>Ralph Lauren: American luxury fashion brand founded by Ralph Lauren in 1967, focused on the "American classic lifestyle", covering men’s, women’s, kids’ apparel, accessories (leather goods, perfume, watches) &amp; homeware. Iconic elements: Polo pony logo, Oxford shirts, tweed suits, classic plaids. Blending vintage elegance &amp; casual luxury, it’s a global representative of American fashion &amp; quality life. Its Polo Ralph Lauren line is a classic example of elevated basics.</t>
         </is>
       </c>
     </row>
     <row r="207" ht="25.5" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Tom Ford</t>
+          <t>Rb Leipzig</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>tom-ford</t>
+          <t>rb-leipzig</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Tom Ford: 2005年由美国设计师Tom Ford创立的高端奢侈品牌，以性感奢华、现代先锋的风格著称，产品线覆盖美妆（经典Lip Color口红、Black Orchid香水）、高级成衣、皮具、眼镜及腕表等领域，甄选丝绒、小羊皮、稀有香原料等顶级材质，工艺精湛，精准契合全球追求品质与独特个性的高端消费者需求，是奢华时尚与创新设计的标志性代表。</t>
+          <t>RB Leipzig: 德国职业足球俱乐部，2009年成立于萨克森州莱比锡，隶属于红牛集团，主场为可容纳超4.2万名观众的莱比锡红牛竞技场，系德甲联赛劲旅。球队以“青春风暴”“高压进攻”战术风格著称，近年稳居德甲积分榜前列，多次晋级欧冠、欧联杯等欧洲顶级赛事，是德国足坛近年快速崛起的代表性球队。</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Tom Ford: Founded by American designer Tom Ford in 2005, a high-end luxury brand celebrated for sexy luxury &amp; modern avant-garde style. Product lines include beauty (iconic Lip Color lipstick, Black Orchid perfume), ready-to-wear, leather goods, eyewear &amp; watches. Uses premium materials (velvet, lambskin, rare fragrance ingredients) with exquisite craftsmanship, catering to global high-end consumers seeking quality &amp; unique personality. An iconic symbol of luxury fashion &amp; innovative design.</t>
+          <t>RB Leipzig: Top Bundesliga club founded 2009. Red Bull-owned, home Red Bull Arena 42,000+. Youth storm &amp; high-pressure attack style. Regular in UEFA Champions League/Europa League, symbol of rapid rise.</t>
         </is>
       </c>
     </row>
     <row r="208" ht="25.5" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Tommy Hilfiger</t>
+          <t>Readymade</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>tommy-hilfiger</t>
+          <t>readymade</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Tommy Hilfiger: 1985年由同名设计师Tommy Hilfiger创立的美国经典休闲时尚品牌，以标志性红白蓝三色logo、预ppy（预科生）风格及高品质棉质面料为核心特色，产品覆盖男装、女装、童装、配饰与香水，融合美式复古底蕴与现代简约设计，打造日常百搭且具高端休闲感的服饰单品，是全球追求经典时尚、舒适质感人群的首选品牌之一。</t>
+          <t>eadymade 由日本设计师细川雄太 (Yuta Hosokawa)于2013 年在大阪创立，主打军事重制服饰与配饰。创始人亲任设计，以和平反战为核心理念，将二战古军布、帐篷帆布与复古军用包袋手工改造成包袋、外套、卫衣等单品。风格融合美式复古、军事工装与解构主义，每件均带原始编号，独一无二。风靡全球潮流圈，受 Virgil Abloh、Travis Scott 等明星追捧，是 Remake 领域标杆。</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Tommy Hilfiger: Founded in 1985 by its eponymous designer, this iconic American casual fashion brand boasts signature red-white-blue logo, preppy style, and premium cotton fabrics. It offers apparel (men, women, kids), accessories, and fragrances, blending American retro roots with modern minimalist design for versatile high-end casual pieces—top choice for classic fashion &amp; comfort seekers.</t>
+          <t>Readymade, founded 2013 in Osaka by Yuta Hosokawa, specializes in military remake apparel/accessories. Core peace anti-war philosophy, handmade from WWII vintage military fabrics, tents &amp; bags. Blends American vintage, military workwear &amp; deconstruction. Unique numbered, global trend icon, Remake benchmark.</t>
         </is>
       </c>
     </row>
     <row r="209" ht="25.5" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>tottenham-hotspur</t>
+          <t>real-madrid</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur: 1882年成立于伦敦的英超足球俱乐部，主场为托特纳姆热刺球场，以进攻足球与青训体系闻名。经典白色球衣与公鸡标志传承百年，现代风格融合激烈比赛与卓越球员培养，吸引全球球迷关注。</t>
+          <t>Real Madrid: 1902年成立于西班牙马德里的顶级职业足球俱乐部，昵称“银河战舰”，是历史上夺得欧洲冠军联赛冠军次数最多（14次）的球队，亦坐拥35次西班牙甲级联赛冠军等荣誉；主场为标志性的伯纳乌球场（Estadio Santiago Bernabéu），以经典白色球衣、带皇冠与“RM”标识的队徽为核心视觉符号；全球拥有超4亿球迷，商业价值常年位居足球俱乐部前列，传承“永不言弃”的竞技精神，代表西班牙足球的巅峰水准与全球影响力。</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur: London Premier League club since 1882, attacking football and youth academy, iconic white kit with cockerel emblem, modern play and player development, global fans.</t>
+          <t>Real Madrid: Elite Spanish football club founded 1902, "Galacticos". Record 14 UEFA Champions League &amp; 35 La Liga titles. Iconic Santiago Bernabéu Stadium, white kits, 400M+ fans, "Never give up" spirit.</t>
         </is>
       </c>
     </row>
     <row r="210" ht="25.5" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Trapstar</t>
+          <t>Revenge</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>trapstar</t>
+          <t>revenge</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Trapstar: 2005年由Mikey Trapstar、Lee Trapstar与Will Trapstar创立于英国伦敦，是扎根街头文化与trap音乐精神的潮流品牌。以标志性星型LOGO、反光材质及军事风剪裁为核心设计符号，产品覆盖卫衣、夹克、配饰等街头单品，曾与Nike、Puma等品牌推出联名系列，深受追求个性表达、热爱街头亚文化与音乐的年轻群体喜爱。</t>
+          <t>Revenge 由Garette 与 Han于2016 年在美国洛杉矶创立，是匿名设计师 Garette 主导的街头潮牌。主营拱门 Logo 帽衫、涂鸦 T 恤、荆棘牛仔与素食皮夹克等，风格暗黑叛逆，融合朋克美学与哥特式手写字体，标志性蜘蛛网与火焰图案极具辨识度。采用重磅纯棉、优质牛仔与环保素食皮等耐用材质，因与 XXXTentacion 合作爆红，风靡全球 Z 世代潮流圈，是地下街头文化标杆。</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Trapstar: Founded in London, UK (2005) by Mikey, Lee &amp; Will Trapstar, a streetwear brand rooted in street culture &amp; trap music spirit. Core design: signature star logo, reflective materials, military cuts. Offers hoodies, jackets, accessories. Collaborated with Nike, Puma. Loved by self-expressive young fans of street subculture &amp; music.</t>
+          <t>Revenge: Streetwear brand founded by Garette &amp; Han in LA 2016, led by anonymous designer Garette. Core products: arched logo hoodies, graffiti tees, thorn denim, vegan leather jackets. Dark rebellious style fuses punk aesthetics with gothic handwritten fonts; iconic spider web &amp; flame patterns. Uses heavy cotton, premium denim, eco vegan leather. Viral via XXXTentacion collab, beloved by global Gen Z—underground street culture icon.</t>
         </is>
       </c>
     </row>
     <row r="211" ht="25.5" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Travis Scott</t>
+          <t>Represent</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>travis-scott</t>
+          <t>represent</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Travis Scott: 美国知名说唱歌手、音乐制作人兼时尚设计师，以其独特音乐风格和跨界联名系列在全球潮流界备受瞩目。品牌产品涵盖联名鞋款、街头服饰及配饰，采用创新设计、优质材质和标志性元素，融合嘻哈文化与高端时尚，风格前卫。经典合作如Travis Scott x Nike Air Jordan系列，深受年轻消费者和收藏家喜爱，推动全球潮流文化发展。</t>
+          <t>Represent 由George Heaton与Mike Heaton兄弟于2011 年在英国大曼彻斯特创立，始于大学 T 恤印花项目。创始人 George 主理设计，主营帽衫、T 恤、夹克、运动裤与鞋履，风格融合奢华街头风与极简主义，以480GSM 重磅针织棉、莱赛尔斜纹布等高端面料打造精品基础款，注重工艺细节。风靡欧美、日韩及全球潮流圈，受明星与时尚达人追捧，是英国奢华街头品牌标杆。</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Travis Scott: Renowned rapper and designer. Iconic Travis Scott x Nike Air Jordan collaborations. Streetwear, sneakers, and accessories. Merging hip-hop with high-fashion innovation.</t>
+          <t>Represent: Founded by George &amp; Mike Heaton in Greater Manchester, UK (2011) from a university T-shirt printing project. George leads design; offers hoodies, T-shirts, jackets, sweatpants, footwear. Blends luxury streetwear with minimalism, using 480GSM heavy knit cotton, Lyocell twill for premium basics, emphasizing craftsmanship. Popular in EU/US/Japan/Korea, favored by celebrities/influencers—UK luxury streetwear benchmark.</t>
         </is>
       </c>
     </row>
     <row r="212" ht="25.5" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>True Religion</t>
+          <t>Rhude</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>true-religion</t>
+          <t>rhude</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>True Religion: 2002年创立于美国的高端牛仔品牌，以标志性马蹄形（Horseshoe）缝线设计、顶级牛仔布材质及精湛水洗工艺闻名，主打男士/女士牛仔裤、牛仔外套及休闲服饰，融合美式复古与街头潮流风格，是追求个性与高品质牛仔单品的消费者首选品牌。</t>
+          <t>Rhude: 2015年由Rhuigi Villaseñor创立于美国的高端街头服饰品牌，以“街头文化与高级时尚融合”为核心定位，标志性设计涵盖经典Logo、复古运动元素与皮革、麂皮等高端材质的结合，产品包括卫衣、夹克、牛仔裤及配饰，曾与Nike、Puma等推出联名系列，主打“街头奢华风”，精准契合追求潮流质感与独特风格的年轻群体需求。</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>True Religion: Founded in the US in 2002, a high-end denim brand renowned for iconic Horseshoe stitching, premium denim, and exquisite wash techniques. Offers men’s/women’s jeans, denim jackets, casual apparel, blending American retro with streetwear—top choice for consumers seeking individuality &amp; high-quality denim.</t>
+          <t>Rhude: Founded by Rhuigi Villaseñor in the US in 2015, a high-end streetwear brand blending street culture with luxury fashion. Signature designs feature classic logos, retro sporty elements, premium leather/suede. Products: hoodies, jackets, jeans, accessories. Collaborated with Nike, Puma. Focuses on "street luxury" for young people pursuing trendy quality &amp; unique styles.</t>
         </is>
       </c>
     </row>
     <row r="213" ht="25.5" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Umbro</t>
+          <t>Rick Owens</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>umbro</t>
+          <t>rick-owens</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Umbro: 1924年创立于英国的专业足球运动装备品牌，以标志性双钻石LOGO著称，深耕足球领域近百年，曾长期为英格兰国家队等顶级球队提供球衣装备。产品覆盖专业足球衣、训练服、足球鞋及配件，融合英伦经典设计与运动科技，专注为球员与球迷打造兼具性能与复古质感的足球装备，传承纯粹足球精神。</t>
+          <t>Rick Owens: 1994年由同名设计师创立于美国洛杉矶的先锋暗黑时尚品牌，以解构主义、工业感轮廓与垂坠美学为核心风格，标志性产品包括Geobasket运动鞋、机车皮革夹克及垂坠剪裁成衣，常用皮革、帆布等质感材质，诠释反主流的个性表达，是全球先锋时尚爱好者与潮流人士追捧的暗黑先锋代表品牌。</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Umbro: Founded in 1924 in England, iconic double diamond logo. Professional football gear, kits, footwear &amp; accessories. Merges classic British design with sport tech for players &amp; fans, honoring pure football heritage.</t>
+          <t>Rick Owens: Founded in Los Angeles, USA in 1994, this avant-garde dark fashion brand focuses on deconstruction, industrial silhouettes, and drape aesthetics. Signature items: Geobasket sneakers, biker leather jackets, draped ready-to-wear. Uses leather/canvas, embodies anti-mainstream self-expression—iconic among global avant-garde fashion lovers.</t>
         </is>
       </c>
     </row>
     <row r="214" ht="25.5" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>UGG</t>
-        </is>
-      </c>
-      <c r="B214"/>
+          <t xml:space="preserve">RivingtonI roi Rebis </t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivingtonI-roi-rebis </t>
+        </is>
+      </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>UGG: 源自澳大利亚的经典保暖鞋服品牌，以标志性羊皮毛一体雪地靴闻名，核心产品涵盖Classic Short经典短靴、Cozy Slide拖鞋及羊毛外套等，采用优质美利奴羊毛与天然皮革材质，主打“温暖不厚重、舒适又时尚”的设计理念，满足冬季保暖及日常休闲穿搭需求，是全球注重质感与舒适度的消费者首选的保暖时尚品牌。</t>
+          <t>RIVINGTON roi Rebis 由前摇滚歌手 Rivington Starchild 于 2019 年创立，品牌设计融合了炼金术哲学、纽约 / 洛杉矶街头文化与摇滚精神，以做旧工艺、夸张印花和先锋廓形著称，是近年高街圈的热门小众潮牌。</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>UGGUGG: Australian brand iconic for sheepskin boots, Classic Short, Cozy Slide, and wool coats. Made with Merino wool and leather for warm, comfortable, stylish winter and casual wear.</t>
+          <t>RivingtonI roi Rebis RIVINGTON roi Rebis: Founded in 2019 by ex-rockstar Rivington Starchild. Fuses alchemy, NYC/LA street culture, and rock spirit with distressed finishes, bold prints, and avant-garde silhouettes. A hot niche high-street brand.</t>
         </is>
       </c>
     </row>
     <row r="215" ht="25.5" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Roberto Cavalli</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>roberto-cavalli</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Valencia: （因未提供该品牌的具体中文描述信息，无法生成符合要求的SEO优化品牌描述。）</t>
+          <t>Roberto Cavalli: 1960年代由意大利设计师Roberto Cavalli创立的奢侈品牌，以「狂野奢华」风格为核心标签，标志性动物纹、大胆印花与精湛手工工艺贯穿高级时装、皮具、香水、配饰等全品类，诠释不羁个性与顶级奢华的融合，是全球追求独特时尚品味、渴望彰显自我风格的高端消费者首选品牌。</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Valencia: Due to the lack of specific Chinese description of the brand, we cannot generate a compliant SEO-optimized brand description.</t>
+          <t>Roberto Cavalli: Italian luxury brand founded by Roberto Cavalli in the 1960s, centered on "wild luxury"—iconic animal prints, bold patterns, exquisite craftsmanship across ready-to-wear, leather goods, fragrances, accessories. Blends unruly individuality with top-tier luxury, favored by global high-end consumers pursuing unique style.</t>
         </is>
       </c>
     </row>
     <row r="216" ht="25.5" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Valentino</t>
+          <t>Rossoneri</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>valentino</t>
+          <t>rossoneri</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Valentino: 1960年由Valentino Garavani创立的意大利顶级奢侈品牌，以高级时装、皮具、鞋履、配饰及美妆为核心产品线，标志性元素包括VLogo标识、Rockstud铆钉系列与经典Valentino Red（华伦天奴红），风格融合奢华、浪漫与经典，凭借精湛工艺与独特设计，成为全球追求高端时尚品味人群的首选品牌之一。</t>
+          <t>Rossoneri 是 AC 米兰官方生活方式品牌，源于1899 年英国创始人Herbert Kilpin创立的红黑军团。由俱乐部设计团队操刀，主营球衣、帽衫、T 恤、配饰等，风格融合意式足球文化与街头潮流，标志性红黑配色与魔鬼队徽极具辨识度。采用100% 精梳棉、聚酯纤维运动面料等优质材质，透气舒适、耐穿易洗。风靡全球足球与潮流圈，尤其在欧洲、南美及亚洲，是球迷彰显信仰与时尚态度的首选，诠释 “Milanismo” 精神。</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Valentino: Founded 1960 by Valentino Garavani, Italian luxury house for haute couture, leather goods, accessories. Iconic VLogo, Rockstuds, Valentino Red. Fusion of luxury, romantic, timeless Italian craftsmanship.</t>
+          <t>Rossoneri AC Milan’s official lifestyle brand, founded by Herbert Kilpin in 1899 (the Rossoneri). Designed by the club’s team, offers jerseys, hoodies, tees, accessories. Blends Italian football culture with streetwear; iconic red-black &amp; devil emblem stand out. Uses premium 100% combed cotton, polyester sport fabrics—breathable, comfy, durable. Popular globally (Europe, S. America, Asia); fans’ top choice for faith &amp; style, embodying “Milanismo.”</t>
         </is>
       </c>
     </row>
     <row r="217" ht="25.5" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Saint Michael</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>vans</t>
+          <t>saint-michael</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Vans: 1966年由Paul Van Doren等创立于美国加州，全球街头潮流与滑板文化的标志性品牌，以“Off The Wall”的自由叛逆精神为内核。经典产品涵盖Authentic、Old Skool、Sk8-Hi等帆布/麂皮滑板鞋款，标志性棋盘格图案、侧边条纹设计深入人心，融合耐用工艺与青年创意表达，成为滑板运动、街头时尚及亚文化群体的核心选择。</t>
+          <t>Saint Michael由日本设计师细川雄太 (Yuta Hosokawa)与美国艺术家Cali Thornhill DeWitt于2020 年创立，细川负责服装制作，Cali 主理平面设计。主营重磅卫衣、印花 T 恤、水洗牛仔与棒球夹克，风格融合日式复古工艺、美式街头文化与宗教符号，标志性做旧水洗与开裂印花极具辨识度。采用420g 精梳棉、重磅牛仔布等优质材质，手工做旧处理每件独一无二。风靡日美欧潮流圈，受明星与潮流博主追捧，是高端复古街头品牌标杆。</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Vans: Iconic skate/streetwear brand since 1966, "Off The Wall" spirit. Durable canvas/suede shoes: Authentic, Old Skool, Sk8-Hi. Signature checkerboard &amp; side stripe for youth culture.</t>
+          <t>Saint Michael: Co-founded by Yuta Hosokawa &amp; Cali Thornhill DeWitt (2020). Hosokawa crafts, DeWitt designs graphics. Heavyweight hoodies, tees, denim, jackets. Fusing Japanese vintage craft, American street, religious symbols. Iconic distressed washes, cracked prints; 420g combed cotton, premium denim. Unique hand-distressing. Trendy Japan/US/Europe, celebrity-loved premium retro streetwear.</t>
         </is>
       </c>
     </row>
     <row r="218" ht="25.5" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Vasco Da Gama</t>
+          <t>Salvatore Ferragamo</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>vasco-da-gama</t>
+          <t>salvatore-ferragamo</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Vasco Da Gama: （由于未提供该品牌的中文描述内容，无法生成符合要求的SEO优化品牌描述。）</t>
+          <t>Salvatore Ferragamo由萨尔瓦多・菲拉格慕于1927 年在意大利佛罗伦萨创立，被誉为 "明星鞋匠"。现任创意总监Maximilian Davis，主营鞋履、皮具、成衣、配饰与香水，标志性 Gancini logo 与 Vara 蝴蝶结鞋款闻名。风格融合意式永恒优雅与现代设计，坚持传统手工与创新结构，采用托斯卡纳小牛皮、鳄鱼皮等顶级材质，每双鞋经超 300 道工序。风靡欧美亚，美日中为核心市场，是意大利奢华时尚标杆。</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Vasco Da Gama: (Due to the lack of Chinese description of the brand, we cannot generate a compliant SEO-optimized brand description.)</t>
+          <t>Salvatore Ferragamo: Luxury Italian shoes &amp; leather goods since 1927, "shoemaker to the stars." Iconic Gancini logo, Vara bow. Handcrafted with premium materials, 300+ steps. Global fashion benchmark.</t>
         </is>
       </c>
     </row>
     <row r="219" ht="25.5" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Versace</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>versace</t>
+          <t>sampdoria</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Versace: 1978年由詹尼·范思哲（Gianni Versace）创立于意大利米兰的奢华时尚品牌，以标志性美杜莎头像、巴洛克印花及大胆撞色为核心视觉符号，涵盖高级时装、成衣、皮具、鞋履、配饰、香水与家居系列，风格融合意大利复古奢华与性感张扬，凭借精湛工艺与先锋设计成为全球红毯、名流及时尚爱好者追捧的高端时尚象征，诠释“致命诱惑”的品牌精神。</t>
+          <t>Sampdoria: 意大利热那亚的职业足球俱乐部，1946年由桑普达雷内塞和安德雷亚·多利亚两支球队合并成立，主场为路易吉·费拉里斯球场，以标志性蓝白条纹球衣著称，昵称“Blucerchiati（蓝环队）”。队史斩获1次意甲冠军（1990-91赛季）、4次意大利杯冠军及1次欧洲优胜者杯亚军，是意大利足坛兼具历史底蕴与地域辨识度的传统劲旅。</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Versace: Italian luxury fashion since 1978, iconic Medusa &amp; Baroque prints, bold colors. Haute couture, accessories, perfumes. Style: retro luxury meets sexy flamboyance. High-end for red carpets, celebrities. Spirit: fatal attraction.</t>
+          <t>Sampdoria: Genoa Italian football club founded 1946. Blue-white stripes, nicknamed Blucerchiati. 1 Serie A, 4 Coppa Italia, 1 UEFA Cup Winners' Cup runner-up. Traditional powerhouse.</t>
         </is>
       </c>
     </row>
     <row r="220" ht="25.5" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Vetements</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>vetements</t>
+          <t>santos</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Vetements: 2014年由Demna Gvasalia与Guram Gvasalia创立于法国的高端街头服饰品牌，以解构主义设计、oversize版型及标志性标语印花为核心特色，融合街头文化与高级时装美学，推出卫衣、外套、配饰等系列单品，曾与Reebok、Juicy Couture等品牌联名，深受追求个性潮流与先锋风格的时尚爱好者喜爱。</t>
+          <t>Santos，巴西桑托斯足球俱乐部生活方式品牌，1912 年由鲁道夫・阿劳霍创立，主营球衣、帽衫、T 恤等，标志性白色底色配黑红细节，采用透气聚酯纤维、精梳棉，风靡巴西及全球足球圈。</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Vetements: French high-end streetwear brand founded 2014, known for deconstructivist designs, oversize fits, slogan prints. Merges street culture with high fashion. Offers hoodies, jackets, accessories. Collaborations with Reebok, Juicy Couture. Loved by avant-garde fashion enthusiasts.</t>
+          <t>SantosSantos: Brazilian football lifestyle brand founded 1912 by Rudolf Araújo, specializing in jerseys, hoodies, tees. Iconic white with black-red details, breathable polyester &amp; combed cotton, popular in Brazil &amp; global football circles.</t>
         </is>
       </c>
     </row>
     <row r="221" ht="25.5" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Vicinity</t>
+          <t>Score Draw</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>vicinity</t>
+          <t>score-draw</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Vicinity 是源自澳大利亚的轻奢休闲街头品牌，由本土设计师团队于2015 年创立。主营都市休闲卫衣、简约衬衫、百搭裤装及轻户外穿搭，坚持本土原创设计。风格主打极简通勤、轻户外休闲，利落百搭适配日常。采用优质纯棉、透气梭织、环保再生面料，舒适亲肤。风靡澳新、欧美及亚太地区，是都市轻休闲穿搭的热门选择。</t>
+          <t>Score Draw 由Michael Roy Phillips于2002 年 9 月在英国创立，是全球领先官方复古足球服饰品牌。主营官方授权复古球衣、训练服及周边，与 40 余家俱乐部和足协合作，复刻 50 余年超 600 款经典款式。设计团队经精密考证，忠于原版细节，风格为复古经典、怀旧情怀。采用正宗聚酯纤维，透气舒适，还原当年穿着体验。风靡欧洲、北美、澳洲足球圈，深受全球球迷与复古潮流爱好者追捧，是足球文化收藏首选。</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Vicinity: Australian luxury casual streetwear since 2015. Local designers craft urban essentials, minimalist commute to light outdoor styles. Premium cotton, breathable woven, eco fabrics. Popular in Australia, NZ, US, EU, Asia-Pacific.</t>
+          <t>Score Draw: Leading official retro football apparel since 2002 UK. Licensed vintage jerseys, training wear with 40+ clubs, 600+ classic styles. Authentic polyester comfort. Popular globally, top for football culture.</t>
         </is>
       </c>
     </row>
     <row r="222" ht="25.5" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>(Vivi)VivienneWestwood</t>
+          <t>Sennheiser</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>VivienneWestwood</t>
+          <t>sennheiser</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>VivienneWestwood: 1971年由英国设计师Vivienne Westwood创立，时尚品牌以朋克和反叛风格著称，产品系列包括服装、配饰、珠宝及鞋履，经典元素有土星标志、格子图案和夸张剪裁，采用皮革、面料等多样材质，工艺创新独特，风格前卫叛逆，融合时尚与艺术，深受全球潮流人士喜爱。</t>
+          <t>森海塞尔（Sennheiser）是德国百年音频品牌，以专业级 HiFi 音质和监听设备闻名。</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Vivienne Westwood: Punk rebellious fashion brand since 1971, offering clothing, accessories, jewelry, footwear with Saturn logo, tartan patterns, exaggerated cuts. Uses leather, fabrics, innovative avant-garde style fusing fashion and art, loved globally.</t>
+          <t>Sennheiser: German audio pioneer for over a century, renowned for professional HiFi sound and premium monitoring equipment.</t>
         </is>
       </c>
     </row>
     <row r="223" ht="25.5" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Vlone</t>
+          <t>Sicko</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>vlone</t>
+          <t>sicko</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Vlone: 由A$AP Rocky与A$AP Bari共同创立的美国街头潮流品牌，以标志性V字Logo、“Live Vlone, Die Vlone”核心标语为识别，融合嘻哈文化与叛逆精神，主打T恤、卫衣、帽款及配件等单品，凭借街头感设计与社群共鸣，成为全球潮流爱好者追捧的街头文化符号。</t>
+          <t>Sicko（全称 Sicko Born From Pain）由美国潮流先锋Ian Connor于2018 年创立，本人担任设计师，洛杉矶限量生产。主营重磅卫衣、印花 T 恤、限定配饰，标志性 “Born From Pain” 标语与婴儿头像 Logo 源自 Björk 专辑封面，融合街头文化与个人艺术表达。采用400g + 精梳棉、透气聚酯纤维等优质面料，手工印花工艺提升质感。风靡全球潮流圈，尤受欧美亚千禧一代追捧，是高街街头与限量收藏的热门选择。</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Vlone: Streetwear brand by A$AP Rocky &amp; Bari. Iconic V logo, "Live Vlone, Die Vlone" mantra. Hip-hop infused, rebellious essentials – tees, hoodies, caps. A global street culture symbol.</t>
+          <t>Sicko Born From Pain: Ian Connor's 2018 LA limited streetwear. Iconic 'Born From Pain' logo, heavy hoodies, tees, accessories. 400g+ combed cotton, manual print. Global millennial favorite for high-street fashion.</t>
         </is>
       </c>
     </row>
     <row r="224" ht="25.5" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Yeezy</t>
+          <t>Snapdragon</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>yeezy</t>
+          <t>snapdragon</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Yeezy: 由美国创作歌手坎耶·维斯特（Kanye West）创立的全球街头潮流标杆品牌，以“椰子鞋”系列奠定潮流地位，核心鞋款融合Boost缓震科技、大地色系极简设计与街头基因，标志性产品如Yeezy Boost 350 V2、Yeezy 500等成为sneaker文化符号，主打“舒适与先锋时尚兼具”的理念，覆盖鞋履、服饰等品类，是街头美学与高端运动属性结合的代表，深受潮流爱好者与收藏家追捧。</t>
+          <t>Snapdragon: 高通（Qualcomm）旗下全球知名移动处理器品牌，专注为智能手机、平板、笔记本及IoT智能设备提供高性能低功耗芯片解决方案，覆盖旗舰（8系列）、中高端（7系列）至主流（6系列）全产品线，核心优势包含5G高速连接、AI智能加速、Adreno图形渲染及Hexagon音频/计算技术，是三星、小米、OPPO等众多品牌旗舰机型的核心处理器选择，持续推动智能设备的体验升级与技术创新。</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Yeezy: Global streetwear icon founded by U.S. artist Kanye West. Core styles (Yeezy Boost 350 V2, 500) feature Boost cushioning, earth-tone minimal design &amp; street DNA—sneaker culture symbols. Blends street aesthetics with high-end sport, offering footwear/apparel for comfort &amp; avant-garde fashion, sought after by streetwear fans &amp; collectors.</t>
+          <t>Snapdragon: Qualcomm's flagship mobile processor for smartphones, tablets, &amp; IoT. Features 5G, AI, Adreno GPU, Hexagon tech. Powers top brands like Samsung, Xiaomi, OPPO.</t>
         </is>
       </c>
     </row>
     <row r="225" ht="25.5" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Yora</t>
+          <t>Sp5der</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>yora</t>
+          <t>sp5der</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Yora 是德国波恩可持续街头服饰品牌，由本土设计师团队于2018 年创立。主营重磅 T 恤、宽松卫衣、立体剪裁裤装及环保配饰，坚持原创设计与青年艺术家合作。风格主打极简街头、可持续时尚，标志性环保认证标识醒目。采用GOTS 认证有机棉、OEKO-TEX 100 环保面料，植物基油墨印花，全系列 PETA 素食认证。风靡德奥、北欧及欧美潮流圈，是环保街头穿搭热门之选。</t>
+          <t>Sp5der: 美国街头潮牌，由说唱歌手Young Thug创立，以标志性蜘蛛元素为核心设计语言，主打卫衣、T恤、棒球帽等潮流单品，风格融合嘻哈文化与街头时尚，版型宽松舒适且注重细节工艺，深受全球年轻潮流爱好者追捧，是街头文化穿搭的热门选择。</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Yora: Sustainable streetwear from Bonn, 2018. Heavy tees, loose hoodies, tailored pants, eco accessories. Minimalist style, artist collaborations. GOTS organic cotton, OEKO-TEX, plant-based ink. PETA vegan certified. Popular in DACH, Nordic, EU/US.</t>
+          <t>Sp5der: Young Thug's streetwear brand. Iconic spider designs, hip-hop style, hoodies, tees, caps. Loose fit, detailed craftsmanship. Globally loved by youth culture.</t>
         </is>
       </c>
     </row>
     <row r="226" ht="25.5" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Yves Saint Laurent</t>
+          <t>Ss Lazio</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>yves-saint-laurent</t>
+          <t>ss-lazio</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Yves Saint Laurent: 1961年由伊夫·圣罗兰（Yves Saint Laurent）与皮埃尔·贝尔热（Pierre Bergé）创立的法国高端奢侈品牌，以先锋设计、性别流动美学与法式优雅著称，核心业务覆盖高级时装、美妆、皮具、香水及配饰。经典产品包括标志性“鸦片（Opium）”香水、Monogram帆布手袋、“自由之水（Libre）”香水与“高能腮红（Power Blush）”，融合艺术感与奢华质感，是全球时尚爱好者追捧的奢华符号，诠释“时尚是一种态度”的品牌理念。</t>
+          <t>Ss Lazio: 意大利罗马老牌职业足球俱乐部，1900年成立，主场为罗马奥林匹克体育场，征战意甲联赛。曾斩获意甲冠军、意大利杯冠军等荣誉，队服以经典天蓝色与白色为主色调，拥有悠久历史与深厚球迷文化，是意甲联赛的传统劲旅之一。</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Yves Saint Laurent: Founded in 1961 by Yves Saint Laurent &amp; Pierre Bergé, French luxury brand known for avant-garde design, gender-fluid aesthetics, French elegance. Core: haute couture, beauty, leather goods, fragrances, accessories. Icons: Opium fragrance, Monogram handbags, Libre perfume, Power Blush. Blends artistry &amp; luxury, sought-after by global fashion lovers, embodies “Fashion is an attitude.”</t>
+          <t>Ss Lazio: A renowned professional football club from Rome, Italy, founded in 1900. It competes in Serie A, plays at Stadio Olimpico Rome, and has won Serie A &amp; Coppa Italia titles. Its classic sky-blue &amp; white kits, long history, and strong fan culture make it a traditional Serie A powerhouse.</t>
         </is>
       </c>
     </row>
     <row r="227" ht="25.5" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Ssc Napoli</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>zara</t>
+          <t>ssc-napoli</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Zara: 1975年创立于西班牙的快时尚领导品牌，隶属于Inditex集团，以“快速反应”供应链模式著称，产品覆盖男女装、童装及配饰，风格紧跟全球潮流、时尚百搭，兼具高性价比与前沿设计，是年轻群体追求即时时尚的核心选择。</t>
+          <t>Ssc Napoli: 1926年成立的意大利甲级联赛传统豪门足球俱乐部，主场为迭戈·阿曼多·马拉多纳球场，以激情进攻风格闻名足坛，曾多次夺得意甲冠军、意大利杯冠军等荣誉，蓝白间条队服是其标志性视觉符号，拥有全球狂热的“tifosi”球迷群体，是意甲赛场极具影响力的劲旅之一。</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Zara: Spanish fast-fashion leader since 1975. Features trendy, versatile apparel &amp; accessories for all, offering high-style designs at great value through its agile supply chain.</t>
+          <t>Ssc Napoli: Founded in 1926, Serie A club with passionate attacking football, multiple championships, iconic blue-white stripes, and global tifosi fans.</t>
         </is>
       </c>
     </row>
     <row r="228" ht="25.5" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
+          <t>Starboy</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>starboy</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Starboy（星男孩）由加拿大流行天王The Weeknd于2016 年随同名专辑推出，本人担任创意主导。主营T 恤、连帽衫、夹克、配饰等街头潮流单品，标志性几何黑豹 Logo、暗黑霓虹美学与 "XO" 标识极具辨识度。风格融合高街奢华与街头反叛，以黑、白、红为主色调，剪裁简约利落。采用重磅精梳棉、透气聚酯纤维等优质材质，舒适耐穿。风靡全球年轻群体，尤在欧美、亚洲及澳洲，是潮流穿搭与音乐文化收藏的热门选择。</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Starboy: Streetwear by The Weeknd. Iconic panther logo, XO, dark neon aesthetics. High-end streetwear blend in black/white/red. Premium fabrics for global trendsetters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="25.5" customHeight="1">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Stone Island</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>stone-island</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Stone Island: 1982年由Massimo Osti创立于意大利的高端机能服饰品牌，以实验性面料研发与创新工艺为核心特色，标志性技术涵盖热粘合无缝工艺、成衣染色等，产品覆盖机能外套、卫衣、休闲裤等品类，完美融合户外实用功能与都市时尚风格，始终致力于将科技材质与美学设计深度结合，是全球机能风爱好者与高端时尚消费者的首选品牌。</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Stone Island: Founded in Italy by Massimo Osti in 1982, a high-end functional apparel brand focusing on experimental fabric R&amp;D &amp; innovative techniques (heat-bonded seamless, garment dyeing). Products include functional jackets, hoodies, casual pants, blending outdoor utility with urban style, integrating tech materials &amp; aesthetic design—top choice for global functional fashion lovers &amp; high-end consumers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="25.5" customHeight="1">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Stray</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>stray</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Stray（Stray Rats）由Julian Consuegra于2010 年在美国迈阿密创立，后迁至纽约。创始人亲任设计师，主营印花 T 恤、卫衣、帽子及配饰，标志性 90 年代复古图案与朋克元素融合，致敬硬核音乐与街头文化。采用重磅精梳棉、透气聚酯纤维，手工丝网印刷工艺提升质感。风靡全球潮流圈，尤在欧美、日本及东南亚，是高街穿搭与收藏的热门选择，常与 New Balance 等品牌联名。</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Stray Rats: 2010 Miami streetwear by Julian Consuegra. 90s retro punk prints on tees, hoodies, hats. Honors hardcore music, street culture. Heavyweight cotton, polyester, hand-screen printing. Global trend, high-street, New Balance collabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="25.5" customHeight="1">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Stussy</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>stussy</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Stussy: 1980年由Shawn Stussy创立于美国加州的传奇街头服饰品牌，以标志性手写体LOGO、融合冲浪、滑板与嘻哈文化的设计内核著称，经典产品线覆盖T恤、卫衣、棒球帽等潮流单品，风格主打复古街头与西海岸随性美学，长期引领全球青年潮流文化，是街头时尚爱好者心中的“复古街头符号”级品牌。</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Stussy: Founded in California, USA in 1980 by Shawn Stussy, iconic streetwear with signature handwritten logo, fuses surfing, skateboarding &amp; hip-hop. Classics (tees, hoodies, baseball caps) feature retro street &amp; West Coast casual aesthetics, leading global youth fashion—an iconic retro street symbol for streetwear lovers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="25.5" customHeight="1">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Supreme</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>supreme</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Supreme: 1994年创立于美国纽约曼哈顿的标志性街头潮流品牌，以经典红色Box Logo、高频跨界联名（涵盖Nike、Louis Vuitton等顶尖品牌）及限量发售机制闻名，产品覆盖卫衣、T恤、滑板、配件等品类，深度绑定青年文化与反主流精神，是全球潮流爱好者追求的「街头圣品」符号。</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Supreme: Iconic streetwear brand founded in Manhattan, NYC (1994), known for classic red Box Logo, frequent collabs (Nike, Louis Vuitton), limited releases, products (hoodies, tees, skateboards, accessories), tied to youth culture &amp; anti-mainstream spirit—global streetwear icon for enthusiasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="25.5" customHeight="1">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Saint Laurent</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Saint Laurent</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Saint Laurent: 1961年由伊夫·圣罗兰（Yves Saint Laurent）创立的法国奢侈品牌，以先锋叛逆的法式酷感风格横扫时尚界，核心覆盖高级时装、成衣、皮具（如Niki包、LouLou包）、鞋履、美妆及香水等品类。品牌标志性元素包括YSL字母标识、Monogram图案，以及打破性别边界的经典吸烟装（Le Smoking）——首次将男性西装剪裁融入女装，重塑时尚规则。从秀场级设计到日常奢华单品，Saint Laurent始终融合优雅与街头感，是全球潮流爱好者追崇的“酷感奢华”代表，持续传递“打破传统、定义自我”的品牌精神。</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Saint Laurent: French luxury brand founded 1961 by Yves Saint Laurent, famed for avant-garde rebellious French cool. Covers haute couture, ready-to-wear, leather goods (Niki, LouLou bags), footwear, beauty, fragrances. Iconic YSL monogram, genderless Le Smoking tuxedo (redefined fashion with men’s tailoring in women’s wear). Blends elegance &amp; streetwear, a “cool luxury” icon conveying “break tradition, define self” spirit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="25.5" customHeight="1">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>So Paulo</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>so-paulo</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>São Paulo（圣保罗足球俱乐部）1930 年由 Firmiano de Morais Pinto Filho 等创立，德国设计师 Walter Ostrich 设计队徽，主营官方球衣、训练服、休闲服饰及配饰，由 New Balance 等品牌操刀设计，标志性白底色配红黑横条纹，象征圣保罗市旗与俱乐部 “信仰、希望、慈善” 理念。采用透气聚酯纤维、AEROREADY 速干面料，舒适耐穿，风靡巴西及全球足球圈，是南美足坛顶级豪门标志性服饰。</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>São Paulo: Founded 1930, São Paulo FC iconic white/red/black stripes symbolize city flag &amp; "faith, hope, charity". New Balance kits/apparel with AEROREADY fabric. Top South American football club.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="25.5" customHeight="1">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Syna World</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>syna-world</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Syna World 以美式街头 / Drill 风格为主，标志性的 “涂鸦字体” 印花是它的核心识别元素，你图中帽子和裤子上的印花，就是品牌的专属涂鸦标识。</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Syna World: American streetwear &amp; drill style brand, featuring iconic graffiti font prints as its core identity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="25.5" customHeight="1">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>The North Face</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>the-north-face</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>The North Face: 1966年创立于美国旧金山，全球专业户外装备领导品牌，专注研发高性能登山、徒步、滑雪等场景装备，经典产品涵盖Summit系列专业冲锋衣、MCMURDO保暖羽绒服、VECTIV轻量化登山鞋等，核心技术搭载Gore-Tex®防水透气膜、Responsible Down Standard认证鹅绒填充及TNF Apex™耐磨面料，兼顾极端环境适应性与日常机能需求，为专业户外爱好者与城市轻户外人群提供耐用、环保的装备选择，风格融合硬核功能性与经典户外美学。</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>The North Face: Founded in San Francisco, USA (1966), global leading pro outdoor gear brand. Specializes in high-performance mountaineering, hiking, skiing gear—signature products: Summit Series hardshells, MCMURDO down jackets, VECTIV hiking shoes. Features Gore-Tex® membranes, RDS-certified down, TNF Apex™ fabrics. Balances extreme adaptability &amp; daily function for pros/urban light outdoor users, blending hardcore functionality with classic outdoor aesthetics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="25.5" customHeight="1">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Thug Club</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>thug-club</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Thug Club 由Thug Min与Jiyool Kwon于2018 年在韩国首尔梨泰院创立。主打宽松 T 恤、美式夹克、做旧牛仔及铆钉配饰，融合嘻哈、机车文化与反叛街头风。采用高品质棉料与耐用牛仔，质感硬朗。风靡全球潮流圈，获 A$AP Rocky、SZA 等明星追捧，是韩系街头潮流代表品牌。</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Thug Club: Seoul-based streetwear since 2018. Oversized tees, vintage denim, &amp; rebel biker style. Premium cotton &amp; hard-wearing fabrics. Worn by A$AP Rocky, SZA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="25.5" customHeight="1">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>TeddyTales</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>tedd-tales</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>莉娜熊（TeddyTales）是俄罗斯设计师 Irina Lekareva 创立的手工泰迪熊品牌，主打 “每只熊都是独一无二” 的手作理念，凭借软萌治愈的造型和丰富的配件套装，成为热门的毛绒玩偶 IP，常被用作礼物。</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>TeddyTales Lina Bear: Unique handcrafted teddy bears by Irina Lekareva. Soft, cute, and collectible with outfit sets. A perfect gift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="25.5" customHeight="1">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Tom Ford</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>tom-ford</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Tom Ford: 2005年由美国设计师Tom Ford创立的高端奢侈品牌，以性感奢华、现代先锋的风格著称，产品线覆盖美妆（经典Lip Color口红、Black Orchid香水）、高级成衣、皮具、眼镜及腕表等领域，甄选丝绒、小羊皮、稀有香原料等顶级材质，工艺精湛，精准契合全球追求品质与独特个性的高端消费者需求，是奢华时尚与创新设计的标志性代表。</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Tom Ford: Founded by American designer Tom Ford in 2005, a high-end luxury brand celebrated for sexy luxury &amp; modern avant-garde style. Product lines include beauty (iconic Lip Color lipstick, Black Orchid perfume), ready-to-wear, leather goods, eyewear &amp; watches. Uses premium materials (velvet, lambskin, rare fragrance ingredients) with exquisite craftsmanship, catering to global high-end consumers seeking quality &amp; unique personality. An iconic symbol of luxury fashion &amp; innovative design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="25.5" customHeight="1">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Tommy Hilfiger</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>tommy-hilfiger</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Tommy Hilfiger: 1985年由同名设计师Tommy Hilfiger创立的美国经典休闲时尚品牌，以标志性红白蓝三色logo、预ppy（预科生）风格及高品质棉质面料为核心特色，产品覆盖男装、女装、童装、配饰与香水，融合美式复古底蕴与现代简约设计，打造日常百搭且具高端休闲感的服饰单品，是全球追求经典时尚、舒适质感人群的首选品牌之一。</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Tommy Hilfiger: Founded in 1985 by its eponymous designer, this iconic American casual fashion brand boasts signature red-white-blue logo, preppy style, and premium cotton fabrics. It offers apparel (men, women, kids), accessories, and fragrances, blending American retro roots with modern minimalist design for versatile high-end casual pieces—top choice for classic fashion &amp; comfort seekers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="25.5" customHeight="1">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Thom Browne</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>thom-browne</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Thom Browne 美国轻奢品牌，以标志性四道杠为核心识别，主打学院风精致剪裁，打造高级休闲与正装兼备的穿搭质感。</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Thom Browne is an American luxury fashion brand, known for its iconic 4-bar stripe design, offering tailored preppy-style apparel for smart casual &amp; formal wear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="25.5" customHeight="1">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>tottenham-hotspur</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur: 1882年成立于伦敦的英超足球俱乐部，主场为托特纳姆热刺球场，以进攻足球与青训体系闻名。经典白色球衣与公鸡标志传承百年，现代风格融合激烈比赛与卓越球员培养，吸引全球球迷关注。</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur: London Premier League club since 1882, attacking football and youth academy, iconic white kit with cockerel emblem, modern play and player development, global fans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="25.5" customHeight="1">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Trapstar</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>trapstar</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Trapstar: 2005年由Mikey Trapstar、Lee Trapstar与Will Trapstar创立于英国伦敦，是扎根街头文化与trap音乐精神的潮流品牌。以标志性星型LOGO、反光材质及军事风剪裁为核心设计符号，产品覆盖卫衣、夹克、配饰等街头单品，曾与Nike、Puma等品牌推出联名系列，深受追求个性表达、热爱街头亚文化与音乐的年轻群体喜爱。</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Trapstar: Founded in London, UK (2005) by Mikey, Lee &amp; Will Trapstar, a streetwear brand rooted in street culture &amp; trap music spirit. Core design: signature star logo, reflective materials, military cuts. Offers hoodies, jackets, accessories. Collaborated with Nike, Puma. Loved by self-expressive young fans of street subculture &amp; music.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="25.5" customHeight="1">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Travis Scott</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>travis-scott</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Travis Scott: 美国知名说唱歌手、音乐制作人兼时尚设计师，以其独特音乐风格和跨界联名系列在全球潮流界备受瞩目。品牌产品涵盖联名鞋款、街头服饰及配饰，采用创新设计、优质材质和标志性元素，融合嘻哈文化与高端时尚，风格前卫。经典合作如Travis Scott x Nike Air Jordan系列，深受年轻消费者和收藏家喜爱，推动全球潮流文化发展。</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Travis Scott: Renowned rapper and designer. Iconic Travis Scott x Nike Air Jordan collaborations. Streetwear, sneakers, and accessories. Merging hip-hop with high-fashion innovation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="25.5" customHeight="1">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>True Religion</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>true-religion</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>True Religion: 2002年创立于美国的高端牛仔品牌，以标志性马蹄形（Horseshoe）缝线设计、顶级牛仔布材质及精湛水洗工艺闻名，主打男士/女士牛仔裤、牛仔外套及休闲服饰，融合美式复古与街头潮流风格，是追求个性与高品质牛仔单品的消费者首选品牌。</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>True Religion: Founded in the US in 2002, a high-end denim brand renowned for iconic Horseshoe stitching, premium denim, and exquisite wash techniques. Offers men’s/women’s jeans, denim jackets, casual apparel, blending American retro with streetwear—top choice for consumers seeking individuality &amp; high-quality denim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="25.5" customHeight="1">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Umbro</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>umbro</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Umbro: 1924年创立于英国的专业足球运动装备品牌，以标志性双钻石LOGO著称，深耕足球领域近百年，曾长期为英格兰国家队等顶级球队提供球衣装备。产品覆盖专业足球衣、训练服、足球鞋及配件，融合英伦经典设计与运动科技，专注为球员与球迷打造兼具性能与复古质感的足球装备，传承纯粹足球精神。</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Umbro: Founded in 1924 in England, iconic double diamond logo. Professional football gear, kits, footwear &amp; accessories. Merges classic British design with sport tech for players &amp; fans, honoring pure football heritage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="25.5" customHeight="1">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>UGG</t>
+        </is>
+      </c>
+      <c r="B247"/>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>UGG: 源自澳大利亚的经典保暖鞋服品牌，以标志性羊皮毛一体雪地靴闻名，核心产品涵盖Classic Short经典短靴、Cozy Slide拖鞋及羊毛外套等，采用优质美利奴羊毛与天然皮革材质，主打“温暖不厚重、舒适又时尚”的设计理念，满足冬季保暖及日常休闲穿搭需求，是全球注重质感与舒适度的消费者首选的保暖时尚品牌。</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>UGGUGG: Australian brand iconic for sheepskin boots, Classic Short, Cozy Slide, and wool coats. Made with Merino wool and leather for warm, comfortable, stylish winter and casual wear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="25.5" customHeight="1">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Valencia: （因未提供该品牌的具体中文描述信息，无法生成符合要求的SEO优化品牌描述。）</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Valencia: Due to the lack of specific Chinese description of the brand, we cannot generate a compliant SEO-optimized brand description.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="25.5" customHeight="1">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Valentino</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>valentino</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Valentino: 1960年由Valentino Garavani创立的意大利顶级奢侈品牌，以高级时装、皮具、鞋履、配饰及美妆为核心产品线，标志性元素包括VLogo标识、Rockstud铆钉系列与经典Valentino Red（华伦天奴红），风格融合奢华、浪漫与经典，凭借精湛工艺与独特设计，成为全球追求高端时尚品味人群的首选品牌之一。</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Valentino: Founded 1960 by Valentino Garavani, Italian luxury house for haute couture, leather goods, accessories. Iconic VLogo, Rockstuds, Valentino Red. Fusion of luxury, romantic, timeless Italian craftsmanship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="25.5" customHeight="1">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>vans</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Vans: 1966年由Paul Van Doren等创立于美国加州，全球街头潮流与滑板文化的标志性品牌，以“Off The Wall”的自由叛逆精神为内核。经典产品涵盖Authentic、Old Skool、Sk8-Hi等帆布/麂皮滑板鞋款，标志性棋盘格图案、侧边条纹设计深入人心，融合耐用工艺与青年创意表达，成为滑板运动、街头时尚及亚文化群体的核心选择。</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Vans: Iconic skate/streetwear brand since 1966, "Off The Wall" spirit. Durable canvas/suede shoes: Authentic, Old Skool, Sk8-Hi. Signature checkerboard &amp; side stripe for youth culture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="25.5" customHeight="1">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Vasco Da Gama</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>vasco-da-gama</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Vasco Da Gama: （由于未提供该品牌的中文描述内容，无法生成符合要求的SEO优化品牌描述。）</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Vasco Da Gama: (Due to the lack of Chinese description of the brand, we cannot generate a compliant SEO-optimized brand description.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="25.5" customHeight="1">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Versace</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>versace</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Versace: 1978年由詹尼·范思哲（Gianni Versace）创立于意大利米兰的奢华时尚品牌，以标志性美杜莎头像、巴洛克印花及大胆撞色为核心视觉符号，涵盖高级时装、成衣、皮具、鞋履、配饰、香水与家居系列，风格融合意大利复古奢华与性感张扬，凭借精湛工艺与先锋设计成为全球红毯、名流及时尚爱好者追捧的高端时尚象征，诠释“致命诱惑”的品牌精神。</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Versace: Italian luxury fashion since 1978, iconic Medusa &amp; Baroque prints, bold colors. Haute couture, accessories, perfumes. Style: retro luxury meets sexy flamboyance. High-end for red carpets, celebrities. Spirit: fatal attraction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="25.5" customHeight="1">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Vetements</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>vetements</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Vetements: 2014年由Demna Gvasalia与Guram Gvasalia创立于法国的高端街头服饰品牌，以解构主义设计、oversize版型及标志性标语印花为核心特色，融合街头文化与高级时装美学，推出卫衣、外套、配饰等系列单品，曾与Reebok、Juicy Couture等品牌联名，深受追求个性潮流与先锋风格的时尚爱好者喜爱。</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Vetements: French high-end streetwear brand founded 2014, known for deconstructivist designs, oversize fits, slogan prints. Merges street culture with high fashion. Offers hoodies, jackets, accessories. Collaborations with Reebok, Juicy Couture. Loved by avant-garde fashion enthusiasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="25.5" customHeight="1">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Vicinity</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>vicinity</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Vicinity 是源自澳大利亚的轻奢休闲街头品牌，由本土设计师团队于2015 年创立。主营都市休闲卫衣、简约衬衫、百搭裤装及轻户外穿搭，坚持本土原创设计。风格主打极简通勤、轻户外休闲，利落百搭适配日常。采用优质纯棉、透气梭织、环保再生面料，舒适亲肤。风靡澳新、欧美及亚太地区，是都市轻休闲穿搭的热门选择。</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Vicinity: Australian luxury casual streetwear since 2015. Local designers craft urban essentials, minimalist commute to light outdoor styles. Premium cotton, breathable woven, eco fabrics. Popular in Australia, NZ, US, EU, Asia-Pacific.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="25.5" customHeight="1">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>(Vivi)VivienneWestwood</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>VivienneWestwood</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>VivienneWestwood: 1971年由英国设计师Vivienne Westwood创立，时尚品牌以朋克和反叛风格著称，产品系列包括服装、配饰、珠宝及鞋履，经典元素有土星标志、格子图案和夸张剪裁，采用皮革、面料等多样材质，工艺创新独特，风格前卫叛逆，融合时尚与艺术，深受全球潮流人士喜爱。</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Vivienne Westwood: Punk rebellious fashion brand since 1971, offering clothing, accessories, jewelry, footwear with Saturn logo, tartan patterns, exaggerated cuts. Uses leather, fabrics, innovative avant-garde style fusing fashion and art, loved globally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="25.5" customHeight="1">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Vlone</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>vlone</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Vlone: 由A$AP Rocky与A$AP Bari共同创立的美国街头潮流品牌，以标志性V字Logo、“Live Vlone, Die Vlone”核心标语为识别，融合嘻哈文化与叛逆精神，主打T恤、卫衣、帽款及配件等单品，凭借街头感设计与社群共鸣，成为全球潮流爱好者追捧的街头文化符号。</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Vlone: Streetwear brand by A$AP Rocky &amp; Bari. Iconic V logo, "Live Vlone, Die Vlone" mantra. Hip-hop infused, rebellious essentials – tees, hoodies, caps. A global street culture symbol.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="25.5" customHeight="1">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Vetements</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>vetements</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Vetements,由格鲁吉亚设计师 Demna Gvasalia 创立，以反主流、解构主义和亚文化符号著称。这件 T 恤通过对过时科技符号的二次创作，传递了品牌对互联网时代文化的反思与反叛态度，是近年话题度极高的街头潮流单品。</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Vetements: Demna Gvasalia's brand, known for deconstruction and subversion. This tee reworks obsolete tech symbols, critiquing internet-era culture. A key streetwear piece.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="25.5" customHeight="1">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Yeezy</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>yeezy</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Yeezy: 由美国创作歌手坎耶·维斯特（Kanye West）创立的全球街头潮流标杆品牌，以“椰子鞋”系列奠定潮流地位，核心鞋款融合Boost缓震科技、大地色系极简设计与街头基因，标志性产品如Yeezy Boost 350 V2、Yeezy 500等成为sneaker文化符号，主打“舒适与先锋时尚兼具”的理念，覆盖鞋履、服饰等品类，是街头美学与高端运动属性结合的代表，深受潮流爱好者与收藏家追捧。</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Yeezy: Global streetwear icon founded by U.S. artist Kanye West. Core styles (Yeezy Boost 350 V2, 500) feature Boost cushioning, earth-tone minimal design &amp; street DNA—sneaker culture symbols. Blends street aesthetics with high-end sport, offering footwear/apparel for comfort &amp; avant-garde fashion, sought after by streetwear fans &amp; collectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="25.5" customHeight="1">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Yora</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>yora</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Yora 是德国波恩可持续街头服饰品牌，由本土设计师团队于2018 年创立。主营重磅 T 恤、宽松卫衣、立体剪裁裤装及环保配饰，坚持原创设计与青年艺术家合作。风格主打极简街头、可持续时尚，标志性环保认证标识醒目。采用GOTS 认证有机棉、OEKO-TEX 100 环保面料，植物基油墨印花，全系列 PETA 素食认证。风靡德奥、北欧及欧美潮流圈，是环保街头穿搭热门之选。</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Yora: Sustainable streetwear from Bonn, 2018. Heavy tees, loose hoodies, tailored pants, eco accessories. Minimalist style, artist collaborations. GOTS organic cotton, OEKO-TEX, plant-based ink. PETA vegan certified. Popular in DACH, Nordic, EU/US.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="25.5" customHeight="1">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Yves Saint Laurent</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>yves-saint-laurent</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Yves Saint Laurent: 1961年由伊夫·圣罗兰（Yves Saint Laurent）与皮埃尔·贝尔热（Pierre Bergé）创立的法国高端奢侈品牌，以先锋设计、性别流动美学与法式优雅著称，核心业务覆盖高级时装、美妆、皮具、香水及配饰。经典产品包括标志性“鸦片（Opium）”香水、Monogram帆布手袋、“自由之水（Libre）”香水与“高能腮红（Power Blush）”，融合艺术感与奢华质感，是全球时尚爱好者追捧的奢华符号，诠释“时尚是一种态度”的品牌理念。</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Yves Saint Laurent: Founded in 1961 by Yves Saint Laurent &amp; Pierre Bergé, French luxury brand known for avant-garde design, gender-fluid aesthetics, French elegance. Core: haute couture, beauty, leather goods, fragrances, accessories. Icons: Opium fragrance, Monogram handbags, Libre perfume, Power Blush. Blends artistry &amp; luxury, sought-after by global fashion lovers, embodies “Fashion is an attitude.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="25.5" customHeight="1">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Zara</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>zara</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Zara: 1975年创立于西班牙的快时尚领导品牌，隶属于Inditex集团，以“快速反应”供应链模式著称，产品覆盖男女装、童装及配饰，风格紧跟全球潮流、时尚百搭，兼具高性价比与前沿设计，是年轻群体追求即时时尚的核心选择。</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Zara: Spanish fast-fashion leader since 1975. Features trendy, versatile apparel &amp; accessories for all, offering high-style designs at great value through its agile supply chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="25.5" customHeight="1">
+      <c r="A262" t="inlineStr">
+        <is>
           <t>Zwball</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B262" t="inlineStr">
         <is>
           <t>zwball</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
+      <c r="C262" t="inlineStr">
         <is>
           <t>ZWOBALL 由日本DropFlava团队于2013 年创立，专注自由式足球装备。创始人亲任设计，主营足球、训练服、花式球鞋及配件，标志性流线型 Logo 与动感街头元素鲜明。风格融合运动活力与潮流个性，适配花式足球与日常穿搭。采用耐磨橡胶、透气聚酯纤维、弹力氨纶，耐用回弹佳。风靡日本、欧美及亚洲足球圈，是自由式足球爱好者的热门选择。</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D262" t="inlineStr">
         <is>
           <t>Zwball: Freestyle football gear since 2013. Sleek logo, street-style designs. Durable rubber, breathable polyester. For tricks and streetwear. Popular worldwide.</t>
         </is>
